--- a/Testes.xlsx
+++ b/Testes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\utilizador\Documents\CTESP\4semestre\LP2\ProjetoTesteLP2\TrabalhoTesteLP2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BDA336A-90B0-4162-A176-A5997184ACAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00705A8F-2E90-4A0C-B0A9-3E222A712310}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-3870" windowWidth="20730" windowHeight="11040" xr2:uid="{17050BBC-8C72-4C7C-BB9E-52ED50A4B6E1}"/>
+    <workbookView xWindow="10704" yWindow="1140" windowWidth="11556" windowHeight="9192" activeTab="1" xr2:uid="{17050BBC-8C72-4C7C-BB9E-52ED50A4B6E1}"/>
   </bookViews>
   <sheets>
     <sheet name="Menus" sheetId="1" r:id="rId1"/>
@@ -27,26 +27,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="178">
   <si>
     <t>===== SISTEMA ISSMF =====</t>
   </si>
   <si>
-    <t>1 - Login</t>
-  </si>
-  <si>
-    <t>2 - Criar Estudante</t>
-  </si>
-  <si>
-    <t>3 - Avançar Ano</t>
-  </si>
-  <si>
-    <t>4 - Recuperar Password</t>
-  </si>
-  <si>
-    <t>0 - Sair</t>
-  </si>
-  <si>
     <t>=== BACKOFFICE - GESTOR ===</t>
   </si>
   <si>
@@ -65,24 +50,9 @@
     <t>5 - Gerir Docentes</t>
   </si>
   <si>
-    <t>6 - Avançar Ano Letivo</t>
-  </si>
-  <si>
-    <t>7 - Listagens e Relatórios</t>
-  </si>
-  <si>
-    <t>8 - Ver Alunos com Dívidas</t>
-  </si>
-  <si>
-    <t>9 - Alterar Preço de Cursos</t>
-  </si>
-  <si>
     <t>10 - Gerir Gestores</t>
   </si>
   <si>
-    <t>0 - Sair / Logout</t>
-  </si>
-  <si>
     <t>--- GERIR DEPARTAMENTOS ---</t>
   </si>
   <si>
@@ -92,9 +62,6 @@
     <t>2 - Alterar Departamento</t>
   </si>
   <si>
-    <t>3 - Listar Departamentos</t>
-  </si>
-  <si>
     <t>0 - Recuar</t>
   </si>
   <si>
@@ -107,90 +74,39 @@
     <t>2 - Alterar Curso</t>
   </si>
   <si>
-    <t>3 - Listar Cursos</t>
-  </si>
-  <si>
-    <t>4 - Ativar/Desativar Curso</t>
-  </si>
-  <si>
     <t>--- GERIR UNIDADES CURRICULARES ---</t>
   </si>
   <si>
-    <t>1 - Criar Nova Unidade Curricular</t>
-  </si>
-  <si>
     <t>2 - Associar UC Existente a outro Curso</t>
   </si>
   <si>
     <t>3 - Alterar Unidade Curricular</t>
   </si>
   <si>
-    <t>4 - Listar Unidades Curriculares</t>
-  </si>
-  <si>
-    <t>5 - Ativar/Desativar UC</t>
-  </si>
-  <si>
-    <t>6 - Remover UC de um Curso</t>
-  </si>
-  <si>
     <t>--- GERIR ESTUDANTES ---</t>
   </si>
   <si>
     <t>1 - Adicionar Estudante</t>
   </si>
   <si>
-    <t>2 - Alterar Estudante</t>
-  </si>
-  <si>
-    <t>3 - Listar Estudantes</t>
-  </si>
-  <si>
-    <t>4 - Ativar/Desativar Estudante</t>
-  </si>
-  <si>
     <t>--- GERIR DOCENTES ---</t>
   </si>
   <si>
     <t>1 - Adicionar Docente</t>
   </si>
   <si>
-    <t>2 - Alterar Docente</t>
-  </si>
-  <si>
     <t>3 - Listar Docentes</t>
   </si>
   <si>
-    <t>4 - Ativar/Desativar Docente</t>
-  </si>
-  <si>
     <t>--- RELATÓRIOS E ESTATÍSTICAS ---</t>
   </si>
   <si>
-    <t>1 - Alunos agrupados por Curso</t>
-  </si>
-  <si>
-    <t>2 - Alunos agrupados por UC</t>
-  </si>
-  <si>
-    <t>3 - UCs agrupadas por Curso</t>
-  </si>
-  <si>
-    <t>4 - Cursos agrupados por Departamento</t>
-  </si>
-  <si>
-    <t>5 - Ver Estatísticas Globais da Faculdade</t>
-  </si>
-  <si>
     <t>--- GERIR GESTORES ---</t>
   </si>
   <si>
     <t>1 - Adicionar Gestor</t>
   </si>
   <si>
-    <t>2 - Desativar Gestor</t>
-  </si>
-  <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
@@ -251,57 +167,27 @@
     <t>Professor Abel</t>
   </si>
   <si>
-    <t>PLG</t>
-  </si>
-  <si>
-    <t>JOUumOtE</t>
-  </si>
-  <si>
-    <t>plg@issmf.ipp.pt</t>
-  </si>
-  <si>
     <t>Faro</t>
   </si>
   <si>
-    <t>PLM</t>
-  </si>
-  <si>
     <t>Professora Ana</t>
   </si>
   <si>
-    <t>hrtLdmnk</t>
-  </si>
-  <si>
-    <t>plm@issmf.ipp.pt</t>
-  </si>
-  <si>
     <t>Professor Rui</t>
   </si>
   <si>
-    <t>PXQ</t>
-  </si>
-  <si>
-    <t>CJtg7TEu</t>
-  </si>
-  <si>
     <t>Viseu</t>
   </si>
   <si>
     <t>Lisboa</t>
   </si>
   <si>
-    <t>pxq@issmf.ipp.pt</t>
-  </si>
-  <si>
     <t>ATIVO</t>
   </si>
   <si>
     <t>INATIVO</t>
   </si>
   <si>
-    <t>5 - Ver Percurso Académico do Curso</t>
-  </si>
-  <si>
     <t>1º</t>
   </si>
   <si>
@@ -320,15 +206,6 @@
     <t>Professor Carlos</t>
   </si>
   <si>
-    <t>PVR</t>
-  </si>
-  <si>
-    <t>lrMSQHfv</t>
-  </si>
-  <si>
-    <t>pvr@issmf.ipp.pt</t>
-  </si>
-  <si>
     <t>Maceda</t>
   </si>
   <si>
@@ -344,9 +221,6 @@
     <t>[ATIVO] MAT1 : Matematica 1</t>
   </si>
   <si>
-    <t>[INATIVO] MAT : Matematica Antiga</t>
-  </si>
-  <si>
     <t>[ATIVO] EST2 : Estruturas 2</t>
   </si>
   <si>
@@ -356,15 +230,6 @@
     <t>Professor Luis</t>
   </si>
   <si>
-    <t>PKX</t>
-  </si>
-  <si>
-    <t>pkx@issmf.ipp.pt</t>
-  </si>
-  <si>
-    <t>enL8Tn6R</t>
-  </si>
-  <si>
     <t>Gondomar</t>
   </si>
   <si>
@@ -374,21 +239,12 @@
     <t>[ATIVO] COM2 : Construções Mecanicas 2</t>
   </si>
   <si>
-    <t>PEU</t>
-  </si>
-  <si>
     <t>Espinho</t>
   </si>
   <si>
-    <t>W8dR2IAV</t>
-  </si>
-  <si>
     <t>Professor Guedes</t>
   </si>
   <si>
-    <t>peu@issmf.ipp.pt</t>
-  </si>
-  <si>
     <t>LEM</t>
   </si>
   <si>
@@ -413,32 +269,335 @@
     <t>[ATIVO] ELE : Eletromagnetismo</t>
   </si>
   <si>
-    <t>backoffice_oleiros@issmf.ipp.pt</t>
-  </si>
-  <si>
-    <t>backoffice_oleiros</t>
-  </si>
-  <si>
-    <t>YX6n8AFb</t>
-  </si>
-  <si>
     <t>backoffice_ovar@issmf.ipp.pt</t>
   </si>
   <si>
-    <t>backoffice_ovar</t>
-  </si>
-  <si>
-    <t>OTFMTAl0</t>
-  </si>
-  <si>
-    <t>3 - Listar Gestores</t>
+    <t>1 - Efetuar Login</t>
+  </si>
+  <si>
+    <t>2 - Auto-Inscrição Estudante</t>
+  </si>
+  <si>
+    <t>3 - Transitar Ano Letívo</t>
+  </si>
+  <si>
+    <t>4 - Recuperar Palavra-passe</t>
+  </si>
+  <si>
+    <t>0 - Encerrar Sistema</t>
+  </si>
+  <si>
+    <t>6 - Processar Transição de Ano Letivo</t>
+  </si>
+  <si>
+    <t>7 - Consultar Relatórios Académicos</t>
+  </si>
+  <si>
+    <t>8 - Listar Alunos com Propinas em Atraso</t>
+  </si>
+  <si>
+    <t>9 - Atualizar Preçário de Cursos</t>
+  </si>
+  <si>
+    <t>0 - Sair (Logout)</t>
+  </si>
+  <si>
+    <t>3 - Listar Todos os Departamentos</t>
+  </si>
+  <si>
+    <t>3 - Listar Cursos por Departamento</t>
+  </si>
+  <si>
+    <t>4 - Alternar Estado (Ativo/Inativo)</t>
+  </si>
+  <si>
+    <t>5 - Consultar Percurso Académico do Curso</t>
+  </si>
+  <si>
+    <t>5 - Alternar Estado (Ativo/Inativo)</t>
+  </si>
+  <si>
+    <t>1 - Listar Alunos por Curso</t>
+  </si>
+  <si>
+    <t>2 - Listar Alunos por Unidade Curricular</t>
+  </si>
+  <si>
+    <t>3 - Listar Unidades Curriculares por Curso</t>
+  </si>
+  <si>
+    <t>4 - Consultar Estatísticas Globais da Faculdade</t>
+  </si>
+  <si>
+    <t>1 - Adicionar Unidade Curricular</t>
+  </si>
+  <si>
+    <t>4 - Listar Todas as Unidades Curriculares</t>
+  </si>
+  <si>
+    <t>6 - Remover Unidade Curricular de Curso</t>
+  </si>
+  <si>
+    <t>2 - Atualizar Ficha do Estudante</t>
+  </si>
+  <si>
+    <t>2 - Atualizar Ficha do Docente</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">3 - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Listar Todos os Estudantes</t>
+    </r>
+  </si>
+  <si>
+    <t>5 - Visualizar Ficha Docente</t>
+  </si>
+  <si>
+    <t>2 - Alterar Gestor para Inativo</t>
+  </si>
+  <si>
+    <t>3 - Listar Todos os Gestores</t>
+  </si>
+  <si>
+    <t>PPA</t>
+  </si>
+  <si>
+    <t>AzAhZFQR</t>
+  </si>
+  <si>
+    <t>PLL</t>
+  </si>
+  <si>
+    <t>J4Wn1RTE</t>
+  </si>
+  <si>
+    <t>PYE</t>
+  </si>
+  <si>
+    <t>ppa@issmf.ipp.pt</t>
+  </si>
+  <si>
+    <t>pll@issmf.ipp.pt</t>
+  </si>
+  <si>
+    <t>pye@issmf.ipp.pt</t>
+  </si>
+  <si>
+    <t>M7cB9BWv</t>
+  </si>
+  <si>
+    <t>PHE</t>
+  </si>
+  <si>
+    <t>phe@issmf.ipp.pt</t>
+  </si>
+  <si>
+    <t>KSufsYmF</t>
+  </si>
+  <si>
+    <t>PHH</t>
+  </si>
+  <si>
+    <t>phh@issmf.ipp.pt</t>
+  </si>
+  <si>
+    <t>O3UfLLHu</t>
+  </si>
+  <si>
+    <t>PTV</t>
+  </si>
+  <si>
+    <t>ptv@issmf.ipp.pt</t>
+  </si>
+  <si>
+    <t>KeZ5WeMb</t>
+  </si>
+  <si>
+    <t>[INATIVO] MAT : Matematica Clássica</t>
+  </si>
+  <si>
+    <t>Ovar</t>
+  </si>
+  <si>
+    <t>jdzaTnLI</t>
+  </si>
+  <si>
+    <t>Brandão</t>
+  </si>
+  <si>
+    <t>backoffice_brandão@issmf.ipp.pt</t>
+  </si>
+  <si>
+    <t>uMzFKVTG</t>
+  </si>
+  <si>
+    <t>Afonso Henriques Moreira</t>
+  </si>
+  <si>
+    <t>Guimarães</t>
+  </si>
+  <si>
+    <t>Beatriz Sofia Antunes</t>
+  </si>
+  <si>
+    <t>Coimbra</t>
+  </si>
+  <si>
+    <t>Cláudio Renato Silva</t>
+  </si>
+  <si>
+    <t>Aveiro</t>
+  </si>
+  <si>
+    <t>Daniela Filipa Pires</t>
+  </si>
+  <si>
+    <t>Eduardo Jorge Mendes</t>
+  </si>
+  <si>
+    <t>Braga</t>
+  </si>
+  <si>
+    <t>Frederico José Santos</t>
+  </si>
+  <si>
+    <t>Gabriela Maria Rocha</t>
+  </si>
+  <si>
+    <t>Porto</t>
+  </si>
+  <si>
+    <t>Hugo Miguel Ferreira</t>
+  </si>
+  <si>
+    <t>Inês Margarida Costa</t>
+  </si>
+  <si>
+    <t>Setúbal</t>
+  </si>
+  <si>
+    <t>João Pedro Oliveira</t>
+  </si>
+  <si>
+    <t>Évora</t>
+  </si>
+  <si>
+    <t>Leonor Clara Gomes</t>
+  </si>
+  <si>
+    <t>Bragança</t>
+  </si>
+  <si>
+    <t>Manuel António Sousa</t>
+  </si>
+  <si>
+    <t>Leiria</t>
+  </si>
+  <si>
+    <t>Nádia Patrícia Lima</t>
+  </si>
+  <si>
+    <t>Funchal</t>
+  </si>
+  <si>
+    <t>Pedro Rafael Couto</t>
+  </si>
+  <si>
+    <t>Portimão</t>
+  </si>
+  <si>
+    <t>Rita Alexandra Neves</t>
+  </si>
+  <si>
+    <t>Chaves</t>
+  </si>
+  <si>
+    <t>Estudante</t>
+  </si>
+  <si>
+    <t>20260001@issmf.ipp.pt</t>
+  </si>
+  <si>
+    <t>20260002@issmf.ipp.pt</t>
+  </si>
+  <si>
+    <t>20260003@issmf.ipp.pt</t>
+  </si>
+  <si>
+    <t>20260004@issmf.ipp.pt</t>
+  </si>
+  <si>
+    <t>20260005@issmf.ipp.pt</t>
+  </si>
+  <si>
+    <t>20260006@issmf.ipp.pt</t>
+  </si>
+  <si>
+    <t>20260007@issmf.ipp.pt</t>
+  </si>
+  <si>
+    <t>20260008@issmf.ipp.pt</t>
+  </si>
+  <si>
+    <t>[ATIVO] SIE : Sistemas de Energia</t>
+  </si>
+  <si>
+    <t>6YfBDm9Z</t>
+  </si>
+  <si>
+    <t>COV0Mqqd</t>
+  </si>
+  <si>
+    <t>My0idwK2</t>
+  </si>
+  <si>
+    <t>epUNyyTa</t>
+  </si>
+  <si>
+    <t>2OOrgOHH</t>
+  </si>
+  <si>
+    <t>sH4jkSUf</t>
+  </si>
+  <si>
+    <t>552xhEqO</t>
+  </si>
+  <si>
+    <t>WBqeQJxN</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="169" formatCode="dd\-mm\-yyyy;@"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -470,14 +629,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -485,11 +642,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hiperligação" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -807,7 +972,7 @@
   <cols>
     <col min="2" max="2" width="27.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:6" x14ac:dyDescent="0.3">
@@ -816,725 +981,1175 @@
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B4" s="3" t="s">
-        <v>1</v>
+      <c r="B4" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>2</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>3</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>4</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>5</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C10" t="s">
-        <v>7</v>
-      </c>
+      <c r="C10" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="8"/>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="D11" t="s">
-        <v>18</v>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="D12" s="3" t="s">
-        <v>19</v>
+      <c r="C12" s="8"/>
+      <c r="D12" s="9" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="D13" s="3" t="s">
-        <v>20</v>
+      <c r="C13" s="8"/>
+      <c r="D13" s="9" t="s">
+        <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="D14" s="3" t="s">
-        <v>21</v>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="D15" s="3" t="s">
-        <v>22</v>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C16" t="s">
-        <v>8</v>
-      </c>
+      <c r="C16" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="8"/>
     </row>
     <row r="17" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D17" s="3" t="s">
-        <v>23</v>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D18" s="3" t="s">
-        <v>24</v>
+      <c r="C18" s="8"/>
+      <c r="D18" s="9" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D19" s="3" t="s">
-        <v>25</v>
+      <c r="C19" s="8"/>
+      <c r="D19" s="9" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D20" s="3" t="s">
-        <v>26</v>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="21" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D21" s="3" t="s">
-        <v>27</v>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="22" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D22" s="3" t="s">
-        <v>90</v>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="23" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D23" s="3" t="s">
-        <v>22</v>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C24" t="s">
-        <v>9</v>
-      </c>
+      <c r="C24" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D24" s="8"/>
     </row>
     <row r="25" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D25" s="3" t="s">
-        <v>28</v>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D26" s="3" t="s">
-        <v>29</v>
+      <c r="C26" s="8"/>
+      <c r="D26" s="9" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D27" s="3" t="s">
-        <v>30</v>
+      <c r="C27" s="8"/>
+      <c r="D27" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="28" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D28" s="3" t="s">
-        <v>31</v>
+      <c r="C28" s="8"/>
+      <c r="D28" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="29" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D29" s="3" t="s">
-        <v>32</v>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="30" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D30" s="3" t="s">
-        <v>33</v>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="31" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D31" s="3" t="s">
-        <v>34</v>
+      <c r="C31" s="8"/>
+      <c r="D31" s="9" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="32" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D32" s="3" t="s">
-        <v>22</v>
+      <c r="C32" s="8"/>
+      <c r="D32" s="8" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="33" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C33" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D34" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
     </row>
     <row r="35" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D35" t="s">
-        <v>36</v>
+      <c r="D35" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="36" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D36" t="s">
-        <v>37</v>
+      <c r="D36" s="6" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="37" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D37" t="s">
-        <v>38</v>
+      <c r="D37" s="6" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="38" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D38" t="s">
-        <v>39</v>
+      <c r="D38" s="6" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="39" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D39" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C40" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D40" s="8"/>
+    </row>
+    <row r="41" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C41" s="8"/>
+      <c r="D41" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C42" s="8"/>
+      <c r="D42" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="43" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C43" s="8"/>
+      <c r="D43" s="9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="44" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C44" s="8"/>
+      <c r="D44" s="9" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="40" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C40" t="s">
+    <row r="45" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C45" s="8"/>
+      <c r="D45" s="9" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="46" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C46" s="8"/>
+      <c r="D46" s="9" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="47" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C47" s="8"/>
+      <c r="D47" s="8" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="41" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D41" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="42" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D42" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="43" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D43" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="44" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D44" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="45" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D45" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="46" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D46" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="47" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C47" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="48" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C48" t="s">
-        <v>13</v>
+        <v>86</v>
       </c>
     </row>
     <row r="49" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D49" t="s">
-        <v>45</v>
+      <c r="C49" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="50" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D50" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
     </row>
     <row r="51" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D51" t="s">
-        <v>47</v>
+        <v>96</v>
       </c>
     </row>
     <row r="52" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D52" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
     </row>
     <row r="53" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D53" t="s">
-        <v>49</v>
+        <v>98</v>
       </c>
     </row>
     <row r="54" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D54" t="s">
-        <v>50</v>
+      <c r="D54" s="6" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="55" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D55" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="56" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C56" t="s">
-        <v>14</v>
+        <v>88</v>
       </c>
     </row>
     <row r="57" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C57" t="s">
-        <v>15</v>
+        <v>89</v>
       </c>
     </row>
     <row r="58" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C58" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D59" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
     </row>
     <row r="60" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D60" s="3" t="s">
-        <v>52</v>
+      <c r="D60" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="61" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D61" s="3" t="s">
-        <v>53</v>
+      <c r="D61" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="62" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D62" s="3" t="s">
-        <v>134</v>
+      <c r="D62" s="6" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="63" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D63" s="3" t="s">
-        <v>22</v>
+      <c r="D63" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="64" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C64" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F6FFC68-BC6E-45A7-9925-0DFE4309B06B}">
-  <dimension ref="A2:I14"/>
+  <dimension ref="A2:J33"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.33203125" customWidth="1"/>
+    <col min="5" max="5" width="33.33203125" customWidth="1"/>
+    <col min="6" max="8" width="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
-        <v>70</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>56</v>
+        <v>43</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>28</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="G3" t="s">
-        <v>88</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>129</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>131</v>
       </c>
       <c r="F4" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G4" t="s">
-        <v>89</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>133</v>
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>128</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F5" t="s">
+        <v>129</v>
       </c>
       <c r="G5" t="s">
-        <v>88</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>122</v>
+        <v>74</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="C9" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>74</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>76</v>
+        <v>109</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>114</v>
       </c>
       <c r="F9" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G9">
         <v>142536748</v>
       </c>
       <c r="H9" t="s">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="I9" t="s">
-        <v>88</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>74</v>
+      </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="C10" t="s">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>78</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>81</v>
+        <v>111</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>115</v>
       </c>
       <c r="F10" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="G10">
         <v>142536747</v>
       </c>
       <c r="H10" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="I10" t="s">
-        <v>88</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>74</v>
+      </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="C11" t="s">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="D11" t="s">
-        <v>83</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>87</v>
+        <v>113</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>116</v>
       </c>
       <c r="F11" t="s">
-        <v>84</v>
+        <v>117</v>
       </c>
       <c r="G11">
         <v>142536746</v>
       </c>
       <c r="H11" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="I11" t="s">
-        <v>89</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>122</v>
+        <v>74</v>
       </c>
       <c r="B12" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s">
-        <v>96</v>
+        <v>58</v>
       </c>
       <c r="D12" t="s">
-        <v>97</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>99</v>
+        <v>118</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>119</v>
       </c>
       <c r="F12" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="G12">
         <v>142536745</v>
       </c>
       <c r="H12" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="I12" t="s">
-        <v>88</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>120</v>
+        <v>72</v>
       </c>
       <c r="B13" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>108</v>
+        <v>66</v>
       </c>
       <c r="D13" t="s">
-        <v>109</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>111</v>
+        <v>121</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="F13" t="s">
+        <v>123</v>
       </c>
       <c r="G13">
         <v>142536744</v>
       </c>
       <c r="H13" t="s">
-        <v>112</v>
+        <v>67</v>
       </c>
       <c r="I13" t="s">
-        <v>88</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>121</v>
+        <v>73</v>
       </c>
       <c r="B14" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="C14" t="s">
-        <v>118</v>
+        <v>71</v>
       </c>
       <c r="D14" t="s">
-        <v>115</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>117</v>
+        <v>124</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="F14" t="s">
+        <v>126</v>
       </c>
       <c r="G14">
         <v>142536743</v>
       </c>
       <c r="H14" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="I14" t="s">
-        <v>88</v>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="F18" s="10"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>74</v>
+      </c>
+      <c r="B19" t="s">
+        <v>160</v>
+      </c>
+      <c r="C19" t="s">
+        <v>133</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="G19">
+        <v>258963147</v>
+      </c>
+      <c r="H19" t="s">
+        <v>134</v>
+      </c>
+      <c r="J19" s="11">
+        <v>37827</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>74</v>
+      </c>
+      <c r="B20" t="s">
+        <v>160</v>
+      </c>
+      <c r="C20" t="s">
+        <v>135</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="G20">
+        <v>241536789</v>
+      </c>
+      <c r="H20" t="s">
+        <v>136</v>
+      </c>
+      <c r="J20" s="11">
+        <v>38058</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>74</v>
+      </c>
+      <c r="B21" t="s">
+        <v>160</v>
+      </c>
+      <c r="C21" t="s">
+        <v>137</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="G21">
+        <v>267489123</v>
+      </c>
+      <c r="H21" t="s">
+        <v>138</v>
+      </c>
+      <c r="J21" s="11">
+        <v>37827</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>74</v>
+      </c>
+      <c r="B22" t="s">
+        <v>160</v>
+      </c>
+      <c r="C22" t="s">
+        <v>139</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="G22">
+        <v>233654789</v>
+      </c>
+      <c r="H22" t="s">
+        <v>49</v>
+      </c>
+      <c r="J22" s="11">
+        <v>37565</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>74</v>
+      </c>
+      <c r="B23" t="s">
+        <v>160</v>
+      </c>
+      <c r="C23" t="s">
+        <v>140</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="G23">
+        <v>259874123</v>
+      </c>
+      <c r="H23" t="s">
+        <v>141</v>
+      </c>
+      <c r="J23" s="11">
+        <v>38370</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>74</v>
+      </c>
+      <c r="B24" t="s">
+        <v>160</v>
+      </c>
+      <c r="C24" t="s">
+        <v>142</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="G24">
+        <v>210456789</v>
+      </c>
+      <c r="H24" t="s">
+        <v>50</v>
+      </c>
+      <c r="J24" s="11">
+        <v>37164</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>72</v>
+      </c>
+      <c r="B25" t="s">
+        <v>160</v>
+      </c>
+      <c r="C25" t="s">
+        <v>143</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="G25">
+        <v>225147896</v>
+      </c>
+      <c r="H25" t="s">
+        <v>144</v>
+      </c>
+      <c r="J25" s="11">
+        <v>38152</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>72</v>
+      </c>
+      <c r="B26" t="s">
+        <v>160</v>
+      </c>
+      <c r="C26" t="s">
+        <v>145</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="G26">
+        <v>278963254</v>
+      </c>
+      <c r="H26" t="s">
+        <v>46</v>
+      </c>
+      <c r="J26" s="11">
+        <v>37977</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>72</v>
+      </c>
+      <c r="B27" t="s">
+        <v>160</v>
+      </c>
+      <c r="C27" t="s">
+        <v>146</v>
+      </c>
+      <c r="E27" s="4"/>
+      <c r="F27" s="10"/>
+      <c r="G27">
+        <v>244123654</v>
+      </c>
+      <c r="H27" t="s">
+        <v>147</v>
+      </c>
+      <c r="J27" s="11">
+        <v>37354</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>72</v>
+      </c>
+      <c r="B28" t="s">
+        <v>160</v>
+      </c>
+      <c r="C28" t="s">
+        <v>148</v>
+      </c>
+      <c r="E28" s="4"/>
+      <c r="F28" s="10"/>
+      <c r="G28">
+        <v>251478963</v>
+      </c>
+      <c r="H28" t="s">
+        <v>149</v>
+      </c>
+      <c r="J28" s="11">
+        <v>38491</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>72</v>
+      </c>
+      <c r="B29" t="s">
+        <v>160</v>
+      </c>
+      <c r="C29" t="s">
+        <v>150</v>
+      </c>
+      <c r="E29" s="4"/>
+      <c r="F29" s="10"/>
+      <c r="G29">
+        <v>266321458</v>
+      </c>
+      <c r="H29" t="s">
+        <v>151</v>
+      </c>
+      <c r="J29" s="10">
+        <v>38044</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C30" t="s">
+        <v>152</v>
+      </c>
+      <c r="F30" s="10"/>
+      <c r="G30">
+        <v>239852147</v>
+      </c>
+      <c r="H30" t="s">
+        <v>153</v>
+      </c>
+      <c r="J30" s="10">
+        <v>37540</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C31" t="s">
+        <v>154</v>
+      </c>
+      <c r="F31" s="10"/>
+      <c r="G31">
+        <v>288741256</v>
+      </c>
+      <c r="H31" t="s">
+        <v>155</v>
+      </c>
+      <c r="J31" s="10">
+        <v>38418</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C32" t="s">
+        <v>156</v>
+      </c>
+      <c r="F32" s="10"/>
+      <c r="G32">
+        <v>255698147</v>
+      </c>
+      <c r="H32" t="s">
+        <v>157</v>
+      </c>
+      <c r="J32" s="10">
+        <v>37149</v>
+      </c>
+    </row>
+    <row r="33" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C33" t="s">
+        <v>158</v>
+      </c>
+      <c r="G33">
+        <v>242365147</v>
+      </c>
+      <c r="H33" t="s">
+        <v>159</v>
+      </c>
+      <c r="J33" s="10">
+        <v>37946</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E10" r:id="rId1" xr:uid="{D10A8BB7-5313-4D3D-A493-3450AA08CCD8}"/>
+    <hyperlink ref="E11" r:id="rId2" xr:uid="{368CF8DD-CD7E-46AD-AE9B-E7E65C437E3C}"/>
+    <hyperlink ref="E9" r:id="rId3" xr:uid="{0EEED5BB-5602-4B69-B84B-1516174F74B5}"/>
+    <hyperlink ref="E12" r:id="rId4" xr:uid="{557A7878-5DDF-4B61-B65F-1B44527D625A}"/>
+    <hyperlink ref="E13" r:id="rId5" xr:uid="{C2380726-E0B9-4E5F-9542-FF6A48821424}"/>
+    <hyperlink ref="E14" r:id="rId6" xr:uid="{4D76E6C8-A1B7-4059-88CD-43D3E0B7D79D}"/>
+    <hyperlink ref="E3" r:id="rId7" xr:uid="{CBA7D91C-314B-4DDE-8827-1F0ECCB5DFC2}"/>
+    <hyperlink ref="E5" r:id="rId8" xr:uid="{EA843EA4-2FA7-4563-970F-ACFC5897E912}"/>
+    <hyperlink ref="E4" r:id="rId9" xr:uid="{5056049A-F4EB-4412-8F7B-590C5940D0A9}"/>
+    <hyperlink ref="E19" r:id="rId10" xr:uid="{BFCE0457-DBC1-4490-9B3F-D1A39C535521}"/>
+    <hyperlink ref="E20" r:id="rId11" xr:uid="{11D67C9B-3BD8-4708-9D7F-9DD6202E9437}"/>
+    <hyperlink ref="E21" r:id="rId12" xr:uid="{F8E9DD72-E789-488D-9161-236D34A836AC}"/>
+    <hyperlink ref="E22" r:id="rId13" xr:uid="{0E837F76-77A4-4EA6-A02A-1967F0219F07}"/>
+    <hyperlink ref="E23" r:id="rId14" xr:uid="{4DB78900-7B9B-4AF0-A2FE-D7F10CADD1B6}"/>
+    <hyperlink ref="E24" r:id="rId15" xr:uid="{50D470A7-0725-410D-8CA4-74B7FA3A0227}"/>
+    <hyperlink ref="E25" r:id="rId16" xr:uid="{E90F5A7A-F49A-435C-880C-5C1E0AE3FCA2}"/>
+    <hyperlink ref="E26" r:id="rId17" xr:uid="{6CC9203C-CB0C-4093-8D16-9E220717B7E5}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId18"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F3342F1-B6E7-460B-9E26-5A8DC1C1AFB6}">
-  <dimension ref="B2:G36"/>
+  <dimension ref="B2:K37"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="3" width="49.5546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="37.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.44140625" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B2" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>95</v>
+    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>57</v>
       </c>
       <c r="F2" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="G2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B3" s="4"/>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B3" s="1"/>
       <c r="D3" t="s">
-        <v>105</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>91</v>
+        <v>127</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>53</v>
       </c>
       <c r="F3" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="G3">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B4" s="4"/>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B5" s="4" t="s">
+      <c r="I3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J3" t="s">
+        <v>109</v>
+      </c>
+      <c r="K3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B4" s="1"/>
+      <c r="I4" t="s">
+        <v>47</v>
+      </c>
+      <c r="J4" t="s">
+        <v>111</v>
+      </c>
+      <c r="K4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J5" t="s">
+        <v>113</v>
+      </c>
+      <c r="K5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" t="s">
+        <v>58</v>
+      </c>
+      <c r="J6" t="s">
+        <v>118</v>
+      </c>
+      <c r="K6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="C7" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" t="s">
+        <v>66</v>
+      </c>
+      <c r="J7" t="s">
+        <v>121</v>
+      </c>
+      <c r="K7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="D8" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="D8" t="s">
-        <v>104</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>91</v>
+      <c r="E8" s="5" t="s">
+        <v>53</v>
       </c>
       <c r="F8" t="s">
-        <v>78</v>
+        <v>111</v>
       </c>
       <c r="G8">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="I8" t="s">
+        <v>71</v>
+      </c>
+      <c r="J8" t="s">
+        <v>124</v>
+      </c>
+      <c r="K8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
       <c r="D9" t="s">
-        <v>102</v>
-      </c>
-      <c r="E9" s="7"/>
+        <v>61</v>
+      </c>
+      <c r="E9" s="5"/>
       <c r="F9" t="s">
-        <v>74</v>
+        <v>118</v>
       </c>
       <c r="G9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
       <c r="D11" t="s">
-        <v>103</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>92</v>
+        <v>62</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>54</v>
       </c>
       <c r="F11" t="s">
-        <v>78</v>
+        <v>111</v>
       </c>
       <c r="G11">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
       <c r="D12" t="s">
-        <v>101</v>
-      </c>
-      <c r="E12" s="7"/>
+        <v>60</v>
+      </c>
+      <c r="E12" s="5"/>
       <c r="F12" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="G12">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
       <c r="D14" t="s">
-        <v>106</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>107</v>
+        <v>64</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>65</v>
       </c>
       <c r="F14" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="G14">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
       <c r="C15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
       <c r="D16" t="s">
-        <v>104</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>91</v>
+        <v>63</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>53</v>
       </c>
       <c r="F16" t="s">
-        <v>78</v>
+        <v>111</v>
       </c>
       <c r="G16">
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:7" x14ac:dyDescent="0.3">
       <c r="D18" t="s">
-        <v>103</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>92</v>
+        <v>62</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>54</v>
       </c>
       <c r="F18" t="s">
-        <v>78</v>
+        <v>111</v>
       </c>
       <c r="G18">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:7" x14ac:dyDescent="0.3">
       <c r="D19" t="s">
-        <v>113</v>
-      </c>
-      <c r="E19" s="7"/>
+        <v>68</v>
+      </c>
+      <c r="E19" s="5"/>
       <c r="F19" t="s">
         <v>109</v>
       </c>
@@ -1542,12 +2157,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:7" x14ac:dyDescent="0.3">
       <c r="D21" t="s">
-        <v>114</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>107</v>
+        <v>69</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>65</v>
       </c>
       <c r="F21" t="s">
         <v>109</v>
@@ -1556,117 +2171,131 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C22" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="3:7" x14ac:dyDescent="0.3">
       <c r="D23" t="s">
-        <v>104</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>91</v>
+        <v>63</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>53</v>
       </c>
       <c r="F23" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G23">
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:7" x14ac:dyDescent="0.3">
       <c r="D24" t="s">
-        <v>123</v>
-      </c>
-      <c r="E24" s="7"/>
+        <v>75</v>
+      </c>
+      <c r="E24" s="5"/>
       <c r="F24" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="G24">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:7" x14ac:dyDescent="0.3">
       <c r="D25" t="s">
+        <v>76</v>
+      </c>
+      <c r="E25" s="5"/>
+      <c r="F25" t="s">
         <v>124</v>
-      </c>
-      <c r="E25" s="7"/>
-      <c r="F25" t="s">
-        <v>115</v>
       </c>
       <c r="G25">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:7" x14ac:dyDescent="0.3">
       <c r="D26" t="s">
-        <v>125</v>
-      </c>
-      <c r="E26" s="7"/>
+        <v>77</v>
+      </c>
+      <c r="E26" s="5"/>
       <c r="F26" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="G26">
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:7" x14ac:dyDescent="0.3">
       <c r="D27" t="s">
-        <v>127</v>
-      </c>
-      <c r="E27" s="7"/>
+        <v>79</v>
+      </c>
+      <c r="E27" s="5"/>
       <c r="F27" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="G27">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="3:7" x14ac:dyDescent="0.3">
       <c r="D29" t="s">
-        <v>126</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>92</v>
+        <v>78</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>54</v>
       </c>
       <c r="F29" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="G29">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C31" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B32" s="4" t="s">
-        <v>64</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="D31" t="s">
+        <v>169</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F31" t="s">
+        <v>124</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="C32" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B33" s="4"/>
-      <c r="C33" t="s">
-        <v>67</v>
+      <c r="B33" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B34" s="4"/>
+      <c r="B34" s="1"/>
       <c r="C34" t="s">
-        <v>68</v>
+        <v>39</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B35" s="4" t="s">
-        <v>65</v>
+      <c r="B35" s="1"/>
+      <c r="C35" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C36" t="s">
-        <v>69</v>
+      <c r="B36" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C37" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/Testes.xlsx
+++ b/Testes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\utilizador\Documents\CTESP\4semestre\LP2\ProjetoTesteLP2\TrabalhoTesteLP2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00705A8F-2E90-4A0C-B0A9-3E222A712310}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F30389FE-48AD-4442-AF0F-22B28D8F26AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10704" yWindow="1140" windowWidth="11556" windowHeight="9192" activeTab="1" xr2:uid="{17050BBC-8C72-4C7C-BB9E-52ED50A4B6E1}"/>
+    <workbookView xWindow="28680" yWindow="-3870" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{17050BBC-8C72-4C7C-BB9E-52ED50A4B6E1}"/>
   </bookViews>
   <sheets>
     <sheet name="Menus" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="172">
   <si>
     <t>===== SISTEMA ISSMF =====</t>
   </si>
@@ -122,37 +122,7 @@
     <t>--- LISTA DE CURSOS ---</t>
   </si>
   <si>
-    <t>- [ATIVO] LEC - Licenciatura em Engenharia Civil</t>
-  </si>
-  <si>
-    <t>- [ATIVO] LIM - Licenciatura de Engenharia Mecanica</t>
-  </si>
-  <si>
-    <t>- [ATIVO] LEE - Licenciatura de Engenharia Eletrotecnica</t>
-  </si>
-  <si>
-    <t>- [INATIVO] LEN - Licenciatura em Engenharia Nuclear</t>
-  </si>
-  <si>
-    <t>- DEN : Departamento de Engenharia</t>
-  </si>
-  <si>
-    <t>- DEC : Departamento de Economia</t>
-  </si>
-  <si>
-    <t>- DCI : Departamento de Ciencias</t>
-  </si>
-  <si>
     <t>--- LISTA DE DEPARTAMENTOS ---</t>
-  </si>
-  <si>
-    <t>- [ATIVO] LEF - Licenciatura em Economia e Financas</t>
-  </si>
-  <si>
-    <t>- [ATIVO] LGE - Licenciatura em Gestao</t>
-  </si>
-  <si>
-    <t>- [ATIVO] LFQ - Licenciatura em Fisica e Quimica</t>
   </si>
   <si>
     <t>Utilizadores</t>
@@ -368,78 +338,21 @@
     <t>3 - Listar Todos os Gestores</t>
   </si>
   <si>
-    <t>PPA</t>
-  </si>
-  <si>
-    <t>AzAhZFQR</t>
-  </si>
-  <si>
-    <t>PLL</t>
-  </si>
-  <si>
-    <t>J4Wn1RTE</t>
-  </si>
-  <si>
     <t>PYE</t>
   </si>
   <si>
-    <t>ppa@issmf.ipp.pt</t>
-  </si>
-  <si>
-    <t>pll@issmf.ipp.pt</t>
-  </si>
-  <si>
-    <t>pye@issmf.ipp.pt</t>
-  </si>
-  <si>
-    <t>M7cB9BWv</t>
-  </si>
-  <si>
-    <t>PHE</t>
-  </si>
-  <si>
-    <t>phe@issmf.ipp.pt</t>
-  </si>
-  <si>
-    <t>KSufsYmF</t>
-  </si>
-  <si>
-    <t>PHH</t>
-  </si>
-  <si>
-    <t>phh@issmf.ipp.pt</t>
-  </si>
-  <si>
-    <t>O3UfLLHu</t>
-  </si>
-  <si>
-    <t>PTV</t>
-  </si>
-  <si>
-    <t>ptv@issmf.ipp.pt</t>
-  </si>
-  <si>
-    <t>KeZ5WeMb</t>
-  </si>
-  <si>
     <t>[INATIVO] MAT : Matematica Clássica</t>
   </si>
   <si>
     <t>Ovar</t>
   </si>
   <si>
-    <t>jdzaTnLI</t>
-  </si>
-  <si>
     <t>Brandão</t>
   </si>
   <si>
     <t>backoffice_brandão@issmf.ipp.pt</t>
   </si>
   <si>
-    <t>uMzFKVTG</t>
-  </si>
-  <si>
     <t>Afonso Henriques Moreira</t>
   </si>
   <si>
@@ -551,28 +464,97 @@
     <t>[ATIVO] SIE : Sistemas de Energia</t>
   </si>
   <si>
-    <t>6YfBDm9Z</t>
-  </si>
-  <si>
-    <t>COV0Mqqd</t>
-  </si>
-  <si>
-    <t>My0idwK2</t>
-  </si>
-  <si>
-    <t>epUNyyTa</t>
-  </si>
-  <si>
-    <t>2OOrgOHH</t>
-  </si>
-  <si>
-    <t>sH4jkSUf</t>
-  </si>
-  <si>
-    <t>552xhEqO</t>
-  </si>
-  <si>
-    <t>WBqeQJxN</t>
+    <t>[ATIVO] LEM - Licenciatura de Engenharia Mecanica</t>
+  </si>
+  <si>
+    <t>[ATIVO] LEC - Licenciatura em Engenharia Civil</t>
+  </si>
+  <si>
+    <t>[ATIVO] LEE - Licenciatura de Engenharia Eletrotecnica</t>
+  </si>
+  <si>
+    <t>[INATIVO] LEN - Licenciatura em Engenharia Nuclear</t>
+  </si>
+  <si>
+    <t>[ATIVO] LFQ - Licenciatura em Fisica e Quimica</t>
+  </si>
+  <si>
+    <t>DCI : Departamento de Ciencias</t>
+  </si>
+  <si>
+    <t>DEN : Departamento de Engenharia</t>
+  </si>
+  <si>
+    <t>1220492@isep.ipp.p</t>
+  </si>
+  <si>
+    <t>PTL</t>
+  </si>
+  <si>
+    <t>ptl@issmf.ipp.pt</t>
+  </si>
+  <si>
+    <t>OhVk5Rm0</t>
+  </si>
+  <si>
+    <t>qFKiVXcM</t>
+  </si>
+  <si>
+    <t>pti@issmf.ipp.pt</t>
+  </si>
+  <si>
+    <t>PTI</t>
+  </si>
+  <si>
+    <t>q3xc2B8O</t>
+  </si>
+  <si>
+    <t>pvm@issmf.ipp.pt</t>
+  </si>
+  <si>
+    <t>PVM</t>
+  </si>
+  <si>
+    <t>pig@issmf.ipp.pt</t>
+  </si>
+  <si>
+    <t>PIG</t>
+  </si>
+  <si>
+    <t>zJJdEn3X</t>
+  </si>
+  <si>
+    <t>PYS</t>
+  </si>
+  <si>
+    <t>pys@issmf.ipp.pt</t>
+  </si>
+  <si>
+    <t>7hUuoXh5</t>
+  </si>
+  <si>
+    <t>pjr@issmf.ipp.pt</t>
+  </si>
+  <si>
+    <t>gGXBFbhb</t>
+  </si>
+  <si>
+    <t>PJR</t>
+  </si>
+  <si>
+    <t>[ATIVO] DES : Desenho Técnico</t>
+  </si>
+  <si>
+    <t>[INATIVO] REA1 : Reatores 1</t>
+  </si>
+  <si>
+    <t>Paços de Brandão</t>
+  </si>
+  <si>
+    <t>kZUIk0qD</t>
+  </si>
+  <si>
+    <t>SALdEiWF</t>
   </si>
 </sst>
 </file>
@@ -580,9 +562,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="169" formatCode="dd\-mm\-yyyy;@"/>
+    <numFmt numFmtId="164" formatCode="dd\-mm\-yyyy;@"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -598,26 +580,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -633,7 +602,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
@@ -643,15 +612,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" quotePrefix="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperligação" xfId="1" builtinId="8"/>
@@ -971,8 +938,8 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="27.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="38.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.44140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.33203125" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:6" x14ac:dyDescent="0.3">
@@ -982,54 +949,50 @@
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C9" t="s">
+      <c r="C9" s="9" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="8"/>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C11" s="8"/>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="9" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C12" s="8"/>
       <c r="D12" s="9" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C13" s="8"/>
       <c r="D13" s="9" t="s">
         <v>10</v>
       </c>
@@ -1038,285 +1001,258 @@
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C14" s="8"/>
-      <c r="D14" s="8" t="s">
-        <v>91</v>
+      <c r="D14" s="9" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C15" s="8"/>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="9" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="D16" s="8"/>
     </row>
     <row r="17" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C17" s="8"/>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="9" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="18" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C18" s="8"/>
       <c r="D18" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="19" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C19" s="8"/>
       <c r="D19" s="9" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="20" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C20" s="8"/>
-      <c r="D20" s="8" t="s">
-        <v>92</v>
+      <c r="D20" s="9" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="21" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C21" s="8"/>
-      <c r="D21" s="8" t="s">
-        <v>93</v>
+      <c r="D21" s="9" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="22" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C22" s="8"/>
-      <c r="D22" s="8" t="s">
-        <v>94</v>
+      <c r="D22" s="9" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="23" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C23" s="8"/>
-      <c r="D23" s="8" t="s">
+      <c r="D23" s="9" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="24" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D24" s="8"/>
     </row>
     <row r="25" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C25" s="8"/>
-      <c r="D25" s="8" t="s">
+      <c r="D25" s="9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="26" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C26" s="8"/>
       <c r="D26" s="9" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="27" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C27" s="8"/>
       <c r="D27" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="28" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C28" s="8"/>
       <c r="D28" s="9" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="29" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C29" s="8"/>
-      <c r="D29" s="8" t="s">
-        <v>101</v>
+      <c r="D29" s="9" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="30" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C30" s="8"/>
-      <c r="D30" s="8" t="s">
+      <c r="D30" s="9" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="31" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D31" s="9" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="32" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D32" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C33" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D34" s="9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D35" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D36" s="9" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="37" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D37" s="9" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="31" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C31" s="8"/>
-      <c r="D31" s="9" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="32" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C32" s="8"/>
-      <c r="D32" s="8" t="s">
+    <row r="38" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D38" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="39" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D39" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="33" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C33" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D34" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="35" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D35" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="36" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D36" s="6" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="37" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D37" s="6" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="38" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D38" s="6" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="39" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D39" t="s">
-        <v>11</v>
-      </c>
-    </row>
     <row r="40" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C40" s="8" t="s">
+      <c r="C40" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D40" s="8"/>
     </row>
     <row r="41" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C41" s="8"/>
-      <c r="D41" s="8" t="s">
+      <c r="D41" s="9" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="42" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C42" s="8"/>
-      <c r="D42" s="8" t="s">
+      <c r="D42" s="9" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="43" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C43" s="8"/>
       <c r="D43" s="9" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
     </row>
     <row r="44" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C44" s="8"/>
       <c r="D44" s="9" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="45" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C45" s="8"/>
       <c r="D45" s="9" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
     </row>
     <row r="46" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C46" s="8"/>
       <c r="D46" s="9" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="47" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C47" s="8"/>
-      <c r="D47" s="8" t="s">
+      <c r="D47" s="9" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="48" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C48" t="s">
+      <c r="C48" s="9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="49" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C49" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="50" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D50" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="51" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D51" s="9" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="49" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C49" t="s">
+    <row r="52" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D52" s="9" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="50" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D50" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="51" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D51" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="52" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D52" t="s">
+    <row r="53" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D53" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="54" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D54" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="55" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D55" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="56" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C56" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="57" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C57" s="9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="58" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C58" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="59" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D59" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="60" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D60" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="61" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D61" s="9" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="53" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D53" t="s">
+    <row r="62" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D62" s="9" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="54" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D54" s="6" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="55" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D55" t="s">
+    <row r="63" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D63" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="56" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C56" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="57" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C57" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="58" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C58" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="59" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D59" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="60" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D60" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="61" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D61" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="62" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D62" s="6" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="63" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D63" t="s">
-        <v>11</v>
-      </c>
-    </row>
     <row r="64" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C64" t="s">
-        <v>90</v>
+      <c r="C64" s="9" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -1327,7 +1263,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F6FFC68-BC6E-45A7-9925-0DFE4309B06B}">
-  <dimension ref="A2:J33"/>
+  <dimension ref="A2:L33"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11.21875" bestFit="1" customWidth="1"/>
@@ -1338,600 +1274,622 @@
     <col min="10" max="10" width="10.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E3" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>28</v>
       </c>
       <c r="F3" t="s">
         <v>29</v>
       </c>
-      <c r="G3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>130</v>
+        <v>102</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="F4" t="s">
-        <v>132</v>
+        <v>170</v>
       </c>
       <c r="G4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+      <c r="I4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>128</v>
+        <v>101</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F5" t="s">
-        <v>129</v>
+        <v>171</v>
       </c>
       <c r="G5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+      <c r="I5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="D9" t="s">
-        <v>109</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>114</v>
+        <v>149</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>150</v>
       </c>
       <c r="F9" t="s">
-        <v>110</v>
+        <v>151</v>
       </c>
       <c r="G9">
         <v>142536748</v>
       </c>
       <c r="H9" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="I9" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+      <c r="J9" s="7">
+        <v>31186</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D10" t="s">
-        <v>111</v>
+        <v>154</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>115</v>
+        <v>153</v>
       </c>
       <c r="F10" t="s">
-        <v>112</v>
+        <v>152</v>
       </c>
       <c r="G10">
         <v>142536747</v>
       </c>
       <c r="H10" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I10" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+      <c r="J10" s="7">
+        <v>30739</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="B11" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="D11" t="s">
-        <v>113</v>
+        <v>157</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>116</v>
+        <v>156</v>
       </c>
       <c r="F11" t="s">
-        <v>117</v>
+        <v>155</v>
       </c>
       <c r="G11">
         <v>142536746</v>
       </c>
       <c r="H11" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="I11" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+      <c r="J11" s="7">
+        <v>22930</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="D12" t="s">
-        <v>118</v>
+        <v>159</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>119</v>
+        <v>158</v>
       </c>
       <c r="F12" t="s">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="G12">
         <v>142536745</v>
       </c>
       <c r="H12" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="I12" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+      <c r="J12" s="7">
+        <v>31113</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="D13" t="s">
-        <v>121</v>
+        <v>161</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>122</v>
+        <v>162</v>
       </c>
       <c r="F13" t="s">
-        <v>123</v>
+        <v>163</v>
       </c>
       <c r="G13">
         <v>142536744</v>
       </c>
       <c r="H13" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="I13" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+      <c r="J13" s="7">
+        <v>33496</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="D14" t="s">
-        <v>124</v>
+        <v>166</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>125</v>
+        <v>164</v>
       </c>
       <c r="F14" t="s">
-        <v>126</v>
+        <v>165</v>
       </c>
       <c r="G14">
         <v>142536743</v>
       </c>
       <c r="H14" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I14" t="s">
-        <v>51</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="J14" s="7">
+        <v>30641</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="J15" s="7"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="J16" s="7"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J17" s="7"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="F18" s="10"/>
+      <c r="F18" s="6"/>
+      <c r="J18" s="7"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="B19" t="s">
-        <v>160</v>
+        <v>131</v>
       </c>
       <c r="C19" t="s">
-        <v>133</v>
+        <v>104</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="F19" s="10" t="s">
-        <v>170</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="F19" s="6"/>
       <c r="G19">
         <v>258963147</v>
       </c>
       <c r="H19" t="s">
-        <v>134</v>
-      </c>
-      <c r="J19" s="11">
+        <v>105</v>
+      </c>
+      <c r="J19" s="7">
         <v>37827</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="B20" t="s">
-        <v>160</v>
+        <v>131</v>
       </c>
       <c r="C20" t="s">
-        <v>135</v>
+        <v>106</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="F20" s="10" t="s">
-        <v>171</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="F20" s="6"/>
       <c r="G20">
         <v>241536789</v>
       </c>
       <c r="H20" t="s">
-        <v>136</v>
-      </c>
-      <c r="J20" s="11">
+        <v>107</v>
+      </c>
+      <c r="J20" s="7">
         <v>38058</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="B21" t="s">
-        <v>160</v>
+        <v>131</v>
       </c>
       <c r="C21" t="s">
-        <v>137</v>
+        <v>108</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="F21" s="10" t="s">
-        <v>172</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="F21" s="6"/>
       <c r="G21">
         <v>267489123</v>
       </c>
       <c r="H21" t="s">
-        <v>138</v>
-      </c>
-      <c r="J21" s="11">
+        <v>109</v>
+      </c>
+      <c r="J21" s="7">
         <v>37827</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="B22" t="s">
-        <v>160</v>
+        <v>131</v>
       </c>
       <c r="C22" t="s">
-        <v>139</v>
+        <v>110</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="F22" s="10" t="s">
-        <v>173</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="F22" s="6"/>
       <c r="G22">
         <v>233654789</v>
       </c>
       <c r="H22" t="s">
-        <v>49</v>
-      </c>
-      <c r="J22" s="11">
+        <v>39</v>
+      </c>
+      <c r="J22" s="7">
         <v>37565</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="B23" t="s">
-        <v>160</v>
+        <v>131</v>
       </c>
       <c r="C23" t="s">
-        <v>140</v>
+        <v>111</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="F23" s="10" t="s">
-        <v>175</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="F23" s="6"/>
       <c r="G23">
         <v>259874123</v>
       </c>
       <c r="H23" t="s">
-        <v>141</v>
-      </c>
-      <c r="J23" s="11">
+        <v>112</v>
+      </c>
+      <c r="J23" s="7">
         <v>38370</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="B24" t="s">
-        <v>160</v>
+        <v>131</v>
       </c>
       <c r="C24" t="s">
-        <v>142</v>
+        <v>113</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="F24" s="10" t="s">
-        <v>176</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="F24" s="6"/>
       <c r="G24">
         <v>210456789</v>
       </c>
       <c r="H24" t="s">
-        <v>50</v>
-      </c>
-      <c r="J24" s="11">
+        <v>40</v>
+      </c>
+      <c r="J24" s="7">
         <v>37164</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="B25" t="s">
-        <v>160</v>
+        <v>131</v>
       </c>
       <c r="C25" t="s">
-        <v>143</v>
+        <v>114</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="F25" s="10" t="s">
-        <v>177</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="F25" s="6"/>
       <c r="G25">
         <v>225147896</v>
       </c>
       <c r="H25" t="s">
-        <v>144</v>
-      </c>
-      <c r="J25" s="11">
+        <v>115</v>
+      </c>
+      <c r="J25" s="7">
         <v>38152</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="B26" t="s">
-        <v>160</v>
+        <v>131</v>
       </c>
       <c r="C26" t="s">
-        <v>145</v>
+        <v>116</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="F26" s="10" t="s">
-        <v>174</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="F26" s="6"/>
       <c r="G26">
         <v>278963254</v>
       </c>
       <c r="H26" t="s">
-        <v>46</v>
-      </c>
-      <c r="J26" s="11">
+        <v>36</v>
+      </c>
+      <c r="J26" s="7">
         <v>37977</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="B27" t="s">
-        <v>160</v>
+        <v>131</v>
       </c>
       <c r="C27" t="s">
-        <v>146</v>
+        <v>117</v>
       </c>
       <c r="E27" s="4"/>
-      <c r="F27" s="10"/>
+      <c r="F27" s="6"/>
       <c r="G27">
         <v>244123654</v>
       </c>
       <c r="H27" t="s">
-        <v>147</v>
-      </c>
-      <c r="J27" s="11">
+        <v>118</v>
+      </c>
+      <c r="J27" s="7">
         <v>37354</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="B28" t="s">
-        <v>160</v>
+        <v>131</v>
       </c>
       <c r="C28" t="s">
-        <v>148</v>
+        <v>119</v>
       </c>
       <c r="E28" s="4"/>
-      <c r="F28" s="10"/>
+      <c r="F28" s="6"/>
       <c r="G28">
         <v>251478963</v>
       </c>
       <c r="H28" t="s">
-        <v>149</v>
-      </c>
-      <c r="J28" s="11">
+        <v>120</v>
+      </c>
+      <c r="J28" s="7">
         <v>38491</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="B29" t="s">
-        <v>160</v>
+        <v>131</v>
       </c>
       <c r="C29" t="s">
-        <v>150</v>
+        <v>121</v>
       </c>
       <c r="E29" s="4"/>
-      <c r="F29" s="10"/>
+      <c r="F29" s="6"/>
       <c r="G29">
         <v>266321458</v>
       </c>
       <c r="H29" t="s">
-        <v>151</v>
-      </c>
-      <c r="J29" s="10">
+        <v>122</v>
+      </c>
+      <c r="J29" s="7">
         <v>38044</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C30" t="s">
-        <v>152</v>
-      </c>
-      <c r="F30" s="10"/>
+        <v>123</v>
+      </c>
+      <c r="F30" s="6"/>
       <c r="G30">
         <v>239852147</v>
       </c>
       <c r="H30" t="s">
-        <v>153</v>
-      </c>
-      <c r="J30" s="10">
+        <v>124</v>
+      </c>
+      <c r="J30" s="7">
         <v>37540</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C31" t="s">
-        <v>154</v>
-      </c>
-      <c r="F31" s="10"/>
+        <v>125</v>
+      </c>
+      <c r="F31" s="6"/>
       <c r="G31">
         <v>288741256</v>
       </c>
       <c r="H31" t="s">
-        <v>155</v>
-      </c>
-      <c r="J31" s="10">
+        <v>126</v>
+      </c>
+      <c r="J31" s="7">
         <v>38418</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C32" t="s">
-        <v>156</v>
-      </c>
-      <c r="F32" s="10"/>
+        <v>127</v>
+      </c>
+      <c r="F32" s="6"/>
       <c r="G32">
         <v>255698147</v>
       </c>
       <c r="H32" t="s">
-        <v>157</v>
-      </c>
-      <c r="J32" s="10">
+        <v>128</v>
+      </c>
+      <c r="J32" s="7">
         <v>37149</v>
       </c>
     </row>
     <row r="33" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C33" t="s">
-        <v>158</v>
+        <v>129</v>
       </c>
       <c r="G33">
         <v>242365147</v>
       </c>
       <c r="H33" t="s">
-        <v>159</v>
-      </c>
-      <c r="J33" s="10">
+        <v>130</v>
+      </c>
+      <c r="J33" s="7">
         <v>37946</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E10" r:id="rId1" xr:uid="{D10A8BB7-5313-4D3D-A493-3450AA08CCD8}"/>
-    <hyperlink ref="E11" r:id="rId2" xr:uid="{368CF8DD-CD7E-46AD-AE9B-E7E65C437E3C}"/>
-    <hyperlink ref="E9" r:id="rId3" xr:uid="{0EEED5BB-5602-4B69-B84B-1516174F74B5}"/>
-    <hyperlink ref="E12" r:id="rId4" xr:uid="{557A7878-5DDF-4B61-B65F-1B44527D625A}"/>
-    <hyperlink ref="E13" r:id="rId5" xr:uid="{C2380726-E0B9-4E5F-9542-FF6A48821424}"/>
-    <hyperlink ref="E14" r:id="rId6" xr:uid="{4D76E6C8-A1B7-4059-88CD-43D3E0B7D79D}"/>
-    <hyperlink ref="E3" r:id="rId7" xr:uid="{CBA7D91C-314B-4DDE-8827-1F0ECCB5DFC2}"/>
-    <hyperlink ref="E5" r:id="rId8" xr:uid="{EA843EA4-2FA7-4563-970F-ACFC5897E912}"/>
-    <hyperlink ref="E4" r:id="rId9" xr:uid="{5056049A-F4EB-4412-8F7B-590C5940D0A9}"/>
-    <hyperlink ref="E19" r:id="rId10" xr:uid="{BFCE0457-DBC1-4490-9B3F-D1A39C535521}"/>
-    <hyperlink ref="E20" r:id="rId11" xr:uid="{11D67C9B-3BD8-4708-9D7F-9DD6202E9437}"/>
-    <hyperlink ref="E21" r:id="rId12" xr:uid="{F8E9DD72-E789-488D-9161-236D34A836AC}"/>
-    <hyperlink ref="E22" r:id="rId13" xr:uid="{0E837F76-77A4-4EA6-A02A-1967F0219F07}"/>
-    <hyperlink ref="E23" r:id="rId14" xr:uid="{4DB78900-7B9B-4AF0-A2FE-D7F10CADD1B6}"/>
-    <hyperlink ref="E24" r:id="rId15" xr:uid="{50D470A7-0725-410D-8CA4-74B7FA3A0227}"/>
-    <hyperlink ref="E25" r:id="rId16" xr:uid="{E90F5A7A-F49A-435C-880C-5C1E0AE3FCA2}"/>
-    <hyperlink ref="E26" r:id="rId17" xr:uid="{6CC9203C-CB0C-4093-8D16-9E220717B7E5}"/>
+    <hyperlink ref="E3" r:id="rId1" xr:uid="{CBA7D91C-314B-4DDE-8827-1F0ECCB5DFC2}"/>
+    <hyperlink ref="E5" r:id="rId2" xr:uid="{EA843EA4-2FA7-4563-970F-ACFC5897E912}"/>
+    <hyperlink ref="E4" r:id="rId3" xr:uid="{5056049A-F4EB-4412-8F7B-590C5940D0A9}"/>
+    <hyperlink ref="E19" r:id="rId4" xr:uid="{BFCE0457-DBC1-4490-9B3F-D1A39C535521}"/>
+    <hyperlink ref="E20" r:id="rId5" xr:uid="{11D67C9B-3BD8-4708-9D7F-9DD6202E9437}"/>
+    <hyperlink ref="E21" r:id="rId6" xr:uid="{F8E9DD72-E789-488D-9161-236D34A836AC}"/>
+    <hyperlink ref="E22" r:id="rId7" xr:uid="{0E837F76-77A4-4EA6-A02A-1967F0219F07}"/>
+    <hyperlink ref="E23" r:id="rId8" xr:uid="{4DB78900-7B9B-4AF0-A2FE-D7F10CADD1B6}"/>
+    <hyperlink ref="E24" r:id="rId9" xr:uid="{50D470A7-0725-410D-8CA4-74B7FA3A0227}"/>
+    <hyperlink ref="E25" r:id="rId10" xr:uid="{E90F5A7A-F49A-435C-880C-5C1E0AE3FCA2}"/>
+    <hyperlink ref="E26" r:id="rId11" xr:uid="{6CC9203C-CB0C-4093-8D16-9E220717B7E5}"/>
+    <hyperlink ref="L9" r:id="rId12" xr:uid="{DA0E6D89-ED3F-463C-B6BD-8D9A06AF649C}"/>
+    <hyperlink ref="E9" r:id="rId13" xr:uid="{ED4D0B84-D01C-45C6-9047-8FBA6284C347}"/>
+    <hyperlink ref="E10" r:id="rId14" xr:uid="{B01B66E4-E795-46A0-B22A-095E62328844}"/>
+    <hyperlink ref="E11" r:id="rId15" xr:uid="{B182685D-A3A1-41E3-B8A8-6A550568922B}"/>
+    <hyperlink ref="E12" r:id="rId16" xr:uid="{2B9985FB-51C9-4BC0-9E56-DDEAB74C5BB6}"/>
+    <hyperlink ref="E13" r:id="rId17" xr:uid="{67362ED9-1BD8-4423-99E8-6B698F272EBF}"/>
+    <hyperlink ref="E14" r:id="rId18" xr:uid="{828414CD-D337-43A1-B8D8-FE44F51C2E4C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId18"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId19"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F3342F1-B6E7-460B-9E26-5A8DC1C1AFB6}">
-  <dimension ref="B2:K37"/>
+  <dimension ref="B2:N36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="3" width="49.5546875" bestFit="1" customWidth="1"/>
@@ -1944,69 +1902,69 @@
   <sheetData>
     <row r="2" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="F2" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="G2" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B3" s="1"/>
       <c r="D3" t="s">
-        <v>127</v>
+        <v>100</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="F3" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="G3">
         <v>2</v>
       </c>
       <c r="I3" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="J3" t="s">
-        <v>109</v>
+        <v>149</v>
       </c>
       <c r="K3" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B4" s="1"/>
       <c r="I4" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="J4" t="s">
-        <v>111</v>
+        <v>154</v>
       </c>
       <c r="K4" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
-        <v>35</v>
+        <v>147</v>
       </c>
       <c r="I5" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="J5" t="s">
-        <v>113</v>
+        <v>157</v>
       </c>
       <c r="K5" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.3">
@@ -2014,296 +1972,305 @@
         <v>30</v>
       </c>
       <c r="I6" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="J6" t="s">
-        <v>118</v>
+        <v>159</v>
       </c>
       <c r="K6" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.3">
       <c r="C7" t="s">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="I7" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="J7" t="s">
-        <v>121</v>
+        <v>161</v>
       </c>
       <c r="K7" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="D8" t="s">
-        <v>63</v>
-      </c>
-      <c r="E8" s="5" t="s">
         <v>53</v>
       </c>
+      <c r="E8" s="8" t="s">
+        <v>43</v>
+      </c>
       <c r="F8" t="s">
-        <v>111</v>
+        <v>154</v>
       </c>
       <c r="G8">
         <v>2</v>
       </c>
       <c r="I8" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="J8" t="s">
-        <v>124</v>
+        <v>166</v>
       </c>
       <c r="K8" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.3">
       <c r="D9" t="s">
-        <v>61</v>
-      </c>
-      <c r="E9" s="5"/>
+        <v>51</v>
+      </c>
+      <c r="E9" s="8"/>
       <c r="F9" t="s">
-        <v>118</v>
+        <v>149</v>
       </c>
       <c r="G9">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="D11" t="s">
-        <v>62</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F11" t="s">
-        <v>111</v>
-      </c>
-      <c r="G11">
-        <v>2</v>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="D10" t="s">
+        <v>167</v>
+      </c>
+      <c r="E10" s="8"/>
+      <c r="F10" t="s">
+        <v>149</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.3">
       <c r="D12" t="s">
-        <v>60</v>
-      </c>
-      <c r="E12" s="5"/>
+        <v>52</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>44</v>
+      </c>
       <c r="F12" t="s">
-        <v>121</v>
+        <v>154</v>
       </c>
       <c r="G12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="D13" t="s">
+        <v>50</v>
+      </c>
+      <c r="E13" s="8"/>
+      <c r="F13" t="s">
+        <v>159</v>
+      </c>
+      <c r="G13">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="D14" t="s">
-        <v>64</v>
-      </c>
-      <c r="E14" s="3" t="s">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="D15" t="s">
+        <v>54</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F15" t="s">
+        <v>159</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="C16" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D17" t="s">
+        <v>53</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F17" t="s">
+        <v>154</v>
+      </c>
+      <c r="G17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D19" t="s">
+        <v>52</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F19" t="s">
+        <v>154</v>
+      </c>
+      <c r="G19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D20" t="s">
+        <v>58</v>
+      </c>
+      <c r="E20" s="8"/>
+      <c r="F20" t="s">
+        <v>161</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D22" t="s">
+        <v>59</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F22" t="s">
+        <v>161</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C23" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D24" t="s">
+        <v>53</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F24" t="s">
+        <v>154</v>
+      </c>
+      <c r="G24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D25" t="s">
         <v>65</v>
       </c>
-      <c r="F14" t="s">
-        <v>121</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="C15" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="D16" t="s">
-        <v>63</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F16" t="s">
-        <v>111</v>
-      </c>
-      <c r="G16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="D18" t="s">
-        <v>62</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F18" t="s">
-        <v>111</v>
-      </c>
-      <c r="G18">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="D19" t="s">
-        <v>68</v>
-      </c>
-      <c r="E19" s="5"/>
-      <c r="F19" t="s">
-        <v>109</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="D21" t="s">
-        <v>69</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F21" t="s">
-        <v>109</v>
-      </c>
-      <c r="G21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C22" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="23" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="D23" t="s">
-        <v>63</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="F23" t="s">
-        <v>111</v>
-      </c>
-      <c r="G23">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="D24" t="s">
-        <v>75</v>
-      </c>
-      <c r="E24" s="5"/>
-      <c r="F24" t="s">
-        <v>124</v>
-      </c>
-      <c r="G24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="D25" t="s">
-        <v>76</v>
-      </c>
-      <c r="E25" s="5"/>
+      <c r="E25" s="8"/>
       <c r="F25" t="s">
-        <v>124</v>
+        <v>166</v>
       </c>
       <c r="G25">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:14" x14ac:dyDescent="0.3">
       <c r="D26" t="s">
-        <v>77</v>
-      </c>
-      <c r="E26" s="5"/>
+        <v>66</v>
+      </c>
+      <c r="E26" s="8"/>
       <c r="F26" t="s">
-        <v>124</v>
+        <v>166</v>
       </c>
       <c r="G26">
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:14" x14ac:dyDescent="0.3">
       <c r="D27" t="s">
-        <v>79</v>
-      </c>
-      <c r="E27" s="5"/>
+        <v>67</v>
+      </c>
+      <c r="E27" s="8"/>
       <c r="F27" t="s">
-        <v>124</v>
+        <v>166</v>
       </c>
       <c r="G27">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="D29" t="s">
-        <v>78</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F29" t="s">
-        <v>124</v>
-      </c>
-      <c r="G29">
+    <row r="28" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D28" t="s">
+        <v>69</v>
+      </c>
+      <c r="E28" s="8"/>
+      <c r="F28" t="s">
+        <v>166</v>
+      </c>
+      <c r="G28">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="D31" t="s">
-        <v>169</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F31" t="s">
-        <v>124</v>
-      </c>
-      <c r="G31">
+    <row r="30" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D30" t="s">
+        <v>68</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F30" t="s">
+        <v>166</v>
+      </c>
+      <c r="G30">
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C32" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B33" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B34" s="1"/>
-      <c r="C34" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B35" s="1"/>
-      <c r="C35" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B36" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C37" t="s">
-        <v>41</v>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="E32" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K32" t="s">
+        <v>140</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="M32" t="s">
+        <v>166</v>
+      </c>
+      <c r="N32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="C33" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="D34" t="s">
+        <v>168</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F34" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="35" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B35" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="36" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="C36" t="s">
+        <v>145</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="E23:E27"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="E24:E28"/>
+    <mergeCell ref="E8:E10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Testes.xlsx
+++ b/Testes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\utilizador\Documents\CTESP\4semestre\LP2\ProjetoTesteLP2\TrabalhoTesteLP2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F30389FE-48AD-4442-AF0F-22B28D8F26AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF294FE5-EBB7-44E9-A73F-1BEA74B2D845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-3870" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{17050BBC-8C72-4C7C-BB9E-52ED50A4B6E1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{17050BBC-8C72-4C7C-BB9E-52ED50A4B6E1}"/>
   </bookViews>
   <sheets>
     <sheet name="Menus" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="186">
   <si>
     <t>===== SISTEMA ISSMF =====</t>
   </si>
@@ -224,16 +224,10 @@
     <t>LEC</t>
   </si>
   <si>
-    <t>[ATIVO] PRO1 : Programacao 1</t>
-  </si>
-  <si>
     <t>[ATIVO] CIR : Circuitos</t>
   </si>
   <si>
     <t>[ATIVO] SDE : Sistemas Digitais Eletricos</t>
-  </si>
-  <si>
-    <t>[ATIVO] PRO2 : Programacao 2</t>
   </si>
   <si>
     <t>[ATIVO] ELE : Eletromagnetismo</t>
@@ -556,6 +550,54 @@
   <si>
     <t>SALdEiWF</t>
   </si>
+  <si>
+    <t>1220492@isep.ipp.pt</t>
+  </si>
+  <si>
+    <t>Professor Renato</t>
+  </si>
+  <si>
+    <t>Matosinhos</t>
+  </si>
+  <si>
+    <t>PZW</t>
+  </si>
+  <si>
+    <t>pzw@issmf.ipp.pt</t>
+  </si>
+  <si>
+    <t>ixHY3WHq</t>
+  </si>
+  <si>
+    <t>[ATIVO] PRO1 : Programação 1</t>
+  </si>
+  <si>
+    <t>[ATIVO] PRO2 : Programação 2</t>
+  </si>
+  <si>
+    <t>vMGjk267</t>
+  </si>
+  <si>
+    <t>A0yAbfyw</t>
+  </si>
+  <si>
+    <t>m02pgLII</t>
+  </si>
+  <si>
+    <t>xyhneMEl</t>
+  </si>
+  <si>
+    <t>cso5rVqR</t>
+  </si>
+  <si>
+    <t>nGF2AsC9</t>
+  </si>
+  <si>
+    <t>T3WvLkPs</t>
+  </si>
+  <si>
+    <t>oGwlX18G</t>
+  </si>
 </sst>
 </file>
 
@@ -564,7 +606,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\-mm\-yyyy;@"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -580,13 +622,48 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -602,7 +679,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
@@ -615,10 +692,23 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" quotePrefix="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperligação" xfId="1" builtinId="8"/>
@@ -938,8 +1028,8 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="27.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.44140625" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="38.33203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:6" x14ac:dyDescent="0.3">
@@ -949,51 +1039,51 @@
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C9" s="9" t="s">
+      <c r="C9" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C10" s="9" t="s">
+      <c r="C10" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="D11" s="9" t="s">
+      <c r="D11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="D12" s="9" t="s">
+      <c r="D12" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="D13" s="9" t="s">
+      <c r="D13" t="s">
         <v>10</v>
       </c>
       <c r="F13" t="s">
@@ -1001,258 +1091,258 @@
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="D14" s="9" t="s">
+      <c r="D14" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="C16" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D17" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D19" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D20" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D21" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="D15" s="9" t="s">
+    <row r="22" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D22" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="23" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D23" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C16" s="9" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D17" s="9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D18" s="9" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D19" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D20" s="9" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="21" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D21" s="9" t="s">
+    <row r="24" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C24" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D25" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D26" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="27" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D27" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D28" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D29" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="30" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D30" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="22" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D22" s="9" t="s">
+    <row r="31" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D31" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="32" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D32" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C33" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D34" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D35" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D36" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="37" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D37" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="38" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D38" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="39" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D39" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C40" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D41" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D42" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="43" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D43" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="44" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D44" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="45" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D45" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="46" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D46" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="47" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D47" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C48" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="49" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C49" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="50" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D50" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="51" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D51" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="23" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D23" s="9" t="s">
+    <row r="52" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D52" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="53" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D53" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="54" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D54" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="55" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D55" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C24" s="9" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D25" s="9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D26" s="9" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="27" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D27" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="28" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D28" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="29" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D29" s="9" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="30" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D30" s="9" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="31" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D31" s="9" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="32" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D32" s="9" t="s">
+    <row r="56" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C56" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="57" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C57" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="58" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C58" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="59" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D59" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="60" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D60" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="61" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D61" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="62" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D62" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="63" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D63" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="33" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C33" s="9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D34" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="35" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D35" s="9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="36" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D36" s="9" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="37" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D37" s="9" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="38" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D38" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="39" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D39" s="9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="40" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C40" s="9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D41" s="9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="42" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D42" s="9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="43" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D43" s="9" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="44" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D44" s="9" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="45" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D45" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="46" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D46" s="9" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="47" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D47" s="9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="48" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C48" s="9" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="49" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C49" s="9" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="50" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D50" s="9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="51" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D51" s="9" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="52" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D52" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="53" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D53" s="9" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="54" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D54" s="9" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="55" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D55" s="9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="56" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C56" s="9" t="s">
+    <row r="64" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C64" t="s">
         <v>78</v>
-      </c>
-    </row>
-    <row r="57" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C57" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="58" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C58" s="9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="59" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D59" s="9" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="60" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D60" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="61" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D61" s="9" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="62" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D62" s="9" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="63" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D63" s="9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="64" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C64" s="9" t="s">
-        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -1272,6 +1362,7 @@
     <col min="5" max="5" width="33.33203125" customWidth="1"/>
     <col min="6" max="8" width="10" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
@@ -1301,16 +1392,16 @@
         <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="I4" t="s">
         <v>42</v>
@@ -1321,16 +1412,16 @@
         <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F5" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="I5" t="s">
         <v>41</v>
@@ -1347,13 +1438,13 @@
         <v>35</v>
       </c>
       <c r="D9" t="s">
+        <v>147</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="F9" t="s">
         <v>149</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="F9" t="s">
-        <v>151</v>
       </c>
       <c r="G9">
         <v>142536748</v>
@@ -1368,7 +1459,7 @@
         <v>31186</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
@@ -1382,13 +1473,13 @@
         <v>37</v>
       </c>
       <c r="D10" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F10" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G10">
         <v>142536747</v>
@@ -1414,13 +1505,13 @@
         <v>38</v>
       </c>
       <c r="D11" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F11" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G11">
         <v>142536746</v>
@@ -1446,13 +1537,13 @@
         <v>48</v>
       </c>
       <c r="D12" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E12" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="F12" t="s">
         <v>158</v>
-      </c>
-      <c r="F12" t="s">
-        <v>160</v>
       </c>
       <c r="G12">
         <v>142536745</v>
@@ -1478,13 +1569,13 @@
         <v>56</v>
       </c>
       <c r="D13" t="s">
+        <v>159</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="F13" t="s">
         <v>161</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="F13" t="s">
-        <v>163</v>
       </c>
       <c r="G13">
         <v>142536744</v>
@@ -1510,13 +1601,13 @@
         <v>61</v>
       </c>
       <c r="D14" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F14" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G14">
         <v>142536743</v>
@@ -1532,219 +1623,282 @@
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="J15" s="7"/>
+      <c r="B15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D15" t="s">
+        <v>173</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="F15" t="s">
+        <v>175</v>
+      </c>
+      <c r="G15">
+        <v>142536742</v>
+      </c>
+      <c r="H15" t="s">
+        <v>172</v>
+      </c>
+      <c r="I15" t="s">
+        <v>41</v>
+      </c>
+      <c r="J15" s="7">
+        <v>32468</v>
+      </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="J16" s="7"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="J17" s="7"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F18" s="6"/>
       <c r="J18" s="7"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>64</v>
       </c>
       <c r="B19" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C19" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="F19" s="6"/>
+        <v>130</v>
+      </c>
+      <c r="F19" t="s">
+        <v>178</v>
+      </c>
       <c r="G19">
         <v>258963147</v>
       </c>
       <c r="H19" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="J19" s="7">
         <v>37827</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K19" s="7"/>
+      <c r="L19" s="4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>64</v>
       </c>
       <c r="B20" t="s">
+        <v>129</v>
+      </c>
+      <c r="C20" t="s">
+        <v>104</v>
+      </c>
+      <c r="E20" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="C20" t="s">
-        <v>106</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="F20" s="6"/>
+      <c r="F20" t="s">
+        <v>185</v>
+      </c>
       <c r="G20">
         <v>241536789</v>
       </c>
       <c r="H20" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="J20" s="7">
         <v>38058</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K20" s="7"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>64</v>
       </c>
       <c r="B21" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C21" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="F21" s="6"/>
+        <v>132</v>
+      </c>
+      <c r="F21" t="s">
+        <v>179</v>
+      </c>
       <c r="G21">
         <v>267489123</v>
       </c>
       <c r="H21" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="J21" s="7">
         <v>37827</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K21" s="7"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>64</v>
       </c>
-      <c r="B22" t="s">
-        <v>131</v>
-      </c>
-      <c r="C22" t="s">
-        <v>110</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="F22" s="6"/>
-      <c r="G22">
+      <c r="B22" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="D22" s="8"/>
+      <c r="E22" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G22" s="8">
         <v>233654789</v>
       </c>
-      <c r="H22" t="s">
+      <c r="H22" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="J22" s="7">
+      <c r="I22" s="8"/>
+      <c r="J22" s="10">
         <v>37565</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K22" s="7"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>64</v>
       </c>
-      <c r="B23" t="s">
-        <v>131</v>
-      </c>
-      <c r="C23" t="s">
-        <v>111</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="F23" s="6"/>
-      <c r="G23">
+      <c r="B23" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="D23" s="15"/>
+      <c r="E23" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="F23" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="G23" s="15">
         <v>259874123</v>
       </c>
-      <c r="H23" t="s">
-        <v>112</v>
-      </c>
-      <c r="J23" s="7">
+      <c r="H23" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="I23" s="15"/>
+      <c r="J23" s="17">
         <v>38370</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K23" s="7"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>64</v>
       </c>
-      <c r="B24" t="s">
-        <v>131</v>
-      </c>
-      <c r="C24" t="s">
+      <c r="B24" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="D24" s="11"/>
+      <c r="E24" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="F24" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="G24" s="11">
+        <v>210456789</v>
+      </c>
+      <c r="H24" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="I24" s="11"/>
+      <c r="J24" s="14">
+        <v>37164</v>
+      </c>
+      <c r="K24" s="7"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A25" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="B25" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="C25" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="D25" s="18"/>
+      <c r="E25" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="F25" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="G25" s="18">
+        <v>225147896</v>
+      </c>
+      <c r="H25" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="I25" s="18"/>
+      <c r="J25" s="21">
+        <v>38152</v>
+      </c>
+      <c r="K25" s="7"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="B26" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="C26" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="D26" s="18"/>
+      <c r="E26" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="F24" s="6"/>
-      <c r="G24">
-        <v>210456789</v>
-      </c>
-      <c r="H24" t="s">
-        <v>40</v>
-      </c>
-      <c r="J24" s="7">
-        <v>37164</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>62</v>
-      </c>
-      <c r="B25" t="s">
-        <v>131</v>
-      </c>
-      <c r="C25" t="s">
-        <v>114</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="F25" s="6"/>
-      <c r="G25">
-        <v>225147896</v>
-      </c>
-      <c r="H25" t="s">
-        <v>115</v>
-      </c>
-      <c r="J25" s="7">
-        <v>38152</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>62</v>
-      </c>
-      <c r="B26" t="s">
-        <v>131</v>
-      </c>
-      <c r="C26" t="s">
-        <v>116</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="F26" s="6"/>
-      <c r="G26">
+      <c r="F26" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="G26" s="18">
         <v>278963254</v>
       </c>
-      <c r="H26" t="s">
+      <c r="H26" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="J26" s="7">
+      <c r="I26" s="18"/>
+      <c r="J26" s="21">
         <v>37977</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K26" s="7"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>62</v>
       </c>
       <c r="B27" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C27" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E27" s="4"/>
       <c r="F27" s="6"/>
@@ -1752,21 +1906,22 @@
         <v>244123654</v>
       </c>
       <c r="H27" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J27" s="7">
         <v>37354</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K27" s="7"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>62</v>
       </c>
       <c r="B28" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C28" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E28" s="4"/>
       <c r="F28" s="6"/>
@@ -1774,21 +1929,22 @@
         <v>251478963</v>
       </c>
       <c r="H28" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J28" s="7">
         <v>38491</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K28" s="7"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>62</v>
       </c>
       <c r="B29" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C29" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E29" s="4"/>
       <c r="F29" s="6"/>
@@ -1796,70 +1952,75 @@
         <v>266321458</v>
       </c>
       <c r="H29" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J29" s="7">
         <v>38044</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K29" s="7"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C30" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F30" s="6"/>
       <c r="G30">
         <v>239852147</v>
       </c>
       <c r="H30" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="J30" s="7">
         <v>37540</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K30" s="7"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C31" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F31" s="6"/>
       <c r="G31">
         <v>288741256</v>
       </c>
       <c r="H31" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="J31" s="7">
         <v>38418</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K31" s="7"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C32" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F32" s="6"/>
       <c r="G32">
         <v>255698147</v>
       </c>
       <c r="H32" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="J32" s="7">
         <v>37149</v>
       </c>
-    </row>
-    <row r="33" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="K32" s="7"/>
+    </row>
+    <row r="33" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C33" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G33">
         <v>242365147</v>
       </c>
       <c r="H33" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="J33" s="7">
         <v>37946</v>
       </c>
+      <c r="K33" s="7"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1869,21 +2030,23 @@
     <hyperlink ref="E19" r:id="rId4" xr:uid="{BFCE0457-DBC1-4490-9B3F-D1A39C535521}"/>
     <hyperlink ref="E20" r:id="rId5" xr:uid="{11D67C9B-3BD8-4708-9D7F-9DD6202E9437}"/>
     <hyperlink ref="E21" r:id="rId6" xr:uid="{F8E9DD72-E789-488D-9161-236D34A836AC}"/>
-    <hyperlink ref="E22" r:id="rId7" xr:uid="{0E837F76-77A4-4EA6-A02A-1967F0219F07}"/>
-    <hyperlink ref="E23" r:id="rId8" xr:uid="{4DB78900-7B9B-4AF0-A2FE-D7F10CADD1B6}"/>
-    <hyperlink ref="E24" r:id="rId9" xr:uid="{50D470A7-0725-410D-8CA4-74B7FA3A0227}"/>
-    <hyperlink ref="E25" r:id="rId10" xr:uid="{E90F5A7A-F49A-435C-880C-5C1E0AE3FCA2}"/>
-    <hyperlink ref="E26" r:id="rId11" xr:uid="{6CC9203C-CB0C-4093-8D16-9E220717B7E5}"/>
-    <hyperlink ref="L9" r:id="rId12" xr:uid="{DA0E6D89-ED3F-463C-B6BD-8D9A06AF649C}"/>
-    <hyperlink ref="E9" r:id="rId13" xr:uid="{ED4D0B84-D01C-45C6-9047-8FBA6284C347}"/>
-    <hyperlink ref="E10" r:id="rId14" xr:uid="{B01B66E4-E795-46A0-B22A-095E62328844}"/>
-    <hyperlink ref="E11" r:id="rId15" xr:uid="{B182685D-A3A1-41E3-B8A8-6A550568922B}"/>
-    <hyperlink ref="E12" r:id="rId16" xr:uid="{2B9985FB-51C9-4BC0-9E56-DDEAB74C5BB6}"/>
-    <hyperlink ref="E13" r:id="rId17" xr:uid="{67362ED9-1BD8-4423-99E8-6B698F272EBF}"/>
-    <hyperlink ref="E14" r:id="rId18" xr:uid="{828414CD-D337-43A1-B8D8-FE44F51C2E4C}"/>
+    <hyperlink ref="E23" r:id="rId7" xr:uid="{4DB78900-7B9B-4AF0-A2FE-D7F10CADD1B6}"/>
+    <hyperlink ref="E24" r:id="rId8" xr:uid="{50D470A7-0725-410D-8CA4-74B7FA3A0227}"/>
+    <hyperlink ref="E25" r:id="rId9" xr:uid="{E90F5A7A-F49A-435C-880C-5C1E0AE3FCA2}"/>
+    <hyperlink ref="E26" r:id="rId10" xr:uid="{6CC9203C-CB0C-4093-8D16-9E220717B7E5}"/>
+    <hyperlink ref="L9" r:id="rId11" xr:uid="{DA0E6D89-ED3F-463C-B6BD-8D9A06AF649C}"/>
+    <hyperlink ref="E9" r:id="rId12" xr:uid="{ED4D0B84-D01C-45C6-9047-8FBA6284C347}"/>
+    <hyperlink ref="E10" r:id="rId13" xr:uid="{B01B66E4-E795-46A0-B22A-095E62328844}"/>
+    <hyperlink ref="E11" r:id="rId14" xr:uid="{B182685D-A3A1-41E3-B8A8-6A550568922B}"/>
+    <hyperlink ref="E12" r:id="rId15" xr:uid="{2B9985FB-51C9-4BC0-9E56-DDEAB74C5BB6}"/>
+    <hyperlink ref="E13" r:id="rId16" xr:uid="{67362ED9-1BD8-4423-99E8-6B698F272EBF}"/>
+    <hyperlink ref="E14" r:id="rId17" xr:uid="{828414CD-D337-43A1-B8D8-FE44F51C2E4C}"/>
+    <hyperlink ref="L19" r:id="rId18" xr:uid="{77EFE0E2-B24B-49A5-A3E8-40BD34FAC10C}"/>
+    <hyperlink ref="E22" r:id="rId19" xr:uid="{0E837F76-77A4-4EA6-A02A-1967F0219F07}"/>
+    <hyperlink ref="E15" r:id="rId20" xr:uid="{9FCFB030-93FD-458E-A7B4-C7BAAE020CBE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId19"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId21"/>
 </worksheet>
 </file>
 
@@ -1920,13 +2083,13 @@
     <row r="3" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B3" s="1"/>
       <c r="D3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>43</v>
       </c>
       <c r="F3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1935,7 +2098,7 @@
         <v>35</v>
       </c>
       <c r="J3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="K3" t="s">
         <v>41</v>
@@ -1947,7 +2110,7 @@
         <v>37</v>
       </c>
       <c r="J4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="K4" t="s">
         <v>41</v>
@@ -1955,13 +2118,13 @@
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="I5" t="s">
         <v>38</v>
       </c>
       <c r="J5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="K5" t="s">
         <v>42</v>
@@ -1975,7 +2138,7 @@
         <v>48</v>
       </c>
       <c r="J6" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="K6" t="s">
         <v>41</v>
@@ -1983,13 +2146,13 @@
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.3">
       <c r="C7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="I7" t="s">
         <v>56</v>
       </c>
       <c r="J7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K7" t="s">
         <v>41</v>
@@ -1999,11 +2162,11 @@
       <c r="D8" t="s">
         <v>53</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="22" t="s">
         <v>43</v>
       </c>
       <c r="F8" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -2012,7 +2175,7 @@
         <v>61</v>
       </c>
       <c r="J8" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="K8" t="s">
         <v>41</v>
@@ -2022,9 +2185,9 @@
       <c r="D9" t="s">
         <v>51</v>
       </c>
-      <c r="E9" s="8"/>
+      <c r="E9" s="22"/>
       <c r="F9" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -2032,11 +2195,11 @@
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.3">
       <c r="D10" t="s">
-        <v>167</v>
-      </c>
-      <c r="E10" s="8"/>
+        <v>165</v>
+      </c>
+      <c r="E10" s="22"/>
       <c r="F10" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -2046,11 +2209,11 @@
       <c r="D12" t="s">
         <v>52</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="22" t="s">
         <v>44</v>
       </c>
       <c r="F12" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -2060,9 +2223,9 @@
       <c r="D13" t="s">
         <v>50</v>
       </c>
-      <c r="E13" s="8"/>
+      <c r="E13" s="22"/>
       <c r="F13" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -2076,7 +2239,7 @@
         <v>55</v>
       </c>
       <c r="F15" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -2084,7 +2247,7 @@
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.3">
       <c r="C16" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="17" spans="3:14" x14ac:dyDescent="0.3">
@@ -2095,7 +2258,7 @@
         <v>43</v>
       </c>
       <c r="F17" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G17">
         <v>2</v>
@@ -2105,11 +2268,11 @@
       <c r="D19" t="s">
         <v>52</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="E19" s="22" t="s">
         <v>44</v>
       </c>
       <c r="F19" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G19">
         <v>2</v>
@@ -2119,9 +2282,9 @@
       <c r="D20" t="s">
         <v>58</v>
       </c>
-      <c r="E20" s="8"/>
+      <c r="E20" s="22"/>
       <c r="F20" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -2135,7 +2298,7 @@
         <v>55</v>
       </c>
       <c r="F22" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -2143,18 +2306,18 @@
     </row>
     <row r="23" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C23" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="24" spans="3:14" x14ac:dyDescent="0.3">
       <c r="D24" t="s">
         <v>53</v>
       </c>
-      <c r="E24" s="8" t="s">
+      <c r="E24" s="22" t="s">
         <v>43</v>
       </c>
       <c r="F24" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G24">
         <v>2</v>
@@ -2162,11 +2325,11 @@
     </row>
     <row r="25" spans="3:14" x14ac:dyDescent="0.3">
       <c r="D25" t="s">
-        <v>65</v>
-      </c>
-      <c r="E25" s="8"/>
+        <v>176</v>
+      </c>
+      <c r="E25" s="22"/>
       <c r="F25" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -2174,11 +2337,11 @@
     </row>
     <row r="26" spans="3:14" x14ac:dyDescent="0.3">
       <c r="D26" t="s">
-        <v>66</v>
-      </c>
-      <c r="E26" s="8"/>
+        <v>65</v>
+      </c>
+      <c r="E26" s="22"/>
       <c r="F26" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -2186,11 +2349,11 @@
     </row>
     <row r="27" spans="3:14" x14ac:dyDescent="0.3">
       <c r="D27" t="s">
-        <v>67</v>
-      </c>
-      <c r="E27" s="8"/>
+        <v>66</v>
+      </c>
+      <c r="E27" s="22"/>
       <c r="F27" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -2198,11 +2361,11 @@
     </row>
     <row r="28" spans="3:14" x14ac:dyDescent="0.3">
       <c r="D28" t="s">
-        <v>69</v>
-      </c>
-      <c r="E28" s="8"/>
+        <v>67</v>
+      </c>
+      <c r="E28" s="22"/>
       <c r="F28" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -2210,13 +2373,13 @@
     </row>
     <row r="30" spans="3:14" x14ac:dyDescent="0.3">
       <c r="D30" t="s">
-        <v>68</v>
+        <v>177</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>44</v>
       </c>
       <c r="F30" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -2227,42 +2390,45 @@
         <v>55</v>
       </c>
       <c r="K32" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L32" s="3" t="s">
         <v>55</v>
       </c>
       <c r="M32" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="N32">
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
       <c r="C33" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.3">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
       <c r="D34" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>43</v>
       </c>
       <c r="F34" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.3">
+        <v>155</v>
+      </c>
+      <c r="G34">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B35" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.3">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.3">
       <c r="C36" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>

--- a/Testes.xlsx
+++ b/Testes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\utilizador\Documents\CTESP\4semestre\LP2\ProjetoTesteLP2\TrabalhoTesteLP2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF294FE5-EBB7-44E9-A73F-1BEA74B2D845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49B0CAE2-46CD-4AD6-8205-0AC00C906970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{17050BBC-8C72-4C7C-BB9E-52ED50A4B6E1}"/>
+    <workbookView xWindow="28680" yWindow="-3870" windowWidth="20730" windowHeight="11040" xr2:uid="{17050BBC-8C72-4C7C-BB9E-52ED50A4B6E1}"/>
   </bookViews>
   <sheets>
     <sheet name="Menus" sheetId="1" r:id="rId1"/>
@@ -27,34 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="186">
-  <si>
-    <t>===== SISTEMA ISSMF =====</t>
-  </si>
-  <si>
-    <t>=== BACKOFFICE - GESTOR ===</t>
-  </si>
-  <si>
-    <t>1 - Gerir Departamentos</t>
-  </si>
-  <si>
-    <t>2 - Gerir Cursos</t>
-  </si>
-  <si>
-    <t>3 - Gerir Unidades Curriculares</t>
-  </si>
-  <si>
-    <t>4 - Gerir Estudantes</t>
-  </si>
-  <si>
-    <t>5 - Gerir Docentes</t>
-  </si>
-  <si>
-    <t>10 - Gerir Gestores</t>
-  </si>
-  <si>
-    <t>--- GERIR DEPARTAMENTOS ---</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="236">
   <si>
     <t>1 - Adicionar Departamento</t>
   </si>
@@ -65,51 +38,27 @@
     <t>0 - Recuar</t>
   </si>
   <si>
-    <t>--- GERIR CURSOS ---</t>
-  </si>
-  <si>
     <t>1 - Adicionar Curso</t>
   </si>
   <si>
     <t>2 - Alterar Curso</t>
   </si>
   <si>
-    <t>--- GERIR UNIDADES CURRICULARES ---</t>
-  </si>
-  <si>
     <t>2 - Associar UC Existente a outro Curso</t>
   </si>
   <si>
     <t>3 - Alterar Unidade Curricular</t>
   </si>
   <si>
-    <t>--- GERIR ESTUDANTES ---</t>
-  </si>
-  <si>
     <t>1 - Adicionar Estudante</t>
   </si>
   <si>
-    <t>--- GERIR DOCENTES ---</t>
-  </si>
-  <si>
     <t>1 - Adicionar Docente</t>
   </si>
   <si>
-    <t>3 - Listar Docentes</t>
-  </si>
-  <si>
-    <t>--- RELATÓRIOS E ESTATÍSTICAS ---</t>
-  </si>
-  <si>
-    <t>--- GERIR GESTORES ---</t>
-  </si>
-  <si>
     <t>1 - Adicionar Gestor</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
     <t>Gestor</t>
   </si>
   <si>
@@ -185,12 +134,6 @@
     <t>[ATIVO] EM1 : Engenharia dos Materiais 1</t>
   </si>
   <si>
-    <t>[ATIVO] MAT2 : Matematica 2</t>
-  </si>
-  <si>
-    <t>[ATIVO] MAT1 : Matematica 1</t>
-  </si>
-  <si>
     <t>[ATIVO] EST2 : Estruturas 2</t>
   </si>
   <si>
@@ -203,12 +146,6 @@
     <t>Gondomar</t>
   </si>
   <si>
-    <t>[ATIVO] COM1 : Construções Mecanicas 1</t>
-  </si>
-  <si>
-    <t>[ATIVO] COM2 : Construções Mecanicas 2</t>
-  </si>
-  <si>
     <t>Espinho</t>
   </si>
   <si>
@@ -227,9 +164,6 @@
     <t>[ATIVO] CIR : Circuitos</t>
   </si>
   <si>
-    <t>[ATIVO] SDE : Sistemas Digitais Eletricos</t>
-  </si>
-  <si>
     <t>[ATIVO] ELE : Eletromagnetismo</t>
   </si>
   <si>
@@ -242,57 +176,21 @@
     <t>2 - Auto-Inscrição Estudante</t>
   </si>
   <si>
-    <t>3 - Transitar Ano Letívo</t>
-  </si>
-  <si>
-    <t>4 - Recuperar Palavra-passe</t>
-  </si>
-  <si>
     <t>0 - Encerrar Sistema</t>
   </si>
   <si>
-    <t>6 - Processar Transição de Ano Letivo</t>
-  </si>
-  <si>
-    <t>7 - Consultar Relatórios Académicos</t>
-  </si>
-  <si>
-    <t>8 - Listar Alunos com Propinas em Atraso</t>
-  </si>
-  <si>
-    <t>9 - Atualizar Preçário de Cursos</t>
-  </si>
-  <si>
     <t>0 - Sair (Logout)</t>
   </si>
   <si>
     <t>3 - Listar Todos os Departamentos</t>
   </si>
   <si>
-    <t>3 - Listar Cursos por Departamento</t>
-  </si>
-  <si>
     <t>4 - Alternar Estado (Ativo/Inativo)</t>
   </si>
   <si>
-    <t>5 - Consultar Percurso Académico do Curso</t>
-  </si>
-  <si>
     <t>5 - Alternar Estado (Ativo/Inativo)</t>
   </si>
   <si>
-    <t>1 - Listar Alunos por Curso</t>
-  </si>
-  <si>
-    <t>2 - Listar Alunos por Unidade Curricular</t>
-  </si>
-  <si>
-    <t>3 - Listar Unidades Curriculares por Curso</t>
-  </si>
-  <si>
-    <t>4 - Consultar Estatísticas Globais da Faculdade</t>
-  </si>
-  <si>
     <t>1 - Adicionar Unidade Curricular</t>
   </si>
   <si>
@@ -308,36 +206,12 @@
     <t>2 - Atualizar Ficha do Docente</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">3 - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Listar Todos os Estudantes</t>
-    </r>
-  </si>
-  <si>
-    <t>5 - Visualizar Ficha Docente</t>
-  </si>
-  <si>
     <t>2 - Alterar Gestor para Inativo</t>
   </si>
   <si>
     <t>3 - Listar Todos os Gestores</t>
   </si>
   <si>
-    <t>PYE</t>
-  </si>
-  <si>
-    <t>[INATIVO] MAT : Matematica Clássica</t>
-  </si>
-  <si>
     <t>Ovar</t>
   </si>
   <si>
@@ -458,99 +332,24 @@
     <t>[ATIVO] SIE : Sistemas de Energia</t>
   </si>
   <si>
-    <t>[ATIVO] LEM - Licenciatura de Engenharia Mecanica</t>
-  </si>
-  <si>
     <t>[ATIVO] LEC - Licenciatura em Engenharia Civil</t>
   </si>
   <si>
-    <t>[ATIVO] LEE - Licenciatura de Engenharia Eletrotecnica</t>
-  </si>
-  <si>
     <t>[INATIVO] LEN - Licenciatura em Engenharia Nuclear</t>
   </si>
   <si>
-    <t>[ATIVO] LFQ - Licenciatura em Fisica e Quimica</t>
-  </si>
-  <si>
     <t>DCI : Departamento de Ciencias</t>
   </si>
   <si>
     <t>DEN : Departamento de Engenharia</t>
   </si>
   <si>
-    <t>1220492@isep.ipp.p</t>
-  </si>
-  <si>
-    <t>PTL</t>
-  </si>
-  <si>
-    <t>ptl@issmf.ipp.pt</t>
-  </si>
-  <si>
-    <t>OhVk5Rm0</t>
-  </si>
-  <si>
-    <t>qFKiVXcM</t>
-  </si>
-  <si>
-    <t>pti@issmf.ipp.pt</t>
-  </si>
-  <si>
-    <t>PTI</t>
-  </si>
-  <si>
-    <t>q3xc2B8O</t>
-  </si>
-  <si>
-    <t>pvm@issmf.ipp.pt</t>
-  </si>
-  <si>
-    <t>PVM</t>
-  </si>
-  <si>
-    <t>pig@issmf.ipp.pt</t>
-  </si>
-  <si>
-    <t>PIG</t>
-  </si>
-  <si>
-    <t>zJJdEn3X</t>
-  </si>
-  <si>
-    <t>PYS</t>
-  </si>
-  <si>
-    <t>pys@issmf.ipp.pt</t>
-  </si>
-  <si>
-    <t>7hUuoXh5</t>
-  </si>
-  <si>
-    <t>pjr@issmf.ipp.pt</t>
-  </si>
-  <si>
-    <t>gGXBFbhb</t>
-  </si>
-  <si>
-    <t>PJR</t>
-  </si>
-  <si>
     <t>[ATIVO] DES : Desenho Técnico</t>
   </si>
   <si>
-    <t>[INATIVO] REA1 : Reatores 1</t>
-  </si>
-  <si>
     <t>Paços de Brandão</t>
   </si>
   <si>
-    <t>kZUIk0qD</t>
-  </si>
-  <si>
-    <t>SALdEiWF</t>
-  </si>
-  <si>
     <t>1220492@isep.ipp.pt</t>
   </si>
   <si>
@@ -560,53 +359,394 @@
     <t>Matosinhos</t>
   </si>
   <si>
-    <t>PZW</t>
-  </si>
-  <si>
-    <t>pzw@issmf.ipp.pt</t>
-  </si>
-  <si>
-    <t>ixHY3WHq</t>
-  </si>
-  <si>
     <t>[ATIVO] PRO1 : Programação 1</t>
   </si>
   <si>
     <t>[ATIVO] PRO2 : Programação 2</t>
   </si>
   <si>
-    <t>vMGjk267</t>
-  </si>
-  <si>
-    <t>A0yAbfyw</t>
-  </si>
-  <si>
-    <t>m02pgLII</t>
-  </si>
-  <si>
-    <t>xyhneMEl</t>
-  </si>
-  <si>
-    <t>cso5rVqR</t>
-  </si>
-  <si>
-    <t>nGF2AsC9</t>
-  </si>
-  <si>
-    <t>T3WvLkPs</t>
-  </si>
-  <si>
-    <t>oGwlX18G</t>
+    <t>Campus Central</t>
+  </si>
+  <si>
+    <t>19-05-1985</t>
+  </si>
+  <si>
+    <t>27-02-1984</t>
+  </si>
+  <si>
+    <t>11-10-1962</t>
+  </si>
+  <si>
+    <t>07-03-1985</t>
+  </si>
+  <si>
+    <t>15-09-1991</t>
+  </si>
+  <si>
+    <t>21-11-1983</t>
+  </si>
+  <si>
+    <t>21-11-1988</t>
+  </si>
+  <si>
+    <t>25-07-2003</t>
+  </si>
+  <si>
+    <t>12-03-2004</t>
+  </si>
+  <si>
+    <t>05-11-2002</t>
+  </si>
+  <si>
+    <t>18-01-2005</t>
+  </si>
+  <si>
+    <t>30-09-2001</t>
+  </si>
+  <si>
+    <t>14-06-2004</t>
+  </si>
+  <si>
+    <t>22-12-2003</t>
+  </si>
+  <si>
+    <t>08-04-2002</t>
+  </si>
+  <si>
+    <t>19-05-2005</t>
+  </si>
+  <si>
+    <t>27-02-2004</t>
+  </si>
+  <si>
+    <t>11-10-2002</t>
+  </si>
+  <si>
+    <t>07-03-2005</t>
+  </si>
+  <si>
+    <t>15-09-2001</t>
+  </si>
+  <si>
+    <t>21-11-2003</t>
+  </si>
+  <si>
+    <t>========= MENU PRINCIPAL =========</t>
+  </si>
+  <si>
+    <t>3 - Recuperar Palavra-Passe</t>
+  </si>
+  <si>
+    <t>4 - Iniciar Ano Letívo</t>
+  </si>
+  <si>
+    <t>5 - Transitar Ano Letivo</t>
+  </si>
+  <si>
+    <t>1  - Gerir Departamentos</t>
+  </si>
+  <si>
+    <t>2  - Gerir Cursos</t>
+  </si>
+  <si>
+    <t>3  - Gerir Unidades Curriculares</t>
+  </si>
+  <si>
+    <t>4  - Gerir Estudantes</t>
+  </si>
+  <si>
+    <t>5  - Gerir Docentes</t>
+  </si>
+  <si>
+    <t>6  - Gerir Gestores</t>
+  </si>
+  <si>
+    <t>7  - Consultar Relatórios Académicos</t>
+  </si>
+  <si>
+    <t>============= BACKOFFICE - GESTÃO CENTRAL =============</t>
+  </si>
+  <si>
+    <t>--- MÓDULO: DEPARTAMENTOS ---</t>
+  </si>
+  <si>
+    <t>4 - Listar Cursos por Departamento</t>
+  </si>
+  <si>
+    <t>--- MÓDULO: CURSOS ---</t>
+  </si>
+  <si>
+    <t>3 - Alternar Estado (Ativo/Inativo)</t>
+  </si>
+  <si>
+    <t>4 - Consultar Percurso Académico do Curso</t>
+  </si>
+  <si>
+    <t>5 - Atualizar Preço do Curso</t>
+  </si>
+  <si>
+    <t>6 - Listar Alunos por Curso</t>
+  </si>
+  <si>
+    <t>--- MÓDULO: UNIDADES CURRICULARES ---</t>
+  </si>
+  <si>
+    <t>7 - Listar Alunos por Unidade Curricular</t>
+  </si>
+  <si>
+    <t>8 - Listar Unidades Curriculares por Curso</t>
+  </si>
+  <si>
+    <t>--- MÓDULO: ESTUDANTES ---</t>
+  </si>
+  <si>
+    <t>3 - Listar Todos os Estudantes</t>
+  </si>
+  <si>
+    <t>5 - Listar Alunos com Dívidas</t>
+  </si>
+  <si>
+    <t>--- MÓDULO: DOCENTES ---</t>
+  </si>
+  <si>
+    <t>3 - Listar Todos os Docentes</t>
+  </si>
+  <si>
+    <t>5 - Visualizar Ficha Profissional</t>
+  </si>
+  <si>
+    <t>--- MÓDULO: EQUIPA ADMINISTRATIVA ---</t>
+  </si>
+  <si>
+    <t>4 - Alterar Palavra-passe</t>
+  </si>
+  <si>
+    <t>--- MÓDULO: RELATÓRIOS ---</t>
+  </si>
+  <si>
+    <t>1 - Consultar Estatísticas</t>
+  </si>
+  <si>
+    <t>========= ÁREA DO DOCENTE =========</t>
+  </si>
+  <si>
+    <t>1 - Ver Dados Pessoais e Profissionais</t>
+  </si>
+  <si>
+    <t>2 - Atualizar Dados de Perfil</t>
+  </si>
+  <si>
+    <t>3 - Gestão de Avaliações e Pautas</t>
+  </si>
+  <si>
+    <t>4 - Consultar Estatísticas de UCs</t>
+  </si>
+  <si>
+    <t>--- GESTÃO DE AVALIAÇÕES ---</t>
+  </si>
+  <si>
+    <t>1 - Lançar Nota Individual</t>
+  </si>
+  <si>
+    <t>2 - Lançar Notas em Lote (Turma Completa)</t>
+  </si>
+  <si>
+    <t>3 - Visualizar Pauta da Disciplina</t>
+  </si>
+  <si>
+    <t>4 - Definir Momentos de Avaliação</t>
+  </si>
+  <si>
+    <t>MÓDULO DOCENTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+MÓDULO GESTOR</t>
+  </si>
+  <si>
+    <t>PBQ</t>
+  </si>
+  <si>
+    <t>pbq@issmf.ipp.pt</t>
+  </si>
+  <si>
+    <t>lMasaXqK</t>
+  </si>
+  <si>
+    <t>fGiK8ONG</t>
+  </si>
+  <si>
+    <t>pdz@issmf.ipp.pt</t>
+  </si>
+  <si>
+    <t>PDZ</t>
+  </si>
+  <si>
+    <t>pim@issmf.ipp.pt</t>
+  </si>
+  <si>
+    <t>YLTS7ASW</t>
+  </si>
+  <si>
+    <t>PIM</t>
+  </si>
+  <si>
+    <t>PYA</t>
+  </si>
+  <si>
+    <t>pya@issmf.ipp.pt</t>
+  </si>
+  <si>
+    <t>VE4UlGEH</t>
+  </si>
+  <si>
+    <t>PCU</t>
+  </si>
+  <si>
+    <t>pcu@issmf.ipp.pt</t>
+  </si>
+  <si>
+    <t>wdxI9Nan</t>
+  </si>
+  <si>
+    <t>PGN</t>
+  </si>
+  <si>
+    <t>pgn@issmf.ipp.pt</t>
+  </si>
+  <si>
+    <t>Uj7eR69F</t>
+  </si>
+  <si>
+    <t>PVU</t>
+  </si>
+  <si>
+    <t>pvu@issmf.ipp.pt</t>
+  </si>
+  <si>
+    <t>dRAsOjSf</t>
+  </si>
+  <si>
+    <t>[INATIVO] MAC : Matemática Clássica</t>
+  </si>
+  <si>
+    <t>[ATIVO] MAT1 : Matemática 1</t>
+  </si>
+  <si>
+    <t>[ATIVO] MAT2 : Matemática 2</t>
+  </si>
+  <si>
+    <t>[ATIVO] COM1 : Construções Mecânicas 1</t>
+  </si>
+  <si>
+    <t>[ATIVO] LEM - Licenciatura de Engenharia Mecânica</t>
+  </si>
+  <si>
+    <t>[ATIVO] LEE - Licenciatura de Engenharia Eletrotécnica</t>
+  </si>
+  <si>
+    <t>[ATIVO] LFQ - Licenciatura em Fisica e Química</t>
+  </si>
+  <si>
+    <t>[ATIVO] COM2 : Construções Mecânicas 2</t>
+  </si>
+  <si>
+    <t>[ATIVO] SDE : Sistemas Digitais Elétricos</t>
+  </si>
+  <si>
+    <t>[INATIVO] REA1 : Reatores</t>
+  </si>
+  <si>
+    <t>5uahyofO</t>
+  </si>
+  <si>
+    <t>8xoEWbpI</t>
+  </si>
+  <si>
+    <t>kfqNwbl1</t>
+  </si>
+  <si>
+    <t>4iGMGR5F</t>
+  </si>
+  <si>
+    <t>JQzW3OhW</t>
+  </si>
+  <si>
+    <t>NTNOvRth</t>
+  </si>
+  <si>
+    <t>nFRS0MxR</t>
+  </si>
+  <si>
+    <t>LxA1lNbP</t>
+  </si>
+  <si>
+    <t>cfmOFDHd</t>
+  </si>
+  <si>
+    <t>jnlWaqRl</t>
+  </si>
+  <si>
+    <t>========= ÁREA DO ESTUDANTE =========</t>
+  </si>
+  <si>
+    <t>1 - Ver Ficha de Estudante</t>
+  </si>
+  <si>
+    <t>2 - Atualizar Dados Pessoais</t>
+  </si>
+  <si>
+    <t>3 - Consultar Percurso Académico</t>
+  </si>
+  <si>
+    <t>4 - Gestão de Propinas e Pagamentos</t>
+  </si>
+  <si>
+    <t>5 - Desativar Conta de Utilizador</t>
+  </si>
+  <si>
+    <t>--- ATUALIZAR DADOS PESSOAIS ---</t>
+  </si>
+  <si>
+    <t>1 - Alterar Nome Completo</t>
+  </si>
+  <si>
+    <t>2 - Alterar NIF</t>
+  </si>
+  <si>
+    <t>3 - Alterar Morada</t>
+  </si>
+  <si>
+    <t>5 - Alterar Email Pessoal</t>
+  </si>
+  <si>
+    <t>--- LIQUIDAÇÃO DE VALORES ---</t>
+  </si>
+  <si>
+    <t>1 - Pagamento Integral (1100,00€)</t>
+  </si>
+  <si>
+    <t>2 - Pagar Prestação Mínima (110,00€)</t>
+  </si>
+  <si>
+    <t>3 - Introduzir Valor Personalizado</t>
+  </si>
+  <si>
+    <t>0 - Cancelar Operação</t>
+  </si>
+  <si>
+    <t>MÓDULO ESTUDANTE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="dd\-mm\-yyyy;@"/>
+    <numFmt numFmtId="165" formatCode="0000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -630,17 +770,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <strike/>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -665,6 +796,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -679,7 +816,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
@@ -694,21 +831,36 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperligação" xfId="1" builtinId="8"/>
@@ -1024,328 +1176,789 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{781029DD-AB0E-45D2-BEA2-289639D498A2}">
-  <dimension ref="B3:F64"/>
+  <dimension ref="B2:D114"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="27.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="38.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>135</v>
+      </c>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>136</v>
+      </c>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
+        <v>137</v>
+      </c>
+      <c r="C7" s="24"/>
+      <c r="D7" s="24"/>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="24"/>
+      <c r="D8" s="24"/>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B9" s="24"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B10" s="26" t="s">
+        <v>177</v>
+      </c>
+      <c r="C10" t="s">
+        <v>145</v>
+      </c>
+      <c r="D10" s="24"/>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B11" s="25"/>
+      <c r="C11" t="s">
+        <v>138</v>
+      </c>
+      <c r="D11" s="24"/>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B12" s="25"/>
+      <c r="C12" t="s">
+        <v>139</v>
+      </c>
+      <c r="D12" s="24"/>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B13" s="25"/>
+      <c r="C13" t="s">
+        <v>140</v>
+      </c>
+      <c r="D13" s="24"/>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B14" s="25"/>
+      <c r="C14" t="s">
+        <v>141</v>
+      </c>
+      <c r="D14" s="24"/>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B15" s="25"/>
+      <c r="C15" t="s">
+        <v>142</v>
+      </c>
+      <c r="D15" s="24"/>
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B16" s="25"/>
+      <c r="C16" t="s">
+        <v>143</v>
+      </c>
+      <c r="D16" s="24"/>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B17" s="25"/>
+      <c r="C17" t="s">
+        <v>144</v>
+      </c>
+      <c r="D17" s="24"/>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B18" s="25"/>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B19" s="25"/>
+      <c r="C19" s="24"/>
+      <c r="D19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B20" s="25"/>
+      <c r="C20" s="24"/>
+      <c r="D20" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B6" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B7" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B8" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C9" t="s">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B21" s="25"/>
+      <c r="C21" s="24"/>
+      <c r="D21" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C10" t="s">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B22" s="25"/>
+      <c r="C22" s="24"/>
+      <c r="D22" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B23" s="25"/>
+      <c r="C23" s="24"/>
+      <c r="D23" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B24" s="25"/>
+      <c r="C24" s="24"/>
+      <c r="D24" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="D11" t="s">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B25" s="25"/>
+      <c r="C25" s="24"/>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B26" s="25"/>
+      <c r="C26" s="24"/>
+      <c r="D26" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B27" s="25"/>
+      <c r="C27" s="24"/>
+      <c r="D27" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B28" s="25"/>
+      <c r="C28" s="24"/>
+      <c r="D28" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B29" s="25"/>
+      <c r="C29" s="24"/>
+      <c r="D29" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B30" s="25"/>
+      <c r="C30" s="24"/>
+      <c r="D30" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B31" s="25"/>
+      <c r="C31" s="24"/>
+      <c r="D31" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B32" s="25"/>
+      <c r="C32" s="24"/>
+      <c r="D32" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B33" s="25"/>
+      <c r="C33" s="24"/>
+      <c r="D33" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B34" s="25"/>
+      <c r="C34" s="24"/>
+    </row>
+    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B35" s="25"/>
+      <c r="C35" s="24"/>
+      <c r="D35" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B36" s="25"/>
+      <c r="C36" s="24"/>
+      <c r="D36" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B37" s="25"/>
+      <c r="C37" s="24"/>
+      <c r="D37" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B38" s="25"/>
+      <c r="C38" s="24"/>
+      <c r="D38" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B39" s="25"/>
+      <c r="C39" s="24"/>
+      <c r="D39" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B40" s="25"/>
+      <c r="C40" s="24"/>
+      <c r="D40" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B41" s="25"/>
+      <c r="C41" s="24"/>
+      <c r="D41" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B42" s="25"/>
+      <c r="C42" s="24"/>
+      <c r="D42" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B43" s="25"/>
+      <c r="C43" s="24"/>
+      <c r="D43" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B44" s="25"/>
+      <c r="C44" s="24"/>
+      <c r="D44" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B45" s="25"/>
+      <c r="C45" s="24"/>
+    </row>
+    <row r="46" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B46" s="25"/>
+      <c r="C46" s="24"/>
+      <c r="D46" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B47" s="25"/>
+      <c r="C47" s="24"/>
+      <c r="D47" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B48" s="25"/>
+      <c r="C48" s="24"/>
+      <c r="D48" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B49" s="25"/>
+      <c r="C49" s="24"/>
+      <c r="D49" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B50" s="25"/>
+      <c r="C50" s="24"/>
+      <c r="D50" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="51" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B51" s="25"/>
+      <c r="C51" s="24"/>
+      <c r="D51" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="52" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B52" s="25"/>
+      <c r="C52" s="24"/>
+      <c r="D52" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B53" s="25"/>
+      <c r="C53" s="24"/>
+    </row>
+    <row r="54" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B54" s="25"/>
+      <c r="C54" s="24"/>
+      <c r="D54" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="55" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B55" s="25"/>
+      <c r="C55" s="24"/>
+      <c r="D55" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="D12" t="s">
+    <row r="56" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B56" s="25"/>
+      <c r="C56" s="24"/>
+      <c r="D56" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="57" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B57" s="25"/>
+      <c r="C57" s="24"/>
+      <c r="D57" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="58" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B58" s="25"/>
+      <c r="C58" s="24"/>
+      <c r="D58" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="59" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B59" s="25"/>
+      <c r="C59" s="24"/>
+      <c r="D59" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="60" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B60" s="25"/>
+      <c r="C60" s="24"/>
+      <c r="D60" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B61" s="25"/>
+      <c r="C61" s="24"/>
+    </row>
+    <row r="62" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B62" s="25"/>
+      <c r="C62" s="24"/>
+      <c r="D62" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="63" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B63" s="25"/>
+      <c r="C63" s="24"/>
+      <c r="D63" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="D13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="D14" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="D15" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C16" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D17" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D18" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D19" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D20" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="21" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D21" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="22" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D22" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="23" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D23" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="24" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C24" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D25" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D26" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="27" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D27" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="28" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D28" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="29" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D29" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="30" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D30" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="31" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D31" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="32" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D32" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="33" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C33" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D34" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="35" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D35" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="36" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D36" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="37" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D37" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="38" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D38" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="39" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D39" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="40" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C40" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D41" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="42" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D42" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="43" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D43" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="44" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D44" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="45" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D45" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="46" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D46" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="47" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D47" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="48" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C48" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="49" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C49" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="50" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D50" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="51" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D51" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="52" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D52" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="53" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D53" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="54" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D54" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="55" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D55" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="56" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C56" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="57" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C57" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="58" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C58" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="59" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D59" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="60" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D60" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="61" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D61" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="62" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D62" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="63" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D63" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="64" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C64" t="s">
-        <v>78</v>
+    <row r="64" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B64" s="25"/>
+      <c r="C64" s="24"/>
+      <c r="D64" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="65" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B65" s="25"/>
+      <c r="C65" s="24"/>
+      <c r="D65" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="66" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B66" s="25"/>
+      <c r="C66" s="24"/>
+      <c r="D66" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="67" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B67" s="25"/>
+      <c r="C67" s="24"/>
+      <c r="D67" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B68" s="25"/>
+      <c r="C68" s="24"/>
+    </row>
+    <row r="69" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B69" s="25"/>
+      <c r="C69" s="24"/>
+      <c r="D69" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="70" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B70" s="25"/>
+      <c r="C70" s="24"/>
+      <c r="D70" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="71" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B71" s="25"/>
+      <c r="C71" s="24"/>
+      <c r="D71" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B72" s="24"/>
+      <c r="C72" s="24"/>
+      <c r="D72" s="24"/>
+    </row>
+    <row r="73" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B73" s="23" t="s">
+        <v>176</v>
+      </c>
+      <c r="C73" t="s">
+        <v>166</v>
+      </c>
+      <c r="D73" s="24"/>
+    </row>
+    <row r="74" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B74" s="23"/>
+      <c r="C74" t="s">
+        <v>167</v>
+      </c>
+      <c r="D74" s="24"/>
+    </row>
+    <row r="75" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B75" s="23"/>
+      <c r="C75" t="s">
+        <v>168</v>
+      </c>
+      <c r="D75" s="24"/>
+    </row>
+    <row r="76" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B76" s="23"/>
+      <c r="C76" t="s">
+        <v>169</v>
+      </c>
+      <c r="D76" s="24"/>
+    </row>
+    <row r="77" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B77" s="23"/>
+      <c r="C77" t="s">
+        <v>170</v>
+      </c>
+      <c r="D77" s="24"/>
+    </row>
+    <row r="78" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B78" s="23"/>
+      <c r="C78" t="s">
+        <v>50</v>
+      </c>
+      <c r="D78" s="24"/>
+    </row>
+    <row r="79" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B79" s="23"/>
+      <c r="C79" s="24"/>
+      <c r="D79" s="24"/>
+    </row>
+    <row r="80" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B80" s="23"/>
+      <c r="C80" s="24"/>
+      <c r="D80" s="28" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="81" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B81" s="23"/>
+      <c r="C81" s="24"/>
+      <c r="D81" s="28" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="82" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B82" s="23"/>
+      <c r="C82" s="24"/>
+      <c r="D82" s="28" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="83" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B83" s="23"/>
+      <c r="C83" s="24"/>
+      <c r="D83" s="28" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="84" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B84" s="23"/>
+      <c r="C84" s="24"/>
+      <c r="D84" s="28" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="85" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B85" s="23"/>
+      <c r="C85" s="24"/>
+      <c r="D85" s="28" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B86" s="23"/>
+      <c r="C86" s="24"/>
+      <c r="D86" s="29"/>
+    </row>
+    <row r="87" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B87" s="23"/>
+      <c r="C87" s="24"/>
+      <c r="D87" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="88" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B88" s="23"/>
+      <c r="C88" s="24"/>
+      <c r="D88" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="89" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B89" s="23"/>
+      <c r="C89" s="24"/>
+      <c r="D89" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="90" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B90" s="23"/>
+      <c r="C90" s="24"/>
+      <c r="D90" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="91" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B91" s="23"/>
+      <c r="C91" s="24"/>
+      <c r="D91" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="92" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B92" s="23"/>
+      <c r="C92" s="24"/>
+      <c r="D92" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B93" s="24"/>
+      <c r="C93" s="24"/>
+      <c r="D93" s="24"/>
+    </row>
+    <row r="94" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B94" s="23" t="s">
+        <v>235</v>
+      </c>
+      <c r="C94" t="s">
+        <v>219</v>
+      </c>
+      <c r="D94" s="24"/>
+    </row>
+    <row r="95" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B95" s="23"/>
+      <c r="C95" t="s">
+        <v>220</v>
+      </c>
+      <c r="D95" s="24"/>
+    </row>
+    <row r="96" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B96" s="23"/>
+      <c r="C96" t="s">
+        <v>221</v>
+      </c>
+      <c r="D96" s="24"/>
+    </row>
+    <row r="97" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B97" s="23"/>
+      <c r="C97" t="s">
+        <v>222</v>
+      </c>
+      <c r="D97" s="24"/>
+    </row>
+    <row r="98" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B98" s="23"/>
+      <c r="C98" t="s">
+        <v>223</v>
+      </c>
+      <c r="D98" s="24"/>
+    </row>
+    <row r="99" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B99" s="23"/>
+      <c r="C99" t="s">
+        <v>224</v>
+      </c>
+      <c r="D99" s="24"/>
+    </row>
+    <row r="100" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B100" s="23"/>
+      <c r="C100" t="s">
+        <v>50</v>
+      </c>
+      <c r="D100" s="24"/>
+    </row>
+    <row r="101" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B101" s="23"/>
+    </row>
+    <row r="102" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B102" s="23"/>
+      <c r="C102" s="24"/>
+      <c r="D102" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="103" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B103" s="23"/>
+      <c r="C103" s="24"/>
+      <c r="D103" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="104" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B104" s="23"/>
+      <c r="C104" s="24"/>
+      <c r="D104" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="105" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B105" s="23"/>
+      <c r="C105" s="24"/>
+      <c r="D105" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="106" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B106" s="23"/>
+      <c r="C106" s="24"/>
+      <c r="D106" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="107" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B107" s="23"/>
+      <c r="C107" s="24"/>
+      <c r="D107" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="108" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B108" s="23"/>
+      <c r="C108" s="24"/>
+      <c r="D108" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B109" s="23"/>
+      <c r="C109" s="24"/>
+    </row>
+    <row r="110" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B110" s="23"/>
+      <c r="C110" s="24"/>
+      <c r="D110" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="111" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B111" s="23"/>
+      <c r="C111" s="24"/>
+      <c r="D111" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="112" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B112" s="23"/>
+      <c r="C112" s="24"/>
+      <c r="D112" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="113" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B113" s="23"/>
+      <c r="C113" s="24"/>
+      <c r="D113" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="114" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B114" s="23"/>
+      <c r="C114" s="24"/>
+      <c r="D114" t="s">
+        <v>234</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="C102:C114"/>
+    <mergeCell ref="B93:D93"/>
+    <mergeCell ref="B94:B114"/>
+    <mergeCell ref="C2:D8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="C80:C92"/>
+    <mergeCell ref="D94:D100"/>
+    <mergeCell ref="B10:B71"/>
+    <mergeCell ref="C19:C71"/>
+    <mergeCell ref="B73:B92"/>
+    <mergeCell ref="D10:D17"/>
+    <mergeCell ref="D73:D78"/>
+    <mergeCell ref="B72:D72"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -1353,13 +1966,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F6FFC68-BC6E-45A7-9925-0DFE4309B06B}">
-  <dimension ref="A2:L33"/>
+  <dimension ref="A2:L34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.33203125" customWidth="1"/>
-    <col min="5" max="5" width="33.33203125" customWidth="1"/>
+    <col min="5" max="5" width="30.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="8" width="10" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.109375" customWidth="1"/>
@@ -1367,683 +1980,696 @@
   <sheetData>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F3" t="s">
-        <v>29</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E3" s="17" t="s">
+        <v>11</v>
       </c>
       <c r="I3" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>101</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>168</v>
+        <v>12</v>
       </c>
       <c r="G4" t="s">
-        <v>167</v>
+        <v>112</v>
       </c>
       <c r="I4" t="s">
-        <v>42</v>
+        <v>24</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>99</v>
+        <v>62</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="F5" t="s">
-        <v>169</v>
+        <v>217</v>
       </c>
       <c r="G5" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="I5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>64</v>
-      </c>
-      <c r="B9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" t="s">
-        <v>147</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="F9" t="s">
-        <v>149</v>
-      </c>
-      <c r="G9">
-        <v>142536748</v>
-      </c>
-      <c r="H9" t="s">
-        <v>36</v>
-      </c>
-      <c r="I9" t="s">
-        <v>41</v>
-      </c>
-      <c r="J9" s="7">
-        <v>31186</v>
-      </c>
-      <c r="L9" s="4" t="s">
-        <v>146</v>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" t="s">
+        <v>218</v>
+      </c>
+      <c r="G6" t="s">
+        <v>61</v>
+      </c>
+      <c r="I6" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="D10" t="s">
-        <v>152</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>151</v>
+        <v>178</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>179</v>
       </c>
       <c r="F10" t="s">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="G10">
-        <v>142536747</v>
+        <v>142536748</v>
       </c>
       <c r="H10" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="I10" t="s">
-        <v>41</v>
-      </c>
-      <c r="J10" s="7">
-        <v>30739</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="J10" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>155</v>
+        <v>183</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>154</v>
+        <v>182</v>
       </c>
       <c r="F11" t="s">
-        <v>153</v>
+        <v>181</v>
       </c>
       <c r="G11">
-        <v>142536746</v>
+        <v>142536747</v>
       </c>
       <c r="H11" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="I11" t="s">
-        <v>42</v>
-      </c>
-      <c r="J11" s="7">
-        <v>22930</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="J11" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="K11" s="4"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="D12" t="s">
-        <v>157</v>
+        <v>186</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>156</v>
+        <v>184</v>
       </c>
       <c r="F12" t="s">
-        <v>158</v>
+        <v>185</v>
       </c>
       <c r="G12">
-        <v>142536745</v>
+        <v>142536746</v>
       </c>
       <c r="H12" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="I12" t="s">
-        <v>41</v>
-      </c>
-      <c r="J12" s="7">
-        <v>31113</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="J12" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="K12" s="4"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="D13" t="s">
-        <v>159</v>
+        <v>187</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>160</v>
+        <v>188</v>
       </c>
       <c r="F13" t="s">
-        <v>161</v>
+        <v>189</v>
       </c>
       <c r="G13">
-        <v>142536744</v>
+        <v>142536745</v>
       </c>
       <c r="H13" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="I13" t="s">
-        <v>41</v>
-      </c>
-      <c r="J13" s="7">
-        <v>33496</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="J13" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="K13" s="4"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="D14" t="s">
-        <v>164</v>
+        <v>190</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>162</v>
+        <v>191</v>
       </c>
       <c r="F14" t="s">
-        <v>163</v>
+        <v>192</v>
       </c>
       <c r="G14">
+        <v>142536744</v>
+      </c>
+      <c r="H14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I14" t="s">
+        <v>24</v>
+      </c>
+      <c r="J14" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="K14" s="4"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" t="s">
+        <v>193</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F15" t="s">
+        <v>195</v>
+      </c>
+      <c r="G15">
         <v>142536743</v>
       </c>
-      <c r="H14" t="s">
-        <v>60</v>
-      </c>
-      <c r="I14" t="s">
-        <v>41</v>
-      </c>
-      <c r="J14" s="7">
-        <v>30641</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B15" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" t="s">
-        <v>171</v>
-      </c>
-      <c r="D15" t="s">
-        <v>173</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="F15" t="s">
-        <v>175</v>
-      </c>
-      <c r="G15">
+      <c r="H15" t="s">
+        <v>39</v>
+      </c>
+      <c r="I15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J15" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="K15" s="4"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" t="s">
+        <v>108</v>
+      </c>
+      <c r="D16" t="s">
+        <v>196</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="F16" t="s">
+        <v>198</v>
+      </c>
+      <c r="G16">
         <v>142536742</v>
       </c>
-      <c r="H15" t="s">
-        <v>172</v>
-      </c>
-      <c r="I15" t="s">
-        <v>41</v>
-      </c>
-      <c r="J15" s="7">
-        <v>32468</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="J16" s="7"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="J17" s="7"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="F18" s="6"/>
-      <c r="J18" s="7"/>
+      <c r="H16" t="s">
+        <v>109</v>
+      </c>
+      <c r="I16" t="s">
+        <v>24</v>
+      </c>
+      <c r="J16" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="K16" s="4"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>64</v>
-      </c>
-      <c r="B19" t="s">
-        <v>129</v>
-      </c>
-      <c r="C19" t="s">
-        <v>102</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="F19" t="s">
-        <v>178</v>
-      </c>
-      <c r="G19">
-        <v>258963147</v>
-      </c>
-      <c r="H19" t="s">
-        <v>103</v>
-      </c>
-      <c r="J19" s="7">
-        <v>37827</v>
-      </c>
-      <c r="K19" s="7"/>
-      <c r="L19" s="4" t="s">
-        <v>170</v>
-      </c>
+      <c r="F19" s="6"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" t="s">
+        <v>91</v>
+      </c>
+      <c r="C20" t="s">
         <v>64</v>
       </c>
-      <c r="B20" t="s">
-        <v>129</v>
-      </c>
-      <c r="C20" t="s">
-        <v>104</v>
-      </c>
       <c r="E20" s="4" t="s">
-        <v>131</v>
+        <v>92</v>
       </c>
       <c r="F20" t="s">
-        <v>185</v>
+        <v>209</v>
       </c>
       <c r="G20">
-        <v>241536789</v>
+        <v>258963147</v>
       </c>
       <c r="H20" t="s">
-        <v>105</v>
-      </c>
-      <c r="J20" s="7">
-        <v>38058</v>
-      </c>
-      <c r="K20" s="7"/>
+        <v>65</v>
+      </c>
+      <c r="J20" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="K20" s="4"/>
+      <c r="L20" s="4"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="B21" t="s">
-        <v>129</v>
+        <v>91</v>
       </c>
       <c r="C21" t="s">
-        <v>106</v>
+        <v>66</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>132</v>
+        <v>93</v>
       </c>
       <c r="F21" t="s">
-        <v>179</v>
+        <v>210</v>
       </c>
       <c r="G21">
-        <v>267489123</v>
+        <v>241536789</v>
       </c>
       <c r="H21" t="s">
-        <v>107</v>
-      </c>
-      <c r="J21" s="7">
-        <v>37827</v>
-      </c>
-      <c r="K21" s="7"/>
+        <v>67</v>
+      </c>
+      <c r="J21" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="K21" s="4"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>64</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="D22" s="8"/>
-      <c r="E22" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="G22" s="8">
-        <v>233654789</v>
-      </c>
-      <c r="H22" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="I22" s="8"/>
-      <c r="J22" s="10">
-        <v>37565</v>
-      </c>
-      <c r="K22" s="7"/>
+        <v>43</v>
+      </c>
+      <c r="B22" t="s">
+        <v>91</v>
+      </c>
+      <c r="C22" t="s">
+        <v>68</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="F22" t="s">
+        <v>211</v>
+      </c>
+      <c r="G22">
+        <v>267489123</v>
+      </c>
+      <c r="H22" t="s">
+        <v>69</v>
+      </c>
+      <c r="J22" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="K22" s="4"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>64</v>
-      </c>
-      <c r="B23" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="C23" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="D23" s="15"/>
-      <c r="E23" s="16" t="s">
-        <v>134</v>
-      </c>
-      <c r="F23" s="15" t="s">
-        <v>181</v>
-      </c>
-      <c r="G23" s="15">
-        <v>259874123</v>
-      </c>
-      <c r="H23" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="I23" s="15"/>
-      <c r="J23" s="17">
-        <v>38370</v>
-      </c>
-      <c r="K23" s="7"/>
+        <v>43</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D23" s="8"/>
+      <c r="E23" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="G23" s="8">
+        <v>233654789</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I23" s="8"/>
+      <c r="J23" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="K23" s="4"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>64</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="D24" s="11"/>
-      <c r="E24" s="12" t="s">
-        <v>135</v>
+        <v>43</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="D24" s="13"/>
+      <c r="E24" s="14" t="s">
+        <v>96</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="G24" s="11">
+        <v>213</v>
+      </c>
+      <c r="G24" s="13">
+        <v>259874123</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="I24" s="13"/>
+      <c r="J24" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="K24" s="4"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D25" s="10"/>
+      <c r="E25" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="G25" s="10">
         <v>210456789</v>
       </c>
-      <c r="H24" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="I24" s="11"/>
-      <c r="J24" s="14">
-        <v>37164</v>
-      </c>
-      <c r="K24" s="7"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="B25" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="C25" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="D25" s="18"/>
-      <c r="E25" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="F25" s="20" t="s">
-        <v>183</v>
-      </c>
-      <c r="G25" s="18">
+      <c r="H25" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I25" s="10"/>
+      <c r="J25" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="K25" s="4"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="D26" s="15"/>
+      <c r="E26" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="F26" s="16" t="s">
+        <v>215</v>
+      </c>
+      <c r="G26" s="15">
         <v>225147896</v>
       </c>
-      <c r="H25" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="I25" s="18"/>
-      <c r="J25" s="21">
-        <v>38152</v>
-      </c>
-      <c r="K25" s="7"/>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A26" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="B26" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="C26" s="18" t="s">
-        <v>114</v>
-      </c>
-      <c r="D26" s="18"/>
-      <c r="E26" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="F26" s="20" t="s">
-        <v>184</v>
-      </c>
-      <c r="G26" s="18">
+      <c r="H26" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I26" s="15"/>
+      <c r="J26" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="K26" s="4"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="D27" s="15"/>
+      <c r="E27" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="F27" s="16" t="s">
+        <v>216</v>
+      </c>
+      <c r="G27" s="15">
         <v>278963254</v>
       </c>
-      <c r="H26" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="I26" s="18"/>
-      <c r="J26" s="21">
-        <v>37977</v>
-      </c>
-      <c r="K26" s="7"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>62</v>
-      </c>
-      <c r="B27" t="s">
-        <v>129</v>
-      </c>
-      <c r="C27" t="s">
-        <v>115</v>
-      </c>
-      <c r="E27" s="4"/>
-      <c r="F27" s="6"/>
-      <c r="G27">
-        <v>244123654</v>
-      </c>
-      <c r="H27" t="s">
-        <v>116</v>
-      </c>
-      <c r="J27" s="7">
-        <v>37354</v>
-      </c>
-      <c r="K27" s="7"/>
+      <c r="H27" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="I27" s="15"/>
+      <c r="J27" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="K27" s="4"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>62</v>
-      </c>
       <c r="B28" t="s">
-        <v>129</v>
+        <v>91</v>
       </c>
       <c r="C28" t="s">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="E28" s="4"/>
       <c r="F28" s="6"/>
       <c r="G28">
-        <v>251478963</v>
+        <v>244123654</v>
       </c>
       <c r="H28" t="s">
-        <v>118</v>
-      </c>
-      <c r="J28" s="7">
-        <v>38491</v>
+        <v>78</v>
+      </c>
+      <c r="J28" s="18" t="s">
+        <v>127</v>
       </c>
       <c r="K28" s="7"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>62</v>
-      </c>
       <c r="B29" t="s">
-        <v>129</v>
+        <v>91</v>
       </c>
       <c r="C29" t="s">
-        <v>119</v>
+        <v>79</v>
       </c>
       <c r="E29" s="4"/>
       <c r="F29" s="6"/>
       <c r="G29">
-        <v>266321458</v>
+        <v>251478963</v>
       </c>
       <c r="H29" t="s">
-        <v>120</v>
-      </c>
-      <c r="J29" s="7">
-        <v>38044</v>
+        <v>80</v>
+      </c>
+      <c r="J29" s="18" t="s">
+        <v>128</v>
       </c>
       <c r="K29" s="7"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B30" t="s">
+        <v>91</v>
+      </c>
       <c r="C30" t="s">
-        <v>121</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="E30" s="4"/>
       <c r="F30" s="6"/>
       <c r="G30">
-        <v>239852147</v>
+        <v>266321458</v>
       </c>
       <c r="H30" t="s">
-        <v>122</v>
-      </c>
-      <c r="J30" s="7">
-        <v>37540</v>
+        <v>82</v>
+      </c>
+      <c r="J30" s="18" t="s">
+        <v>129</v>
       </c>
       <c r="K30" s="7"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B31" t="s">
+        <v>91</v>
+      </c>
       <c r="C31" t="s">
-        <v>123</v>
+        <v>83</v>
       </c>
       <c r="F31" s="6"/>
       <c r="G31">
-        <v>288741256</v>
+        <v>239852147</v>
       </c>
       <c r="H31" t="s">
-        <v>124</v>
-      </c>
-      <c r="J31" s="7">
-        <v>38418</v>
+        <v>84</v>
+      </c>
+      <c r="J31" s="18" t="s">
+        <v>130</v>
       </c>
       <c r="K31" s="7"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B32" t="s">
+        <v>91</v>
+      </c>
       <c r="C32" t="s">
-        <v>125</v>
+        <v>85</v>
       </c>
       <c r="F32" s="6"/>
       <c r="G32">
+        <v>288741256</v>
+      </c>
+      <c r="H32" t="s">
+        <v>86</v>
+      </c>
+      <c r="J32" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="K32" s="7"/>
+    </row>
+    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B33" t="s">
+        <v>91</v>
+      </c>
+      <c r="C33" t="s">
+        <v>87</v>
+      </c>
+      <c r="F33" s="6"/>
+      <c r="G33">
         <v>255698147</v>
       </c>
-      <c r="H32" t="s">
-        <v>126</v>
-      </c>
-      <c r="J32" s="7">
-        <v>37149</v>
-      </c>
-      <c r="K32" s="7"/>
-    </row>
-    <row r="33" spans="3:11" x14ac:dyDescent="0.3">
-      <c r="C33" t="s">
-        <v>127</v>
-      </c>
-      <c r="G33">
+      <c r="H33" t="s">
+        <v>88</v>
+      </c>
+      <c r="J33" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="K33" s="7"/>
+    </row>
+    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B34" t="s">
+        <v>91</v>
+      </c>
+      <c r="C34" t="s">
+        <v>89</v>
+      </c>
+      <c r="G34">
         <v>242365147</v>
       </c>
-      <c r="H33" t="s">
-        <v>128</v>
-      </c>
-      <c r="J33" s="7">
-        <v>37946</v>
-      </c>
-      <c r="K33" s="7"/>
+      <c r="H34" t="s">
+        <v>90</v>
+      </c>
+      <c r="J34" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="K34" s="7"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E3" r:id="rId1" xr:uid="{CBA7D91C-314B-4DDE-8827-1F0ECCB5DFC2}"/>
-    <hyperlink ref="E5" r:id="rId2" xr:uid="{EA843EA4-2FA7-4563-970F-ACFC5897E912}"/>
-    <hyperlink ref="E4" r:id="rId3" xr:uid="{5056049A-F4EB-4412-8F7B-590C5940D0A9}"/>
-    <hyperlink ref="E19" r:id="rId4" xr:uid="{BFCE0457-DBC1-4490-9B3F-D1A39C535521}"/>
-    <hyperlink ref="E20" r:id="rId5" xr:uid="{11D67C9B-3BD8-4708-9D7F-9DD6202E9437}"/>
-    <hyperlink ref="E21" r:id="rId6" xr:uid="{F8E9DD72-E789-488D-9161-236D34A836AC}"/>
-    <hyperlink ref="E23" r:id="rId7" xr:uid="{4DB78900-7B9B-4AF0-A2FE-D7F10CADD1B6}"/>
-    <hyperlink ref="E24" r:id="rId8" xr:uid="{50D470A7-0725-410D-8CA4-74B7FA3A0227}"/>
-    <hyperlink ref="E25" r:id="rId9" xr:uid="{E90F5A7A-F49A-435C-880C-5C1E0AE3FCA2}"/>
-    <hyperlink ref="E26" r:id="rId10" xr:uid="{6CC9203C-CB0C-4093-8D16-9E220717B7E5}"/>
-    <hyperlink ref="L9" r:id="rId11" xr:uid="{DA0E6D89-ED3F-463C-B6BD-8D9A06AF649C}"/>
-    <hyperlink ref="E9" r:id="rId12" xr:uid="{ED4D0B84-D01C-45C6-9047-8FBA6284C347}"/>
-    <hyperlink ref="E10" r:id="rId13" xr:uid="{B01B66E4-E795-46A0-B22A-095E62328844}"/>
-    <hyperlink ref="E11" r:id="rId14" xr:uid="{B182685D-A3A1-41E3-B8A8-6A550568922B}"/>
-    <hyperlink ref="E12" r:id="rId15" xr:uid="{2B9985FB-51C9-4BC0-9E56-DDEAB74C5BB6}"/>
-    <hyperlink ref="E13" r:id="rId16" xr:uid="{67362ED9-1BD8-4423-99E8-6B698F272EBF}"/>
-    <hyperlink ref="E14" r:id="rId17" xr:uid="{828414CD-D337-43A1-B8D8-FE44F51C2E4C}"/>
-    <hyperlink ref="L19" r:id="rId18" xr:uid="{77EFE0E2-B24B-49A5-A3E8-40BD34FAC10C}"/>
-    <hyperlink ref="E22" r:id="rId19" xr:uid="{0E837F76-77A4-4EA6-A02A-1967F0219F07}"/>
-    <hyperlink ref="E15" r:id="rId20" xr:uid="{9FCFB030-93FD-458E-A7B4-C7BAAE020CBE}"/>
+    <hyperlink ref="E3" r:id="rId1" xr:uid="{90136737-50D8-4624-BF9F-7BB076958402}"/>
+    <hyperlink ref="E4" r:id="rId2" xr:uid="{9B3EB29C-D4D1-4DE8-950C-D636533C4ACC}"/>
+    <hyperlink ref="E10" r:id="rId3" xr:uid="{9DB0FA28-5476-41E6-A22A-0FE2AB0E3D78}"/>
+    <hyperlink ref="J4" r:id="rId4" xr:uid="{4CEB1E42-A151-45A2-9B0C-B4A90B4D0D5F}"/>
+    <hyperlink ref="E11" r:id="rId5" xr:uid="{D665EDE0-327E-4FA6-8FFA-BBB4E2AD16BE}"/>
+    <hyperlink ref="E12" r:id="rId6" xr:uid="{60E685BC-23C7-4334-9747-091601A99EF8}"/>
+    <hyperlink ref="E13" r:id="rId7" xr:uid="{DE1AFF63-932A-44A1-8199-E076E5122B2E}"/>
+    <hyperlink ref="E14" r:id="rId8" xr:uid="{96F76F7C-CD0B-4492-9177-4EA32F927FED}"/>
+    <hyperlink ref="E15" r:id="rId9" xr:uid="{4E73F26C-D44B-43E8-BE11-AC15CAC3B84C}"/>
+    <hyperlink ref="E16" r:id="rId10" xr:uid="{3744A8CF-A7F6-48D7-AB83-F4CD2BAEE4D0}"/>
+    <hyperlink ref="E20" r:id="rId11" xr:uid="{19ED9BF7-712A-4DC1-8755-8EF0FCFF0B53}"/>
+    <hyperlink ref="E21" r:id="rId12" xr:uid="{73FA2062-31DC-43F6-87BF-4CAD4118EDC0}"/>
+    <hyperlink ref="E22" r:id="rId13" xr:uid="{C9A706E5-980E-4F35-AC05-0CAA97DB6C86}"/>
+    <hyperlink ref="E23" r:id="rId14" xr:uid="{1638B543-22A0-4123-BFF1-150CE5050E28}"/>
+    <hyperlink ref="E24" r:id="rId15" xr:uid="{D691BEA8-794F-47A6-A4F5-E83DC2372430}"/>
+    <hyperlink ref="E25" r:id="rId16" xr:uid="{10013824-D875-4ED4-BB1D-3CB1D985BC39}"/>
+    <hyperlink ref="E26" r:id="rId17" xr:uid="{0ABFA8B0-714A-4556-B801-F31F8ACC5FCF}"/>
+    <hyperlink ref="E27" r:id="rId18" xr:uid="{B7F3917F-0DF5-41C1-AA91-81F7691BF7EE}"/>
+    <hyperlink ref="E5" r:id="rId19" xr:uid="{BCAA6600-DE24-422D-96D4-0791B494C9D2}"/>
+    <hyperlink ref="E6" r:id="rId20" xr:uid="{EAF8ADB9-58E9-4CBC-AAD5-DA37B223DFD2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId21"/>
@@ -2052,7 +2678,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F3342F1-B6E7-460B-9E26-5A8DC1C1AFB6}">
-  <dimension ref="B2:N36"/>
+  <dimension ref="B2:L36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="3" width="49.5546875" bestFit="1" customWidth="1"/>
@@ -2060,146 +2686,156 @@
     <col min="5" max="5" width="4.44140625" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="29.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="F2" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="G2" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B3" s="1"/>
       <c r="D3" t="s">
-        <v>98</v>
+        <v>199</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="F3" t="s">
-        <v>97</v>
+        <v>183</v>
       </c>
       <c r="G3">
         <v>2</v>
       </c>
       <c r="I3" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="J3" t="s">
-        <v>147</v>
+        <v>178</v>
       </c>
       <c r="K3" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B4" s="1"/>
       <c r="I4" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="J4" t="s">
-        <v>152</v>
+        <v>183</v>
       </c>
       <c r="K4" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
-        <v>145</v>
+        <v>104</v>
       </c>
       <c r="I5" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="J5" t="s">
-        <v>155</v>
+        <v>186</v>
       </c>
       <c r="K5" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.3">
       <c r="C6" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="I6" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="J6" t="s">
-        <v>157</v>
+        <v>187</v>
       </c>
       <c r="K6" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.3">
       <c r="C7" t="s">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="I7" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="J7" t="s">
-        <v>159</v>
+        <v>190</v>
       </c>
       <c r="K7" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="D8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E8" s="22" t="s">
-        <v>43</v>
+        <v>200</v>
+      </c>
+      <c r="E8" s="23" t="s">
+        <v>26</v>
       </c>
       <c r="F8" t="s">
-        <v>152</v>
+        <v>183</v>
       </c>
       <c r="G8">
         <v>2</v>
       </c>
       <c r="I8" t="s">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="J8" t="s">
-        <v>164</v>
+        <v>193</v>
       </c>
       <c r="K8" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.3">
       <c r="D9" t="s">
-        <v>51</v>
-      </c>
-      <c r="E9" s="22"/>
+        <v>34</v>
+      </c>
+      <c r="E9" s="23"/>
       <c r="F9" t="s">
-        <v>147</v>
+        <v>178</v>
       </c>
       <c r="G9">
         <v>1</v>
       </c>
+      <c r="I9" t="s">
+        <v>108</v>
+      </c>
+      <c r="J9" t="s">
+        <v>196</v>
+      </c>
+      <c r="K9" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.3">
       <c r="D10" t="s">
-        <v>165</v>
-      </c>
-      <c r="E10" s="22"/>
+        <v>105</v>
+      </c>
+      <c r="E10" s="23"/>
       <c r="F10" t="s">
-        <v>147</v>
+        <v>178</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -2207,13 +2843,13 @@
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.3">
       <c r="D12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E12" s="22" t="s">
-        <v>44</v>
+        <v>201</v>
+      </c>
+      <c r="E12" s="23" t="s">
+        <v>27</v>
       </c>
       <c r="F12" t="s">
-        <v>152</v>
+        <v>183</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -2221,11 +2857,11 @@
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.3">
       <c r="D13" t="s">
-        <v>50</v>
-      </c>
-      <c r="E13" s="22"/>
+        <v>33</v>
+      </c>
+      <c r="E13" s="23"/>
       <c r="F13" t="s">
-        <v>157</v>
+        <v>187</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -2233,13 +2869,13 @@
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.3">
       <c r="D15" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="F15" t="s">
-        <v>157</v>
+        <v>187</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -2247,175 +2883,175 @@
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.3">
       <c r="C16" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="D17" t="s">
-        <v>53</v>
+        <v>203</v>
+      </c>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="D17" s="27" t="s">
+        <v>200</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="F17" t="s">
-        <v>152</v>
+        <v>183</v>
       </c>
       <c r="G17">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="D19" t="s">
-        <v>52</v>
-      </c>
-      <c r="E19" s="22" t="s">
-        <v>44</v>
+    <row r="19" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="D19" s="27" t="s">
+        <v>201</v>
+      </c>
+      <c r="E19" s="23" t="s">
+        <v>27</v>
       </c>
       <c r="F19" t="s">
-        <v>152</v>
+        <v>183</v>
       </c>
       <c r="G19">
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:12" x14ac:dyDescent="0.3">
       <c r="D20" t="s">
-        <v>58</v>
-      </c>
-      <c r="E20" s="22"/>
+        <v>202</v>
+      </c>
+      <c r="E20" s="23"/>
       <c r="F20" t="s">
-        <v>159</v>
+        <v>190</v>
       </c>
       <c r="G20">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:12" x14ac:dyDescent="0.3">
       <c r="D22" t="s">
-        <v>59</v>
+        <v>206</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="F22" t="s">
-        <v>159</v>
+        <v>190</v>
       </c>
       <c r="G22">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C23" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="D24" t="s">
-        <v>53</v>
-      </c>
-      <c r="E24" s="22" t="s">
-        <v>43</v>
+        <v>204</v>
+      </c>
+    </row>
+    <row r="24" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="D24" s="27" t="s">
+        <v>200</v>
+      </c>
+      <c r="E24" s="23" t="s">
+        <v>26</v>
       </c>
       <c r="F24" t="s">
-        <v>152</v>
+        <v>183</v>
       </c>
       <c r="G24">
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:12" x14ac:dyDescent="0.3">
       <c r="D25" t="s">
-        <v>176</v>
-      </c>
-      <c r="E25" s="22"/>
+        <v>110</v>
+      </c>
+      <c r="E25" s="23"/>
       <c r="F25" t="s">
-        <v>164</v>
+        <v>193</v>
       </c>
       <c r="G25">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:12" x14ac:dyDescent="0.3">
       <c r="D26" t="s">
-        <v>65</v>
-      </c>
-      <c r="E26" s="22"/>
+        <v>44</v>
+      </c>
+      <c r="E26" s="23"/>
       <c r="F26" t="s">
-        <v>164</v>
+        <v>193</v>
       </c>
       <c r="G26">
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:12" x14ac:dyDescent="0.3">
       <c r="D27" t="s">
-        <v>66</v>
-      </c>
-      <c r="E27" s="22"/>
+        <v>207</v>
+      </c>
+      <c r="E27" s="23"/>
       <c r="F27" t="s">
-        <v>164</v>
+        <v>193</v>
       </c>
       <c r="G27">
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:12" x14ac:dyDescent="0.3">
       <c r="D28" t="s">
-        <v>67</v>
-      </c>
-      <c r="E28" s="22"/>
+        <v>45</v>
+      </c>
+      <c r="E28" s="23"/>
       <c r="F28" t="s">
-        <v>164</v>
+        <v>193</v>
       </c>
       <c r="G28">
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:12" x14ac:dyDescent="0.3">
       <c r="D30" t="s">
-        <v>177</v>
+        <v>111</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="F30" t="s">
-        <v>164</v>
+        <v>193</v>
       </c>
       <c r="G30">
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="32" spans="3:12" x14ac:dyDescent="0.3">
       <c r="E32" s="3" t="s">
-        <v>55</v>
+        <v>36</v>
+      </c>
+      <c r="I32" t="s">
+        <v>100</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>36</v>
       </c>
       <c r="K32" t="s">
-        <v>138</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="M32" t="s">
-        <v>164</v>
-      </c>
-      <c r="N32">
+        <v>193</v>
+      </c>
+      <c r="L32">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.3">
       <c r="C33" t="s">
-        <v>142</v>
+        <v>102</v>
       </c>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.3">
       <c r="D34" t="s">
-        <v>166</v>
+        <v>208</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="F34" t="s">
-        <v>155</v>
+        <v>186</v>
       </c>
       <c r="G34">
         <v>3</v>
@@ -2423,12 +3059,12 @@
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B35" s="1" t="s">
-        <v>144</v>
+        <v>103</v>
       </c>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.3">
       <c r="C36" t="s">
-        <v>143</v>
+        <v>205</v>
       </c>
     </row>
   </sheetData>

--- a/Testes.xlsx
+++ b/Testes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\utilizador\Documents\CTESP\4semestre\LP2\ProjetoTesteLP2\TrabalhoTesteLP2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15415CE3-91AB-4976-92FD-2F2852032C0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D8DDE33-BFFC-43F1-A777-D8136E15A36A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{17050BBC-8C72-4C7C-BB9E-52ED50A4B6E1}"/>
   </bookViews>
@@ -467,9 +467,6 @@
     <t>--- MÓDULO: DEPARTAMENTOS ---</t>
   </si>
   <si>
-    <t>4 - Listar Cursos por Departamento</t>
-  </si>
-  <si>
     <t>--- MÓDULO: CURSOS ---</t>
   </si>
   <si>
@@ -758,6 +755,9 @@
   </si>
   <si>
     <t>ELIMINADO</t>
+  </si>
+  <si>
+    <t>7 - Listar Cursos por Departamento</t>
   </si>
 </sst>
 </file>
@@ -765,7 +765,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="0000"/>
+    <numFmt numFmtId="164" formatCode="0000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -1006,86 +1006,17 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -1098,7 +1029,7 @@
     <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1112,56 +1043,125 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1487,1025 +1487,1029 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B2" s="17"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="19"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="41"/>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B3" s="20"/>
-      <c r="C3" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="21"/>
+      <c r="B3" s="44"/>
+      <c r="C3" s="36" t="s">
+        <v>235</v>
+      </c>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="42"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B4" s="20"/>
+      <c r="B4" s="44"/>
       <c r="C4" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="21"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="42"/>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B5" s="20"/>
+      <c r="B5" s="44"/>
       <c r="C5" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="21"/>
+      <c r="D5" s="46"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="42"/>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B6" s="20"/>
+      <c r="B6" s="44"/>
       <c r="C6" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="21"/>
+      <c r="D6" s="46"/>
+      <c r="E6" s="46"/>
+      <c r="F6" s="42"/>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B7" s="20"/>
+      <c r="B7" s="44"/>
       <c r="C7" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="21"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="42"/>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B8" s="20"/>
+      <c r="B8" s="44"/>
       <c r="C8" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="21"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="42"/>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B9" s="20"/>
+      <c r="B9" s="44"/>
       <c r="C9" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="21"/>
+      <c r="D9" s="46"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="42"/>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B10" s="20"/>
+      <c r="B10" s="44"/>
       <c r="C10" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="21"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="42"/>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B11" s="20"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="21"/>
+      <c r="B11" s="44"/>
+      <c r="C11" s="47"/>
+      <c r="D11" s="47"/>
+      <c r="E11" s="47"/>
+      <c r="F11" s="42"/>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B12" s="20"/>
-      <c r="C12" s="5" t="s">
-        <v>235</v>
+      <c r="B12" s="44"/>
+      <c r="C12" s="49" t="s">
+        <v>234</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="E12" s="9"/>
-      <c r="F12" s="21"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="42"/>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B13" s="20"/>
-      <c r="C13" s="6"/>
+      <c r="B13" s="44"/>
+      <c r="C13" s="50"/>
       <c r="D13" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="21"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="42"/>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B14" s="20"/>
-      <c r="C14" s="6"/>
+      <c r="B14" s="44"/>
+      <c r="C14" s="50"/>
       <c r="D14" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="E14" s="9"/>
-      <c r="F14" s="21"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="42"/>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B15" s="20"/>
-      <c r="C15" s="6"/>
+      <c r="B15" s="44"/>
+      <c r="C15" s="50"/>
       <c r="D15" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="E15" s="9"/>
-      <c r="F15" s="21"/>
+      <c r="E15" s="46"/>
+      <c r="F15" s="42"/>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B16" s="20"/>
-      <c r="C16" s="6"/>
+      <c r="B16" s="44"/>
+      <c r="C16" s="50"/>
       <c r="D16" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="E16" s="9"/>
-      <c r="F16" s="21"/>
+      <c r="E16" s="46"/>
+      <c r="F16" s="42"/>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B17" s="20"/>
-      <c r="C17" s="6"/>
+      <c r="B17" s="44"/>
+      <c r="C17" s="50"/>
       <c r="D17" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="E17" s="9"/>
-      <c r="F17" s="21"/>
+      <c r="E17" s="46"/>
+      <c r="F17" s="42"/>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B18" s="20"/>
-      <c r="C18" s="6"/>
+      <c r="B18" s="44"/>
+      <c r="C18" s="50"/>
       <c r="D18" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="E18" s="9"/>
-      <c r="F18" s="21"/>
+      <c r="E18" s="46"/>
+      <c r="F18" s="42"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B19" s="20"/>
-      <c r="C19" s="6"/>
+      <c r="B19" s="44"/>
+      <c r="C19" s="50"/>
       <c r="D19" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="E19" s="9"/>
-      <c r="F19" s="21"/>
+      <c r="E19" s="46"/>
+      <c r="F19" s="42"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B20" s="20"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="21"/>
+      <c r="B20" s="44"/>
+      <c r="C20" s="50"/>
+      <c r="D20" s="37"/>
+      <c r="E20" s="38"/>
+      <c r="F20" s="42"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B21" s="20"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="9"/>
+      <c r="B21" s="44"/>
+      <c r="C21" s="50"/>
+      <c r="D21" s="46"/>
       <c r="E21" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="F21" s="21"/>
+      <c r="F21" s="42"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B22" s="20"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="9"/>
+      <c r="B22" s="44"/>
+      <c r="C22" s="50"/>
+      <c r="D22" s="46"/>
       <c r="E22" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="F22" s="21"/>
+      <c r="F22" s="42"/>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B23" s="20"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="9"/>
+      <c r="B23" s="44"/>
+      <c r="C23" s="50"/>
+      <c r="D23" s="46"/>
       <c r="E23" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="F23" s="21"/>
+      <c r="F23" s="42"/>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B24" s="20"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="9"/>
+      <c r="B24" s="44"/>
+      <c r="C24" s="50"/>
+      <c r="D24" s="46"/>
       <c r="E24" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="F24" s="21"/>
+      <c r="F24" s="42"/>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B25" s="20"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="9"/>
+      <c r="B25" s="44"/>
+      <c r="C25" s="50"/>
+      <c r="D25" s="46"/>
       <c r="E25" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F25" s="42"/>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B26" s="44"/>
+      <c r="C26" s="50"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="42"/>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B27" s="44"/>
+      <c r="C27" s="50"/>
+      <c r="D27" s="46"/>
+      <c r="E27" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="F25" s="21"/>
-    </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B26" s="20"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F26" s="21"/>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B27" s="20"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="21"/>
+      <c r="F27" s="42"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B28" s="20"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="9"/>
+      <c r="B28" s="44"/>
+      <c r="C28" s="50"/>
+      <c r="D28" s="46"/>
       <c r="E28" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F28" s="42"/>
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B29" s="44"/>
+      <c r="C29" s="50"/>
+      <c r="D29" s="46"/>
+      <c r="E29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F29" s="42"/>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B30" s="44"/>
+      <c r="C30" s="50"/>
+      <c r="D30" s="46"/>
+      <c r="E30" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="F28" s="21"/>
-    </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B29" s="20"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F29" s="21"/>
-    </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B30" s="20"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F30" s="21"/>
+      <c r="F30" s="42"/>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B31" s="20"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="9"/>
+      <c r="B31" s="44"/>
+      <c r="C31" s="50"/>
+      <c r="D31" s="46"/>
       <c r="E31" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="F31" s="21"/>
+      <c r="F31" s="42"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B32" s="20"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="9"/>
+      <c r="B32" s="44"/>
+      <c r="C32" s="50"/>
+      <c r="D32" s="46"/>
       <c r="E32" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="F32" s="21"/>
+      <c r="F32" s="42"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B33" s="20"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="9"/>
+      <c r="B33" s="44"/>
+      <c r="C33" s="50"/>
+      <c r="D33" s="46"/>
       <c r="E33" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="F33" s="21"/>
+      <c r="F33" s="42"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B34" s="20"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="9"/>
+      <c r="B34" s="44"/>
+      <c r="C34" s="50"/>
+      <c r="D34" s="46"/>
       <c r="E34" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="F34" s="21"/>
+        <v>242</v>
+      </c>
+      <c r="F34" s="42"/>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B35" s="20"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="9"/>
+      <c r="B35" s="44"/>
+      <c r="C35" s="50"/>
+      <c r="D35" s="46"/>
       <c r="E35" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F35" s="21"/>
+      <c r="F35" s="42"/>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B36" s="20"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="16"/>
-      <c r="F36" s="21"/>
+      <c r="B36" s="44"/>
+      <c r="C36" s="50"/>
+      <c r="D36" s="46"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="42"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B37" s="20"/>
-      <c r="C37" s="6"/>
-      <c r="D37" s="9"/>
+      <c r="B37" s="44"/>
+      <c r="C37" s="50"/>
+      <c r="D37" s="46"/>
       <c r="E37" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="F37" s="21"/>
+        <v>151</v>
+      </c>
+      <c r="F37" s="42"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B38" s="20"/>
-      <c r="C38" s="6"/>
-      <c r="D38" s="9"/>
+      <c r="B38" s="44"/>
+      <c r="C38" s="50"/>
+      <c r="D38" s="46"/>
       <c r="E38" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="F38" s="21"/>
+      <c r="F38" s="42"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B39" s="20"/>
-      <c r="C39" s="6"/>
-      <c r="D39" s="9"/>
+      <c r="B39" s="44"/>
+      <c r="C39" s="50"/>
+      <c r="D39" s="46"/>
       <c r="E39" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F39" s="21"/>
+      <c r="F39" s="42"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B40" s="20"/>
-      <c r="C40" s="6"/>
-      <c r="D40" s="9"/>
+      <c r="B40" s="44"/>
+      <c r="C40" s="50"/>
+      <c r="D40" s="46"/>
       <c r="E40" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F40" s="21"/>
+      <c r="F40" s="42"/>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B41" s="20"/>
-      <c r="C41" s="6"/>
-      <c r="D41" s="9"/>
+      <c r="B41" s="44"/>
+      <c r="C41" s="50"/>
+      <c r="D41" s="46"/>
       <c r="E41" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="F41" s="21"/>
+      <c r="F41" s="42"/>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B42" s="20"/>
-      <c r="C42" s="6"/>
-      <c r="D42" s="9"/>
+      <c r="B42" s="44"/>
+      <c r="C42" s="50"/>
+      <c r="D42" s="46"/>
       <c r="E42" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="F42" s="21"/>
+      <c r="F42" s="42"/>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B43" s="20"/>
-      <c r="C43" s="6"/>
-      <c r="D43" s="9"/>
+      <c r="B43" s="44"/>
+      <c r="C43" s="50"/>
+      <c r="D43" s="46"/>
       <c r="E43" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="F43" s="21"/>
+      <c r="F43" s="42"/>
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B44" s="20"/>
-      <c r="C44" s="6"/>
-      <c r="D44" s="9"/>
+      <c r="B44" s="44"/>
+      <c r="C44" s="50"/>
+      <c r="D44" s="46"/>
       <c r="E44" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="F44" s="42"/>
+    </row>
+    <row r="45" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B45" s="44"/>
+      <c r="C45" s="50"/>
+      <c r="D45" s="46"/>
+      <c r="E45" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="F44" s="21"/>
-    </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B45" s="20"/>
-      <c r="C45" s="6"/>
-      <c r="D45" s="9"/>
-      <c r="E45" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="F45" s="21"/>
+      <c r="F45" s="42"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B46" s="20"/>
-      <c r="C46" s="6"/>
-      <c r="D46" s="9"/>
+      <c r="B46" s="44"/>
+      <c r="C46" s="50"/>
+      <c r="D46" s="46"/>
       <c r="E46" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F46" s="21"/>
+      <c r="F46" s="42"/>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B47" s="20"/>
-      <c r="C47" s="6"/>
-      <c r="D47" s="9"/>
-      <c r="E47" s="16"/>
-      <c r="F47" s="21"/>
+      <c r="B47" s="44"/>
+      <c r="C47" s="50"/>
+      <c r="D47" s="46"/>
+      <c r="E47" s="7"/>
+      <c r="F47" s="42"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B48" s="20"/>
-      <c r="C48" s="6"/>
-      <c r="D48" s="9"/>
+      <c r="B48" s="44"/>
+      <c r="C48" s="50"/>
+      <c r="D48" s="46"/>
       <c r="E48" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="F48" s="21"/>
+        <v>154</v>
+      </c>
+      <c r="F48" s="42"/>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B49" s="20"/>
-      <c r="C49" s="6"/>
-      <c r="D49" s="9"/>
+      <c r="B49" s="44"/>
+      <c r="C49" s="50"/>
+      <c r="D49" s="46"/>
       <c r="E49" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F49" s="21"/>
+      <c r="F49" s="42"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B50" s="20"/>
-      <c r="C50" s="6"/>
-      <c r="D50" s="9"/>
+      <c r="B50" s="44"/>
+      <c r="C50" s="50"/>
+      <c r="D50" s="46"/>
       <c r="E50" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F50" s="21"/>
+      <c r="F50" s="42"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B51" s="20"/>
-      <c r="C51" s="6"/>
-      <c r="D51" s="9"/>
+      <c r="B51" s="44"/>
+      <c r="C51" s="50"/>
+      <c r="D51" s="46"/>
       <c r="E51" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="F51" s="21"/>
+        <v>155</v>
+      </c>
+      <c r="F51" s="42"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B52" s="20"/>
-      <c r="C52" s="6"/>
-      <c r="D52" s="9"/>
+      <c r="B52" s="44"/>
+      <c r="C52" s="50"/>
+      <c r="D52" s="46"/>
       <c r="E52" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F52" s="21"/>
+      <c r="F52" s="42"/>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B53" s="20"/>
-      <c r="C53" s="6"/>
-      <c r="D53" s="9"/>
+      <c r="B53" s="44"/>
+      <c r="C53" s="50"/>
+      <c r="D53" s="46"/>
       <c r="E53" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="F53" s="21"/>
+        <v>156</v>
+      </c>
+      <c r="F53" s="42"/>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B54" s="20"/>
-      <c r="C54" s="6"/>
-      <c r="D54" s="9"/>
+      <c r="B54" s="44"/>
+      <c r="C54" s="50"/>
+      <c r="D54" s="46"/>
       <c r="E54" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F54" s="21"/>
+      <c r="F54" s="42"/>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B55" s="20"/>
-      <c r="C55" s="6"/>
-      <c r="D55" s="9"/>
-      <c r="E55" s="16"/>
-      <c r="F55" s="21"/>
+      <c r="B55" s="44"/>
+      <c r="C55" s="50"/>
+      <c r="D55" s="46"/>
+      <c r="E55" s="7"/>
+      <c r="F55" s="42"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B56" s="20"/>
-      <c r="C56" s="6"/>
-      <c r="D56" s="9"/>
+      <c r="B56" s="44"/>
+      <c r="C56" s="50"/>
+      <c r="D56" s="46"/>
       <c r="E56" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="F56" s="21"/>
+        <v>157</v>
+      </c>
+      <c r="F56" s="42"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B57" s="20"/>
-      <c r="C57" s="6"/>
-      <c r="D57" s="9"/>
+      <c r="B57" s="44"/>
+      <c r="C57" s="50"/>
+      <c r="D57" s="46"/>
       <c r="E57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F57" s="21"/>
+      <c r="F57" s="42"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B58" s="20"/>
-      <c r="C58" s="6"/>
-      <c r="D58" s="9"/>
+      <c r="B58" s="44"/>
+      <c r="C58" s="50"/>
+      <c r="D58" s="46"/>
       <c r="E58" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F58" s="21"/>
+      <c r="F58" s="42"/>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B59" s="20"/>
-      <c r="C59" s="6"/>
-      <c r="D59" s="9"/>
+      <c r="B59" s="44"/>
+      <c r="C59" s="50"/>
+      <c r="D59" s="46"/>
       <c r="E59" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="F59" s="21"/>
+        <v>158</v>
+      </c>
+      <c r="F59" s="42"/>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B60" s="20"/>
-      <c r="C60" s="6"/>
-      <c r="D60" s="9"/>
+      <c r="B60" s="44"/>
+      <c r="C60" s="50"/>
+      <c r="D60" s="46"/>
       <c r="E60" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F60" s="21"/>
+      <c r="F60" s="42"/>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B61" s="20"/>
-      <c r="C61" s="6"/>
-      <c r="D61" s="9"/>
+      <c r="B61" s="44"/>
+      <c r="C61" s="50"/>
+      <c r="D61" s="46"/>
       <c r="E61" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="F61" s="21"/>
+        <v>159</v>
+      </c>
+      <c r="F61" s="42"/>
     </row>
     <row r="62" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B62" s="20"/>
-      <c r="C62" s="6"/>
-      <c r="D62" s="9"/>
+      <c r="B62" s="44"/>
+      <c r="C62" s="50"/>
+      <c r="D62" s="46"/>
       <c r="E62" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F62" s="21"/>
+      <c r="F62" s="42"/>
     </row>
     <row r="63" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B63" s="20"/>
-      <c r="C63" s="6"/>
-      <c r="D63" s="9"/>
-      <c r="E63" s="16"/>
-      <c r="F63" s="21"/>
+      <c r="B63" s="44"/>
+      <c r="C63" s="50"/>
+      <c r="D63" s="46"/>
+      <c r="E63" s="7"/>
+      <c r="F63" s="42"/>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B64" s="20"/>
-      <c r="C64" s="6"/>
-      <c r="D64" s="9"/>
+      <c r="B64" s="44"/>
+      <c r="C64" s="50"/>
+      <c r="D64" s="46"/>
       <c r="E64" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="F64" s="21"/>
+        <v>160</v>
+      </c>
+      <c r="F64" s="42"/>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B65" s="20"/>
-      <c r="C65" s="6"/>
-      <c r="D65" s="9"/>
+      <c r="B65" s="44"/>
+      <c r="C65" s="50"/>
+      <c r="D65" s="46"/>
       <c r="E65" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F65" s="21"/>
+      <c r="F65" s="42"/>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B66" s="20"/>
-      <c r="C66" s="6"/>
-      <c r="D66" s="9"/>
+      <c r="B66" s="44"/>
+      <c r="C66" s="50"/>
+      <c r="D66" s="46"/>
       <c r="E66" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="F66" s="21"/>
+      <c r="F66" s="42"/>
     </row>
     <row r="67" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B67" s="20"/>
-      <c r="C67" s="6"/>
-      <c r="D67" s="9"/>
+      <c r="B67" s="44"/>
+      <c r="C67" s="50"/>
+      <c r="D67" s="46"/>
       <c r="E67" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F67" s="21"/>
+      <c r="F67" s="42"/>
     </row>
     <row r="68" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B68" s="20"/>
-      <c r="C68" s="6"/>
-      <c r="D68" s="9"/>
+      <c r="B68" s="44"/>
+      <c r="C68" s="50"/>
+      <c r="D68" s="46"/>
       <c r="E68" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="F68" s="21"/>
+        <v>161</v>
+      </c>
+      <c r="F68" s="42"/>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B69" s="20"/>
-      <c r="C69" s="6"/>
-      <c r="D69" s="9"/>
+      <c r="B69" s="44"/>
+      <c r="C69" s="50"/>
+      <c r="D69" s="46"/>
       <c r="E69" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F69" s="21"/>
+      <c r="F69" s="42"/>
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B70" s="20"/>
-      <c r="C70" s="6"/>
-      <c r="D70" s="9"/>
-      <c r="E70" s="16"/>
-      <c r="F70" s="21"/>
+      <c r="B70" s="44"/>
+      <c r="C70" s="50"/>
+      <c r="D70" s="46"/>
+      <c r="E70" s="7"/>
+      <c r="F70" s="42"/>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B71" s="20"/>
-      <c r="C71" s="6"/>
-      <c r="D71" s="9"/>
+      <c r="B71" s="44"/>
+      <c r="C71" s="50"/>
+      <c r="D71" s="46"/>
       <c r="E71" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="F71" s="42"/>
+    </row>
+    <row r="72" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B72" s="44"/>
+      <c r="C72" s="50"/>
+      <c r="D72" s="46"/>
+      <c r="E72" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="F71" s="21"/>
-    </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B72" s="20"/>
-      <c r="C72" s="6"/>
-      <c r="D72" s="9"/>
-      <c r="E72" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="F72" s="21"/>
+      <c r="F72" s="42"/>
     </row>
     <row r="73" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B73" s="20"/>
-      <c r="C73" s="6"/>
-      <c r="D73" s="9"/>
+      <c r="B73" s="44"/>
+      <c r="C73" s="50"/>
+      <c r="D73" s="46"/>
       <c r="E73" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F73" s="21"/>
+      <c r="F73" s="42"/>
     </row>
     <row r="74" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B74" s="20"/>
-      <c r="C74" s="15"/>
-      <c r="D74" s="15"/>
-      <c r="E74" s="15"/>
-      <c r="F74" s="21"/>
+      <c r="B74" s="44"/>
+      <c r="C74" s="47"/>
+      <c r="D74" s="47"/>
+      <c r="E74" s="47"/>
+      <c r="F74" s="42"/>
     </row>
     <row r="75" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B75" s="20"/>
-      <c r="C75" s="7" t="s">
-        <v>175</v>
+      <c r="B75" s="44"/>
+      <c r="C75" s="48" t="s">
+        <v>174</v>
       </c>
       <c r="D75" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="E75" s="46"/>
+      <c r="F75" s="42"/>
+    </row>
+    <row r="76" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B76" s="44"/>
+      <c r="C76" s="48"/>
+      <c r="D76" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="E75" s="9"/>
-      <c r="F75" s="21"/>
-    </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B76" s="20"/>
-      <c r="C76" s="7"/>
-      <c r="D76" s="3" t="s">
+      <c r="E76" s="46"/>
+      <c r="F76" s="42"/>
+    </row>
+    <row r="77" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B77" s="44"/>
+      <c r="C77" s="48"/>
+      <c r="D77" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="E76" s="9"/>
-      <c r="F76" s="21"/>
-    </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B77" s="20"/>
-      <c r="C77" s="7"/>
-      <c r="D77" s="3" t="s">
+      <c r="E77" s="46"/>
+      <c r="F77" s="42"/>
+    </row>
+    <row r="78" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B78" s="44"/>
+      <c r="C78" s="48"/>
+      <c r="D78" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="E77" s="9"/>
-      <c r="F77" s="21"/>
-    </row>
-    <row r="78" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B78" s="20"/>
-      <c r="C78" s="7"/>
-      <c r="D78" s="3" t="s">
+      <c r="E78" s="46"/>
+      <c r="F78" s="42"/>
+    </row>
+    <row r="79" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B79" s="44"/>
+      <c r="C79" s="48"/>
+      <c r="D79" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="E78" s="9"/>
-      <c r="F78" s="21"/>
-    </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B79" s="20"/>
-      <c r="C79" s="7"/>
-      <c r="D79" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="E79" s="9"/>
-      <c r="F79" s="21"/>
+      <c r="E79" s="46"/>
+      <c r="F79" s="42"/>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B80" s="20"/>
-      <c r="C80" s="7"/>
+      <c r="B80" s="44"/>
+      <c r="C80" s="48"/>
       <c r="D80" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E80" s="9"/>
-      <c r="F80" s="21"/>
+      <c r="E80" s="46"/>
+      <c r="F80" s="42"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B81" s="20"/>
-      <c r="C81" s="7"/>
-      <c r="D81" s="9"/>
-      <c r="E81" s="9"/>
-      <c r="F81" s="21"/>
+      <c r="B81" s="44"/>
+      <c r="C81" s="48"/>
+      <c r="D81" s="46"/>
+      <c r="E81" s="46"/>
+      <c r="F81" s="42"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B82" s="20"/>
-      <c r="C82" s="7"/>
-      <c r="D82" s="9"/>
-      <c r="E82" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="F82" s="21"/>
+      <c r="B82" s="44"/>
+      <c r="C82" s="48"/>
+      <c r="D82" s="46"/>
+      <c r="E82" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="F82" s="42"/>
     </row>
     <row r="83" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B83" s="20"/>
-      <c r="C83" s="7"/>
-      <c r="D83" s="9"/>
-      <c r="E83" s="8" t="s">
+      <c r="B83" s="44"/>
+      <c r="C83" s="48"/>
+      <c r="D83" s="46"/>
+      <c r="E83" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="F83" s="42"/>
+    </row>
+    <row r="84" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B84" s="44"/>
+      <c r="C84" s="48"/>
+      <c r="D84" s="46"/>
+      <c r="E84" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="F83" s="21"/>
-    </row>
-    <row r="84" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B84" s="20"/>
-      <c r="C84" s="7"/>
-      <c r="D84" s="9"/>
-      <c r="E84" s="8" t="s">
+      <c r="F84" s="42"/>
+    </row>
+    <row r="85" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B85" s="44"/>
+      <c r="C85" s="48"/>
+      <c r="D85" s="46"/>
+      <c r="E85" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="F84" s="21"/>
-    </row>
-    <row r="85" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B85" s="20"/>
-      <c r="C85" s="7"/>
-      <c r="D85" s="9"/>
-      <c r="E85" s="8" t="s">
-        <v>226</v>
-      </c>
-      <c r="F85" s="21"/>
+      <c r="F85" s="42"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B86" s="20"/>
-      <c r="C86" s="7"/>
-      <c r="D86" s="9"/>
-      <c r="E86" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="F86" s="21"/>
+      <c r="B86" s="44"/>
+      <c r="C86" s="48"/>
+      <c r="D86" s="46"/>
+      <c r="E86" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="F86" s="42"/>
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B87" s="20"/>
-      <c r="C87" s="7"/>
-      <c r="D87" s="9"/>
-      <c r="E87" s="8" t="s">
+      <c r="B87" s="44"/>
+      <c r="C87" s="48"/>
+      <c r="D87" s="46"/>
+      <c r="E87" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F87" s="21"/>
+      <c r="F87" s="42"/>
     </row>
     <row r="88" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B88" s="20"/>
-      <c r="C88" s="7"/>
-      <c r="D88" s="9"/>
-      <c r="E88" s="16"/>
-      <c r="F88" s="21"/>
+      <c r="B88" s="44"/>
+      <c r="C88" s="48"/>
+      <c r="D88" s="46"/>
+      <c r="E88" s="7"/>
+      <c r="F88" s="42"/>
     </row>
     <row r="89" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B89" s="20"/>
-      <c r="C89" s="7"/>
-      <c r="D89" s="9"/>
+      <c r="B89" s="44"/>
+      <c r="C89" s="48"/>
+      <c r="D89" s="46"/>
       <c r="E89" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="F89" s="42"/>
+    </row>
+    <row r="90" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B90" s="44"/>
+      <c r="C90" s="48"/>
+      <c r="D90" s="46"/>
+      <c r="E90" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="F89" s="21"/>
-    </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B90" s="20"/>
-      <c r="C90" s="7"/>
-      <c r="D90" s="9"/>
-      <c r="E90" s="3" t="s">
+      <c r="F90" s="42"/>
+    </row>
+    <row r="91" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B91" s="44"/>
+      <c r="C91" s="48"/>
+      <c r="D91" s="46"/>
+      <c r="E91" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="F90" s="21"/>
-    </row>
-    <row r="91" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B91" s="20"/>
-      <c r="C91" s="7"/>
-      <c r="D91" s="9"/>
-      <c r="E91" s="3" t="s">
+      <c r="F91" s="42"/>
+    </row>
+    <row r="92" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B92" s="44"/>
+      <c r="C92" s="48"/>
+      <c r="D92" s="46"/>
+      <c r="E92" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="F91" s="21"/>
-    </row>
-    <row r="92" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B92" s="20"/>
-      <c r="C92" s="7"/>
-      <c r="D92" s="9"/>
-      <c r="E92" s="3" t="s">
+      <c r="F92" s="42"/>
+    </row>
+    <row r="93" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B93" s="44"/>
+      <c r="C93" s="48"/>
+      <c r="D93" s="46"/>
+      <c r="E93" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="F92" s="21"/>
-    </row>
-    <row r="93" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B93" s="20"/>
-      <c r="C93" s="7"/>
-      <c r="D93" s="9"/>
-      <c r="E93" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="F93" s="21"/>
+      <c r="F93" s="42"/>
     </row>
     <row r="94" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B94" s="20"/>
-      <c r="C94" s="7"/>
-      <c r="D94" s="9"/>
+      <c r="B94" s="44"/>
+      <c r="C94" s="48"/>
+      <c r="D94" s="46"/>
       <c r="E94" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F94" s="21"/>
+      <c r="F94" s="42"/>
     </row>
     <row r="95" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B95" s="20"/>
-      <c r="C95" s="15"/>
-      <c r="D95" s="15"/>
-      <c r="E95" s="15"/>
-      <c r="F95" s="21"/>
+      <c r="B95" s="44"/>
+      <c r="C95" s="47"/>
+      <c r="D95" s="47"/>
+      <c r="E95" s="47"/>
+      <c r="F95" s="42"/>
     </row>
     <row r="96" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B96" s="20"/>
-      <c r="C96" s="7" t="s">
-        <v>231</v>
+      <c r="B96" s="44"/>
+      <c r="C96" s="48" t="s">
+        <v>230</v>
       </c>
       <c r="D96" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="E96" s="46"/>
+      <c r="F96" s="42"/>
+    </row>
+    <row r="97" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B97" s="44"/>
+      <c r="C97" s="48"/>
+      <c r="D97" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="E96" s="9"/>
-      <c r="F96" s="21"/>
-    </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B97" s="20"/>
-      <c r="C97" s="7"/>
-      <c r="D97" s="3" t="s">
+      <c r="E97" s="46"/>
+      <c r="F97" s="42"/>
+    </row>
+    <row r="98" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B98" s="44"/>
+      <c r="C98" s="48"/>
+      <c r="D98" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="E97" s="9"/>
-      <c r="F97" s="21"/>
-    </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B98" s="20"/>
-      <c r="C98" s="7"/>
-      <c r="D98" s="3" t="s">
+      <c r="E98" s="46"/>
+      <c r="F98" s="42"/>
+    </row>
+    <row r="99" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B99" s="44"/>
+      <c r="C99" s="48"/>
+      <c r="D99" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="E98" s="9"/>
-      <c r="F98" s="21"/>
-    </row>
-    <row r="99" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B99" s="20"/>
-      <c r="C99" s="7"/>
-      <c r="D99" s="3" t="s">
+      <c r="E99" s="46"/>
+      <c r="F99" s="42"/>
+    </row>
+    <row r="100" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B100" s="44"/>
+      <c r="C100" s="48"/>
+      <c r="D100" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="E99" s="9"/>
-      <c r="F99" s="21"/>
-    </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B100" s="20"/>
-      <c r="C100" s="7"/>
-      <c r="D100" s="3" t="s">
+      <c r="E100" s="46"/>
+      <c r="F100" s="42"/>
+    </row>
+    <row r="101" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B101" s="44"/>
+      <c r="C101" s="48"/>
+      <c r="D101" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="E100" s="9"/>
-      <c r="F100" s="21"/>
-    </row>
-    <row r="101" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B101" s="20"/>
-      <c r="C101" s="7"/>
-      <c r="D101" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="E101" s="9"/>
-      <c r="F101" s="21"/>
+      <c r="E101" s="46"/>
+      <c r="F101" s="42"/>
     </row>
     <row r="102" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B102" s="20"/>
-      <c r="C102" s="7"/>
+      <c r="B102" s="44"/>
+      <c r="C102" s="48"/>
       <c r="D102" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E102" s="9"/>
-      <c r="F102" s="21"/>
+      <c r="E102" s="46"/>
+      <c r="F102" s="42"/>
     </row>
     <row r="103" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B103" s="20"/>
-      <c r="C103" s="7"/>
-      <c r="D103" s="9"/>
-      <c r="E103" s="9"/>
-      <c r="F103" s="21"/>
+      <c r="B103" s="44"/>
+      <c r="C103" s="48"/>
+      <c r="D103" s="46"/>
+      <c r="E103" s="46"/>
+      <c r="F103" s="42"/>
     </row>
     <row r="104" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B104" s="20"/>
-      <c r="C104" s="7"/>
-      <c r="D104" s="9"/>
+      <c r="B104" s="44"/>
+      <c r="C104" s="48"/>
+      <c r="D104" s="46"/>
       <c r="E104" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="F104" s="42"/>
+    </row>
+    <row r="105" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B105" s="44"/>
+      <c r="C105" s="48"/>
+      <c r="D105" s="46"/>
+      <c r="E105" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="F104" s="21"/>
-    </row>
-    <row r="105" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B105" s="20"/>
-      <c r="C105" s="7"/>
-      <c r="D105" s="9"/>
-      <c r="E105" s="3" t="s">
+      <c r="F105" s="42"/>
+    </row>
+    <row r="106" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B106" s="44"/>
+      <c r="C106" s="48"/>
+      <c r="D106" s="46"/>
+      <c r="E106" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="F105" s="21"/>
-    </row>
-    <row r="106" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B106" s="20"/>
-      <c r="C106" s="7"/>
-      <c r="D106" s="9"/>
-      <c r="E106" s="3" t="s">
+      <c r="F106" s="42"/>
+    </row>
+    <row r="107" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B107" s="44"/>
+      <c r="C107" s="48"/>
+      <c r="D107" s="46"/>
+      <c r="E107" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="F106" s="21"/>
-    </row>
-    <row r="107" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B107" s="20"/>
-      <c r="C107" s="7"/>
-      <c r="D107" s="9"/>
-      <c r="E107" s="3" t="s">
+      <c r="F107" s="42"/>
+    </row>
+    <row r="108" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B108" s="44"/>
+      <c r="C108" s="48"/>
+      <c r="D108" s="46"/>
+      <c r="E108" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="F108" s="42"/>
+    </row>
+    <row r="109" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B109" s="44"/>
+      <c r="C109" s="48"/>
+      <c r="D109" s="46"/>
+      <c r="E109" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="F107" s="21"/>
-    </row>
-    <row r="108" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B108" s="20"/>
-      <c r="C108" s="7"/>
-      <c r="D108" s="9"/>
-      <c r="E108" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="F108" s="21"/>
-    </row>
-    <row r="109" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B109" s="20"/>
-      <c r="C109" s="7"/>
-      <c r="D109" s="9"/>
-      <c r="E109" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="F109" s="21"/>
+      <c r="F109" s="42"/>
     </row>
     <row r="110" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B110" s="20"/>
-      <c r="C110" s="7"/>
-      <c r="D110" s="9"/>
+      <c r="B110" s="44"/>
+      <c r="C110" s="48"/>
+      <c r="D110" s="46"/>
       <c r="E110" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F110" s="21"/>
+      <c r="F110" s="42"/>
     </row>
     <row r="111" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B111" s="20"/>
-      <c r="C111" s="7"/>
-      <c r="D111" s="9"/>
-      <c r="E111" s="16"/>
-      <c r="F111" s="21"/>
+      <c r="B111" s="44"/>
+      <c r="C111" s="48"/>
+      <c r="D111" s="46"/>
+      <c r="E111" s="7"/>
+      <c r="F111" s="42"/>
     </row>
     <row r="112" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B112" s="20"/>
-      <c r="C112" s="7"/>
-      <c r="D112" s="9"/>
+      <c r="B112" s="44"/>
+      <c r="C112" s="48"/>
+      <c r="D112" s="46"/>
       <c r="E112" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="F112" s="42"/>
+    </row>
+    <row r="113" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B113" s="44"/>
+      <c r="C113" s="48"/>
+      <c r="D113" s="46"/>
+      <c r="E113" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="F113" s="42"/>
+    </row>
+    <row r="114" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B114" s="44"/>
+      <c r="C114" s="48"/>
+      <c r="D114" s="46"/>
+      <c r="E114" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="F114" s="42"/>
+    </row>
+    <row r="115" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B115" s="44"/>
+      <c r="C115" s="48"/>
+      <c r="D115" s="46"/>
+      <c r="E115" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="F112" s="21"/>
-    </row>
-    <row r="113" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B113" s="20"/>
-      <c r="C113" s="7"/>
-      <c r="D113" s="9"/>
-      <c r="E113" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="F113" s="21"/>
-    </row>
-    <row r="114" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B114" s="20"/>
-      <c r="C114" s="7"/>
-      <c r="D114" s="9"/>
-      <c r="E114" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="F114" s="21"/>
-    </row>
-    <row r="115" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B115" s="20"/>
-      <c r="C115" s="7"/>
-      <c r="D115" s="9"/>
-      <c r="E115" s="3" t="s">
+      <c r="F115" s="42"/>
+    </row>
+    <row r="116" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B116" s="44"/>
+      <c r="C116" s="48"/>
+      <c r="D116" s="46"/>
+      <c r="E116" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="F115" s="21"/>
-    </row>
-    <row r="116" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B116" s="20"/>
-      <c r="C116" s="7"/>
-      <c r="D116" s="9"/>
-      <c r="E116" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="F116" s="21"/>
+      <c r="F116" s="42"/>
     </row>
     <row r="117" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B117" s="22"/>
-      <c r="C117" s="23"/>
-      <c r="D117" s="23"/>
-      <c r="E117" s="23"/>
-      <c r="F117" s="24"/>
+      <c r="B117" s="45"/>
+      <c r="C117" s="8"/>
+      <c r="D117" s="8"/>
+      <c r="E117" s="8"/>
+      <c r="F117" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="E12:E19"/>
+    <mergeCell ref="E75:E80"/>
+    <mergeCell ref="C74:E74"/>
+    <mergeCell ref="D103:E103"/>
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="D20:E20"/>
     <mergeCell ref="B2:F2"/>
@@ -2522,10 +2526,6 @@
     <mergeCell ref="C12:C73"/>
     <mergeCell ref="D21:D73"/>
     <mergeCell ref="C75:C94"/>
-    <mergeCell ref="E12:E19"/>
-    <mergeCell ref="E75:E80"/>
-    <mergeCell ref="C74:E74"/>
-    <mergeCell ref="D103:E103"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2548,46 +2548,46 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B2" s="17"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
-      <c r="L2" s="18"/>
-      <c r="M2" s="18"/>
-      <c r="N2" s="18"/>
-      <c r="O2" s="19"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="40"/>
+      <c r="M2" s="40"/>
+      <c r="N2" s="40"/>
+      <c r="O2" s="41"/>
     </row>
     <row r="3" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B3" s="20"/>
-      <c r="C3" s="66" t="s">
-        <v>237</v>
-      </c>
-      <c r="D3" s="66"/>
-      <c r="E3" s="66"/>
-      <c r="F3" s="66"/>
-      <c r="G3" s="66"/>
-      <c r="H3" s="66"/>
-      <c r="I3" s="66"/>
-      <c r="J3" s="66"/>
-      <c r="K3" s="66"/>
-      <c r="L3" s="66"/>
-      <c r="M3" s="66"/>
-      <c r="N3" s="66"/>
-      <c r="O3" s="21"/>
+      <c r="B3" s="44"/>
+      <c r="C3" s="65" t="s">
+        <v>236</v>
+      </c>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="65"/>
+      <c r="K3" s="65"/>
+      <c r="L3" s="65"/>
+      <c r="M3" s="65"/>
+      <c r="N3" s="65"/>
+      <c r="O3" s="42"/>
     </row>
     <row r="4" spans="2:15" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="20"/>
+      <c r="B4" s="44"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="25" t="s">
+      <c r="F4" s="6"/>
+      <c r="G4" s="9" t="s">
         <v>11</v>
       </c>
       <c r="H4" s="3"/>
@@ -2599,130 +2599,130 @@
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
-      <c r="O4" s="21"/>
+      <c r="O4" s="42"/>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B5" s="20"/>
-      <c r="C5" s="9"/>
+      <c r="B5" s="44"/>
+      <c r="C5" s="46"/>
       <c r="D5" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="70"/>
-      <c r="G5" s="26" t="s">
+      <c r="F5" s="66"/>
+      <c r="G5" s="10" t="s">
         <v>11</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="68" t="s">
+      <c r="I5" s="53" t="s">
         <v>111</v>
       </c>
-      <c r="J5" s="69"/>
+      <c r="J5" s="54"/>
       <c r="K5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="L5" s="27" t="s">
+      <c r="L5" s="56" t="s">
         <v>106</v>
       </c>
-      <c r="M5" s="54"/>
-      <c r="N5" s="28"/>
-      <c r="O5" s="21"/>
+      <c r="M5" s="57"/>
+      <c r="N5" s="58"/>
+      <c r="O5" s="42"/>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B6" s="20"/>
-      <c r="C6" s="9"/>
+      <c r="B6" s="44"/>
+      <c r="C6" s="46"/>
       <c r="D6" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="F6" s="70"/>
-      <c r="G6" s="26" t="s">
+      <c r="F6" s="66"/>
+      <c r="G6" s="10" t="s">
         <v>62</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="I6" s="68" t="s">
+        <v>214</v>
+      </c>
+      <c r="I6" s="53" t="s">
         <v>105</v>
       </c>
-      <c r="J6" s="69"/>
+      <c r="J6" s="54"/>
       <c r="K6" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="L6" s="29"/>
-      <c r="M6" s="55"/>
-      <c r="N6" s="30"/>
-      <c r="O6" s="21"/>
+      <c r="L6" s="59"/>
+      <c r="M6" s="60"/>
+      <c r="N6" s="61"/>
+      <c r="O6" s="42"/>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B7" s="20"/>
-      <c r="C7" s="9"/>
+      <c r="B7" s="44"/>
+      <c r="C7" s="46"/>
       <c r="D7" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F7" s="70"/>
-      <c r="G7" s="26" t="s">
+      <c r="F7" s="66"/>
+      <c r="G7" s="10" t="s">
         <v>45</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="I7" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="I7" s="53" t="s">
         <v>60</v>
       </c>
-      <c r="J7" s="69"/>
+      <c r="J7" s="54"/>
       <c r="K7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="L7" s="31"/>
-      <c r="M7" s="56"/>
-      <c r="N7" s="32"/>
-      <c r="O7" s="21"/>
+      <c r="L7" s="62"/>
+      <c r="M7" s="63"/>
+      <c r="N7" s="64"/>
+      <c r="O7" s="42"/>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B8" s="20"/>
-      <c r="C8" s="67"/>
-      <c r="D8" s="67"/>
-      <c r="E8" s="67"/>
-      <c r="F8" s="67"/>
-      <c r="G8" s="67"/>
-      <c r="H8" s="67"/>
-      <c r="I8" s="67"/>
-      <c r="J8" s="67"/>
-      <c r="K8" s="67"/>
-      <c r="L8" s="67"/>
-      <c r="M8" s="67"/>
-      <c r="N8" s="67"/>
-      <c r="O8" s="21"/>
+      <c r="B8" s="44"/>
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="51"/>
+      <c r="F8" s="51"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="51"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="51"/>
+      <c r="K8" s="51"/>
+      <c r="L8" s="51"/>
+      <c r="M8" s="51"/>
+      <c r="N8" s="51"/>
+      <c r="O8" s="42"/>
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B9" s="20"/>
-      <c r="C9" s="66" t="s">
-        <v>238</v>
-      </c>
-      <c r="D9" s="66"/>
-      <c r="E9" s="66"/>
-      <c r="F9" s="66"/>
-      <c r="G9" s="66"/>
-      <c r="H9" s="66"/>
-      <c r="I9" s="66"/>
-      <c r="J9" s="66"/>
-      <c r="K9" s="66"/>
-      <c r="L9" s="66"/>
-      <c r="M9" s="66"/>
-      <c r="N9" s="66"/>
-      <c r="O9" s="21"/>
+      <c r="B9" s="44"/>
+      <c r="C9" s="65" t="s">
+        <v>237</v>
+      </c>
+      <c r="D9" s="65"/>
+      <c r="E9" s="65"/>
+      <c r="F9" s="65"/>
+      <c r="G9" s="65"/>
+      <c r="H9" s="65"/>
+      <c r="I9" s="65"/>
+      <c r="J9" s="65"/>
+      <c r="K9" s="65"/>
+      <c r="L9" s="65"/>
+      <c r="M9" s="65"/>
+      <c r="N9" s="65"/>
+      <c r="O9" s="42"/>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B10" s="20"/>
+      <c r="B10" s="44"/>
       <c r="C10" s="3" t="s">
         <v>42</v>
       </c>
@@ -2732,14 +2732,14 @@
       <c r="E10" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="G10" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="G10" s="33" t="s">
+      <c r="H10" s="3" t="s">
         <v>177</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>178</v>
       </c>
       <c r="I10" s="3">
         <v>142536748</v>
@@ -2750,17 +2750,17 @@
       <c r="K10" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="L10" s="34" t="s">
+      <c r="L10" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="M10" s="35" t="s">
+      <c r="M10" s="55" t="s">
         <v>106</v>
       </c>
-      <c r="N10" s="35"/>
-      <c r="O10" s="21"/>
+      <c r="N10" s="55"/>
+      <c r="O10" s="42"/>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B11" s="20"/>
+      <c r="B11" s="44"/>
       <c r="C11" s="3" t="s">
         <v>42</v>
       </c>
@@ -2770,14 +2770,14 @@
       <c r="E11" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F11" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="G11" s="26" t="s">
+      <c r="F11" s="6" t="s">
         <v>180</v>
       </c>
+      <c r="G11" s="10" t="s">
+        <v>179</v>
+      </c>
       <c r="H11" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I11" s="3">
         <v>142536747</v>
@@ -2788,15 +2788,15 @@
       <c r="K11" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="L11" s="34" t="s">
+      <c r="L11" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="M11" s="35"/>
-      <c r="N11" s="35"/>
-      <c r="O11" s="21"/>
+      <c r="M11" s="55"/>
+      <c r="N11" s="55"/>
+      <c r="O11" s="42"/>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B12" s="20"/>
+      <c r="B12" s="44"/>
       <c r="C12" s="3" t="s">
         <v>42</v>
       </c>
@@ -2806,14 +2806,14 @@
       <c r="E12" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F12" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="G12" s="26" t="s">
+      <c r="F12" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="H12" s="3" t="s">
         <v>182</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>183</v>
       </c>
       <c r="I12" s="3">
         <v>142536746</v>
@@ -2824,15 +2824,15 @@
       <c r="K12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="L12" s="34" t="s">
+      <c r="L12" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="M12" s="35"/>
-      <c r="N12" s="35"/>
-      <c r="O12" s="21"/>
+      <c r="M12" s="55"/>
+      <c r="N12" s="55"/>
+      <c r="O12" s="42"/>
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B13" s="20"/>
+      <c r="B13" s="44"/>
       <c r="C13" s="3" t="s">
         <v>42</v>
       </c>
@@ -2842,14 +2842,14 @@
       <c r="E13" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F13" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="G13" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="G13" s="26" t="s">
+      <c r="H13" s="3" t="s">
         <v>186</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>187</v>
       </c>
       <c r="I13" s="3">
         <v>142536745</v>
@@ -2860,15 +2860,15 @@
       <c r="K13" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="L13" s="34" t="s">
+      <c r="L13" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="M13" s="35"/>
-      <c r="N13" s="35"/>
-      <c r="O13" s="21"/>
+      <c r="M13" s="55"/>
+      <c r="N13" s="55"/>
+      <c r="O13" s="42"/>
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B14" s="20"/>
+      <c r="B14" s="44"/>
       <c r="C14" s="3" t="s">
         <v>40</v>
       </c>
@@ -2878,14 +2878,14 @@
       <c r="E14" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F14" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="G14" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="G14" s="26" t="s">
+      <c r="H14" s="3" t="s">
         <v>189</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>190</v>
       </c>
       <c r="I14" s="3">
         <v>142536744</v>
@@ -2896,15 +2896,15 @@
       <c r="K14" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="L14" s="34" t="s">
+      <c r="L14" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="M14" s="35"/>
-      <c r="N14" s="35"/>
-      <c r="O14" s="21"/>
+      <c r="M14" s="55"/>
+      <c r="N14" s="55"/>
+      <c r="O14" s="42"/>
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B15" s="20"/>
+      <c r="B15" s="44"/>
       <c r="C15" s="3" t="s">
         <v>41</v>
       </c>
@@ -2914,14 +2914,14 @@
       <c r="E15" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="F15" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="G15" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="G15" s="26" t="s">
+      <c r="H15" s="3" t="s">
         <v>192</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>193</v>
       </c>
       <c r="I15" s="3">
         <v>142536743</v>
@@ -2932,15 +2932,15 @@
       <c r="K15" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="L15" s="34" t="s">
+      <c r="L15" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="M15" s="35"/>
-      <c r="N15" s="35"/>
-      <c r="O15" s="21"/>
+      <c r="M15" s="55"/>
+      <c r="N15" s="55"/>
+      <c r="O15" s="42"/>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B16" s="20"/>
+      <c r="B16" s="44"/>
       <c r="C16" s="3"/>
       <c r="D16" s="3" t="s">
         <v>16</v>
@@ -2948,14 +2948,14 @@
       <c r="E16" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="F16" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="G16" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="G16" s="26" t="s">
+      <c r="H16" s="3" t="s">
         <v>195</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>196</v>
       </c>
       <c r="I16" s="3">
         <v>142536742</v>
@@ -2966,49 +2966,49 @@
       <c r="K16" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="L16" s="34" t="s">
+      <c r="L16" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="M16" s="35"/>
-      <c r="N16" s="35"/>
-      <c r="O16" s="21"/>
+      <c r="M16" s="55"/>
+      <c r="N16" s="55"/>
+      <c r="O16" s="42"/>
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B17" s="20"/>
-      <c r="C17" s="67"/>
-      <c r="D17" s="67"/>
-      <c r="E17" s="67"/>
-      <c r="F17" s="67"/>
-      <c r="G17" s="67"/>
-      <c r="H17" s="67"/>
-      <c r="I17" s="67"/>
-      <c r="J17" s="67"/>
-      <c r="K17" s="67"/>
-      <c r="L17" s="67"/>
-      <c r="M17" s="67"/>
-      <c r="N17" s="67"/>
-      <c r="O17" s="21"/>
+      <c r="B17" s="44"/>
+      <c r="C17" s="51"/>
+      <c r="D17" s="51"/>
+      <c r="E17" s="51"/>
+      <c r="F17" s="51"/>
+      <c r="G17" s="51"/>
+      <c r="H17" s="51"/>
+      <c r="I17" s="51"/>
+      <c r="J17" s="51"/>
+      <c r="K17" s="51"/>
+      <c r="L17" s="51"/>
+      <c r="M17" s="51"/>
+      <c r="N17" s="51"/>
+      <c r="O17" s="42"/>
     </row>
     <row r="18" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B18" s="20"/>
-      <c r="C18" s="66" t="s">
-        <v>239</v>
-      </c>
-      <c r="D18" s="66"/>
-      <c r="E18" s="66"/>
-      <c r="F18" s="66"/>
-      <c r="G18" s="66"/>
-      <c r="H18" s="66"/>
-      <c r="I18" s="66"/>
-      <c r="J18" s="66"/>
-      <c r="K18" s="66"/>
-      <c r="L18" s="66"/>
-      <c r="M18" s="66"/>
-      <c r="N18" s="66"/>
-      <c r="O18" s="21"/>
+      <c r="B18" s="44"/>
+      <c r="C18" s="65" t="s">
+        <v>238</v>
+      </c>
+      <c r="D18" s="65"/>
+      <c r="E18" s="65"/>
+      <c r="F18" s="65"/>
+      <c r="G18" s="65"/>
+      <c r="H18" s="65"/>
+      <c r="I18" s="65"/>
+      <c r="J18" s="65"/>
+      <c r="K18" s="65"/>
+      <c r="L18" s="65"/>
+      <c r="M18" s="65"/>
+      <c r="N18" s="65"/>
+      <c r="O18" s="42"/>
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B19" s="20"/>
+      <c r="B19" s="44"/>
       <c r="C19" s="3" t="s">
         <v>42</v>
       </c>
@@ -3018,14 +3018,14 @@
       <c r="E19" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F19" s="8">
+      <c r="F19" s="6">
         <v>20260001</v>
       </c>
-      <c r="G19" s="26" t="s">
+      <c r="G19" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I19" s="3">
         <v>258963147</v>
@@ -3036,17 +3036,17 @@
       <c r="K19" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="L19" s="34" t="s">
+      <c r="L19" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="M19" s="35" t="s">
+      <c r="M19" s="55" t="s">
         <v>106</v>
       </c>
-      <c r="N19" s="35"/>
-      <c r="O19" s="21"/>
+      <c r="N19" s="55"/>
+      <c r="O19" s="42"/>
     </row>
     <row r="20" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B20" s="20"/>
+      <c r="B20" s="44"/>
       <c r="C20" s="3" t="s">
         <v>42</v>
       </c>
@@ -3056,14 +3056,14 @@
       <c r="E20" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="F20" s="8">
+      <c r="F20" s="6">
         <v>20260002</v>
       </c>
-      <c r="G20" s="26" t="s">
+      <c r="G20" s="10" t="s">
         <v>92</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I20" s="3">
         <v>241536789</v>
@@ -3074,15 +3074,15 @@
       <c r="K20" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="L20" s="34" t="s">
+      <c r="L20" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="M20" s="35"/>
-      <c r="N20" s="35"/>
-      <c r="O20" s="21"/>
+      <c r="M20" s="55"/>
+      <c r="N20" s="55"/>
+      <c r="O20" s="42"/>
     </row>
     <row r="21" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B21" s="20"/>
+      <c r="B21" s="44"/>
       <c r="C21" s="3" t="s">
         <v>42</v>
       </c>
@@ -3092,14 +3092,14 @@
       <c r="E21" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F21" s="8">
+      <c r="F21" s="6">
         <v>20260003</v>
       </c>
-      <c r="G21" s="26" t="s">
+      <c r="G21" s="10" t="s">
         <v>93</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I21" s="3">
         <v>267489123</v>
@@ -3110,195 +3110,195 @@
       <c r="K21" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="L21" s="34" t="s">
+      <c r="L21" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="M21" s="35"/>
-      <c r="N21" s="35"/>
-      <c r="O21" s="21"/>
+      <c r="M21" s="55"/>
+      <c r="N21" s="55"/>
+      <c r="O21" s="42"/>
     </row>
     <row r="22" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B22" s="20"/>
+      <c r="B22" s="44"/>
       <c r="C22" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D22" s="36" t="s">
+      <c r="D22" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="E22" s="36" t="s">
+      <c r="E22" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="F22" s="50">
+      <c r="F22" s="27">
         <v>20260004</v>
       </c>
-      <c r="G22" s="37" t="s">
+      <c r="G22" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="H22" s="36" t="s">
-        <v>210</v>
-      </c>
-      <c r="I22" s="36">
+      <c r="H22" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="I22" s="13">
         <v>233654789</v>
       </c>
-      <c r="J22" s="36" t="s">
+      <c r="J22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="K22" s="36" t="s">
+      <c r="K22" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="L22" s="38" t="s">
+      <c r="L22" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="M22" s="35"/>
-      <c r="N22" s="35"/>
-      <c r="O22" s="21"/>
+      <c r="M22" s="55"/>
+      <c r="N22" s="55"/>
+      <c r="O22" s="42"/>
     </row>
     <row r="23" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B23" s="20"/>
+      <c r="B23" s="44"/>
       <c r="C23" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D23" s="39" t="s">
+      <c r="D23" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="E23" s="39" t="s">
+      <c r="E23" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="F23" s="51">
+      <c r="F23" s="28">
         <v>20260005</v>
       </c>
-      <c r="G23" s="40" t="s">
+      <c r="G23" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="H23" s="39" t="s">
-        <v>211</v>
-      </c>
-      <c r="I23" s="39">
+      <c r="H23" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="I23" s="16">
         <v>259874123</v>
       </c>
-      <c r="J23" s="39" t="s">
+      <c r="J23" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="K23" s="39" t="s">
+      <c r="K23" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="L23" s="41" t="s">
+      <c r="L23" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="M23" s="35"/>
-      <c r="N23" s="35"/>
-      <c r="O23" s="21"/>
+      <c r="M23" s="55"/>
+      <c r="N23" s="55"/>
+      <c r="O23" s="42"/>
     </row>
     <row r="24" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B24" s="20"/>
+      <c r="B24" s="44"/>
       <c r="C24" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D24" s="42" t="s">
+      <c r="D24" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="E24" s="42" t="s">
+      <c r="E24" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="F24" s="52">
+      <c r="F24" s="29">
         <v>20260006</v>
       </c>
-      <c r="G24" s="43" t="s">
+      <c r="G24" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="H24" s="44" t="s">
+      <c r="H24" s="21" t="s">
+        <v>211</v>
+      </c>
+      <c r="I24" s="19">
+        <v>210456789</v>
+      </c>
+      <c r="J24" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="K24" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="L24" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="M24" s="55"/>
+      <c r="N24" s="55"/>
+      <c r="O24" s="42"/>
+    </row>
+    <row r="25" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B25" s="44"/>
+      <c r="C25" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="D25" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="E25" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="F25" s="30">
+        <v>20260007</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H25" s="24" t="s">
         <v>212</v>
       </c>
-      <c r="I24" s="42">
-        <v>210456789</v>
-      </c>
-      <c r="J24" s="42" t="s">
-        <v>22</v>
-      </c>
-      <c r="K24" s="42" t="s">
-        <v>23</v>
-      </c>
-      <c r="L24" s="45" t="s">
-        <v>123</v>
-      </c>
-      <c r="M24" s="35"/>
-      <c r="N24" s="35"/>
-      <c r="O24" s="21"/>
-    </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B25" s="20"/>
-      <c r="C25" s="46" t="s">
+      <c r="I25" s="23">
+        <v>225147896</v>
+      </c>
+      <c r="J25" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="K25" s="23" t="s">
+        <v>241</v>
+      </c>
+      <c r="L25" s="25" t="s">
+        <v>124</v>
+      </c>
+      <c r="M25" s="55"/>
+      <c r="N25" s="55"/>
+      <c r="O25" s="42"/>
+    </row>
+    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B26" s="44"/>
+      <c r="C26" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="D25" s="46" t="s">
+      <c r="D26" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="E25" s="46" t="s">
-        <v>73</v>
-      </c>
-      <c r="F25" s="53">
-        <v>20260007</v>
-      </c>
-      <c r="G25" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="H25" s="47" t="s">
+      <c r="E26" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="F26" s="30">
+        <v>20260008</v>
+      </c>
+      <c r="G26" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="H26" s="24" t="s">
         <v>213</v>
       </c>
-      <c r="I25" s="46">
-        <v>225147896</v>
-      </c>
-      <c r="J25" s="46" t="s">
-        <v>74</v>
-      </c>
-      <c r="K25" s="46" t="s">
-        <v>242</v>
-      </c>
-      <c r="L25" s="48" t="s">
-        <v>124</v>
-      </c>
-      <c r="M25" s="35"/>
-      <c r="N25" s="35"/>
-      <c r="O25" s="21"/>
-    </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B26" s="20"/>
-      <c r="C26" s="46" t="s">
-        <v>40</v>
-      </c>
-      <c r="D26" s="46" t="s">
-        <v>90</v>
-      </c>
-      <c r="E26" s="46" t="s">
-        <v>75</v>
-      </c>
-      <c r="F26" s="53">
-        <v>20260008</v>
-      </c>
-      <c r="G26" s="26" t="s">
-        <v>98</v>
-      </c>
-      <c r="H26" s="47" t="s">
-        <v>214</v>
-      </c>
-      <c r="I26" s="46">
+      <c r="I26" s="23">
         <v>278963254</v>
       </c>
-      <c r="J26" s="46" t="s">
+      <c r="J26" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="K26" s="46" t="s">
-        <v>242</v>
-      </c>
-      <c r="L26" s="48" t="s">
+      <c r="K26" s="23" t="s">
+        <v>241</v>
+      </c>
+      <c r="L26" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="M26" s="35"/>
-      <c r="N26" s="35"/>
-      <c r="O26" s="21"/>
+      <c r="M26" s="55"/>
+      <c r="N26" s="55"/>
+      <c r="O26" s="42"/>
     </row>
     <row r="27" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B27" s="20"/>
+      <c r="B27" s="44"/>
       <c r="C27" s="3"/>
       <c r="D27" s="3" t="s">
         <v>90</v>
@@ -3306,9 +3306,9 @@
       <c r="E27" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="F27" s="8"/>
-      <c r="G27" s="26"/>
-      <c r="H27" s="49"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="10"/>
+      <c r="H27" s="26"/>
       <c r="I27" s="3">
         <v>244123654</v>
       </c>
@@ -3316,15 +3316,15 @@
         <v>77</v>
       </c>
       <c r="K27" s="3"/>
-      <c r="L27" s="34" t="s">
+      <c r="L27" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="M27" s="35"/>
-      <c r="N27" s="35"/>
-      <c r="O27" s="21"/>
+      <c r="M27" s="55"/>
+      <c r="N27" s="55"/>
+      <c r="O27" s="42"/>
     </row>
     <row r="28" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B28" s="20"/>
+      <c r="B28" s="44"/>
       <c r="C28" s="3"/>
       <c r="D28" s="3" t="s">
         <v>90</v>
@@ -3332,9 +3332,9 @@
       <c r="E28" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="F28" s="8"/>
-      <c r="G28" s="26"/>
-      <c r="H28" s="49"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="26"/>
       <c r="I28" s="3">
         <v>251478963</v>
       </c>
@@ -3342,15 +3342,15 @@
         <v>79</v>
       </c>
       <c r="K28" s="3"/>
-      <c r="L28" s="34" t="s">
+      <c r="L28" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="M28" s="35"/>
-      <c r="N28" s="35"/>
-      <c r="O28" s="21"/>
+      <c r="M28" s="55"/>
+      <c r="N28" s="55"/>
+      <c r="O28" s="42"/>
     </row>
     <row r="29" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B29" s="20"/>
+      <c r="B29" s="44"/>
       <c r="C29" s="3"/>
       <c r="D29" s="3" t="s">
         <v>90</v>
@@ -3358,9 +3358,9 @@
       <c r="E29" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="F29" s="8"/>
-      <c r="G29" s="26"/>
-      <c r="H29" s="49"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="10"/>
+      <c r="H29" s="26"/>
       <c r="I29" s="3">
         <v>266321458</v>
       </c>
@@ -3368,15 +3368,15 @@
         <v>81</v>
       </c>
       <c r="K29" s="3"/>
-      <c r="L29" s="34" t="s">
+      <c r="L29" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="M29" s="35"/>
-      <c r="N29" s="35"/>
-      <c r="O29" s="21"/>
+      <c r="M29" s="55"/>
+      <c r="N29" s="55"/>
+      <c r="O29" s="42"/>
     </row>
     <row r="30" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B30" s="20"/>
+      <c r="B30" s="44"/>
       <c r="C30" s="3"/>
       <c r="D30" s="3" t="s">
         <v>90</v>
@@ -3384,9 +3384,9 @@
       <c r="E30" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="F30" s="8"/>
+      <c r="F30" s="6"/>
       <c r="G30" s="3"/>
-      <c r="H30" s="49"/>
+      <c r="H30" s="26"/>
       <c r="I30" s="3">
         <v>239852147</v>
       </c>
@@ -3394,15 +3394,15 @@
         <v>83</v>
       </c>
       <c r="K30" s="3"/>
-      <c r="L30" s="34" t="s">
+      <c r="L30" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="M30" s="35"/>
-      <c r="N30" s="35"/>
-      <c r="O30" s="21"/>
+      <c r="M30" s="55"/>
+      <c r="N30" s="55"/>
+      <c r="O30" s="42"/>
     </row>
     <row r="31" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B31" s="20"/>
+      <c r="B31" s="44"/>
       <c r="C31" s="3"/>
       <c r="D31" s="3" t="s">
         <v>90</v>
@@ -3410,9 +3410,9 @@
       <c r="E31" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="F31" s="8"/>
+      <c r="F31" s="6"/>
       <c r="G31" s="3"/>
-      <c r="H31" s="49"/>
+      <c r="H31" s="26"/>
       <c r="I31" s="3">
         <v>288741256</v>
       </c>
@@ -3420,15 +3420,15 @@
         <v>85</v>
       </c>
       <c r="K31" s="3"/>
-      <c r="L31" s="34" t="s">
+      <c r="L31" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="M31" s="35"/>
-      <c r="N31" s="35"/>
-      <c r="O31" s="21"/>
+      <c r="M31" s="55"/>
+      <c r="N31" s="55"/>
+      <c r="O31" s="42"/>
     </row>
     <row r="32" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B32" s="20"/>
+      <c r="B32" s="44"/>
       <c r="C32" s="3"/>
       <c r="D32" s="3" t="s">
         <v>90</v>
@@ -3436,9 +3436,9 @@
       <c r="E32" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="F32" s="8"/>
+      <c r="F32" s="6"/>
       <c r="G32" s="3"/>
-      <c r="H32" s="49"/>
+      <c r="H32" s="26"/>
       <c r="I32" s="3">
         <v>255698147</v>
       </c>
@@ -3446,15 +3446,15 @@
         <v>87</v>
       </c>
       <c r="K32" s="3"/>
-      <c r="L32" s="34" t="s">
+      <c r="L32" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="M32" s="35"/>
-      <c r="N32" s="35"/>
-      <c r="O32" s="21"/>
+      <c r="M32" s="55"/>
+      <c r="N32" s="55"/>
+      <c r="O32" s="42"/>
     </row>
     <row r="33" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B33" s="20"/>
+      <c r="B33" s="44"/>
       <c r="C33" s="3"/>
       <c r="D33" s="3" t="s">
         <v>90</v>
@@ -3462,7 +3462,7 @@
       <c r="E33" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="F33" s="8"/>
+      <c r="F33" s="6"/>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
       <c r="I33" s="3">
@@ -3472,36 +3472,31 @@
         <v>89</v>
       </c>
       <c r="K33" s="3"/>
-      <c r="L33" s="34" t="s">
+      <c r="L33" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="M33" s="35"/>
-      <c r="N33" s="35"/>
-      <c r="O33" s="21"/>
+      <c r="M33" s="55"/>
+      <c r="N33" s="55"/>
+      <c r="O33" s="42"/>
     </row>
     <row r="34" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B34" s="22"/>
-      <c r="C34" s="64"/>
-      <c r="D34" s="64"/>
-      <c r="E34" s="64"/>
-      <c r="F34" s="64"/>
-      <c r="G34" s="64"/>
-      <c r="H34" s="64"/>
-      <c r="I34" s="64"/>
-      <c r="J34" s="64"/>
-      <c r="K34" s="64"/>
-      <c r="L34" s="64"/>
-      <c r="M34" s="64"/>
-      <c r="N34" s="64"/>
-      <c r="O34" s="24"/>
+      <c r="B34" s="45"/>
+      <c r="C34" s="52"/>
+      <c r="D34" s="52"/>
+      <c r="E34" s="52"/>
+      <c r="F34" s="52"/>
+      <c r="G34" s="52"/>
+      <c r="H34" s="52"/>
+      <c r="I34" s="52"/>
+      <c r="J34" s="52"/>
+      <c r="K34" s="52"/>
+      <c r="L34" s="52"/>
+      <c r="M34" s="52"/>
+      <c r="N34" s="52"/>
+      <c r="O34" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B2:O2"/>
-    <mergeCell ref="O3:O33"/>
-    <mergeCell ref="B3:B33"/>
-    <mergeCell ref="C8:N8"/>
-    <mergeCell ref="C17:N17"/>
     <mergeCell ref="B34:O34"/>
     <mergeCell ref="I7:J7"/>
     <mergeCell ref="I5:J5"/>
@@ -3511,9 +3506,14 @@
     <mergeCell ref="I6:J6"/>
     <mergeCell ref="C18:N18"/>
     <mergeCell ref="C9:N9"/>
-    <mergeCell ref="C3:N3"/>
     <mergeCell ref="C5:C7"/>
     <mergeCell ref="F5:F7"/>
+    <mergeCell ref="B2:O2"/>
+    <mergeCell ref="O3:O33"/>
+    <mergeCell ref="B3:B33"/>
+    <mergeCell ref="C8:N8"/>
+    <mergeCell ref="C17:N17"/>
+    <mergeCell ref="C3:N3"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="G4" r:id="rId1" xr:uid="{90136737-50D8-4624-BF9F-7BB076958402}"/>
@@ -3560,587 +3560,595 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="17"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="19"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="41"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B3" s="20"/>
-      <c r="C3" s="60" t="s">
+      <c r="B3" s="44"/>
+      <c r="C3" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="60" t="s">
+      <c r="E3" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="I3" s="21"/>
-      <c r="J3" s="11" t="s">
-        <v>238</v>
-      </c>
-      <c r="K3" s="65"/>
-      <c r="L3" s="12"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="67" t="s">
+        <v>237</v>
+      </c>
+      <c r="K3" s="68"/>
+      <c r="L3" s="69"/>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="20"/>
-      <c r="C4" s="60" t="s">
-        <v>241</v>
-      </c>
-      <c r="D4" s="61" t="s">
+      <c r="B4" s="44"/>
+      <c r="C4" s="32" t="s">
         <v>240</v>
       </c>
+      <c r="D4" s="5" t="s">
+        <v>239</v>
+      </c>
       <c r="E4" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="F4" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>25</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H4" s="3">
         <v>2</v>
       </c>
-      <c r="I4" s="21"/>
-      <c r="J4" s="63" t="s">
+      <c r="I4" s="42"/>
+      <c r="J4" s="33" t="s">
         <v>17</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="L4" s="3" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B5" s="20"/>
-      <c r="C5" s="62"/>
-      <c r="D5" s="62"/>
-      <c r="E5" s="62"/>
-      <c r="F5" s="62"/>
-      <c r="G5" s="62"/>
-      <c r="H5" s="62"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="63" t="s">
+      <c r="B5" s="44"/>
+      <c r="C5" s="71"/>
+      <c r="D5" s="71"/>
+      <c r="E5" s="71"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="71"/>
+      <c r="H5" s="71"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="33" t="s">
         <v>19</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B6" s="20"/>
-      <c r="C6" s="57" t="s">
+      <c r="B6" s="44"/>
+      <c r="C6" s="72" t="s">
         <v>103</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="48" t="s">
         <v>100</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="F6" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="F6" s="48" t="s">
         <v>25</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H6" s="3">
         <v>2</v>
       </c>
-      <c r="I6" s="21"/>
-      <c r="J6" s="63" t="s">
+      <c r="I6" s="42"/>
+      <c r="J6" s="33" t="s">
         <v>20</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L6" s="3" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B7" s="20"/>
-      <c r="C7" s="57"/>
-      <c r="D7" s="7"/>
+      <c r="B7" s="44"/>
+      <c r="C7" s="72"/>
+      <c r="D7" s="48"/>
       <c r="E7" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="7"/>
+      <c r="F7" s="48"/>
       <c r="G7" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H7" s="3">
         <v>1</v>
       </c>
-      <c r="I7" s="21"/>
-      <c r="J7" s="63" t="s">
+      <c r="I7" s="42"/>
+      <c r="J7" s="33" t="s">
         <v>30</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L7" s="3" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B8" s="20"/>
-      <c r="C8" s="57"/>
-      <c r="D8" s="7"/>
+      <c r="B8" s="44"/>
+      <c r="C8" s="72"/>
+      <c r="D8" s="48"/>
       <c r="E8" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="F8" s="7"/>
+      <c r="F8" s="48"/>
       <c r="G8" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H8" s="3">
         <v>1</v>
       </c>
-      <c r="I8" s="21"/>
-      <c r="J8" s="63" t="s">
+      <c r="I8" s="42"/>
+      <c r="J8" s="33" t="s">
         <v>36</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="L8" s="3" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B9" s="20"/>
-      <c r="C9" s="57"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="21"/>
-      <c r="J9" s="63" t="s">
+      <c r="B9" s="44"/>
+      <c r="C9" s="72"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="46"/>
+      <c r="G9" s="46"/>
+      <c r="H9" s="46"/>
+      <c r="I9" s="42"/>
+      <c r="J9" s="33" t="s">
         <v>39</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B10" s="20"/>
-      <c r="C10" s="57"/>
-      <c r="D10" s="7"/>
+      <c r="B10" s="44"/>
+      <c r="C10" s="72"/>
+      <c r="D10" s="48"/>
       <c r="E10" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="F10" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="F10" s="48" t="s">
         <v>26</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H10" s="3">
         <v>2</v>
       </c>
-      <c r="I10" s="21"/>
-      <c r="J10" s="63" t="s">
+      <c r="I10" s="42"/>
+      <c r="J10" s="33" t="s">
         <v>107</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B11" s="20"/>
-      <c r="C11" s="57"/>
-      <c r="D11" s="7"/>
+      <c r="B11" s="44"/>
+      <c r="C11" s="72"/>
+      <c r="D11" s="48"/>
       <c r="E11" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F11" s="7"/>
+      <c r="F11" s="48"/>
       <c r="G11" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H11" s="3">
         <v>1</v>
       </c>
-      <c r="I11" s="21"/>
+      <c r="I11" s="42"/>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B12" s="20"/>
-      <c r="C12" s="57"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="21"/>
+      <c r="B12" s="44"/>
+      <c r="C12" s="72"/>
+      <c r="D12" s="48"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="46"/>
+      <c r="G12" s="46"/>
+      <c r="H12" s="46"/>
+      <c r="I12" s="42"/>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B13" s="20"/>
-      <c r="C13" s="57"/>
-      <c r="D13" s="7"/>
+      <c r="B13" s="44"/>
+      <c r="C13" s="72"/>
+      <c r="D13" s="48"/>
       <c r="E13" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="4" t="s">
         <v>35</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H13" s="3">
         <v>1</v>
       </c>
-      <c r="I13" s="21"/>
+      <c r="I13" s="42"/>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B14" s="20"/>
-      <c r="C14" s="57"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
-      <c r="I14" s="21"/>
+      <c r="B14" s="44"/>
+      <c r="C14" s="72"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="47"/>
+      <c r="F14" s="47"/>
+      <c r="G14" s="47"/>
+      <c r="H14" s="47"/>
+      <c r="I14" s="42"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B15" s="20"/>
-      <c r="C15" s="57"/>
-      <c r="D15" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="E15" s="58" t="s">
-        <v>198</v>
-      </c>
-      <c r="F15" s="10" t="s">
+      <c r="B15" s="44"/>
+      <c r="C15" s="72"/>
+      <c r="D15" s="48" t="s">
+        <v>200</v>
+      </c>
+      <c r="E15" s="31" t="s">
+        <v>197</v>
+      </c>
+      <c r="F15" s="4" t="s">
         <v>25</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H15" s="3">
         <v>2</v>
       </c>
-      <c r="I15" s="21"/>
+      <c r="I15" s="42"/>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B16" s="20"/>
-      <c r="C16" s="57"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="21"/>
+      <c r="B16" s="44"/>
+      <c r="C16" s="72"/>
+      <c r="D16" s="48"/>
+      <c r="E16" s="46"/>
+      <c r="F16" s="46"/>
+      <c r="G16" s="46"/>
+      <c r="H16" s="46"/>
+      <c r="I16" s="42"/>
     </row>
     <row r="17" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B17" s="20"/>
-      <c r="C17" s="57"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="58" t="s">
-        <v>199</v>
-      </c>
-      <c r="F17" s="7" t="s">
+      <c r="B17" s="44"/>
+      <c r="C17" s="72"/>
+      <c r="D17" s="48"/>
+      <c r="E17" s="31" t="s">
+        <v>198</v>
+      </c>
+      <c r="F17" s="48" t="s">
         <v>26</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H17" s="3">
         <v>2</v>
       </c>
-      <c r="I17" s="21"/>
+      <c r="I17" s="42"/>
     </row>
     <row r="18" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B18" s="20"/>
-      <c r="C18" s="57"/>
-      <c r="D18" s="7"/>
+      <c r="B18" s="44"/>
+      <c r="C18" s="72"/>
+      <c r="D18" s="48"/>
       <c r="E18" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="F18" s="7"/>
+        <v>199</v>
+      </c>
+      <c r="F18" s="48"/>
       <c r="G18" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H18" s="3">
         <v>1</v>
       </c>
-      <c r="I18" s="21"/>
+      <c r="I18" s="42"/>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B19" s="20"/>
-      <c r="C19" s="57"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="21"/>
+      <c r="B19" s="44"/>
+      <c r="C19" s="72"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="46"/>
+      <c r="F19" s="46"/>
+      <c r="G19" s="46"/>
+      <c r="H19" s="46"/>
+      <c r="I19" s="42"/>
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B20" s="20"/>
-      <c r="C20" s="57"/>
-      <c r="D20" s="7"/>
+      <c r="B20" s="44"/>
+      <c r="C20" s="72"/>
+      <c r="D20" s="48"/>
       <c r="E20" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F20" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="F20" s="4" t="s">
         <v>35</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H20" s="3">
         <v>1</v>
       </c>
-      <c r="I20" s="21"/>
+      <c r="I20" s="42"/>
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B21" s="20"/>
-      <c r="C21" s="57"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="15"/>
-      <c r="I21" s="21"/>
+      <c r="B21" s="44"/>
+      <c r="C21" s="72"/>
+      <c r="D21" s="47"/>
+      <c r="E21" s="47"/>
+      <c r="F21" s="47"/>
+      <c r="G21" s="47"/>
+      <c r="H21" s="47"/>
+      <c r="I21" s="42"/>
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B22" s="20"/>
-      <c r="C22" s="57"/>
-      <c r="D22" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="E22" s="58" t="s">
-        <v>198</v>
-      </c>
-      <c r="F22" s="7" t="s">
+      <c r="B22" s="44"/>
+      <c r="C22" s="72"/>
+      <c r="D22" s="48" t="s">
+        <v>201</v>
+      </c>
+      <c r="E22" s="31" t="s">
+        <v>197</v>
+      </c>
+      <c r="F22" s="48" t="s">
         <v>25</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H22" s="3">
         <v>2</v>
       </c>
-      <c r="I22" s="21"/>
+      <c r="I22" s="42"/>
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B23" s="20"/>
-      <c r="C23" s="57"/>
-      <c r="D23" s="7"/>
+      <c r="B23" s="44"/>
+      <c r="C23" s="72"/>
+      <c r="D23" s="48"/>
       <c r="E23" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="F23" s="7"/>
+      <c r="F23" s="48"/>
       <c r="G23" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H23" s="3">
         <v>1</v>
       </c>
-      <c r="I23" s="21"/>
+      <c r="I23" s="42"/>
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B24" s="20"/>
-      <c r="C24" s="57"/>
-      <c r="D24" s="7"/>
+      <c r="B24" s="44"/>
+      <c r="C24" s="72"/>
+      <c r="D24" s="48"/>
       <c r="E24" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F24" s="7"/>
+      <c r="F24" s="48"/>
       <c r="G24" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H24" s="3">
         <v>1</v>
       </c>
-      <c r="I24" s="21"/>
+      <c r="I24" s="42"/>
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B25" s="20"/>
-      <c r="C25" s="57"/>
-      <c r="D25" s="7"/>
+      <c r="B25" s="44"/>
+      <c r="C25" s="72"/>
+      <c r="D25" s="48"/>
       <c r="E25" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="F25" s="7"/>
+        <v>204</v>
+      </c>
+      <c r="F25" s="48"/>
       <c r="G25" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H25" s="3">
         <v>1</v>
       </c>
-      <c r="I25" s="21"/>
+      <c r="I25" s="42"/>
     </row>
     <row r="26" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B26" s="20"/>
-      <c r="C26" s="57"/>
-      <c r="D26" s="7"/>
+      <c r="B26" s="44"/>
+      <c r="C26" s="72"/>
+      <c r="D26" s="48"/>
       <c r="E26" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="F26" s="7"/>
+      <c r="F26" s="48"/>
       <c r="G26" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H26" s="3">
         <v>1</v>
       </c>
-      <c r="I26" s="21"/>
+      <c r="I26" s="42"/>
     </row>
     <row r="27" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B27" s="20"/>
-      <c r="C27" s="57"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="21"/>
+      <c r="B27" s="44"/>
+      <c r="C27" s="72"/>
+      <c r="D27" s="48"/>
+      <c r="E27" s="46"/>
+      <c r="F27" s="46"/>
+      <c r="G27" s="46"/>
+      <c r="H27" s="46"/>
+      <c r="I27" s="42"/>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B28" s="20"/>
-      <c r="C28" s="57"/>
-      <c r="D28" s="7"/>
+      <c r="B28" s="44"/>
+      <c r="C28" s="72"/>
+      <c r="D28" s="48"/>
       <c r="E28" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="F28" s="10" t="s">
+      <c r="F28" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H28" s="3">
         <v>1</v>
       </c>
-      <c r="I28" s="21"/>
+      <c r="I28" s="42"/>
     </row>
     <row r="29" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B29" s="20"/>
-      <c r="C29" s="57"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="21"/>
+      <c r="B29" s="44"/>
+      <c r="C29" s="72"/>
+      <c r="D29" s="48"/>
+      <c r="E29" s="46"/>
+      <c r="F29" s="46"/>
+      <c r="G29" s="46"/>
+      <c r="H29" s="46"/>
+      <c r="I29" s="42"/>
     </row>
     <row r="30" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B30" s="20"/>
-      <c r="C30" s="57"/>
-      <c r="D30" s="7"/>
+      <c r="B30" s="44"/>
+      <c r="C30" s="72"/>
+      <c r="D30" s="48"/>
       <c r="E30" s="3"/>
-      <c r="F30" s="10" t="s">
+      <c r="F30" s="4" t="s">
         <v>35</v>
       </c>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
-      <c r="I30" s="21"/>
-      <c r="J30" s="71" t="s">
+      <c r="I30" s="42"/>
+      <c r="J30" s="34" t="s">
         <v>99</v>
       </c>
-      <c r="K30" s="72" t="s">
+      <c r="K30" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="L30" s="71" t="s">
-        <v>191</v>
-      </c>
-      <c r="M30" s="71">
+      <c r="L30" s="34" t="s">
+        <v>190</v>
+      </c>
+      <c r="M30" s="34">
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B31" s="20"/>
-      <c r="C31" s="57"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="15"/>
-      <c r="H31" s="15"/>
-      <c r="I31" s="21"/>
+      <c r="B31" s="44"/>
+      <c r="C31" s="72"/>
+      <c r="D31" s="47"/>
+      <c r="E31" s="47"/>
+      <c r="F31" s="47"/>
+      <c r="G31" s="47"/>
+      <c r="H31" s="47"/>
+      <c r="I31" s="42"/>
     </row>
     <row r="32" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B32" s="20"/>
-      <c r="C32" s="57"/>
-      <c r="D32" s="10" t="s">
+      <c r="B32" s="44"/>
+      <c r="C32" s="72"/>
+      <c r="D32" s="4" t="s">
         <v>101</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="F32" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="F32" s="4" t="s">
         <v>25</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H32" s="3">
         <v>3</v>
       </c>
-      <c r="I32" s="21"/>
+      <c r="I32" s="42"/>
     </row>
     <row r="33" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B33" s="20"/>
-      <c r="C33" s="59"/>
-      <c r="D33" s="59"/>
-      <c r="E33" s="59"/>
-      <c r="F33" s="59"/>
-      <c r="G33" s="59"/>
-      <c r="H33" s="59"/>
-      <c r="I33" s="21"/>
+      <c r="B33" s="44"/>
+      <c r="C33" s="70"/>
+      <c r="D33" s="70"/>
+      <c r="E33" s="70"/>
+      <c r="F33" s="70"/>
+      <c r="G33" s="70"/>
+      <c r="H33" s="70"/>
+      <c r="I33" s="42"/>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B34" s="20"/>
-      <c r="C34" s="60" t="s">
+      <c r="B34" s="44"/>
+      <c r="C34" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="D34" s="10" t="s">
-        <v>203</v>
+      <c r="D34" s="4" t="s">
+        <v>202</v>
       </c>
       <c r="E34" s="3"/>
-      <c r="F34" s="10"/>
+      <c r="F34" s="4"/>
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
-      <c r="I34" s="21"/>
+      <c r="I34" s="42"/>
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B35" s="22"/>
-      <c r="C35" s="64"/>
-      <c r="D35" s="64"/>
-      <c r="E35" s="64"/>
-      <c r="F35" s="64"/>
-      <c r="G35" s="64"/>
-      <c r="H35" s="64"/>
-      <c r="I35" s="24"/>
+      <c r="B35" s="45"/>
+      <c r="C35" s="52"/>
+      <c r="D35" s="52"/>
+      <c r="E35" s="52"/>
+      <c r="F35" s="52"/>
+      <c r="G35" s="52"/>
+      <c r="H35" s="52"/>
+      <c r="I35" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="C6:C32"/>
+    <mergeCell ref="E27:H27"/>
+    <mergeCell ref="E29:H29"/>
+    <mergeCell ref="E9:H9"/>
+    <mergeCell ref="E12:H12"/>
+    <mergeCell ref="D6:D13"/>
+    <mergeCell ref="D15:D20"/>
+    <mergeCell ref="D22:D30"/>
     <mergeCell ref="J3:L3"/>
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="B35:I35"/>
@@ -4157,14 +4165,6 @@
     <mergeCell ref="C5:H5"/>
     <mergeCell ref="D14:H14"/>
     <mergeCell ref="D21:H21"/>
-    <mergeCell ref="E9:H9"/>
-    <mergeCell ref="E12:H12"/>
-    <mergeCell ref="D6:D13"/>
-    <mergeCell ref="D15:D20"/>
-    <mergeCell ref="D22:D30"/>
-    <mergeCell ref="C6:C32"/>
-    <mergeCell ref="E27:H27"/>
-    <mergeCell ref="E29:H29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Testes.xlsx
+++ b/Testes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\utilizador\Documents\CTESP\4semestre\LP2\ProjetoTesteLP2\TrabalhoTesteLP2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D8DDE33-BFFC-43F1-A777-D8136E15A36A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C70B6BD-CBE6-4EE7-9321-6FC1F3DDEE64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{17050BBC-8C72-4C7C-BB9E-52ED50A4B6E1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{17050BBC-8C72-4C7C-BB9E-52ED50A4B6E1}"/>
   </bookViews>
   <sheets>
     <sheet name="Menus" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="245">
   <si>
     <t>1 - Adicionar Departamento</t>
   </si>
@@ -333,12 +333,6 @@
   </si>
   <si>
     <t>[INATIVO] LEN - Licenciatura em Engenharia Nuclear</t>
-  </si>
-  <si>
-    <t>DCI : Departamento de Ciencias</t>
-  </si>
-  <si>
-    <t>DEN : Departamento de Engenharia</t>
   </si>
   <si>
     <t>[ATIVO] DES : Desenho Técnico</t>
@@ -758,6 +752,18 @@
   </si>
   <si>
     <t>7 - Listar Cursos por Departamento</t>
+  </si>
+  <si>
+    <t>4. Ativar/Inativar Departamento</t>
+  </si>
+  <si>
+    <t>5. Alterar Curso de Departamento</t>
+  </si>
+  <si>
+    <t>[ATIVO] DEN : Departamento de Engenharia</t>
+  </si>
+  <si>
+    <t>[ATIVO] DCI : Departamento de Ciencias</t>
   </si>
 </sst>
 </file>
@@ -1478,7 +1484,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{781029DD-AB0E-45D2-BEA2-289639D498A2}">
-  <dimension ref="B2:F117"/>
+  <dimension ref="B2:F119"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="35" bestFit="1" customWidth="1"/>
@@ -1496,7 +1502,7 @@
     <row r="3" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B3" s="44"/>
       <c r="C3" s="36" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D3" s="36"/>
       <c r="E3" s="36"/>
@@ -1505,7 +1511,7 @@
     <row r="4" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B4" s="44"/>
       <c r="C4" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D4" s="46"/>
       <c r="E4" s="46"/>
@@ -1532,7 +1538,7 @@
     <row r="7" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B7" s="44"/>
       <c r="C7" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D7" s="46"/>
       <c r="E7" s="46"/>
@@ -1541,7 +1547,7 @@
     <row r="8" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B8" s="44"/>
       <c r="C8" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D8" s="46"/>
       <c r="E8" s="46"/>
@@ -1550,7 +1556,7 @@
     <row r="9" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B9" s="44"/>
       <c r="C9" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D9" s="46"/>
       <c r="E9" s="46"/>
@@ -1575,10 +1581,10 @@
     <row r="12" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B12" s="44"/>
       <c r="C12" s="49" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E12" s="46"/>
       <c r="F12" s="42"/>
@@ -1587,7 +1593,7 @@
       <c r="B13" s="44"/>
       <c r="C13" s="50"/>
       <c r="D13" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E13" s="46"/>
       <c r="F13" s="42"/>
@@ -1596,7 +1602,7 @@
       <c r="B14" s="44"/>
       <c r="C14" s="50"/>
       <c r="D14" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E14" s="46"/>
       <c r="F14" s="42"/>
@@ -1605,7 +1611,7 @@
       <c r="B15" s="44"/>
       <c r="C15" s="50"/>
       <c r="D15" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E15" s="46"/>
       <c r="F15" s="42"/>
@@ -1614,7 +1620,7 @@
       <c r="B16" s="44"/>
       <c r="C16" s="50"/>
       <c r="D16" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E16" s="46"/>
       <c r="F16" s="42"/>
@@ -1623,7 +1629,7 @@
       <c r="B17" s="44"/>
       <c r="C17" s="50"/>
       <c r="D17" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E17" s="46"/>
       <c r="F17" s="42"/>
@@ -1632,7 +1638,7 @@
       <c r="B18" s="44"/>
       <c r="C18" s="50"/>
       <c r="D18" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E18" s="46"/>
       <c r="F18" s="42"/>
@@ -1641,7 +1647,7 @@
       <c r="B19" s="44"/>
       <c r="C19" s="50"/>
       <c r="D19" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E19" s="46"/>
       <c r="F19" s="42"/>
@@ -1658,7 +1664,7 @@
       <c r="C21" s="50"/>
       <c r="D21" s="46"/>
       <c r="E21" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F21" s="42"/>
     </row>
@@ -1694,7 +1700,7 @@
       <c r="C25" s="50"/>
       <c r="D25" s="46"/>
       <c r="E25" s="3" t="s">
-        <v>2</v>
+        <v>241</v>
       </c>
       <c r="F25" s="42"/>
     </row>
@@ -1702,7 +1708,9 @@
       <c r="B26" s="44"/>
       <c r="C26" s="50"/>
       <c r="D26" s="46"/>
-      <c r="E26" s="7"/>
+      <c r="E26" s="3" t="s">
+        <v>242</v>
+      </c>
       <c r="F26" s="42"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.3">
@@ -1710,7 +1718,7 @@
       <c r="C27" s="50"/>
       <c r="D27" s="46"/>
       <c r="E27" s="3" t="s">
-        <v>146</v>
+        <v>2</v>
       </c>
       <c r="F27" s="42"/>
     </row>
@@ -1718,9 +1726,7 @@
       <c r="B28" s="44"/>
       <c r="C28" s="50"/>
       <c r="D28" s="46"/>
-      <c r="E28" s="3" t="s">
-        <v>3</v>
-      </c>
+      <c r="E28" s="7"/>
       <c r="F28" s="42"/>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.3">
@@ -1728,7 +1734,7 @@
       <c r="C29" s="50"/>
       <c r="D29" s="46"/>
       <c r="E29" s="3" t="s">
-        <v>4</v>
+        <v>144</v>
       </c>
       <c r="F29" s="42"/>
     </row>
@@ -1737,7 +1743,7 @@
       <c r="C30" s="50"/>
       <c r="D30" s="46"/>
       <c r="E30" s="3" t="s">
-        <v>147</v>
+        <v>3</v>
       </c>
       <c r="F30" s="42"/>
     </row>
@@ -1746,7 +1752,7 @@
       <c r="C31" s="50"/>
       <c r="D31" s="46"/>
       <c r="E31" s="3" t="s">
-        <v>148</v>
+        <v>4</v>
       </c>
       <c r="F31" s="42"/>
     </row>
@@ -1755,7 +1761,7 @@
       <c r="C32" s="50"/>
       <c r="D32" s="46"/>
       <c r="E32" s="3" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="F32" s="42"/>
     </row>
@@ -1764,7 +1770,7 @@
       <c r="C33" s="50"/>
       <c r="D33" s="46"/>
       <c r="E33" s="3" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F33" s="42"/>
     </row>
@@ -1773,7 +1779,7 @@
       <c r="C34" s="50"/>
       <c r="D34" s="46"/>
       <c r="E34" s="3" t="s">
-        <v>242</v>
+        <v>147</v>
       </c>
       <c r="F34" s="42"/>
     </row>
@@ -1782,7 +1788,7 @@
       <c r="C35" s="50"/>
       <c r="D35" s="46"/>
       <c r="E35" s="3" t="s">
-        <v>2</v>
+        <v>148</v>
       </c>
       <c r="F35" s="42"/>
     </row>
@@ -1790,7 +1796,9 @@
       <c r="B36" s="44"/>
       <c r="C36" s="50"/>
       <c r="D36" s="46"/>
-      <c r="E36" s="7"/>
+      <c r="E36" s="3" t="s">
+        <v>240</v>
+      </c>
       <c r="F36" s="42"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.3">
@@ -1798,7 +1806,7 @@
       <c r="C37" s="50"/>
       <c r="D37" s="46"/>
       <c r="E37" s="3" t="s">
-        <v>151</v>
+        <v>2</v>
       </c>
       <c r="F37" s="42"/>
     </row>
@@ -1806,9 +1814,7 @@
       <c r="B38" s="44"/>
       <c r="C38" s="50"/>
       <c r="D38" s="46"/>
-      <c r="E38" s="3" t="s">
-        <v>53</v>
-      </c>
+      <c r="E38" s="7"/>
       <c r="F38" s="42"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.3">
@@ -1816,7 +1822,7 @@
       <c r="C39" s="50"/>
       <c r="D39" s="46"/>
       <c r="E39" s="3" t="s">
-        <v>5</v>
+        <v>149</v>
       </c>
       <c r="F39" s="42"/>
     </row>
@@ -1825,7 +1831,7 @@
       <c r="C40" s="50"/>
       <c r="D40" s="46"/>
       <c r="E40" s="3" t="s">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="F40" s="42"/>
     </row>
@@ -1834,7 +1840,7 @@
       <c r="C41" s="50"/>
       <c r="D41" s="46"/>
       <c r="E41" s="3" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="F41" s="42"/>
     </row>
@@ -1843,7 +1849,7 @@
       <c r="C42" s="50"/>
       <c r="D42" s="46"/>
       <c r="E42" s="3" t="s">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="F42" s="42"/>
     </row>
@@ -1852,7 +1858,7 @@
       <c r="C43" s="50"/>
       <c r="D43" s="46"/>
       <c r="E43" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F43" s="42"/>
     </row>
@@ -1861,7 +1867,7 @@
       <c r="C44" s="50"/>
       <c r="D44" s="46"/>
       <c r="E44" s="3" t="s">
-        <v>152</v>
+        <v>52</v>
       </c>
       <c r="F44" s="42"/>
     </row>
@@ -1870,7 +1876,7 @@
       <c r="C45" s="50"/>
       <c r="D45" s="46"/>
       <c r="E45" s="3" t="s">
-        <v>153</v>
+        <v>55</v>
       </c>
       <c r="F45" s="42"/>
     </row>
@@ -1879,7 +1885,7 @@
       <c r="C46" s="50"/>
       <c r="D46" s="46"/>
       <c r="E46" s="3" t="s">
-        <v>2</v>
+        <v>150</v>
       </c>
       <c r="F46" s="42"/>
     </row>
@@ -1887,7 +1893,9 @@
       <c r="B47" s="44"/>
       <c r="C47" s="50"/>
       <c r="D47" s="46"/>
-      <c r="E47" s="7"/>
+      <c r="E47" s="3" t="s">
+        <v>151</v>
+      </c>
       <c r="F47" s="42"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.3">
@@ -1895,7 +1903,7 @@
       <c r="C48" s="50"/>
       <c r="D48" s="46"/>
       <c r="E48" s="3" t="s">
-        <v>154</v>
+        <v>2</v>
       </c>
       <c r="F48" s="42"/>
     </row>
@@ -1903,9 +1911,7 @@
       <c r="B49" s="44"/>
       <c r="C49" s="50"/>
       <c r="D49" s="46"/>
-      <c r="E49" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="E49" s="7"/>
       <c r="F49" s="42"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.3">
@@ -1913,7 +1919,7 @@
       <c r="C50" s="50"/>
       <c r="D50" s="46"/>
       <c r="E50" s="3" t="s">
-        <v>56</v>
+        <v>152</v>
       </c>
       <c r="F50" s="42"/>
     </row>
@@ -1922,7 +1928,7 @@
       <c r="C51" s="50"/>
       <c r="D51" s="46"/>
       <c r="E51" s="3" t="s">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="F51" s="42"/>
     </row>
@@ -1931,7 +1937,7 @@
       <c r="C52" s="50"/>
       <c r="D52" s="46"/>
       <c r="E52" s="3" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F52" s="42"/>
     </row>
@@ -1940,7 +1946,7 @@
       <c r="C53" s="50"/>
       <c r="D53" s="46"/>
       <c r="E53" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="F53" s="42"/>
     </row>
@@ -1949,7 +1955,7 @@
       <c r="C54" s="50"/>
       <c r="D54" s="46"/>
       <c r="E54" s="3" t="s">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="F54" s="42"/>
     </row>
@@ -1957,7 +1963,9 @@
       <c r="B55" s="44"/>
       <c r="C55" s="50"/>
       <c r="D55" s="46"/>
-      <c r="E55" s="7"/>
+      <c r="E55" s="3" t="s">
+        <v>154</v>
+      </c>
       <c r="F55" s="42"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.3">
@@ -1965,7 +1973,7 @@
       <c r="C56" s="50"/>
       <c r="D56" s="46"/>
       <c r="E56" s="3" t="s">
-        <v>157</v>
+        <v>2</v>
       </c>
       <c r="F56" s="42"/>
     </row>
@@ -1973,9 +1981,7 @@
       <c r="B57" s="44"/>
       <c r="C57" s="50"/>
       <c r="D57" s="46"/>
-      <c r="E57" s="3" t="s">
-        <v>8</v>
-      </c>
+      <c r="E57" s="7"/>
       <c r="F57" s="42"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.3">
@@ -1983,7 +1989,7 @@
       <c r="C58" s="50"/>
       <c r="D58" s="46"/>
       <c r="E58" s="3" t="s">
-        <v>57</v>
+        <v>155</v>
       </c>
       <c r="F58" s="42"/>
     </row>
@@ -1992,7 +1998,7 @@
       <c r="C59" s="50"/>
       <c r="D59" s="46"/>
       <c r="E59" s="3" t="s">
-        <v>158</v>
+        <v>8</v>
       </c>
       <c r="F59" s="42"/>
     </row>
@@ -2001,7 +2007,7 @@
       <c r="C60" s="50"/>
       <c r="D60" s="46"/>
       <c r="E60" s="3" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="F60" s="42"/>
     </row>
@@ -2010,7 +2016,7 @@
       <c r="C61" s="50"/>
       <c r="D61" s="46"/>
       <c r="E61" s="3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="F61" s="42"/>
     </row>
@@ -2019,7 +2025,7 @@
       <c r="C62" s="50"/>
       <c r="D62" s="46"/>
       <c r="E62" s="3" t="s">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="F62" s="42"/>
     </row>
@@ -2027,7 +2033,9 @@
       <c r="B63" s="44"/>
       <c r="C63" s="50"/>
       <c r="D63" s="46"/>
-      <c r="E63" s="7"/>
+      <c r="E63" s="3" t="s">
+        <v>157</v>
+      </c>
       <c r="F63" s="42"/>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.3">
@@ -2035,7 +2043,7 @@
       <c r="C64" s="50"/>
       <c r="D64" s="46"/>
       <c r="E64" s="3" t="s">
-        <v>160</v>
+        <v>2</v>
       </c>
       <c r="F64" s="42"/>
     </row>
@@ -2043,9 +2051,7 @@
       <c r="B65" s="44"/>
       <c r="C65" s="50"/>
       <c r="D65" s="46"/>
-      <c r="E65" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="E65" s="7"/>
       <c r="F65" s="42"/>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.3">
@@ -2053,7 +2059,7 @@
       <c r="C66" s="50"/>
       <c r="D66" s="46"/>
       <c r="E66" s="3" t="s">
-        <v>58</v>
+        <v>158</v>
       </c>
       <c r="F66" s="42"/>
     </row>
@@ -2062,7 +2068,7 @@
       <c r="C67" s="50"/>
       <c r="D67" s="46"/>
       <c r="E67" s="3" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="F67" s="42"/>
     </row>
@@ -2071,7 +2077,7 @@
       <c r="C68" s="50"/>
       <c r="D68" s="46"/>
       <c r="E68" s="3" t="s">
-        <v>161</v>
+        <v>58</v>
       </c>
       <c r="F68" s="42"/>
     </row>
@@ -2080,7 +2086,7 @@
       <c r="C69" s="50"/>
       <c r="D69" s="46"/>
       <c r="E69" s="3" t="s">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="F69" s="42"/>
     </row>
@@ -2088,7 +2094,9 @@
       <c r="B70" s="44"/>
       <c r="C70" s="50"/>
       <c r="D70" s="46"/>
-      <c r="E70" s="7"/>
+      <c r="E70" s="3" t="s">
+        <v>159</v>
+      </c>
       <c r="F70" s="42"/>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.3">
@@ -2096,7 +2104,7 @@
       <c r="C71" s="50"/>
       <c r="D71" s="46"/>
       <c r="E71" s="3" t="s">
-        <v>162</v>
+        <v>2</v>
       </c>
       <c r="F71" s="42"/>
     </row>
@@ -2104,9 +2112,7 @@
       <c r="B72" s="44"/>
       <c r="C72" s="50"/>
       <c r="D72" s="46"/>
-      <c r="E72" s="3" t="s">
-        <v>163</v>
-      </c>
+      <c r="E72" s="7"/>
       <c r="F72" s="42"/>
     </row>
     <row r="73" spans="2:6" x14ac:dyDescent="0.3">
@@ -2114,42 +2120,42 @@
       <c r="C73" s="50"/>
       <c r="D73" s="46"/>
       <c r="E73" s="3" t="s">
-        <v>2</v>
+        <v>160</v>
       </c>
       <c r="F73" s="42"/>
     </row>
     <row r="74" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B74" s="44"/>
-      <c r="C74" s="47"/>
-      <c r="D74" s="47"/>
-      <c r="E74" s="47"/>
+      <c r="C74" s="50"/>
+      <c r="D74" s="46"/>
+      <c r="E74" s="3" t="s">
+        <v>161</v>
+      </c>
       <c r="F74" s="42"/>
     </row>
     <row r="75" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B75" s="44"/>
-      <c r="C75" s="48" t="s">
-        <v>174</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E75" s="46"/>
+      <c r="C75" s="50"/>
+      <c r="D75" s="46"/>
+      <c r="E75" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="F75" s="42"/>
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B76" s="44"/>
-      <c r="C76" s="48"/>
-      <c r="D76" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="E76" s="46"/>
+      <c r="C76" s="47"/>
+      <c r="D76" s="47"/>
+      <c r="E76" s="47"/>
       <c r="F76" s="42"/>
     </row>
     <row r="77" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B77" s="44"/>
-      <c r="C77" s="48"/>
+      <c r="C77" s="48" t="s">
+        <v>172</v>
+      </c>
       <c r="D77" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E77" s="46"/>
       <c r="F77" s="42"/>
@@ -2158,7 +2164,7 @@
       <c r="B78" s="44"/>
       <c r="C78" s="48"/>
       <c r="D78" s="3" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E78" s="46"/>
       <c r="F78" s="42"/>
@@ -2167,7 +2173,7 @@
       <c r="B79" s="44"/>
       <c r="C79" s="48"/>
       <c r="D79" s="3" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E79" s="46"/>
       <c r="F79" s="42"/>
@@ -2176,7 +2182,7 @@
       <c r="B80" s="44"/>
       <c r="C80" s="48"/>
       <c r="D80" s="3" t="s">
-        <v>49</v>
+        <v>165</v>
       </c>
       <c r="E80" s="46"/>
       <c r="F80" s="42"/>
@@ -2184,26 +2190,26 @@
     <row r="81" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B81" s="44"/>
       <c r="C81" s="48"/>
-      <c r="D81" s="46"/>
+      <c r="D81" s="3" t="s">
+        <v>166</v>
+      </c>
       <c r="E81" s="46"/>
       <c r="F81" s="42"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B82" s="44"/>
       <c r="C82" s="48"/>
-      <c r="D82" s="46"/>
-      <c r="E82" s="6" t="s">
-        <v>231</v>
-      </c>
+      <c r="D82" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E82" s="46"/>
       <c r="F82" s="42"/>
     </row>
     <row r="83" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B83" s="44"/>
       <c r="C83" s="48"/>
       <c r="D83" s="46"/>
-      <c r="E83" s="6" t="s">
-        <v>223</v>
-      </c>
+      <c r="E83" s="46"/>
       <c r="F83" s="42"/>
     </row>
     <row r="84" spans="2:6" x14ac:dyDescent="0.3">
@@ -2211,7 +2217,7 @@
       <c r="C84" s="48"/>
       <c r="D84" s="46"/>
       <c r="E84" s="6" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="F84" s="42"/>
     </row>
@@ -2220,7 +2226,7 @@
       <c r="C85" s="48"/>
       <c r="D85" s="46"/>
       <c r="E85" s="6" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="F85" s="42"/>
     </row>
@@ -2229,7 +2235,7 @@
       <c r="C86" s="48"/>
       <c r="D86" s="46"/>
       <c r="E86" s="6" t="s">
-        <v>161</v>
+        <v>222</v>
       </c>
       <c r="F86" s="42"/>
     </row>
@@ -2238,7 +2244,7 @@
       <c r="C87" s="48"/>
       <c r="D87" s="46"/>
       <c r="E87" s="6" t="s">
-        <v>2</v>
+        <v>223</v>
       </c>
       <c r="F87" s="42"/>
     </row>
@@ -2246,15 +2252,17 @@
       <c r="B88" s="44"/>
       <c r="C88" s="48"/>
       <c r="D88" s="46"/>
-      <c r="E88" s="7"/>
+      <c r="E88" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="F88" s="42"/>
     </row>
     <row r="89" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B89" s="44"/>
       <c r="C89" s="48"/>
       <c r="D89" s="46"/>
-      <c r="E89" s="3" t="s">
-        <v>169</v>
+      <c r="E89" s="6" t="s">
+        <v>2</v>
       </c>
       <c r="F89" s="42"/>
     </row>
@@ -2262,9 +2270,7 @@
       <c r="B90" s="44"/>
       <c r="C90" s="48"/>
       <c r="D90" s="46"/>
-      <c r="E90" s="3" t="s">
-        <v>170</v>
-      </c>
+      <c r="E90" s="7"/>
       <c r="F90" s="42"/>
     </row>
     <row r="91" spans="2:6" x14ac:dyDescent="0.3">
@@ -2272,7 +2278,7 @@
       <c r="C91" s="48"/>
       <c r="D91" s="46"/>
       <c r="E91" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="F91" s="42"/>
     </row>
@@ -2281,7 +2287,7 @@
       <c r="C92" s="48"/>
       <c r="D92" s="46"/>
       <c r="E92" s="3" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F92" s="42"/>
     </row>
@@ -2290,7 +2296,7 @@
       <c r="C93" s="48"/>
       <c r="D93" s="46"/>
       <c r="E93" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="F93" s="42"/>
     </row>
@@ -2299,42 +2305,42 @@
       <c r="C94" s="48"/>
       <c r="D94" s="46"/>
       <c r="E94" s="3" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="F94" s="42"/>
     </row>
     <row r="95" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B95" s="44"/>
-      <c r="C95" s="47"/>
-      <c r="D95" s="47"/>
-      <c r="E95" s="47"/>
+      <c r="C95" s="48"/>
+      <c r="D95" s="46"/>
+      <c r="E95" s="3" t="s">
+        <v>171</v>
+      </c>
       <c r="F95" s="42"/>
     </row>
     <row r="96" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B96" s="44"/>
-      <c r="C96" s="48" t="s">
-        <v>230</v>
-      </c>
-      <c r="D96" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="E96" s="46"/>
+      <c r="C96" s="48"/>
+      <c r="D96" s="46"/>
+      <c r="E96" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="F96" s="42"/>
     </row>
     <row r="97" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B97" s="44"/>
-      <c r="C97" s="48"/>
-      <c r="D97" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="E97" s="46"/>
+      <c r="C97" s="47"/>
+      <c r="D97" s="47"/>
+      <c r="E97" s="47"/>
       <c r="F97" s="42"/>
     </row>
     <row r="98" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B98" s="44"/>
-      <c r="C98" s="48"/>
+      <c r="C98" s="48" t="s">
+        <v>228</v>
+      </c>
       <c r="D98" s="3" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="E98" s="46"/>
       <c r="F98" s="42"/>
@@ -2343,7 +2349,7 @@
       <c r="B99" s="44"/>
       <c r="C99" s="48"/>
       <c r="D99" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="E99" s="46"/>
       <c r="F99" s="42"/>
@@ -2352,7 +2358,7 @@
       <c r="B100" s="44"/>
       <c r="C100" s="48"/>
       <c r="D100" s="3" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="E100" s="46"/>
       <c r="F100" s="42"/>
@@ -2361,7 +2367,7 @@
       <c r="B101" s="44"/>
       <c r="C101" s="48"/>
       <c r="D101" s="3" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="E101" s="46"/>
       <c r="F101" s="42"/>
@@ -2370,7 +2376,7 @@
       <c r="B102" s="44"/>
       <c r="C102" s="48"/>
       <c r="D102" s="3" t="s">
-        <v>49</v>
+        <v>218</v>
       </c>
       <c r="E102" s="46"/>
       <c r="F102" s="42"/>
@@ -2378,26 +2384,26 @@
     <row r="103" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B103" s="44"/>
       <c r="C103" s="48"/>
-      <c r="D103" s="46"/>
+      <c r="D103" s="3" t="s">
+        <v>219</v>
+      </c>
       <c r="E103" s="46"/>
       <c r="F103" s="42"/>
     </row>
     <row r="104" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B104" s="44"/>
       <c r="C104" s="48"/>
-      <c r="D104" s="46"/>
-      <c r="E104" s="3" t="s">
-        <v>222</v>
-      </c>
+      <c r="D104" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E104" s="46"/>
       <c r="F104" s="42"/>
     </row>
     <row r="105" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B105" s="44"/>
       <c r="C105" s="48"/>
       <c r="D105" s="46"/>
-      <c r="E105" s="3" t="s">
-        <v>223</v>
-      </c>
+      <c r="E105" s="46"/>
       <c r="F105" s="42"/>
     </row>
     <row r="106" spans="2:6" x14ac:dyDescent="0.3">
@@ -2405,7 +2411,7 @@
       <c r="C106" s="48"/>
       <c r="D106" s="46"/>
       <c r="E106" s="3" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="F106" s="42"/>
     </row>
@@ -2414,7 +2420,7 @@
       <c r="C107" s="48"/>
       <c r="D107" s="46"/>
       <c r="E107" s="3" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="F107" s="42"/>
     </row>
@@ -2423,7 +2429,7 @@
       <c r="C108" s="48"/>
       <c r="D108" s="46"/>
       <c r="E108" s="3" t="s">
-        <v>161</v>
+        <v>222</v>
       </c>
       <c r="F108" s="42"/>
     </row>
@@ -2432,7 +2438,7 @@
       <c r="C109" s="48"/>
       <c r="D109" s="46"/>
       <c r="E109" s="3" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F109" s="42"/>
     </row>
@@ -2441,7 +2447,7 @@
       <c r="C110" s="48"/>
       <c r="D110" s="46"/>
       <c r="E110" s="3" t="s">
-        <v>2</v>
+        <v>159</v>
       </c>
       <c r="F110" s="42"/>
     </row>
@@ -2449,7 +2455,9 @@
       <c r="B111" s="44"/>
       <c r="C111" s="48"/>
       <c r="D111" s="46"/>
-      <c r="E111" s="7"/>
+      <c r="E111" s="3" t="s">
+        <v>224</v>
+      </c>
       <c r="F111" s="42"/>
     </row>
     <row r="112" spans="2:6" x14ac:dyDescent="0.3">
@@ -2457,7 +2465,7 @@
       <c r="C112" s="48"/>
       <c r="D112" s="46"/>
       <c r="E112" s="3" t="s">
-        <v>227</v>
+        <v>2</v>
       </c>
       <c r="F112" s="42"/>
     </row>
@@ -2465,9 +2473,7 @@
       <c r="B113" s="44"/>
       <c r="C113" s="48"/>
       <c r="D113" s="46"/>
-      <c r="E113" s="3" t="s">
-        <v>232</v>
-      </c>
+      <c r="E113" s="7"/>
       <c r="F113" s="42"/>
     </row>
     <row r="114" spans="2:6" x14ac:dyDescent="0.3">
@@ -2475,7 +2481,7 @@
       <c r="C114" s="48"/>
       <c r="D114" s="46"/>
       <c r="E114" s="3" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="F114" s="42"/>
     </row>
@@ -2484,7 +2490,7 @@
       <c r="C115" s="48"/>
       <c r="D115" s="46"/>
       <c r="E115" s="3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F115" s="42"/>
     </row>
@@ -2493,39 +2499,57 @@
       <c r="C116" s="48"/>
       <c r="D116" s="46"/>
       <c r="E116" s="3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F116" s="42"/>
     </row>
     <row r="117" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B117" s="45"/>
-      <c r="C117" s="8"/>
-      <c r="D117" s="8"/>
-      <c r="E117" s="8"/>
-      <c r="F117" s="43"/>
+      <c r="B117" s="44"/>
+      <c r="C117" s="48"/>
+      <c r="D117" s="46"/>
+      <c r="E117" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="F117" s="42"/>
+    </row>
+    <row r="118" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B118" s="44"/>
+      <c r="C118" s="48"/>
+      <c r="D118" s="46"/>
+      <c r="E118" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="F118" s="42"/>
+    </row>
+    <row r="119" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B119" s="45"/>
+      <c r="C119" s="8"/>
+      <c r="D119" s="8"/>
+      <c r="E119" s="8"/>
+      <c r="F119" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="E12:E19"/>
-    <mergeCell ref="E75:E80"/>
-    <mergeCell ref="C74:E74"/>
-    <mergeCell ref="D103:E103"/>
+    <mergeCell ref="E77:E82"/>
+    <mergeCell ref="C76:E76"/>
+    <mergeCell ref="D105:E105"/>
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="D20:E20"/>
     <mergeCell ref="B2:F2"/>
-    <mergeCell ref="F3:F117"/>
-    <mergeCell ref="B3:B117"/>
-    <mergeCell ref="D104:D116"/>
-    <mergeCell ref="C95:E95"/>
-    <mergeCell ref="C96:C116"/>
+    <mergeCell ref="F3:F119"/>
+    <mergeCell ref="B3:B119"/>
+    <mergeCell ref="D106:D118"/>
+    <mergeCell ref="C97:E97"/>
+    <mergeCell ref="C98:C118"/>
     <mergeCell ref="D4:E10"/>
     <mergeCell ref="C11:E11"/>
-    <mergeCell ref="D81:E81"/>
-    <mergeCell ref="D82:D94"/>
-    <mergeCell ref="E96:E102"/>
-    <mergeCell ref="C12:C73"/>
-    <mergeCell ref="D21:D73"/>
-    <mergeCell ref="C75:C94"/>
+    <mergeCell ref="D83:E83"/>
+    <mergeCell ref="D84:D96"/>
+    <mergeCell ref="E98:E104"/>
+    <mergeCell ref="C12:C75"/>
+    <mergeCell ref="D21:D75"/>
+    <mergeCell ref="C77:C96"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2566,7 +2590,7 @@
     <row r="3" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B3" s="44"/>
       <c r="C3" s="65" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D3" s="65"/>
       <c r="E3" s="65"/>
@@ -2618,14 +2642,14 @@
         <v>12</v>
       </c>
       <c r="I5" s="53" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="J5" s="54"/>
       <c r="K5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="L5" s="56" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="M5" s="57"/>
       <c r="N5" s="58"/>
@@ -2645,10 +2669,10 @@
         <v>62</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I6" s="53" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="J6" s="54"/>
       <c r="K6" s="3" t="s">
@@ -2673,7 +2697,7 @@
         <v>45</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="I7" s="53" t="s">
         <v>60</v>
@@ -2706,7 +2730,7 @@
     <row r="9" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B9" s="44"/>
       <c r="C9" s="65" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D9" s="65"/>
       <c r="E9" s="65"/>
@@ -2733,13 +2757,13 @@
         <v>17</v>
       </c>
       <c r="F10" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="H10" s="3" t="s">
         <v>175</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="I10" s="3">
         <v>142536748</v>
@@ -2751,10 +2775,10 @@
         <v>23</v>
       </c>
       <c r="L10" s="12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="M10" s="55" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="N10" s="55"/>
       <c r="O10" s="42"/>
@@ -2771,13 +2795,13 @@
         <v>19</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I11" s="3">
         <v>142536747</v>
@@ -2789,7 +2813,7 @@
         <v>23</v>
       </c>
       <c r="L11" s="12" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M11" s="55"/>
       <c r="N11" s="55"/>
@@ -2807,13 +2831,13 @@
         <v>20</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I12" s="3">
         <v>142536746</v>
@@ -2825,7 +2849,7 @@
         <v>24</v>
       </c>
       <c r="L12" s="12" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="M12" s="55"/>
       <c r="N12" s="55"/>
@@ -2843,13 +2867,13 @@
         <v>30</v>
       </c>
       <c r="F13" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="H13" s="3" t="s">
         <v>184</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>186</v>
       </c>
       <c r="I13" s="3">
         <v>142536745</v>
@@ -2861,7 +2885,7 @@
         <v>23</v>
       </c>
       <c r="L13" s="12" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="M13" s="55"/>
       <c r="N13" s="55"/>
@@ -2879,13 +2903,13 @@
         <v>36</v>
       </c>
       <c r="F14" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="H14" s="3" t="s">
         <v>187</v>
-      </c>
-      <c r="G14" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>189</v>
       </c>
       <c r="I14" s="3">
         <v>142536744</v>
@@ -2897,7 +2921,7 @@
         <v>23</v>
       </c>
       <c r="L14" s="12" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="M14" s="55"/>
       <c r="N14" s="55"/>
@@ -2915,13 +2939,13 @@
         <v>39</v>
       </c>
       <c r="F15" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="H15" s="3" t="s">
         <v>190</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>192</v>
       </c>
       <c r="I15" s="3">
         <v>142536743</v>
@@ -2933,7 +2957,7 @@
         <v>23</v>
       </c>
       <c r="L15" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="M15" s="55"/>
       <c r="N15" s="55"/>
@@ -2946,28 +2970,28 @@
         <v>16</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F16" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="H16" s="3" t="s">
         <v>193</v>
-      </c>
-      <c r="G16" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>195</v>
       </c>
       <c r="I16" s="3">
         <v>142536742</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="K16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="L16" s="12" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="M16" s="55"/>
       <c r="N16" s="55"/>
@@ -2992,7 +3016,7 @@
     <row r="18" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B18" s="44"/>
       <c r="C18" s="65" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D18" s="65"/>
       <c r="E18" s="65"/>
@@ -3025,7 +3049,7 @@
         <v>91</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="I19" s="3">
         <v>258963147</v>
@@ -3037,10 +3061,10 @@
         <v>23</v>
       </c>
       <c r="L19" s="12" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="M19" s="55" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="N19" s="55"/>
       <c r="O19" s="42"/>
@@ -3063,7 +3087,7 @@
         <v>92</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I20" s="3">
         <v>241536789</v>
@@ -3075,7 +3099,7 @@
         <v>23</v>
       </c>
       <c r="L20" s="12" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="M20" s="55"/>
       <c r="N20" s="55"/>
@@ -3099,7 +3123,7 @@
         <v>93</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="I21" s="3">
         <v>267489123</v>
@@ -3111,7 +3135,7 @@
         <v>23</v>
       </c>
       <c r="L21" s="12" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="M21" s="55"/>
       <c r="N21" s="55"/>
@@ -3135,7 +3159,7 @@
         <v>94</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I22" s="13">
         <v>233654789</v>
@@ -3147,7 +3171,7 @@
         <v>23</v>
       </c>
       <c r="L22" s="15" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="M22" s="55"/>
       <c r="N22" s="55"/>
@@ -3171,7 +3195,7 @@
         <v>95</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I23" s="16">
         <v>259874123</v>
@@ -3183,7 +3207,7 @@
         <v>23</v>
       </c>
       <c r="L23" s="18" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="M23" s="55"/>
       <c r="N23" s="55"/>
@@ -3207,7 +3231,7 @@
         <v>96</v>
       </c>
       <c r="H24" s="21" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="I24" s="19">
         <v>210456789</v>
@@ -3219,7 +3243,7 @@
         <v>23</v>
       </c>
       <c r="L24" s="22" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="M24" s="55"/>
       <c r="N24" s="55"/>
@@ -3243,7 +3267,7 @@
         <v>97</v>
       </c>
       <c r="H25" s="24" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="I25" s="23">
         <v>225147896</v>
@@ -3252,10 +3276,10 @@
         <v>74</v>
       </c>
       <c r="K25" s="23" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L25" s="25" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M25" s="55"/>
       <c r="N25" s="55"/>
@@ -3279,7 +3303,7 @@
         <v>98</v>
       </c>
       <c r="H26" s="24" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I26" s="23">
         <v>278963254</v>
@@ -3288,10 +3312,10 @@
         <v>18</v>
       </c>
       <c r="K26" s="23" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L26" s="25" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="M26" s="55"/>
       <c r="N26" s="55"/>
@@ -3317,7 +3341,7 @@
       </c>
       <c r="K27" s="3"/>
       <c r="L27" s="12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M27" s="55"/>
       <c r="N27" s="55"/>
@@ -3343,7 +3367,7 @@
       </c>
       <c r="K28" s="3"/>
       <c r="L28" s="12" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="M28" s="55"/>
       <c r="N28" s="55"/>
@@ -3369,7 +3393,7 @@
       </c>
       <c r="K29" s="3"/>
       <c r="L29" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="M29" s="55"/>
       <c r="N29" s="55"/>
@@ -3395,7 +3419,7 @@
       </c>
       <c r="K30" s="3"/>
       <c r="L30" s="12" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="M30" s="55"/>
       <c r="N30" s="55"/>
@@ -3421,7 +3445,7 @@
       </c>
       <c r="K31" s="3"/>
       <c r="L31" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="M31" s="55"/>
       <c r="N31" s="55"/>
@@ -3447,7 +3471,7 @@
       </c>
       <c r="K32" s="3"/>
       <c r="L32" s="12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="M32" s="55"/>
       <c r="N32" s="55"/>
@@ -3473,7 +3497,7 @@
       </c>
       <c r="K33" s="3"/>
       <c r="L33" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="M33" s="55"/>
       <c r="N33" s="55"/>
@@ -3591,7 +3615,7 @@
       </c>
       <c r="I3" s="42"/>
       <c r="J3" s="67" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="K3" s="68"/>
       <c r="L3" s="69"/>
@@ -3599,19 +3623,19 @@
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B4" s="44"/>
       <c r="C4" s="32" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>25</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H4" s="3">
         <v>2</v>
@@ -3621,7 +3645,7 @@
         <v>17</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="L4" s="3" t="s">
         <v>23</v>
@@ -3640,7 +3664,7 @@
         <v>19</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>23</v>
@@ -3649,19 +3673,19 @@
     <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B6" s="44"/>
       <c r="C6" s="72" t="s">
-        <v>103</v>
+        <v>243</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>100</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F6" s="48" t="s">
         <v>25</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H6" s="3">
         <v>2</v>
@@ -3671,7 +3695,7 @@
         <v>20</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="L6" s="3" t="s">
         <v>24</v>
@@ -3686,7 +3710,7 @@
       </c>
       <c r="F7" s="48"/>
       <c r="G7" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H7" s="3">
         <v>1</v>
@@ -3696,7 +3720,7 @@
         <v>30</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="L7" s="3" t="s">
         <v>23</v>
@@ -3707,11 +3731,11 @@
       <c r="C8" s="72"/>
       <c r="D8" s="48"/>
       <c r="E8" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F8" s="48"/>
       <c r="G8" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H8" s="3">
         <v>1</v>
@@ -3721,7 +3745,7 @@
         <v>36</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="L8" s="3" t="s">
         <v>23</v>
@@ -3740,7 +3764,7 @@
         <v>39</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>23</v>
@@ -3751,23 +3775,23 @@
       <c r="C10" s="72"/>
       <c r="D10" s="48"/>
       <c r="E10" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F10" s="48" t="s">
         <v>26</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H10" s="3">
         <v>2</v>
       </c>
       <c r="I10" s="42"/>
       <c r="J10" s="33" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>23</v>
@@ -3782,7 +3806,7 @@
       </c>
       <c r="F11" s="48"/>
       <c r="G11" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H11" s="3">
         <v>1</v>
@@ -3810,7 +3834,7 @@
         <v>35</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H13" s="3">
         <v>1</v>
@@ -3831,16 +3855,16 @@
       <c r="B15" s="44"/>
       <c r="C15" s="72"/>
       <c r="D15" s="48" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E15" s="31" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>25</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H15" s="3">
         <v>2</v>
@@ -3862,13 +3886,13 @@
       <c r="C17" s="72"/>
       <c r="D17" s="48"/>
       <c r="E17" s="31" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F17" s="48" t="s">
         <v>26</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H17" s="3">
         <v>2</v>
@@ -3880,11 +3904,11 @@
       <c r="C18" s="72"/>
       <c r="D18" s="48"/>
       <c r="E18" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F18" s="48"/>
       <c r="G18" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H18" s="3">
         <v>1</v>
@@ -3906,13 +3930,13 @@
       <c r="C20" s="72"/>
       <c r="D20" s="48"/>
       <c r="E20" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>35</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H20" s="3">
         <v>1</v>
@@ -3933,16 +3957,16 @@
       <c r="B22" s="44"/>
       <c r="C22" s="72"/>
       <c r="D22" s="48" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E22" s="31" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F22" s="48" t="s">
         <v>25</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H22" s="3">
         <v>2</v>
@@ -3954,11 +3978,11 @@
       <c r="C23" s="72"/>
       <c r="D23" s="48"/>
       <c r="E23" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F23" s="48"/>
       <c r="G23" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H23" s="3">
         <v>1</v>
@@ -3974,7 +3998,7 @@
       </c>
       <c r="F24" s="48"/>
       <c r="G24" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H24" s="3">
         <v>1</v>
@@ -3986,11 +4010,11 @@
       <c r="C25" s="72"/>
       <c r="D25" s="48"/>
       <c r="E25" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F25" s="48"/>
       <c r="G25" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H25" s="3">
         <v>1</v>
@@ -4006,7 +4030,7 @@
       </c>
       <c r="F26" s="48"/>
       <c r="G26" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H26" s="3">
         <v>1</v>
@@ -4028,13 +4052,13 @@
       <c r="C28" s="72"/>
       <c r="D28" s="48"/>
       <c r="E28" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H28" s="3">
         <v>1</v>
@@ -4069,7 +4093,7 @@
         <v>35</v>
       </c>
       <c r="L30" s="34" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="M30" s="34">
         <v>1</v>
@@ -4092,13 +4116,13 @@
         <v>101</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>25</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H32" s="3">
         <v>3</v>
@@ -4118,10 +4142,10 @@
     <row r="34" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B34" s="44"/>
       <c r="C34" s="32" t="s">
-        <v>102</v>
+        <v>244</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="4"/>

--- a/Testes.xlsx
+++ b/Testes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\utilizador\Documents\CTESP\4semestre\LP2\ProjetoTesteLP2\TrabalhoTesteLP2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C70B6BD-CBE6-4EE7-9321-6FC1F3DDEE64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCE88386-85CE-4E78-89A9-B6D562879437}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{17050BBC-8C72-4C7C-BB9E-52ED50A4B6E1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{17050BBC-8C72-4C7C-BB9E-52ED50A4B6E1}"/>
   </bookViews>
   <sheets>
     <sheet name="Menus" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="244">
   <si>
     <t>1 - Adicionar Departamento</t>
   </si>
@@ -754,16 +754,13 @@
     <t>7 - Listar Cursos por Departamento</t>
   </si>
   <si>
-    <t>4. Ativar/Inativar Departamento</t>
-  </si>
-  <si>
-    <t>5. Alterar Curso de Departamento</t>
-  </si>
-  <si>
     <t>[ATIVO] DEN : Departamento de Engenharia</t>
   </si>
   <si>
     <t>[ATIVO] DCI : Departamento de Ciencias</t>
+  </si>
+  <si>
+    <t>8 - Alterar Curso de Departamento</t>
   </si>
 </sst>
 </file>
@@ -1700,7 +1697,7 @@
       <c r="C25" s="50"/>
       <c r="D25" s="46"/>
       <c r="E25" s="3" t="s">
-        <v>241</v>
+        <v>51</v>
       </c>
       <c r="F25" s="42"/>
     </row>
@@ -1709,7 +1706,7 @@
       <c r="C26" s="50"/>
       <c r="D26" s="46"/>
       <c r="E26" s="3" t="s">
-        <v>242</v>
+        <v>2</v>
       </c>
       <c r="F26" s="42"/>
     </row>
@@ -1717,16 +1714,16 @@
       <c r="B27" s="44"/>
       <c r="C27" s="50"/>
       <c r="D27" s="46"/>
-      <c r="E27" s="3" t="s">
-        <v>2</v>
-      </c>
+      <c r="E27" s="7"/>
       <c r="F27" s="42"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B28" s="44"/>
       <c r="C28" s="50"/>
       <c r="D28" s="46"/>
-      <c r="E28" s="7"/>
+      <c r="E28" s="3" t="s">
+        <v>144</v>
+      </c>
       <c r="F28" s="42"/>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.3">
@@ -1734,7 +1731,7 @@
       <c r="C29" s="50"/>
       <c r="D29" s="46"/>
       <c r="E29" s="3" t="s">
-        <v>144</v>
+        <v>3</v>
       </c>
       <c r="F29" s="42"/>
     </row>
@@ -1743,7 +1740,7 @@
       <c r="C30" s="50"/>
       <c r="D30" s="46"/>
       <c r="E30" s="3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F30" s="42"/>
     </row>
@@ -1752,7 +1749,7 @@
       <c r="C31" s="50"/>
       <c r="D31" s="46"/>
       <c r="E31" s="3" t="s">
-        <v>4</v>
+        <v>145</v>
       </c>
       <c r="F31" s="42"/>
     </row>
@@ -1761,7 +1758,7 @@
       <c r="C32" s="50"/>
       <c r="D32" s="46"/>
       <c r="E32" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F32" s="42"/>
     </row>
@@ -1770,7 +1767,7 @@
       <c r="C33" s="50"/>
       <c r="D33" s="46"/>
       <c r="E33" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F33" s="42"/>
     </row>
@@ -1779,7 +1776,7 @@
       <c r="C34" s="50"/>
       <c r="D34" s="46"/>
       <c r="E34" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F34" s="42"/>
     </row>
@@ -1788,7 +1785,7 @@
       <c r="C35" s="50"/>
       <c r="D35" s="46"/>
       <c r="E35" s="3" t="s">
-        <v>148</v>
+        <v>240</v>
       </c>
       <c r="F35" s="42"/>
     </row>
@@ -1797,7 +1794,7 @@
       <c r="C36" s="50"/>
       <c r="D36" s="46"/>
       <c r="E36" s="3" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="F36" s="42"/>
     </row>
@@ -3673,7 +3670,7 @@
     <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B6" s="44"/>
       <c r="C6" s="72" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>100</v>
@@ -4142,7 +4139,7 @@
     <row r="34" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B34" s="44"/>
       <c r="C34" s="32" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>200</v>

--- a/Testes.xlsx
+++ b/Testes.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\utilizador\Documents\CTESP\4semestre\LP2\ProjetoTesteLP2\TrabalhoTesteLP2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCE88386-85CE-4E78-89A9-B6D562879437}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{937A0731-2BA4-49B8-8D44-8351DC4F522F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{17050BBC-8C72-4C7C-BB9E-52ED50A4B6E1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{17050BBC-8C72-4C7C-BB9E-52ED50A4B6E1}"/>
   </bookViews>
   <sheets>
     <sheet name="Menus" sheetId="1" r:id="rId1"/>
-    <sheet name="Utilizadores" sheetId="2" r:id="rId2"/>
-    <sheet name="Escola" sheetId="3" r:id="rId3"/>
+    <sheet name="Escola" sheetId="3" r:id="rId2"/>
+    <sheet name="Utilizadores" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -2554,6 +2554,632 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F3342F1-B6E7-460B-9E26-5A8DC1C1AFB6}">
+  <dimension ref="B2:M35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="4" width="49.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="37.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.5546875" customWidth="1"/>
+    <col min="11" max="11" width="4.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B2" s="39"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="41"/>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B3" s="44"/>
+      <c r="C3" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" s="42"/>
+      <c r="J3" s="67" t="s">
+        <v>235</v>
+      </c>
+      <c r="K3" s="68"/>
+      <c r="L3" s="69"/>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B4" s="44"/>
+      <c r="C4" s="32" t="s">
+        <v>238</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H4" s="3">
+        <v>2</v>
+      </c>
+      <c r="I4" s="42"/>
+      <c r="J4" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B5" s="44"/>
+      <c r="C5" s="71"/>
+      <c r="D5" s="71"/>
+      <c r="E5" s="71"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="71"/>
+      <c r="H5" s="71"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B6" s="44"/>
+      <c r="C6" s="72" t="s">
+        <v>241</v>
+      </c>
+      <c r="D6" s="48" t="s">
+        <v>100</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="F6" s="48" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H6" s="3">
+        <v>2</v>
+      </c>
+      <c r="I6" s="42"/>
+      <c r="J6" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B7" s="44"/>
+      <c r="C7" s="72"/>
+      <c r="D7" s="48"/>
+      <c r="E7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" s="48"/>
+      <c r="G7" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H7" s="3">
+        <v>1</v>
+      </c>
+      <c r="I7" s="42"/>
+      <c r="J7" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B8" s="44"/>
+      <c r="C8" s="72"/>
+      <c r="D8" s="48"/>
+      <c r="E8" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="F8" s="48"/>
+      <c r="G8" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H8" s="3">
+        <v>1</v>
+      </c>
+      <c r="I8" s="42"/>
+      <c r="J8" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B9" s="44"/>
+      <c r="C9" s="72"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="46"/>
+      <c r="G9" s="46"/>
+      <c r="H9" s="46"/>
+      <c r="I9" s="42"/>
+      <c r="J9" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B10" s="44"/>
+      <c r="C10" s="72"/>
+      <c r="D10" s="48"/>
+      <c r="E10" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="F10" s="48" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H10" s="3">
+        <v>2</v>
+      </c>
+      <c r="I10" s="42"/>
+      <c r="J10" s="33" t="s">
+        <v>105</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B11" s="44"/>
+      <c r="C11" s="72"/>
+      <c r="D11" s="48"/>
+      <c r="E11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" s="48"/>
+      <c r="G11" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H11" s="3">
+        <v>1</v>
+      </c>
+      <c r="I11" s="42"/>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B12" s="44"/>
+      <c r="C12" s="72"/>
+      <c r="D12" s="48"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="46"/>
+      <c r="G12" s="46"/>
+      <c r="H12" s="46"/>
+      <c r="I12" s="42"/>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B13" s="44"/>
+      <c r="C13" s="72"/>
+      <c r="D13" s="48"/>
+      <c r="E13" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H13" s="3">
+        <v>1</v>
+      </c>
+      <c r="I13" s="42"/>
+    </row>
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B14" s="44"/>
+      <c r="C14" s="72"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="47"/>
+      <c r="F14" s="47"/>
+      <c r="G14" s="47"/>
+      <c r="H14" s="47"/>
+      <c r="I14" s="42"/>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B15" s="44"/>
+      <c r="C15" s="72"/>
+      <c r="D15" s="48" t="s">
+        <v>198</v>
+      </c>
+      <c r="E15" s="31" t="s">
+        <v>195</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H15" s="3">
+        <v>2</v>
+      </c>
+      <c r="I15" s="42"/>
+    </row>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B16" s="44"/>
+      <c r="C16" s="72"/>
+      <c r="D16" s="48"/>
+      <c r="E16" s="46"/>
+      <c r="F16" s="46"/>
+      <c r="G16" s="46"/>
+      <c r="H16" s="46"/>
+      <c r="I16" s="42"/>
+    </row>
+    <row r="17" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B17" s="44"/>
+      <c r="C17" s="72"/>
+      <c r="D17" s="48"/>
+      <c r="E17" s="31" t="s">
+        <v>196</v>
+      </c>
+      <c r="F17" s="48" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H17" s="3">
+        <v>2</v>
+      </c>
+      <c r="I17" s="42"/>
+    </row>
+    <row r="18" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B18" s="44"/>
+      <c r="C18" s="72"/>
+      <c r="D18" s="48"/>
+      <c r="E18" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="F18" s="48"/>
+      <c r="G18" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="H18" s="3">
+        <v>1</v>
+      </c>
+      <c r="I18" s="42"/>
+    </row>
+    <row r="19" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B19" s="44"/>
+      <c r="C19" s="72"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="46"/>
+      <c r="F19" s="46"/>
+      <c r="G19" s="46"/>
+      <c r="H19" s="46"/>
+      <c r="I19" s="42"/>
+    </row>
+    <row r="20" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B20" s="44"/>
+      <c r="C20" s="72"/>
+      <c r="D20" s="48"/>
+      <c r="E20" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="H20" s="3">
+        <v>1</v>
+      </c>
+      <c r="I20" s="42"/>
+    </row>
+    <row r="21" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B21" s="44"/>
+      <c r="C21" s="72"/>
+      <c r="D21" s="47"/>
+      <c r="E21" s="47"/>
+      <c r="F21" s="47"/>
+      <c r="G21" s="47"/>
+      <c r="H21" s="47"/>
+      <c r="I21" s="42"/>
+    </row>
+    <row r="22" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B22" s="44"/>
+      <c r="C22" s="72"/>
+      <c r="D22" s="48" t="s">
+        <v>199</v>
+      </c>
+      <c r="E22" s="31" t="s">
+        <v>195</v>
+      </c>
+      <c r="F22" s="48" t="s">
+        <v>25</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H22" s="3">
+        <v>2</v>
+      </c>
+      <c r="I22" s="42"/>
+    </row>
+    <row r="23" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B23" s="44"/>
+      <c r="C23" s="72"/>
+      <c r="D23" s="48"/>
+      <c r="E23" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="F23" s="48"/>
+      <c r="G23" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="H23" s="3">
+        <v>1</v>
+      </c>
+      <c r="I23" s="42"/>
+    </row>
+    <row r="24" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B24" s="44"/>
+      <c r="C24" s="72"/>
+      <c r="D24" s="48"/>
+      <c r="E24" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F24" s="48"/>
+      <c r="G24" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="H24" s="3">
+        <v>1</v>
+      </c>
+      <c r="I24" s="42"/>
+    </row>
+    <row r="25" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B25" s="44"/>
+      <c r="C25" s="72"/>
+      <c r="D25" s="48"/>
+      <c r="E25" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F25" s="48"/>
+      <c r="G25" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="H25" s="3">
+        <v>1</v>
+      </c>
+      <c r="I25" s="42"/>
+    </row>
+    <row r="26" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B26" s="44"/>
+      <c r="C26" s="72"/>
+      <c r="D26" s="48"/>
+      <c r="E26" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F26" s="48"/>
+      <c r="G26" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="H26" s="3">
+        <v>1</v>
+      </c>
+      <c r="I26" s="42"/>
+    </row>
+    <row r="27" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B27" s="44"/>
+      <c r="C27" s="72"/>
+      <c r="D27" s="48"/>
+      <c r="E27" s="46"/>
+      <c r="F27" s="46"/>
+      <c r="G27" s="46"/>
+      <c r="H27" s="46"/>
+      <c r="I27" s="42"/>
+    </row>
+    <row r="28" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B28" s="44"/>
+      <c r="C28" s="72"/>
+      <c r="D28" s="48"/>
+      <c r="E28" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="H28" s="3">
+        <v>1</v>
+      </c>
+      <c r="I28" s="42"/>
+    </row>
+    <row r="29" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B29" s="44"/>
+      <c r="C29" s="72"/>
+      <c r="D29" s="48"/>
+      <c r="E29" s="46"/>
+      <c r="F29" s="46"/>
+      <c r="G29" s="46"/>
+      <c r="H29" s="46"/>
+      <c r="I29" s="42"/>
+    </row>
+    <row r="30" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B30" s="44"/>
+      <c r="C30" s="72"/>
+      <c r="D30" s="48"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="42"/>
+      <c r="J30" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="K30" s="35" t="s">
+        <v>35</v>
+      </c>
+      <c r="L30" s="34" t="s">
+        <v>188</v>
+      </c>
+      <c r="M30" s="34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B31" s="44"/>
+      <c r="C31" s="72"/>
+      <c r="D31" s="47"/>
+      <c r="E31" s="47"/>
+      <c r="F31" s="47"/>
+      <c r="G31" s="47"/>
+      <c r="H31" s="47"/>
+      <c r="I31" s="42"/>
+    </row>
+    <row r="32" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B32" s="44"/>
+      <c r="C32" s="72"/>
+      <c r="D32" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="H32" s="3">
+        <v>3</v>
+      </c>
+      <c r="I32" s="42"/>
+    </row>
+    <row r="33" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B33" s="44"/>
+      <c r="C33" s="70"/>
+      <c r="D33" s="70"/>
+      <c r="E33" s="70"/>
+      <c r="F33" s="70"/>
+      <c r="G33" s="70"/>
+      <c r="H33" s="70"/>
+      <c r="I33" s="42"/>
+    </row>
+    <row r="34" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B34" s="44"/>
+      <c r="C34" s="32" t="s">
+        <v>242</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="E34" s="3"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="42"/>
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B35" s="45"/>
+      <c r="C35" s="52"/>
+      <c r="D35" s="52"/>
+      <c r="E35" s="52"/>
+      <c r="F35" s="52"/>
+      <c r="G35" s="52"/>
+      <c r="H35" s="52"/>
+      <c r="I35" s="43"/>
+    </row>
+  </sheetData>
+  <mergeCells count="24">
+    <mergeCell ref="C6:C32"/>
+    <mergeCell ref="E27:H27"/>
+    <mergeCell ref="E29:H29"/>
+    <mergeCell ref="E9:H9"/>
+    <mergeCell ref="E12:H12"/>
+    <mergeCell ref="D6:D13"/>
+    <mergeCell ref="D15:D20"/>
+    <mergeCell ref="D22:D30"/>
+    <mergeCell ref="J3:L3"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B35:I35"/>
+    <mergeCell ref="B3:B34"/>
+    <mergeCell ref="I3:I34"/>
+    <mergeCell ref="C33:H33"/>
+    <mergeCell ref="D31:H31"/>
+    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="F22:F26"/>
+    <mergeCell ref="E19:H19"/>
+    <mergeCell ref="E16:H16"/>
+    <mergeCell ref="C5:H5"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="D21:H21"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F6FFC68-BC6E-45A7-9925-0DFE4309B06B}">
   <dimension ref="B2:O34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3563,630 +4189,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId23"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F3342F1-B6E7-460B-9E26-5A8DC1C1AFB6}">
-  <dimension ref="B2:M35"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="3" max="4" width="49.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="37.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.5546875" customWidth="1"/>
-    <col min="11" max="11" width="4.5546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="39"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="41"/>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B3" s="44"/>
-      <c r="C3" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I3" s="42"/>
-      <c r="J3" s="67" t="s">
-        <v>235</v>
-      </c>
-      <c r="K3" s="68"/>
-      <c r="L3" s="69"/>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="44"/>
-      <c r="C4" s="32" t="s">
-        <v>238</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H4" s="3">
-        <v>2</v>
-      </c>
-      <c r="I4" s="42"/>
-      <c r="J4" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B5" s="44"/>
-      <c r="C5" s="71"/>
-      <c r="D5" s="71"/>
-      <c r="E5" s="71"/>
-      <c r="F5" s="71"/>
-      <c r="G5" s="71"/>
-      <c r="H5" s="71"/>
-      <c r="I5" s="42"/>
-      <c r="J5" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B6" s="44"/>
-      <c r="C6" s="72" t="s">
-        <v>241</v>
-      </c>
-      <c r="D6" s="48" t="s">
-        <v>100</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="F6" s="48" t="s">
-        <v>25</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H6" s="3">
-        <v>2</v>
-      </c>
-      <c r="I6" s="42"/>
-      <c r="J6" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B7" s="44"/>
-      <c r="C7" s="72"/>
-      <c r="D7" s="48"/>
-      <c r="E7" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F7" s="48"/>
-      <c r="G7" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H7" s="3">
-        <v>1</v>
-      </c>
-      <c r="I7" s="42"/>
-      <c r="J7" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B8" s="44"/>
-      <c r="C8" s="72"/>
-      <c r="D8" s="48"/>
-      <c r="E8" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="F8" s="48"/>
-      <c r="G8" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H8" s="3">
-        <v>1</v>
-      </c>
-      <c r="I8" s="42"/>
-      <c r="J8" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B9" s="44"/>
-      <c r="C9" s="72"/>
-      <c r="D9" s="48"/>
-      <c r="E9" s="46"/>
-      <c r="F9" s="46"/>
-      <c r="G9" s="46"/>
-      <c r="H9" s="46"/>
-      <c r="I9" s="42"/>
-      <c r="J9" s="33" t="s">
-        <v>39</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B10" s="44"/>
-      <c r="C10" s="72"/>
-      <c r="D10" s="48"/>
-      <c r="E10" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="F10" s="48" t="s">
-        <v>26</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H10" s="3">
-        <v>2</v>
-      </c>
-      <c r="I10" s="42"/>
-      <c r="J10" s="33" t="s">
-        <v>105</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B11" s="44"/>
-      <c r="C11" s="72"/>
-      <c r="D11" s="48"/>
-      <c r="E11" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F11" s="48"/>
-      <c r="G11" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="H11" s="3">
-        <v>1</v>
-      </c>
-      <c r="I11" s="42"/>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B12" s="44"/>
-      <c r="C12" s="72"/>
-      <c r="D12" s="48"/>
-      <c r="E12" s="46"/>
-      <c r="F12" s="46"/>
-      <c r="G12" s="46"/>
-      <c r="H12" s="46"/>
-      <c r="I12" s="42"/>
-    </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B13" s="44"/>
-      <c r="C13" s="72"/>
-      <c r="D13" s="48"/>
-      <c r="E13" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="H13" s="3">
-        <v>1</v>
-      </c>
-      <c r="I13" s="42"/>
-    </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B14" s="44"/>
-      <c r="C14" s="72"/>
-      <c r="D14" s="47"/>
-      <c r="E14" s="47"/>
-      <c r="F14" s="47"/>
-      <c r="G14" s="47"/>
-      <c r="H14" s="47"/>
-      <c r="I14" s="42"/>
-    </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B15" s="44"/>
-      <c r="C15" s="72"/>
-      <c r="D15" s="48" t="s">
-        <v>198</v>
-      </c>
-      <c r="E15" s="31" t="s">
-        <v>195</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H15" s="3">
-        <v>2</v>
-      </c>
-      <c r="I15" s="42"/>
-    </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B16" s="44"/>
-      <c r="C16" s="72"/>
-      <c r="D16" s="48"/>
-      <c r="E16" s="46"/>
-      <c r="F16" s="46"/>
-      <c r="G16" s="46"/>
-      <c r="H16" s="46"/>
-      <c r="I16" s="42"/>
-    </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B17" s="44"/>
-      <c r="C17" s="72"/>
-      <c r="D17" s="48"/>
-      <c r="E17" s="31" t="s">
-        <v>196</v>
-      </c>
-      <c r="F17" s="48" t="s">
-        <v>26</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H17" s="3">
-        <v>2</v>
-      </c>
-      <c r="I17" s="42"/>
-    </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B18" s="44"/>
-      <c r="C18" s="72"/>
-      <c r="D18" s="48"/>
-      <c r="E18" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="F18" s="48"/>
-      <c r="G18" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="H18" s="3">
-        <v>1</v>
-      </c>
-      <c r="I18" s="42"/>
-    </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B19" s="44"/>
-      <c r="C19" s="72"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="46"/>
-      <c r="F19" s="46"/>
-      <c r="G19" s="46"/>
-      <c r="H19" s="46"/>
-      <c r="I19" s="42"/>
-    </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B20" s="44"/>
-      <c r="C20" s="72"/>
-      <c r="D20" s="48"/>
-      <c r="E20" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="H20" s="3">
-        <v>1</v>
-      </c>
-      <c r="I20" s="42"/>
-    </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B21" s="44"/>
-      <c r="C21" s="72"/>
-      <c r="D21" s="47"/>
-      <c r="E21" s="47"/>
-      <c r="F21" s="47"/>
-      <c r="G21" s="47"/>
-      <c r="H21" s="47"/>
-      <c r="I21" s="42"/>
-    </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B22" s="44"/>
-      <c r="C22" s="72"/>
-      <c r="D22" s="48" t="s">
-        <v>199</v>
-      </c>
-      <c r="E22" s="31" t="s">
-        <v>195</v>
-      </c>
-      <c r="F22" s="48" t="s">
-        <v>25</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H22" s="3">
-        <v>2</v>
-      </c>
-      <c r="I22" s="42"/>
-    </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B23" s="44"/>
-      <c r="C23" s="72"/>
-      <c r="D23" s="48"/>
-      <c r="E23" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="F23" s="48"/>
-      <c r="G23" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="H23" s="3">
-        <v>1</v>
-      </c>
-      <c r="I23" s="42"/>
-    </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B24" s="44"/>
-      <c r="C24" s="72"/>
-      <c r="D24" s="48"/>
-      <c r="E24" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F24" s="48"/>
-      <c r="G24" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="H24" s="3">
-        <v>1</v>
-      </c>
-      <c r="I24" s="42"/>
-    </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B25" s="44"/>
-      <c r="C25" s="72"/>
-      <c r="D25" s="48"/>
-      <c r="E25" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="F25" s="48"/>
-      <c r="G25" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="H25" s="3">
-        <v>1</v>
-      </c>
-      <c r="I25" s="42"/>
-    </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B26" s="44"/>
-      <c r="C26" s="72"/>
-      <c r="D26" s="48"/>
-      <c r="E26" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F26" s="48"/>
-      <c r="G26" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="H26" s="3">
-        <v>1</v>
-      </c>
-      <c r="I26" s="42"/>
-    </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B27" s="44"/>
-      <c r="C27" s="72"/>
-      <c r="D27" s="48"/>
-      <c r="E27" s="46"/>
-      <c r="F27" s="46"/>
-      <c r="G27" s="46"/>
-      <c r="H27" s="46"/>
-      <c r="I27" s="42"/>
-    </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B28" s="44"/>
-      <c r="C28" s="72"/>
-      <c r="D28" s="48"/>
-      <c r="E28" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="H28" s="3">
-        <v>1</v>
-      </c>
-      <c r="I28" s="42"/>
-    </row>
-    <row r="29" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B29" s="44"/>
-      <c r="C29" s="72"/>
-      <c r="D29" s="48"/>
-      <c r="E29" s="46"/>
-      <c r="F29" s="46"/>
-      <c r="G29" s="46"/>
-      <c r="H29" s="46"/>
-      <c r="I29" s="42"/>
-    </row>
-    <row r="30" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B30" s="44"/>
-      <c r="C30" s="72"/>
-      <c r="D30" s="48"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="42"/>
-      <c r="J30" s="34" t="s">
-        <v>99</v>
-      </c>
-      <c r="K30" s="35" t="s">
-        <v>35</v>
-      </c>
-      <c r="L30" s="34" t="s">
-        <v>188</v>
-      </c>
-      <c r="M30" s="34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B31" s="44"/>
-      <c r="C31" s="72"/>
-      <c r="D31" s="47"/>
-      <c r="E31" s="47"/>
-      <c r="F31" s="47"/>
-      <c r="G31" s="47"/>
-      <c r="H31" s="47"/>
-      <c r="I31" s="42"/>
-    </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B32" s="44"/>
-      <c r="C32" s="72"/>
-      <c r="D32" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="H32" s="3">
-        <v>3</v>
-      </c>
-      <c r="I32" s="42"/>
-    </row>
-    <row r="33" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B33" s="44"/>
-      <c r="C33" s="70"/>
-      <c r="D33" s="70"/>
-      <c r="E33" s="70"/>
-      <c r="F33" s="70"/>
-      <c r="G33" s="70"/>
-      <c r="H33" s="70"/>
-      <c r="I33" s="42"/>
-    </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B34" s="44"/>
-      <c r="C34" s="32" t="s">
-        <v>242</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="E34" s="3"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
-      <c r="I34" s="42"/>
-    </row>
-    <row r="35" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B35" s="45"/>
-      <c r="C35" s="52"/>
-      <c r="D35" s="52"/>
-      <c r="E35" s="52"/>
-      <c r="F35" s="52"/>
-      <c r="G35" s="52"/>
-      <c r="H35" s="52"/>
-      <c r="I35" s="43"/>
-    </row>
-  </sheetData>
-  <mergeCells count="24">
-    <mergeCell ref="C6:C32"/>
-    <mergeCell ref="E27:H27"/>
-    <mergeCell ref="E29:H29"/>
-    <mergeCell ref="E9:H9"/>
-    <mergeCell ref="E12:H12"/>
-    <mergeCell ref="D6:D13"/>
-    <mergeCell ref="D15:D20"/>
-    <mergeCell ref="D22:D30"/>
-    <mergeCell ref="J3:L3"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B35:I35"/>
-    <mergeCell ref="B3:B34"/>
-    <mergeCell ref="I3:I34"/>
-    <mergeCell ref="C33:H33"/>
-    <mergeCell ref="D31:H31"/>
-    <mergeCell ref="F6:F8"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="F17:F18"/>
-    <mergeCell ref="F22:F26"/>
-    <mergeCell ref="E19:H19"/>
-    <mergeCell ref="E16:H16"/>
-    <mergeCell ref="C5:H5"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="D21:H21"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Testes.xlsx
+++ b/Testes.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\utilizador\Documents\CTESP\4semestre\LP2\ProjetoTesteLP2\TrabalhoTesteLP2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{937A0731-2BA4-49B8-8D44-8351DC4F522F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1449C5A4-D388-4B24-9534-489117247C7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{17050BBC-8C72-4C7C-BB9E-52ED50A4B6E1}"/>
+    <workbookView xWindow="38940" yWindow="-3750" windowWidth="10185" windowHeight="10905" activeTab="1" xr2:uid="{17050BBC-8C72-4C7C-BB9E-52ED50A4B6E1}"/>
   </bookViews>
   <sheets>
     <sheet name="Menus" sheetId="1" r:id="rId1"/>
-    <sheet name="Escola" sheetId="3" r:id="rId2"/>
-    <sheet name="Utilizadores" sheetId="2" r:id="rId3"/>
+    <sheet name="Utilizadores" sheetId="2" r:id="rId2"/>
+    <sheet name="Escola" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -548,69 +548,6 @@
     <t>MÓDULO DOCENTE</t>
   </si>
   <si>
-    <t>PBQ</t>
-  </si>
-  <si>
-    <t>pbq@issmf.ipp.pt</t>
-  </si>
-  <si>
-    <t>lMasaXqK</t>
-  </si>
-  <si>
-    <t>fGiK8ONG</t>
-  </si>
-  <si>
-    <t>pdz@issmf.ipp.pt</t>
-  </si>
-  <si>
-    <t>PDZ</t>
-  </si>
-  <si>
-    <t>pim@issmf.ipp.pt</t>
-  </si>
-  <si>
-    <t>YLTS7ASW</t>
-  </si>
-  <si>
-    <t>PIM</t>
-  </si>
-  <si>
-    <t>PYA</t>
-  </si>
-  <si>
-    <t>pya@issmf.ipp.pt</t>
-  </si>
-  <si>
-    <t>VE4UlGEH</t>
-  </si>
-  <si>
-    <t>PCU</t>
-  </si>
-  <si>
-    <t>pcu@issmf.ipp.pt</t>
-  </si>
-  <si>
-    <t>wdxI9Nan</t>
-  </si>
-  <si>
-    <t>PGN</t>
-  </si>
-  <si>
-    <t>pgn@issmf.ipp.pt</t>
-  </si>
-  <si>
-    <t>Uj7eR69F</t>
-  </si>
-  <si>
-    <t>PVU</t>
-  </si>
-  <si>
-    <t>pvu@issmf.ipp.pt</t>
-  </si>
-  <si>
-    <t>dRAsOjSf</t>
-  </si>
-  <si>
     <t>[INATIVO] MAC : Matemática Clássica</t>
   </si>
   <si>
@@ -636,39 +573,6 @@
   </si>
   <si>
     <t>[ATIVO] SDE : Sistemas Digitais Elétricos</t>
-  </si>
-  <si>
-    <t>[INATIVO] REA1 : Reatores</t>
-  </si>
-  <si>
-    <t>5uahyofO</t>
-  </si>
-  <si>
-    <t>8xoEWbpI</t>
-  </si>
-  <si>
-    <t>kfqNwbl1</t>
-  </si>
-  <si>
-    <t>4iGMGR5F</t>
-  </si>
-  <si>
-    <t>JQzW3OhW</t>
-  </si>
-  <si>
-    <t>NTNOvRth</t>
-  </si>
-  <si>
-    <t>nFRS0MxR</t>
-  </si>
-  <si>
-    <t>LxA1lNbP</t>
-  </si>
-  <si>
-    <t>cfmOFDHd</t>
-  </si>
-  <si>
-    <t>jnlWaqRl</t>
   </si>
   <si>
     <t>========= ÁREA DO ESTUDANTE =========</t>
@@ -761,6 +665,102 @@
   </si>
   <si>
     <t>8 - Alterar Curso de Departamento</t>
+  </si>
+  <si>
+    <t>[INATIVO] REA1 : Reatores 1</t>
+  </si>
+  <si>
+    <t>PKF</t>
+  </si>
+  <si>
+    <t>pkf@issmf.ipp.pt</t>
+  </si>
+  <si>
+    <t>GzZvpVu3</t>
+  </si>
+  <si>
+    <t>PHH</t>
+  </si>
+  <si>
+    <t>phh@issmf.ipp.pt</t>
+  </si>
+  <si>
+    <t>PDU</t>
+  </si>
+  <si>
+    <t>pdu@issmf.ipp.pt</t>
+  </si>
+  <si>
+    <t>RgbjQBEq</t>
+  </si>
+  <si>
+    <t>PTW</t>
+  </si>
+  <si>
+    <t>ptw@issmf.ipp.pt</t>
+  </si>
+  <si>
+    <t>5kHRR2MS</t>
+  </si>
+  <si>
+    <t>PIW</t>
+  </si>
+  <si>
+    <t>piw@issmf.ipp.pt</t>
+  </si>
+  <si>
+    <t>nsNDz5jU</t>
+  </si>
+  <si>
+    <t>pbr@issmf.ipp.pt</t>
+  </si>
+  <si>
+    <t>rUU3Zypq</t>
+  </si>
+  <si>
+    <t>PBR</t>
+  </si>
+  <si>
+    <t>PAY</t>
+  </si>
+  <si>
+    <t>pay@issmf.ipp.pt</t>
+  </si>
+  <si>
+    <t>emvUipW5</t>
+  </si>
+  <si>
+    <t>uGGeeIQK</t>
+  </si>
+  <si>
+    <t>tUI7CGjC</t>
+  </si>
+  <si>
+    <t>DfgH3J7f</t>
+  </si>
+  <si>
+    <t>ZFymXJYt</t>
+  </si>
+  <si>
+    <t>5RE65Aos</t>
+  </si>
+  <si>
+    <t>Pffw8aDE</t>
+  </si>
+  <si>
+    <t>5EYoKChp</t>
+  </si>
+  <si>
+    <t>miBfIPQ8</t>
+  </si>
+  <si>
+    <t>J0NvIfDG</t>
+  </si>
+  <si>
+    <t>ZESsuAJn</t>
+  </si>
+  <si>
+    <t>D3EyYfxw</t>
   </si>
 </sst>
 </file>
@@ -851,7 +851,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -991,12 +991,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1018,7 +1031,6 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
@@ -1050,11 +1062,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1085,12 +1102,6 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1100,72 +1111,68 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperligação" xfId="1" builtinId="8"/>
@@ -1499,7 +1506,7 @@
     <row r="3" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B3" s="44"/>
       <c r="C3" s="36" t="s">
-        <v>233</v>
+        <v>201</v>
       </c>
       <c r="D3" s="36"/>
       <c r="E3" s="36"/>
@@ -1510,8 +1517,8 @@
       <c r="C4" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
       <c r="F4" s="42"/>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.3">
@@ -1519,8 +1526,8 @@
       <c r="C5" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D5" s="46"/>
-      <c r="E5" s="46"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="34"/>
       <c r="F5" s="42"/>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.3">
@@ -1528,8 +1535,8 @@
       <c r="C6" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D6" s="46"/>
-      <c r="E6" s="46"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="34"/>
       <c r="F6" s="42"/>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.3">
@@ -1537,8 +1544,8 @@
       <c r="C7" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D7" s="46"/>
-      <c r="E7" s="46"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="34"/>
       <c r="F7" s="42"/>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.3">
@@ -1546,8 +1553,8 @@
       <c r="C8" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="D8" s="46"/>
-      <c r="E8" s="46"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="34"/>
       <c r="F8" s="42"/>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.3">
@@ -1555,8 +1562,8 @@
       <c r="C9" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="D9" s="46"/>
-      <c r="E9" s="46"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="34"/>
       <c r="F9" s="42"/>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.3">
@@ -1564,102 +1571,102 @@
       <c r="C10" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D10" s="46"/>
-      <c r="E10" s="46"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="34"/>
       <c r="F10" s="42"/>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B11" s="44"/>
-      <c r="C11" s="47"/>
-      <c r="D11" s="47"/>
-      <c r="E11" s="47"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="35"/>
       <c r="F11" s="42"/>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B12" s="44"/>
-      <c r="C12" s="49" t="s">
-        <v>232</v>
+      <c r="C12" s="47" t="s">
+        <v>200</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="E12" s="46"/>
+      <c r="E12" s="34"/>
       <c r="F12" s="42"/>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B13" s="44"/>
-      <c r="C13" s="50"/>
+      <c r="C13" s="48"/>
       <c r="D13" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="E13" s="46"/>
+      <c r="E13" s="34"/>
       <c r="F13" s="42"/>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B14" s="44"/>
-      <c r="C14" s="50"/>
+      <c r="C14" s="48"/>
       <c r="D14" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="E14" s="46"/>
+      <c r="E14" s="34"/>
       <c r="F14" s="42"/>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B15" s="44"/>
-      <c r="C15" s="50"/>
+      <c r="C15" s="48"/>
       <c r="D15" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="E15" s="46"/>
+      <c r="E15" s="34"/>
       <c r="F15" s="42"/>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B16" s="44"/>
-      <c r="C16" s="50"/>
+      <c r="C16" s="48"/>
       <c r="D16" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="E16" s="46"/>
+      <c r="E16" s="34"/>
       <c r="F16" s="42"/>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B17" s="44"/>
-      <c r="C17" s="50"/>
+      <c r="C17" s="48"/>
       <c r="D17" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="E17" s="46"/>
+      <c r="E17" s="34"/>
       <c r="F17" s="42"/>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B18" s="44"/>
-      <c r="C18" s="50"/>
+      <c r="C18" s="48"/>
       <c r="D18" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="E18" s="46"/>
+      <c r="E18" s="34"/>
       <c r="F18" s="42"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B19" s="44"/>
-      <c r="C19" s="50"/>
+      <c r="C19" s="48"/>
       <c r="D19" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="E19" s="46"/>
+      <c r="E19" s="34"/>
       <c r="F19" s="42"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B20" s="44"/>
-      <c r="C20" s="50"/>
+      <c r="C20" s="48"/>
       <c r="D20" s="37"/>
       <c r="E20" s="38"/>
       <c r="F20" s="42"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B21" s="44"/>
-      <c r="C21" s="50"/>
-      <c r="D21" s="46"/>
+      <c r="C21" s="48"/>
+      <c r="D21" s="34"/>
       <c r="E21" s="3" t="s">
         <v>143</v>
       </c>
@@ -1667,8 +1674,8 @@
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B22" s="44"/>
-      <c r="C22" s="50"/>
-      <c r="D22" s="46"/>
+      <c r="C22" s="48"/>
+      <c r="D22" s="34"/>
       <c r="E22" s="3" t="s">
         <v>0</v>
       </c>
@@ -1676,8 +1683,8 @@
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B23" s="44"/>
-      <c r="C23" s="50"/>
-      <c r="D23" s="46"/>
+      <c r="C23" s="48"/>
+      <c r="D23" s="34"/>
       <c r="E23" s="3" t="s">
         <v>1</v>
       </c>
@@ -1685,8 +1692,8 @@
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B24" s="44"/>
-      <c r="C24" s="50"/>
-      <c r="D24" s="46"/>
+      <c r="C24" s="48"/>
+      <c r="D24" s="34"/>
       <c r="E24" s="3" t="s">
         <v>50</v>
       </c>
@@ -1694,8 +1701,8 @@
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B25" s="44"/>
-      <c r="C25" s="50"/>
-      <c r="D25" s="46"/>
+      <c r="C25" s="48"/>
+      <c r="D25" s="34"/>
       <c r="E25" s="3" t="s">
         <v>51</v>
       </c>
@@ -1703,8 +1710,8 @@
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B26" s="44"/>
-      <c r="C26" s="50"/>
-      <c r="D26" s="46"/>
+      <c r="C26" s="48"/>
+      <c r="D26" s="34"/>
       <c r="E26" s="3" t="s">
         <v>2</v>
       </c>
@@ -1712,15 +1719,15 @@
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B27" s="44"/>
-      <c r="C27" s="50"/>
-      <c r="D27" s="46"/>
+      <c r="C27" s="48"/>
+      <c r="D27" s="34"/>
       <c r="E27" s="7"/>
       <c r="F27" s="42"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B28" s="44"/>
-      <c r="C28" s="50"/>
-      <c r="D28" s="46"/>
+      <c r="C28" s="48"/>
+      <c r="D28" s="34"/>
       <c r="E28" s="3" t="s">
         <v>144</v>
       </c>
@@ -1728,8 +1735,8 @@
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B29" s="44"/>
-      <c r="C29" s="50"/>
-      <c r="D29" s="46"/>
+      <c r="C29" s="48"/>
+      <c r="D29" s="34"/>
       <c r="E29" s="3" t="s">
         <v>3</v>
       </c>
@@ -1737,8 +1744,8 @@
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B30" s="44"/>
-      <c r="C30" s="50"/>
-      <c r="D30" s="46"/>
+      <c r="C30" s="48"/>
+      <c r="D30" s="34"/>
       <c r="E30" s="3" t="s">
         <v>4</v>
       </c>
@@ -1746,8 +1753,8 @@
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B31" s="44"/>
-      <c r="C31" s="50"/>
-      <c r="D31" s="46"/>
+      <c r="C31" s="48"/>
+      <c r="D31" s="34"/>
       <c r="E31" s="3" t="s">
         <v>145</v>
       </c>
@@ -1755,8 +1762,8 @@
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B32" s="44"/>
-      <c r="C32" s="50"/>
-      <c r="D32" s="46"/>
+      <c r="C32" s="48"/>
+      <c r="D32" s="34"/>
       <c r="E32" s="3" t="s">
         <v>146</v>
       </c>
@@ -1764,8 +1771,8 @@
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B33" s="44"/>
-      <c r="C33" s="50"/>
-      <c r="D33" s="46"/>
+      <c r="C33" s="48"/>
+      <c r="D33" s="34"/>
       <c r="E33" s="3" t="s">
         <v>147</v>
       </c>
@@ -1773,8 +1780,8 @@
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B34" s="44"/>
-      <c r="C34" s="50"/>
-      <c r="D34" s="46"/>
+      <c r="C34" s="48"/>
+      <c r="D34" s="34"/>
       <c r="E34" s="3" t="s">
         <v>148</v>
       </c>
@@ -1782,26 +1789,26 @@
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B35" s="44"/>
-      <c r="C35" s="50"/>
-      <c r="D35" s="46"/>
+      <c r="C35" s="48"/>
+      <c r="D35" s="34"/>
       <c r="E35" s="3" t="s">
-        <v>240</v>
+        <v>208</v>
       </c>
       <c r="F35" s="42"/>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B36" s="44"/>
-      <c r="C36" s="50"/>
-      <c r="D36" s="46"/>
+      <c r="C36" s="48"/>
+      <c r="D36" s="34"/>
       <c r="E36" s="3" t="s">
-        <v>243</v>
+        <v>211</v>
       </c>
       <c r="F36" s="42"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B37" s="44"/>
-      <c r="C37" s="50"/>
-      <c r="D37" s="46"/>
+      <c r="C37" s="48"/>
+      <c r="D37" s="34"/>
       <c r="E37" s="3" t="s">
         <v>2</v>
       </c>
@@ -1809,15 +1816,15 @@
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B38" s="44"/>
-      <c r="C38" s="50"/>
-      <c r="D38" s="46"/>
+      <c r="C38" s="48"/>
+      <c r="D38" s="34"/>
       <c r="E38" s="7"/>
       <c r="F38" s="42"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B39" s="44"/>
-      <c r="C39" s="50"/>
-      <c r="D39" s="46"/>
+      <c r="C39" s="48"/>
+      <c r="D39" s="34"/>
       <c r="E39" s="3" t="s">
         <v>149</v>
       </c>
@@ -1825,8 +1832,8 @@
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B40" s="44"/>
-      <c r="C40" s="50"/>
-      <c r="D40" s="46"/>
+      <c r="C40" s="48"/>
+      <c r="D40" s="34"/>
       <c r="E40" s="3" t="s">
         <v>53</v>
       </c>
@@ -1834,8 +1841,8 @@
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B41" s="44"/>
-      <c r="C41" s="50"/>
-      <c r="D41" s="46"/>
+      <c r="C41" s="48"/>
+      <c r="D41" s="34"/>
       <c r="E41" s="3" t="s">
         <v>5</v>
       </c>
@@ -1843,8 +1850,8 @@
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B42" s="44"/>
-      <c r="C42" s="50"/>
-      <c r="D42" s="46"/>
+      <c r="C42" s="48"/>
+      <c r="D42" s="34"/>
       <c r="E42" s="3" t="s">
         <v>6</v>
       </c>
@@ -1852,8 +1859,8 @@
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B43" s="44"/>
-      <c r="C43" s="50"/>
-      <c r="D43" s="46"/>
+      <c r="C43" s="48"/>
+      <c r="D43" s="34"/>
       <c r="E43" s="3" t="s">
         <v>54</v>
       </c>
@@ -1861,8 +1868,8 @@
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B44" s="44"/>
-      <c r="C44" s="50"/>
-      <c r="D44" s="46"/>
+      <c r="C44" s="48"/>
+      <c r="D44" s="34"/>
       <c r="E44" s="3" t="s">
         <v>52</v>
       </c>
@@ -1870,8 +1877,8 @@
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B45" s="44"/>
-      <c r="C45" s="50"/>
-      <c r="D45" s="46"/>
+      <c r="C45" s="48"/>
+      <c r="D45" s="34"/>
       <c r="E45" s="3" t="s">
         <v>55</v>
       </c>
@@ -1879,8 +1886,8 @@
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B46" s="44"/>
-      <c r="C46" s="50"/>
-      <c r="D46" s="46"/>
+      <c r="C46" s="48"/>
+      <c r="D46" s="34"/>
       <c r="E46" s="3" t="s">
         <v>150</v>
       </c>
@@ -1888,8 +1895,8 @@
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B47" s="44"/>
-      <c r="C47" s="50"/>
-      <c r="D47" s="46"/>
+      <c r="C47" s="48"/>
+      <c r="D47" s="34"/>
       <c r="E47" s="3" t="s">
         <v>151</v>
       </c>
@@ -1897,8 +1904,8 @@
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B48" s="44"/>
-      <c r="C48" s="50"/>
-      <c r="D48" s="46"/>
+      <c r="C48" s="48"/>
+      <c r="D48" s="34"/>
       <c r="E48" s="3" t="s">
         <v>2</v>
       </c>
@@ -1906,15 +1913,15 @@
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B49" s="44"/>
-      <c r="C49" s="50"/>
-      <c r="D49" s="46"/>
+      <c r="C49" s="48"/>
+      <c r="D49" s="34"/>
       <c r="E49" s="7"/>
       <c r="F49" s="42"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B50" s="44"/>
-      <c r="C50" s="50"/>
-      <c r="D50" s="46"/>
+      <c r="C50" s="48"/>
+      <c r="D50" s="34"/>
       <c r="E50" s="3" t="s">
         <v>152</v>
       </c>
@@ -1922,8 +1929,8 @@
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B51" s="44"/>
-      <c r="C51" s="50"/>
-      <c r="D51" s="46"/>
+      <c r="C51" s="48"/>
+      <c r="D51" s="34"/>
       <c r="E51" s="3" t="s">
         <v>7</v>
       </c>
@@ -1931,8 +1938,8 @@
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B52" s="44"/>
-      <c r="C52" s="50"/>
-      <c r="D52" s="46"/>
+      <c r="C52" s="48"/>
+      <c r="D52" s="34"/>
       <c r="E52" s="3" t="s">
         <v>56</v>
       </c>
@@ -1940,8 +1947,8 @@
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B53" s="44"/>
-      <c r="C53" s="50"/>
-      <c r="D53" s="46"/>
+      <c r="C53" s="48"/>
+      <c r="D53" s="34"/>
       <c r="E53" s="3" t="s">
         <v>153</v>
       </c>
@@ -1949,8 +1956,8 @@
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B54" s="44"/>
-      <c r="C54" s="50"/>
-      <c r="D54" s="46"/>
+      <c r="C54" s="48"/>
+      <c r="D54" s="34"/>
       <c r="E54" s="3" t="s">
         <v>51</v>
       </c>
@@ -1958,8 +1965,8 @@
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B55" s="44"/>
-      <c r="C55" s="50"/>
-      <c r="D55" s="46"/>
+      <c r="C55" s="48"/>
+      <c r="D55" s="34"/>
       <c r="E55" s="3" t="s">
         <v>154</v>
       </c>
@@ -1967,8 +1974,8 @@
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B56" s="44"/>
-      <c r="C56" s="50"/>
-      <c r="D56" s="46"/>
+      <c r="C56" s="48"/>
+      <c r="D56" s="34"/>
       <c r="E56" s="3" t="s">
         <v>2</v>
       </c>
@@ -1976,15 +1983,15 @@
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B57" s="44"/>
-      <c r="C57" s="50"/>
-      <c r="D57" s="46"/>
+      <c r="C57" s="48"/>
+      <c r="D57" s="34"/>
       <c r="E57" s="7"/>
       <c r="F57" s="42"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B58" s="44"/>
-      <c r="C58" s="50"/>
-      <c r="D58" s="46"/>
+      <c r="C58" s="48"/>
+      <c r="D58" s="34"/>
       <c r="E58" s="3" t="s">
         <v>155</v>
       </c>
@@ -1992,8 +1999,8 @@
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B59" s="44"/>
-      <c r="C59" s="50"/>
-      <c r="D59" s="46"/>
+      <c r="C59" s="48"/>
+      <c r="D59" s="34"/>
       <c r="E59" s="3" t="s">
         <v>8</v>
       </c>
@@ -2001,8 +2008,8 @@
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B60" s="44"/>
-      <c r="C60" s="50"/>
-      <c r="D60" s="46"/>
+      <c r="C60" s="48"/>
+      <c r="D60" s="34"/>
       <c r="E60" s="3" t="s">
         <v>57</v>
       </c>
@@ -2010,8 +2017,8 @@
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B61" s="44"/>
-      <c r="C61" s="50"/>
-      <c r="D61" s="46"/>
+      <c r="C61" s="48"/>
+      <c r="D61" s="34"/>
       <c r="E61" s="3" t="s">
         <v>156</v>
       </c>
@@ -2019,8 +2026,8 @@
     </row>
     <row r="62" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B62" s="44"/>
-      <c r="C62" s="50"/>
-      <c r="D62" s="46"/>
+      <c r="C62" s="48"/>
+      <c r="D62" s="34"/>
       <c r="E62" s="3" t="s">
         <v>51</v>
       </c>
@@ -2028,8 +2035,8 @@
     </row>
     <row r="63" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B63" s="44"/>
-      <c r="C63" s="50"/>
-      <c r="D63" s="46"/>
+      <c r="C63" s="48"/>
+      <c r="D63" s="34"/>
       <c r="E63" s="3" t="s">
         <v>157</v>
       </c>
@@ -2037,8 +2044,8 @@
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B64" s="44"/>
-      <c r="C64" s="50"/>
-      <c r="D64" s="46"/>
+      <c r="C64" s="48"/>
+      <c r="D64" s="34"/>
       <c r="E64" s="3" t="s">
         <v>2</v>
       </c>
@@ -2046,15 +2053,15 @@
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B65" s="44"/>
-      <c r="C65" s="50"/>
-      <c r="D65" s="46"/>
+      <c r="C65" s="48"/>
+      <c r="D65" s="34"/>
       <c r="E65" s="7"/>
       <c r="F65" s="42"/>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B66" s="44"/>
-      <c r="C66" s="50"/>
-      <c r="D66" s="46"/>
+      <c r="C66" s="48"/>
+      <c r="D66" s="34"/>
       <c r="E66" s="3" t="s">
         <v>158</v>
       </c>
@@ -2062,8 +2069,8 @@
     </row>
     <row r="67" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B67" s="44"/>
-      <c r="C67" s="50"/>
-      <c r="D67" s="46"/>
+      <c r="C67" s="48"/>
+      <c r="D67" s="34"/>
       <c r="E67" s="3" t="s">
         <v>9</v>
       </c>
@@ -2071,8 +2078,8 @@
     </row>
     <row r="68" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B68" s="44"/>
-      <c r="C68" s="50"/>
-      <c r="D68" s="46"/>
+      <c r="C68" s="48"/>
+      <c r="D68" s="34"/>
       <c r="E68" s="3" t="s">
         <v>58</v>
       </c>
@@ -2080,8 +2087,8 @@
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B69" s="44"/>
-      <c r="C69" s="50"/>
-      <c r="D69" s="46"/>
+      <c r="C69" s="48"/>
+      <c r="D69" s="34"/>
       <c r="E69" s="3" t="s">
         <v>59</v>
       </c>
@@ -2089,8 +2096,8 @@
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B70" s="44"/>
-      <c r="C70" s="50"/>
-      <c r="D70" s="46"/>
+      <c r="C70" s="48"/>
+      <c r="D70" s="34"/>
       <c r="E70" s="3" t="s">
         <v>159</v>
       </c>
@@ -2098,8 +2105,8 @@
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B71" s="44"/>
-      <c r="C71" s="50"/>
-      <c r="D71" s="46"/>
+      <c r="C71" s="48"/>
+      <c r="D71" s="34"/>
       <c r="E71" s="3" t="s">
         <v>2</v>
       </c>
@@ -2107,15 +2114,15 @@
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B72" s="44"/>
-      <c r="C72" s="50"/>
-      <c r="D72" s="46"/>
+      <c r="C72" s="48"/>
+      <c r="D72" s="34"/>
       <c r="E72" s="7"/>
       <c r="F72" s="42"/>
     </row>
     <row r="73" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B73" s="44"/>
-      <c r="C73" s="50"/>
-      <c r="D73" s="46"/>
+      <c r="C73" s="48"/>
+      <c r="D73" s="34"/>
       <c r="E73" s="3" t="s">
         <v>160</v>
       </c>
@@ -2123,8 +2130,8 @@
     </row>
     <row r="74" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B74" s="44"/>
-      <c r="C74" s="50"/>
-      <c r="D74" s="46"/>
+      <c r="C74" s="48"/>
+      <c r="D74" s="34"/>
       <c r="E74" s="3" t="s">
         <v>161</v>
       </c>
@@ -2132,8 +2139,8 @@
     </row>
     <row r="75" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B75" s="44"/>
-      <c r="C75" s="50"/>
-      <c r="D75" s="46"/>
+      <c r="C75" s="48"/>
+      <c r="D75" s="34"/>
       <c r="E75" s="3" t="s">
         <v>2</v>
       </c>
@@ -2141,114 +2148,114 @@
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B76" s="44"/>
-      <c r="C76" s="47"/>
-      <c r="D76" s="47"/>
-      <c r="E76" s="47"/>
+      <c r="C76" s="35"/>
+      <c r="D76" s="35"/>
+      <c r="E76" s="35"/>
       <c r="F76" s="42"/>
     </row>
     <row r="77" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B77" s="44"/>
-      <c r="C77" s="48" t="s">
+      <c r="C77" s="46" t="s">
         <v>172</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="E77" s="46"/>
+      <c r="E77" s="34"/>
       <c r="F77" s="42"/>
     </row>
     <row r="78" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B78" s="44"/>
-      <c r="C78" s="48"/>
+      <c r="C78" s="46"/>
       <c r="D78" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="E78" s="46"/>
+      <c r="E78" s="34"/>
       <c r="F78" s="42"/>
     </row>
     <row r="79" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B79" s="44"/>
-      <c r="C79" s="48"/>
+      <c r="C79" s="46"/>
       <c r="D79" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="E79" s="46"/>
+      <c r="E79" s="34"/>
       <c r="F79" s="42"/>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B80" s="44"/>
-      <c r="C80" s="48"/>
+      <c r="C80" s="46"/>
       <c r="D80" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="E80" s="46"/>
+      <c r="E80" s="34"/>
       <c r="F80" s="42"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B81" s="44"/>
-      <c r="C81" s="48"/>
+      <c r="C81" s="46"/>
       <c r="D81" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="E81" s="46"/>
+      <c r="E81" s="34"/>
       <c r="F81" s="42"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B82" s="44"/>
-      <c r="C82" s="48"/>
+      <c r="C82" s="46"/>
       <c r="D82" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E82" s="46"/>
+      <c r="E82" s="34"/>
       <c r="F82" s="42"/>
     </row>
     <row r="83" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B83" s="44"/>
-      <c r="C83" s="48"/>
-      <c r="D83" s="46"/>
-      <c r="E83" s="46"/>
+      <c r="C83" s="46"/>
+      <c r="D83" s="34"/>
+      <c r="E83" s="34"/>
       <c r="F83" s="42"/>
     </row>
     <row r="84" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B84" s="44"/>
-      <c r="C84" s="48"/>
-      <c r="D84" s="46"/>
+      <c r="C84" s="46"/>
+      <c r="D84" s="34"/>
       <c r="E84" s="6" t="s">
-        <v>229</v>
+        <v>197</v>
       </c>
       <c r="F84" s="42"/>
     </row>
     <row r="85" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B85" s="44"/>
-      <c r="C85" s="48"/>
-      <c r="D85" s="46"/>
+      <c r="C85" s="46"/>
+      <c r="D85" s="34"/>
       <c r="E85" s="6" t="s">
-        <v>221</v>
+        <v>189</v>
       </c>
       <c r="F85" s="42"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B86" s="44"/>
-      <c r="C86" s="48"/>
-      <c r="D86" s="46"/>
+      <c r="C86" s="46"/>
+      <c r="D86" s="34"/>
       <c r="E86" s="6" t="s">
-        <v>222</v>
+        <v>190</v>
       </c>
       <c r="F86" s="42"/>
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B87" s="44"/>
-      <c r="C87" s="48"/>
-      <c r="D87" s="46"/>
+      <c r="C87" s="46"/>
+      <c r="D87" s="34"/>
       <c r="E87" s="6" t="s">
-        <v>223</v>
+        <v>191</v>
       </c>
       <c r="F87" s="42"/>
     </row>
     <row r="88" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B88" s="44"/>
-      <c r="C88" s="48"/>
-      <c r="D88" s="46"/>
+      <c r="C88" s="46"/>
+      <c r="D88" s="34"/>
       <c r="E88" s="6" t="s">
         <v>159</v>
       </c>
@@ -2256,8 +2263,8 @@
     </row>
     <row r="89" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B89" s="44"/>
-      <c r="C89" s="48"/>
-      <c r="D89" s="46"/>
+      <c r="C89" s="46"/>
+      <c r="D89" s="34"/>
       <c r="E89" s="6" t="s">
         <v>2</v>
       </c>
@@ -2265,15 +2272,15 @@
     </row>
     <row r="90" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B90" s="44"/>
-      <c r="C90" s="48"/>
-      <c r="D90" s="46"/>
+      <c r="C90" s="46"/>
+      <c r="D90" s="34"/>
       <c r="E90" s="7"/>
       <c r="F90" s="42"/>
     </row>
     <row r="91" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B91" s="44"/>
-      <c r="C91" s="48"/>
-      <c r="D91" s="46"/>
+      <c r="C91" s="46"/>
+      <c r="D91" s="34"/>
       <c r="E91" s="3" t="s">
         <v>167</v>
       </c>
@@ -2281,8 +2288,8 @@
     </row>
     <row r="92" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B92" s="44"/>
-      <c r="C92" s="48"/>
-      <c r="D92" s="46"/>
+      <c r="C92" s="46"/>
+      <c r="D92" s="34"/>
       <c r="E92" s="3" t="s">
         <v>168</v>
       </c>
@@ -2290,8 +2297,8 @@
     </row>
     <row r="93" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B93" s="44"/>
-      <c r="C93" s="48"/>
-      <c r="D93" s="46"/>
+      <c r="C93" s="46"/>
+      <c r="D93" s="34"/>
       <c r="E93" s="3" t="s">
         <v>169</v>
       </c>
@@ -2299,8 +2306,8 @@
     </row>
     <row r="94" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B94" s="44"/>
-      <c r="C94" s="48"/>
-      <c r="D94" s="46"/>
+      <c r="C94" s="46"/>
+      <c r="D94" s="34"/>
       <c r="E94" s="3" t="s">
         <v>170</v>
       </c>
@@ -2308,8 +2315,8 @@
     </row>
     <row r="95" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B95" s="44"/>
-      <c r="C95" s="48"/>
-      <c r="D95" s="46"/>
+      <c r="C95" s="46"/>
+      <c r="D95" s="34"/>
       <c r="E95" s="3" t="s">
         <v>171</v>
       </c>
@@ -2317,8 +2324,8 @@
     </row>
     <row r="96" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B96" s="44"/>
-      <c r="C96" s="48"/>
-      <c r="D96" s="46"/>
+      <c r="C96" s="46"/>
+      <c r="D96" s="34"/>
       <c r="E96" s="3" t="s">
         <v>2</v>
       </c>
@@ -2326,123 +2333,123 @@
     </row>
     <row r="97" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B97" s="44"/>
-      <c r="C97" s="47"/>
-      <c r="D97" s="47"/>
-      <c r="E97" s="47"/>
+      <c r="C97" s="35"/>
+      <c r="D97" s="35"/>
+      <c r="E97" s="35"/>
       <c r="F97" s="42"/>
     </row>
     <row r="98" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B98" s="44"/>
-      <c r="C98" s="48" t="s">
-        <v>228</v>
+      <c r="C98" s="46" t="s">
+        <v>196</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="E98" s="46"/>
+        <v>182</v>
+      </c>
+      <c r="E98" s="34"/>
       <c r="F98" s="42"/>
     </row>
     <row r="99" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B99" s="44"/>
-      <c r="C99" s="48"/>
+      <c r="C99" s="46"/>
       <c r="D99" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="E99" s="46"/>
+        <v>183</v>
+      </c>
+      <c r="E99" s="34"/>
       <c r="F99" s="42"/>
     </row>
     <row r="100" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B100" s="44"/>
-      <c r="C100" s="48"/>
+      <c r="C100" s="46"/>
       <c r="D100" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="E100" s="46"/>
+        <v>184</v>
+      </c>
+      <c r="E100" s="34"/>
       <c r="F100" s="42"/>
     </row>
     <row r="101" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B101" s="44"/>
-      <c r="C101" s="48"/>
+      <c r="C101" s="46"/>
       <c r="D101" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="E101" s="46"/>
+        <v>185</v>
+      </c>
+      <c r="E101" s="34"/>
       <c r="F101" s="42"/>
     </row>
     <row r="102" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B102" s="44"/>
-      <c r="C102" s="48"/>
+      <c r="C102" s="46"/>
       <c r="D102" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="E102" s="46"/>
+        <v>186</v>
+      </c>
+      <c r="E102" s="34"/>
       <c r="F102" s="42"/>
     </row>
     <row r="103" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B103" s="44"/>
-      <c r="C103" s="48"/>
+      <c r="C103" s="46"/>
       <c r="D103" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="E103" s="46"/>
+        <v>187</v>
+      </c>
+      <c r="E103" s="34"/>
       <c r="F103" s="42"/>
     </row>
     <row r="104" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B104" s="44"/>
-      <c r="C104" s="48"/>
+      <c r="C104" s="46"/>
       <c r="D104" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E104" s="46"/>
+      <c r="E104" s="34"/>
       <c r="F104" s="42"/>
     </row>
     <row r="105" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B105" s="44"/>
-      <c r="C105" s="48"/>
-      <c r="D105" s="46"/>
-      <c r="E105" s="46"/>
+      <c r="C105" s="46"/>
+      <c r="D105" s="34"/>
+      <c r="E105" s="34"/>
       <c r="F105" s="42"/>
     </row>
     <row r="106" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B106" s="44"/>
-      <c r="C106" s="48"/>
-      <c r="D106" s="46"/>
+      <c r="C106" s="46"/>
+      <c r="D106" s="34"/>
       <c r="E106" s="3" t="s">
-        <v>220</v>
+        <v>188</v>
       </c>
       <c r="F106" s="42"/>
     </row>
     <row r="107" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B107" s="44"/>
-      <c r="C107" s="48"/>
-      <c r="D107" s="46"/>
+      <c r="C107" s="46"/>
+      <c r="D107" s="34"/>
       <c r="E107" s="3" t="s">
-        <v>221</v>
+        <v>189</v>
       </c>
       <c r="F107" s="42"/>
     </row>
     <row r="108" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B108" s="44"/>
-      <c r="C108" s="48"/>
-      <c r="D108" s="46"/>
+      <c r="C108" s="46"/>
+      <c r="D108" s="34"/>
       <c r="E108" s="3" t="s">
-        <v>222</v>
+        <v>190</v>
       </c>
       <c r="F108" s="42"/>
     </row>
     <row r="109" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B109" s="44"/>
-      <c r="C109" s="48"/>
-      <c r="D109" s="46"/>
+      <c r="C109" s="46"/>
+      <c r="D109" s="34"/>
       <c r="E109" s="3" t="s">
-        <v>223</v>
+        <v>191</v>
       </c>
       <c r="F109" s="42"/>
     </row>
     <row r="110" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B110" s="44"/>
-      <c r="C110" s="48"/>
-      <c r="D110" s="46"/>
+      <c r="C110" s="46"/>
+      <c r="D110" s="34"/>
       <c r="E110" s="3" t="s">
         <v>159</v>
       </c>
@@ -2450,17 +2457,17 @@
     </row>
     <row r="111" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B111" s="44"/>
-      <c r="C111" s="48"/>
-      <c r="D111" s="46"/>
+      <c r="C111" s="46"/>
+      <c r="D111" s="34"/>
       <c r="E111" s="3" t="s">
-        <v>224</v>
+        <v>192</v>
       </c>
       <c r="F111" s="42"/>
     </row>
     <row r="112" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B112" s="44"/>
-      <c r="C112" s="48"/>
-      <c r="D112" s="46"/>
+      <c r="C112" s="46"/>
+      <c r="D112" s="34"/>
       <c r="E112" s="3" t="s">
         <v>2</v>
       </c>
@@ -2468,53 +2475,53 @@
     </row>
     <row r="113" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B113" s="44"/>
-      <c r="C113" s="48"/>
-      <c r="D113" s="46"/>
+      <c r="C113" s="46"/>
+      <c r="D113" s="34"/>
       <c r="E113" s="7"/>
       <c r="F113" s="42"/>
     </row>
     <row r="114" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B114" s="44"/>
-      <c r="C114" s="48"/>
-      <c r="D114" s="46"/>
+      <c r="C114" s="46"/>
+      <c r="D114" s="34"/>
       <c r="E114" s="3" t="s">
-        <v>225</v>
+        <v>193</v>
       </c>
       <c r="F114" s="42"/>
     </row>
     <row r="115" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B115" s="44"/>
-      <c r="C115" s="48"/>
-      <c r="D115" s="46"/>
+      <c r="C115" s="46"/>
+      <c r="D115" s="34"/>
       <c r="E115" s="3" t="s">
-        <v>230</v>
+        <v>198</v>
       </c>
       <c r="F115" s="42"/>
     </row>
     <row r="116" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B116" s="44"/>
-      <c r="C116" s="48"/>
-      <c r="D116" s="46"/>
+      <c r="C116" s="46"/>
+      <c r="D116" s="34"/>
       <c r="E116" s="3" t="s">
-        <v>231</v>
+        <v>199</v>
       </c>
       <c r="F116" s="42"/>
     </row>
     <row r="117" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B117" s="44"/>
-      <c r="C117" s="48"/>
-      <c r="D117" s="46"/>
+      <c r="C117" s="46"/>
+      <c r="D117" s="34"/>
       <c r="E117" s="3" t="s">
-        <v>226</v>
+        <v>194</v>
       </c>
       <c r="F117" s="42"/>
     </row>
     <row r="118" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B118" s="44"/>
-      <c r="C118" s="48"/>
-      <c r="D118" s="46"/>
+      <c r="C118" s="46"/>
+      <c r="D118" s="34"/>
       <c r="E118" s="3" t="s">
-        <v>227</v>
+        <v>195</v>
       </c>
       <c r="F118" s="42"/>
     </row>
@@ -2527,12 +2534,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="E12:E19"/>
-    <mergeCell ref="E77:E82"/>
-    <mergeCell ref="C76:E76"/>
-    <mergeCell ref="D105:E105"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="D20:E20"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="F3:F119"/>
     <mergeCell ref="B3:B119"/>
@@ -2547,6 +2548,12 @@
     <mergeCell ref="C12:C75"/>
     <mergeCell ref="D21:D75"/>
     <mergeCell ref="C77:C96"/>
+    <mergeCell ref="E12:E19"/>
+    <mergeCell ref="E77:E82"/>
+    <mergeCell ref="C76:E76"/>
+    <mergeCell ref="D105:E105"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="D20:E20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2554,632 +2561,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F3342F1-B6E7-460B-9E26-5A8DC1C1AFB6}">
-  <dimension ref="B2:M35"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="3" max="4" width="49.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="37.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.5546875" customWidth="1"/>
-    <col min="11" max="11" width="4.5546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="39"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="41"/>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B3" s="44"/>
-      <c r="C3" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I3" s="42"/>
-      <c r="J3" s="67" t="s">
-        <v>235</v>
-      </c>
-      <c r="K3" s="68"/>
-      <c r="L3" s="69"/>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="44"/>
-      <c r="C4" s="32" t="s">
-        <v>238</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H4" s="3">
-        <v>2</v>
-      </c>
-      <c r="I4" s="42"/>
-      <c r="J4" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B5" s="44"/>
-      <c r="C5" s="71"/>
-      <c r="D5" s="71"/>
-      <c r="E5" s="71"/>
-      <c r="F5" s="71"/>
-      <c r="G5" s="71"/>
-      <c r="H5" s="71"/>
-      <c r="I5" s="42"/>
-      <c r="J5" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B6" s="44"/>
-      <c r="C6" s="72" t="s">
-        <v>241</v>
-      </c>
-      <c r="D6" s="48" t="s">
-        <v>100</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="F6" s="48" t="s">
-        <v>25</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H6" s="3">
-        <v>2</v>
-      </c>
-      <c r="I6" s="42"/>
-      <c r="J6" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B7" s="44"/>
-      <c r="C7" s="72"/>
-      <c r="D7" s="48"/>
-      <c r="E7" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F7" s="48"/>
-      <c r="G7" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H7" s="3">
-        <v>1</v>
-      </c>
-      <c r="I7" s="42"/>
-      <c r="J7" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B8" s="44"/>
-      <c r="C8" s="72"/>
-      <c r="D8" s="48"/>
-      <c r="E8" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="F8" s="48"/>
-      <c r="G8" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H8" s="3">
-        <v>1</v>
-      </c>
-      <c r="I8" s="42"/>
-      <c r="J8" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B9" s="44"/>
-      <c r="C9" s="72"/>
-      <c r="D9" s="48"/>
-      <c r="E9" s="46"/>
-      <c r="F9" s="46"/>
-      <c r="G9" s="46"/>
-      <c r="H9" s="46"/>
-      <c r="I9" s="42"/>
-      <c r="J9" s="33" t="s">
-        <v>39</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B10" s="44"/>
-      <c r="C10" s="72"/>
-      <c r="D10" s="48"/>
-      <c r="E10" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="F10" s="48" t="s">
-        <v>26</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H10" s="3">
-        <v>2</v>
-      </c>
-      <c r="I10" s="42"/>
-      <c r="J10" s="33" t="s">
-        <v>105</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B11" s="44"/>
-      <c r="C11" s="72"/>
-      <c r="D11" s="48"/>
-      <c r="E11" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F11" s="48"/>
-      <c r="G11" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="H11" s="3">
-        <v>1</v>
-      </c>
-      <c r="I11" s="42"/>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B12" s="44"/>
-      <c r="C12" s="72"/>
-      <c r="D12" s="48"/>
-      <c r="E12" s="46"/>
-      <c r="F12" s="46"/>
-      <c r="G12" s="46"/>
-      <c r="H12" s="46"/>
-      <c r="I12" s="42"/>
-    </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B13" s="44"/>
-      <c r="C13" s="72"/>
-      <c r="D13" s="48"/>
-      <c r="E13" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="H13" s="3">
-        <v>1</v>
-      </c>
-      <c r="I13" s="42"/>
-    </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B14" s="44"/>
-      <c r="C14" s="72"/>
-      <c r="D14" s="47"/>
-      <c r="E14" s="47"/>
-      <c r="F14" s="47"/>
-      <c r="G14" s="47"/>
-      <c r="H14" s="47"/>
-      <c r="I14" s="42"/>
-    </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B15" s="44"/>
-      <c r="C15" s="72"/>
-      <c r="D15" s="48" t="s">
-        <v>198</v>
-      </c>
-      <c r="E15" s="31" t="s">
-        <v>195</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H15" s="3">
-        <v>2</v>
-      </c>
-      <c r="I15" s="42"/>
-    </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B16" s="44"/>
-      <c r="C16" s="72"/>
-      <c r="D16" s="48"/>
-      <c r="E16" s="46"/>
-      <c r="F16" s="46"/>
-      <c r="G16" s="46"/>
-      <c r="H16" s="46"/>
-      <c r="I16" s="42"/>
-    </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B17" s="44"/>
-      <c r="C17" s="72"/>
-      <c r="D17" s="48"/>
-      <c r="E17" s="31" t="s">
-        <v>196</v>
-      </c>
-      <c r="F17" s="48" t="s">
-        <v>26</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H17" s="3">
-        <v>2</v>
-      </c>
-      <c r="I17" s="42"/>
-    </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B18" s="44"/>
-      <c r="C18" s="72"/>
-      <c r="D18" s="48"/>
-      <c r="E18" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="F18" s="48"/>
-      <c r="G18" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="H18" s="3">
-        <v>1</v>
-      </c>
-      <c r="I18" s="42"/>
-    </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B19" s="44"/>
-      <c r="C19" s="72"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="46"/>
-      <c r="F19" s="46"/>
-      <c r="G19" s="46"/>
-      <c r="H19" s="46"/>
-      <c r="I19" s="42"/>
-    </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B20" s="44"/>
-      <c r="C20" s="72"/>
-      <c r="D20" s="48"/>
-      <c r="E20" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="H20" s="3">
-        <v>1</v>
-      </c>
-      <c r="I20" s="42"/>
-    </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B21" s="44"/>
-      <c r="C21" s="72"/>
-      <c r="D21" s="47"/>
-      <c r="E21" s="47"/>
-      <c r="F21" s="47"/>
-      <c r="G21" s="47"/>
-      <c r="H21" s="47"/>
-      <c r="I21" s="42"/>
-    </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B22" s="44"/>
-      <c r="C22" s="72"/>
-      <c r="D22" s="48" t="s">
-        <v>199</v>
-      </c>
-      <c r="E22" s="31" t="s">
-        <v>195</v>
-      </c>
-      <c r="F22" s="48" t="s">
-        <v>25</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H22" s="3">
-        <v>2</v>
-      </c>
-      <c r="I22" s="42"/>
-    </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B23" s="44"/>
-      <c r="C23" s="72"/>
-      <c r="D23" s="48"/>
-      <c r="E23" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="F23" s="48"/>
-      <c r="G23" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="H23" s="3">
-        <v>1</v>
-      </c>
-      <c r="I23" s="42"/>
-    </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B24" s="44"/>
-      <c r="C24" s="72"/>
-      <c r="D24" s="48"/>
-      <c r="E24" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F24" s="48"/>
-      <c r="G24" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="H24" s="3">
-        <v>1</v>
-      </c>
-      <c r="I24" s="42"/>
-    </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B25" s="44"/>
-      <c r="C25" s="72"/>
-      <c r="D25" s="48"/>
-      <c r="E25" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="F25" s="48"/>
-      <c r="G25" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="H25" s="3">
-        <v>1</v>
-      </c>
-      <c r="I25" s="42"/>
-    </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B26" s="44"/>
-      <c r="C26" s="72"/>
-      <c r="D26" s="48"/>
-      <c r="E26" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F26" s="48"/>
-      <c r="G26" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="H26" s="3">
-        <v>1</v>
-      </c>
-      <c r="I26" s="42"/>
-    </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B27" s="44"/>
-      <c r="C27" s="72"/>
-      <c r="D27" s="48"/>
-      <c r="E27" s="46"/>
-      <c r="F27" s="46"/>
-      <c r="G27" s="46"/>
-      <c r="H27" s="46"/>
-      <c r="I27" s="42"/>
-    </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B28" s="44"/>
-      <c r="C28" s="72"/>
-      <c r="D28" s="48"/>
-      <c r="E28" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="H28" s="3">
-        <v>1</v>
-      </c>
-      <c r="I28" s="42"/>
-    </row>
-    <row r="29" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B29" s="44"/>
-      <c r="C29" s="72"/>
-      <c r="D29" s="48"/>
-      <c r="E29" s="46"/>
-      <c r="F29" s="46"/>
-      <c r="G29" s="46"/>
-      <c r="H29" s="46"/>
-      <c r="I29" s="42"/>
-    </row>
-    <row r="30" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B30" s="44"/>
-      <c r="C30" s="72"/>
-      <c r="D30" s="48"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="42"/>
-      <c r="J30" s="34" t="s">
-        <v>99</v>
-      </c>
-      <c r="K30" s="35" t="s">
-        <v>35</v>
-      </c>
-      <c r="L30" s="34" t="s">
-        <v>188</v>
-      </c>
-      <c r="M30" s="34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B31" s="44"/>
-      <c r="C31" s="72"/>
-      <c r="D31" s="47"/>
-      <c r="E31" s="47"/>
-      <c r="F31" s="47"/>
-      <c r="G31" s="47"/>
-      <c r="H31" s="47"/>
-      <c r="I31" s="42"/>
-    </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B32" s="44"/>
-      <c r="C32" s="72"/>
-      <c r="D32" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="H32" s="3">
-        <v>3</v>
-      </c>
-      <c r="I32" s="42"/>
-    </row>
-    <row r="33" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B33" s="44"/>
-      <c r="C33" s="70"/>
-      <c r="D33" s="70"/>
-      <c r="E33" s="70"/>
-      <c r="F33" s="70"/>
-      <c r="G33" s="70"/>
-      <c r="H33" s="70"/>
-      <c r="I33" s="42"/>
-    </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B34" s="44"/>
-      <c r="C34" s="32" t="s">
-        <v>242</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="E34" s="3"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
-      <c r="I34" s="42"/>
-    </row>
-    <row r="35" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B35" s="45"/>
-      <c r="C35" s="52"/>
-      <c r="D35" s="52"/>
-      <c r="E35" s="52"/>
-      <c r="F35" s="52"/>
-      <c r="G35" s="52"/>
-      <c r="H35" s="52"/>
-      <c r="I35" s="43"/>
-    </row>
-  </sheetData>
-  <mergeCells count="24">
-    <mergeCell ref="C6:C32"/>
-    <mergeCell ref="E27:H27"/>
-    <mergeCell ref="E29:H29"/>
-    <mergeCell ref="E9:H9"/>
-    <mergeCell ref="E12:H12"/>
-    <mergeCell ref="D6:D13"/>
-    <mergeCell ref="D15:D20"/>
-    <mergeCell ref="D22:D30"/>
-    <mergeCell ref="J3:L3"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B35:I35"/>
-    <mergeCell ref="B3:B34"/>
-    <mergeCell ref="I3:I34"/>
-    <mergeCell ref="C33:H33"/>
-    <mergeCell ref="D31:H31"/>
-    <mergeCell ref="F6:F8"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="F17:F18"/>
-    <mergeCell ref="F22:F26"/>
-    <mergeCell ref="E19:H19"/>
-    <mergeCell ref="E16:H16"/>
-    <mergeCell ref="C5:H5"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="D21:H21"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F6FFC68-BC6E-45A7-9925-0DFE4309B06B}">
   <dimension ref="B2:O34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3213,7 +2594,7 @@
     <row r="3" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B3" s="44"/>
       <c r="C3" s="65" t="s">
-        <v>234</v>
+        <v>202</v>
       </c>
       <c r="D3" s="65"/>
       <c r="E3" s="65"/>
@@ -3250,7 +2631,7 @@
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B5" s="44"/>
-      <c r="C5" s="46"/>
+      <c r="C5" s="34"/>
       <c r="D5" s="3" t="s">
         <v>10</v>
       </c>
@@ -3280,7 +2661,7 @@
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B6" s="44"/>
-      <c r="C6" s="46"/>
+      <c r="C6" s="34"/>
       <c r="D6" s="3" t="s">
         <v>10</v>
       </c>
@@ -3292,7 +2673,7 @@
         <v>62</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>212</v>
+        <v>243</v>
       </c>
       <c r="I6" s="53" t="s">
         <v>103</v>
@@ -3308,7 +2689,7 @@
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B7" s="44"/>
-      <c r="C7" s="46"/>
+      <c r="C7" s="34"/>
       <c r="D7" s="3" t="s">
         <v>10</v>
       </c>
@@ -3320,7 +2701,7 @@
         <v>45</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>213</v>
+        <v>242</v>
       </c>
       <c r="I7" s="53" t="s">
         <v>60</v>
@@ -3336,24 +2717,24 @@
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B8" s="44"/>
-      <c r="C8" s="51"/>
-      <c r="D8" s="51"/>
-      <c r="E8" s="51"/>
-      <c r="F8" s="51"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="51"/>
-      <c r="I8" s="51"/>
-      <c r="J8" s="51"/>
-      <c r="K8" s="51"/>
-      <c r="L8" s="51"/>
-      <c r="M8" s="51"/>
-      <c r="N8" s="51"/>
+      <c r="C8" s="67"/>
+      <c r="D8" s="67"/>
+      <c r="E8" s="67"/>
+      <c r="F8" s="67"/>
+      <c r="G8" s="67"/>
+      <c r="H8" s="67"/>
+      <c r="I8" s="67"/>
+      <c r="J8" s="67"/>
+      <c r="K8" s="67"/>
+      <c r="L8" s="67"/>
+      <c r="M8" s="67"/>
+      <c r="N8" s="67"/>
       <c r="O8" s="42"/>
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B9" s="44"/>
       <c r="C9" s="65" t="s">
-        <v>235</v>
+        <v>203</v>
       </c>
       <c r="D9" s="65"/>
       <c r="E9" s="65"/>
@@ -3380,13 +2761,13 @@
         <v>17</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>174</v>
+        <v>213</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>214</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>175</v>
+        <v>215</v>
       </c>
       <c r="I10" s="3">
         <v>142536748</v>
@@ -3397,7 +2778,7 @@
       <c r="K10" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="L10" s="12" t="s">
+      <c r="L10" s="11" t="s">
         <v>110</v>
       </c>
       <c r="M10" s="55" t="s">
@@ -3418,13 +2799,13 @@
         <v>19</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>178</v>
+        <v>216</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>177</v>
+        <v>217</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>176</v>
+        <v>233</v>
       </c>
       <c r="I11" s="3">
         <v>142536747</v>
@@ -3435,7 +2816,7 @@
       <c r="K11" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="L11" s="12" t="s">
+      <c r="L11" s="11" t="s">
         <v>111</v>
       </c>
       <c r="M11" s="55"/>
@@ -3454,13 +2835,13 @@
         <v>20</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>181</v>
+        <v>218</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>179</v>
+        <v>219</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="I12" s="3">
         <v>142536746</v>
@@ -3471,7 +2852,7 @@
       <c r="K12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="L12" s="12" t="s">
+      <c r="L12" s="11" t="s">
         <v>112</v>
       </c>
       <c r="M12" s="55"/>
@@ -3490,13 +2871,13 @@
         <v>30</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>182</v>
+        <v>221</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>183</v>
+        <v>222</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>184</v>
+        <v>223</v>
       </c>
       <c r="I13" s="3">
         <v>142536745</v>
@@ -3507,7 +2888,7 @@
       <c r="K13" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="L13" s="12" t="s">
+      <c r="L13" s="11" t="s">
         <v>113</v>
       </c>
       <c r="M13" s="55"/>
@@ -3526,13 +2907,13 @@
         <v>36</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>185</v>
+        <v>224</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>186</v>
+        <v>225</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>187</v>
+        <v>226</v>
       </c>
       <c r="I14" s="3">
         <v>142536744</v>
@@ -3543,7 +2924,7 @@
       <c r="K14" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="L14" s="12" t="s">
+      <c r="L14" s="11" t="s">
         <v>114</v>
       </c>
       <c r="M14" s="55"/>
@@ -3562,13 +2943,13 @@
         <v>39</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>188</v>
+        <v>229</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>189</v>
+        <v>227</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>190</v>
+        <v>228</v>
       </c>
       <c r="I15" s="3">
         <v>142536743</v>
@@ -3579,7 +2960,7 @@
       <c r="K15" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="L15" s="12" t="s">
+      <c r="L15" s="11" t="s">
         <v>115</v>
       </c>
       <c r="M15" s="55"/>
@@ -3596,13 +2977,13 @@
         <v>105</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="G16" s="10" t="s">
-        <v>192</v>
+        <v>230</v>
+      </c>
+      <c r="G16" t="s">
+        <v>231</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>193</v>
+        <v>232</v>
       </c>
       <c r="I16" s="3">
         <v>142536742</v>
@@ -3613,7 +2994,7 @@
       <c r="K16" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="L16" s="12" t="s">
+      <c r="L16" s="11" t="s">
         <v>116</v>
       </c>
       <c r="M16" s="55"/>
@@ -3622,24 +3003,24 @@
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B17" s="44"/>
-      <c r="C17" s="51"/>
-      <c r="D17" s="51"/>
-      <c r="E17" s="51"/>
-      <c r="F17" s="51"/>
-      <c r="G17" s="51"/>
-      <c r="H17" s="51"/>
-      <c r="I17" s="51"/>
-      <c r="J17" s="51"/>
-      <c r="K17" s="51"/>
-      <c r="L17" s="51"/>
-      <c r="M17" s="51"/>
-      <c r="N17" s="51"/>
+      <c r="C17" s="67"/>
+      <c r="D17" s="67"/>
+      <c r="E17" s="67"/>
+      <c r="F17" s="67"/>
+      <c r="G17" s="67"/>
+      <c r="H17" s="67"/>
+      <c r="I17" s="67"/>
+      <c r="J17" s="67"/>
+      <c r="K17" s="67"/>
+      <c r="L17" s="67"/>
+      <c r="M17" s="67"/>
+      <c r="N17" s="67"/>
       <c r="O17" s="42"/>
     </row>
     <row r="18" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B18" s="44"/>
       <c r="C18" s="65" t="s">
-        <v>236</v>
+        <v>204</v>
       </c>
       <c r="D18" s="65"/>
       <c r="E18" s="65"/>
@@ -3672,7 +3053,7 @@
         <v>91</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>204</v>
+        <v>234</v>
       </c>
       <c r="I19" s="3">
         <v>258963147</v>
@@ -3683,7 +3064,7 @@
       <c r="K19" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="L19" s="12" t="s">
+      <c r="L19" s="11" t="s">
         <v>117</v>
       </c>
       <c r="M19" s="55" t="s">
@@ -3710,7 +3091,7 @@
         <v>92</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>205</v>
+        <v>235</v>
       </c>
       <c r="I20" s="3">
         <v>241536789</v>
@@ -3721,7 +3102,7 @@
       <c r="K20" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="L20" s="12" t="s">
+      <c r="L20" s="11" t="s">
         <v>118</v>
       </c>
       <c r="M20" s="55"/>
@@ -3746,7 +3127,7 @@
         <v>93</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>206</v>
+        <v>236</v>
       </c>
       <c r="I21" s="3">
         <v>267489123</v>
@@ -3757,7 +3138,7 @@
       <c r="K21" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="L21" s="12" t="s">
+      <c r="L21" s="11" t="s">
         <v>117</v>
       </c>
       <c r="M21" s="55"/>
@@ -3769,31 +3150,31 @@
       <c r="C22" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D22" s="13" t="s">
+      <c r="D22" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="E22" s="13" t="s">
+      <c r="E22" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="F22" s="27">
+      <c r="F22" s="26">
         <v>20260004</v>
       </c>
-      <c r="G22" s="14" t="s">
+      <c r="G22" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="H22" s="13" t="s">
-        <v>207</v>
-      </c>
-      <c r="I22" s="13">
+      <c r="H22" s="12" t="s">
+        <v>237</v>
+      </c>
+      <c r="I22" s="12">
         <v>233654789</v>
       </c>
-      <c r="J22" s="13" t="s">
+      <c r="J22" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K22" s="13" t="s">
+      <c r="K22" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="L22" s="15" t="s">
+      <c r="L22" s="14" t="s">
         <v>119</v>
       </c>
       <c r="M22" s="55"/>
@@ -3805,31 +3186,31 @@
       <c r="C23" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D23" s="16" t="s">
+      <c r="D23" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="E23" s="16" t="s">
+      <c r="E23" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="F23" s="28">
+      <c r="F23" s="27">
         <v>20260005</v>
       </c>
-      <c r="G23" s="17" t="s">
+      <c r="G23" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="H23" s="16" t="s">
-        <v>208</v>
-      </c>
-      <c r="I23" s="16">
+      <c r="H23" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="I23" s="15">
         <v>259874123</v>
       </c>
-      <c r="J23" s="16" t="s">
+      <c r="J23" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="K23" s="16" t="s">
+      <c r="K23" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="L23" s="18" t="s">
+      <c r="L23" s="17" t="s">
         <v>120</v>
       </c>
       <c r="M23" s="55"/>
@@ -3841,31 +3222,31 @@
       <c r="C24" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D24" s="19" t="s">
+      <c r="D24" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="E24" s="19" t="s">
+      <c r="E24" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="F24" s="29">
+      <c r="F24" s="28">
         <v>20260006</v>
       </c>
-      <c r="G24" s="20" t="s">
+      <c r="G24" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="H24" s="21" t="s">
-        <v>209</v>
-      </c>
-      <c r="I24" s="19">
+      <c r="H24" s="20" t="s">
+        <v>239</v>
+      </c>
+      <c r="I24" s="18">
         <v>210456789</v>
       </c>
-      <c r="J24" s="19" t="s">
+      <c r="J24" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="K24" s="19" t="s">
+      <c r="K24" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="L24" s="22" t="s">
+      <c r="L24" s="21" t="s">
         <v>121</v>
       </c>
       <c r="M24" s="55"/>
@@ -3874,34 +3255,34 @@
     </row>
     <row r="25" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B25" s="44"/>
-      <c r="C25" s="23" t="s">
+      <c r="C25" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="D25" s="23" t="s">
+      <c r="D25" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="E25" s="23" t="s">
+      <c r="E25" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="F25" s="30">
+      <c r="F25" s="29">
         <v>20260007</v>
       </c>
       <c r="G25" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="H25" s="24" t="s">
-        <v>210</v>
-      </c>
-      <c r="I25" s="23">
+      <c r="H25" s="23" t="s">
+        <v>240</v>
+      </c>
+      <c r="I25" s="22">
         <v>225147896</v>
       </c>
-      <c r="J25" s="23" t="s">
+      <c r="J25" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="K25" s="23" t="s">
-        <v>239</v>
-      </c>
-      <c r="L25" s="25" t="s">
+      <c r="K25" s="22" t="s">
+        <v>207</v>
+      </c>
+      <c r="L25" s="70" t="s">
         <v>122</v>
       </c>
       <c r="M25" s="55"/>
@@ -3910,34 +3291,34 @@
     </row>
     <row r="26" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B26" s="44"/>
-      <c r="C26" s="23" t="s">
+      <c r="C26" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="D26" s="23" t="s">
+      <c r="D26" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="E26" s="23" t="s">
+      <c r="E26" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="F26" s="30">
+      <c r="F26" s="29">
         <v>20260008</v>
       </c>
       <c r="G26" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="H26" s="24" t="s">
-        <v>211</v>
-      </c>
-      <c r="I26" s="23">
+      <c r="H26" s="23" t="s">
+        <v>241</v>
+      </c>
+      <c r="I26" s="22">
         <v>278963254</v>
       </c>
-      <c r="J26" s="23" t="s">
+      <c r="J26" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="K26" s="23" t="s">
-        <v>239</v>
-      </c>
-      <c r="L26" s="25" t="s">
+      <c r="K26" s="22" t="s">
+        <v>207</v>
+      </c>
+      <c r="L26" s="24" t="s">
         <v>123</v>
       </c>
       <c r="M26" s="55"/>
@@ -3955,7 +3336,7 @@
       </c>
       <c r="F27" s="6"/>
       <c r="G27" s="10"/>
-      <c r="H27" s="26"/>
+      <c r="H27" s="25"/>
       <c r="I27" s="3">
         <v>244123654</v>
       </c>
@@ -3963,7 +3344,7 @@
         <v>77</v>
       </c>
       <c r="K27" s="3"/>
-      <c r="L27" s="12" t="s">
+      <c r="L27" s="11" t="s">
         <v>124</v>
       </c>
       <c r="M27" s="55"/>
@@ -3981,7 +3362,7 @@
       </c>
       <c r="F28" s="6"/>
       <c r="G28" s="10"/>
-      <c r="H28" s="26"/>
+      <c r="H28" s="25"/>
       <c r="I28" s="3">
         <v>251478963</v>
       </c>
@@ -3989,7 +3370,7 @@
         <v>79</v>
       </c>
       <c r="K28" s="3"/>
-      <c r="L28" s="12" t="s">
+      <c r="L28" s="11" t="s">
         <v>125</v>
       </c>
       <c r="M28" s="55"/>
@@ -4007,7 +3388,7 @@
       </c>
       <c r="F29" s="6"/>
       <c r="G29" s="10"/>
-      <c r="H29" s="26"/>
+      <c r="H29" s="25"/>
       <c r="I29" s="3">
         <v>266321458</v>
       </c>
@@ -4015,7 +3396,7 @@
         <v>81</v>
       </c>
       <c r="K29" s="3"/>
-      <c r="L29" s="12" t="s">
+      <c r="L29" s="11" t="s">
         <v>126</v>
       </c>
       <c r="M29" s="55"/>
@@ -4033,7 +3414,7 @@
       </c>
       <c r="F30" s="6"/>
       <c r="G30" s="3"/>
-      <c r="H30" s="26"/>
+      <c r="H30" s="25"/>
       <c r="I30" s="3">
         <v>239852147</v>
       </c>
@@ -4041,7 +3422,7 @@
         <v>83</v>
       </c>
       <c r="K30" s="3"/>
-      <c r="L30" s="12" t="s">
+      <c r="L30" s="11" t="s">
         <v>127</v>
       </c>
       <c r="M30" s="55"/>
@@ -4059,7 +3440,7 @@
       </c>
       <c r="F31" s="6"/>
       <c r="G31" s="3"/>
-      <c r="H31" s="26"/>
+      <c r="H31" s="25"/>
       <c r="I31" s="3">
         <v>288741256</v>
       </c>
@@ -4067,7 +3448,7 @@
         <v>85</v>
       </c>
       <c r="K31" s="3"/>
-      <c r="L31" s="12" t="s">
+      <c r="L31" s="11" t="s">
         <v>128</v>
       </c>
       <c r="M31" s="55"/>
@@ -4085,7 +3466,7 @@
       </c>
       <c r="F32" s="6"/>
       <c r="G32" s="3"/>
-      <c r="H32" s="26"/>
+      <c r="H32" s="25"/>
       <c r="I32" s="3">
         <v>255698147</v>
       </c>
@@ -4093,7 +3474,7 @@
         <v>87</v>
       </c>
       <c r="K32" s="3"/>
-      <c r="L32" s="12" t="s">
+      <c r="L32" s="11" t="s">
         <v>129</v>
       </c>
       <c r="M32" s="55"/>
@@ -4119,7 +3500,7 @@
         <v>89</v>
       </c>
       <c r="K33" s="3"/>
-      <c r="L33" s="12" t="s">
+      <c r="L33" s="11" t="s">
         <v>130</v>
       </c>
       <c r="M33" s="55"/>
@@ -4128,22 +3509,28 @@
     </row>
     <row r="34" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B34" s="45"/>
-      <c r="C34" s="52"/>
-      <c r="D34" s="52"/>
-      <c r="E34" s="52"/>
-      <c r="F34" s="52"/>
-      <c r="G34" s="52"/>
-      <c r="H34" s="52"/>
-      <c r="I34" s="52"/>
-      <c r="J34" s="52"/>
-      <c r="K34" s="52"/>
-      <c r="L34" s="52"/>
-      <c r="M34" s="52"/>
-      <c r="N34" s="52"/>
+      <c r="C34" s="50"/>
+      <c r="D34" s="50"/>
+      <c r="E34" s="50"/>
+      <c r="F34" s="50"/>
+      <c r="G34" s="50"/>
+      <c r="H34" s="50"/>
+      <c r="I34" s="50"/>
+      <c r="J34" s="50"/>
+      <c r="K34" s="50"/>
+      <c r="L34" s="50"/>
+      <c r="M34" s="50"/>
+      <c r="N34" s="50"/>
       <c r="O34" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B2:O2"/>
+    <mergeCell ref="O3:O33"/>
+    <mergeCell ref="B3:B33"/>
+    <mergeCell ref="C8:N8"/>
+    <mergeCell ref="C17:N17"/>
+    <mergeCell ref="C3:N3"/>
     <mergeCell ref="B34:O34"/>
     <mergeCell ref="I7:J7"/>
     <mergeCell ref="I5:J5"/>
@@ -4155,38 +3542,759 @@
     <mergeCell ref="C9:N9"/>
     <mergeCell ref="C5:C7"/>
     <mergeCell ref="F5:F7"/>
-    <mergeCell ref="B2:O2"/>
-    <mergeCell ref="O3:O33"/>
-    <mergeCell ref="B3:B33"/>
-    <mergeCell ref="C8:N8"/>
-    <mergeCell ref="C17:N17"/>
-    <mergeCell ref="C3:N3"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="G4" r:id="rId1" xr:uid="{90136737-50D8-4624-BF9F-7BB076958402}"/>
     <hyperlink ref="G5" r:id="rId2" xr:uid="{9B3EB29C-D4D1-4DE8-950C-D636533C4ACC}"/>
-    <hyperlink ref="G10" r:id="rId3" xr:uid="{9DB0FA28-5476-41E6-A22A-0FE2AB0E3D78}"/>
-    <hyperlink ref="L5" r:id="rId4" xr:uid="{4CEB1E42-A151-45A2-9B0C-B4A90B4D0D5F}"/>
-    <hyperlink ref="G11" r:id="rId5" xr:uid="{D665EDE0-327E-4FA6-8FFA-BBB4E2AD16BE}"/>
-    <hyperlink ref="G12" r:id="rId6" xr:uid="{60E685BC-23C7-4334-9747-091601A99EF8}"/>
-    <hyperlink ref="G13" r:id="rId7" xr:uid="{DE1AFF63-932A-44A1-8199-E076E5122B2E}"/>
-    <hyperlink ref="G14" r:id="rId8" xr:uid="{96F76F7C-CD0B-4492-9177-4EA32F927FED}"/>
-    <hyperlink ref="G15" r:id="rId9" xr:uid="{4E73F26C-D44B-43E8-BE11-AC15CAC3B84C}"/>
-    <hyperlink ref="G16" r:id="rId10" xr:uid="{3744A8CF-A7F6-48D7-AB83-F4CD2BAEE4D0}"/>
-    <hyperlink ref="G19" r:id="rId11" xr:uid="{19ED9BF7-712A-4DC1-8755-8EF0FCFF0B53}"/>
-    <hyperlink ref="G20" r:id="rId12" xr:uid="{73FA2062-31DC-43F6-87BF-4CAD4118EDC0}"/>
-    <hyperlink ref="G21" r:id="rId13" xr:uid="{C9A706E5-980E-4F35-AC05-0CAA97DB6C86}"/>
-    <hyperlink ref="G22" r:id="rId14" xr:uid="{1638B543-22A0-4123-BFF1-150CE5050E28}"/>
-    <hyperlink ref="G23" r:id="rId15" xr:uid="{D691BEA8-794F-47A6-A4F5-E83DC2372430}"/>
-    <hyperlink ref="G24" r:id="rId16" xr:uid="{10013824-D875-4ED4-BB1D-3CB1D985BC39}"/>
-    <hyperlink ref="G25" r:id="rId17" xr:uid="{0ABFA8B0-714A-4556-B801-F31F8ACC5FCF}"/>
-    <hyperlink ref="G26" r:id="rId18" xr:uid="{B7F3917F-0DF5-41C1-AA91-81F7691BF7EE}"/>
-    <hyperlink ref="G6" r:id="rId19" xr:uid="{BCAA6600-DE24-422D-96D4-0791B494C9D2}"/>
-    <hyperlink ref="G7" r:id="rId20" xr:uid="{EAF8ADB9-58E9-4CBC-AAD5-DA37B223DFD2}"/>
-    <hyperlink ref="M10" r:id="rId21" xr:uid="{889087D1-E240-4465-90CC-97DF6ABEF439}"/>
-    <hyperlink ref="M19" r:id="rId22" xr:uid="{6FC1A60E-B0CE-457F-BEEE-3AC36283B66B}"/>
+    <hyperlink ref="L5" r:id="rId3" xr:uid="{4CEB1E42-A151-45A2-9B0C-B4A90B4D0D5F}"/>
+    <hyperlink ref="G19" r:id="rId4" xr:uid="{19ED9BF7-712A-4DC1-8755-8EF0FCFF0B53}"/>
+    <hyperlink ref="G20" r:id="rId5" xr:uid="{73FA2062-31DC-43F6-87BF-4CAD4118EDC0}"/>
+    <hyperlink ref="G21" r:id="rId6" xr:uid="{C9A706E5-980E-4F35-AC05-0CAA97DB6C86}"/>
+    <hyperlink ref="G22" r:id="rId7" xr:uid="{1638B543-22A0-4123-BFF1-150CE5050E28}"/>
+    <hyperlink ref="G23" r:id="rId8" xr:uid="{D691BEA8-794F-47A6-A4F5-E83DC2372430}"/>
+    <hyperlink ref="G24" r:id="rId9" xr:uid="{10013824-D875-4ED4-BB1D-3CB1D985BC39}"/>
+    <hyperlink ref="G25" r:id="rId10" xr:uid="{0ABFA8B0-714A-4556-B801-F31F8ACC5FCF}"/>
+    <hyperlink ref="G26" r:id="rId11" xr:uid="{B7F3917F-0DF5-41C1-AA91-81F7691BF7EE}"/>
+    <hyperlink ref="G6" r:id="rId12" xr:uid="{BCAA6600-DE24-422D-96D4-0791B494C9D2}"/>
+    <hyperlink ref="G7" r:id="rId13" xr:uid="{EAF8ADB9-58E9-4CBC-AAD5-DA37B223DFD2}"/>
+    <hyperlink ref="M10" r:id="rId14" xr:uid="{889087D1-E240-4465-90CC-97DF6ABEF439}"/>
+    <hyperlink ref="G10" r:id="rId15" xr:uid="{BF051BD1-75FB-4461-962C-7EF5E5C1AE60}"/>
+    <hyperlink ref="G11" r:id="rId16" xr:uid="{140DDC62-C64B-477C-A68A-862BD945F18D}"/>
+    <hyperlink ref="G12" r:id="rId17" xr:uid="{852FABFE-D926-4FF9-88CA-E3EE084E98A0}"/>
+    <hyperlink ref="G13" r:id="rId18" xr:uid="{93C9AE13-3AEE-4784-B47E-237396405ABB}"/>
+    <hyperlink ref="G14" r:id="rId19" xr:uid="{7BFFBDC4-2665-4081-9203-07EDBD46AD4A}"/>
+    <hyperlink ref="G15" r:id="rId20" xr:uid="{C36D3D31-89F6-4BF8-8D42-4F100C606AB9}"/>
+    <hyperlink ref="M19" r:id="rId21" xr:uid="{6FC1A60E-B0CE-457F-BEEE-3AC36283B66B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId23"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId22"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F3342F1-B6E7-460B-9E26-5A8DC1C1AFB6}">
+  <dimension ref="B2:O35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="4" width="49.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="37.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.21875" style="1" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.5546875" customWidth="1"/>
+    <col min="12" max="12" width="4.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.21875" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="8" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B2" s="39"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="41"/>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B3" s="44"/>
+      <c r="C3" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" s="68"/>
+      <c r="K3" s="36" t="s">
+        <v>203</v>
+      </c>
+      <c r="L3" s="36"/>
+      <c r="M3" s="36"/>
+      <c r="N3" s="36"/>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B4" s="44"/>
+      <c r="C4" s="31" t="s">
+        <v>206</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" s="3" t="str">
+        <f>VLOOKUP(G4,K$4:L$10,2,FALSE)</f>
+        <v>PHH</v>
+      </c>
+      <c r="I4" s="3">
+        <v>2</v>
+      </c>
+      <c r="J4" s="42"/>
+      <c r="K4" s="69" t="s">
+        <v>17</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="M4" s="3"/>
+      <c r="N4" s="69" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B5" s="44"/>
+      <c r="C5" s="52"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
+      <c r="F5" s="52"/>
+      <c r="G5" s="52"/>
+      <c r="H5" s="52"/>
+      <c r="I5" s="52"/>
+      <c r="J5" s="42"/>
+      <c r="K5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B6" s="44"/>
+      <c r="C6" s="49" t="s">
+        <v>209</v>
+      </c>
+      <c r="D6" s="46" t="s">
+        <v>100</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="F6" s="46" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" s="3" t="str">
+        <f>VLOOKUP(G6,K$4:L$10,2,FALSE)</f>
+        <v>PHH</v>
+      </c>
+      <c r="I6" s="3">
+        <v>2</v>
+      </c>
+      <c r="J6" s="42"/>
+      <c r="K6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B7" s="44"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" s="46"/>
+      <c r="G7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7" s="3" t="str">
+        <f>VLOOKUP(G7,K$4:L$10,2,FALSE)</f>
+        <v>PKF</v>
+      </c>
+      <c r="I7" s="3">
+        <v>1</v>
+      </c>
+      <c r="J7" s="42"/>
+      <c r="K7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B8" s="44"/>
+      <c r="C8" s="49"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="F8" s="46"/>
+      <c r="G8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" s="3" t="str">
+        <f>VLOOKUP(G8,K$4:L$10,2,FALSE)</f>
+        <v>PKF</v>
+      </c>
+      <c r="I8" s="3">
+        <v>1</v>
+      </c>
+      <c r="J8" s="42"/>
+      <c r="K8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B9" s="44"/>
+      <c r="C9" s="49"/>
+      <c r="D9" s="46"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="34"/>
+      <c r="H9" s="34"/>
+      <c r="I9" s="34"/>
+      <c r="J9" s="42"/>
+      <c r="K9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B10" s="44"/>
+      <c r="C10" s="49"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F10" s="46" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H10" s="3" t="str">
+        <f>VLOOKUP(G10,K$4:L$10,2,FALSE)</f>
+        <v>PHH</v>
+      </c>
+      <c r="I10" s="3">
+        <v>2</v>
+      </c>
+      <c r="J10" s="42"/>
+      <c r="K10" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B11" s="44"/>
+      <c r="C11" s="49"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" s="46"/>
+      <c r="G11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H11" s="3" t="str">
+        <f>VLOOKUP(G11,K$4:L$10,2,FALSE)</f>
+        <v>PTW</v>
+      </c>
+      <c r="I11" s="3">
+        <v>1</v>
+      </c>
+      <c r="J11" s="42"/>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B12" s="44"/>
+      <c r="C12" s="49"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="34"/>
+      <c r="I12" s="34"/>
+      <c r="J12" s="42"/>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B13" s="44"/>
+      <c r="C13" s="49"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H13" s="3" t="str">
+        <f>VLOOKUP(G13,K$4:L$10,2,FALSE)</f>
+        <v>PTW</v>
+      </c>
+      <c r="I13" s="3">
+        <v>1</v>
+      </c>
+      <c r="J13" s="42"/>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B14" s="44"/>
+      <c r="C14" s="49"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="35"/>
+      <c r="I14" s="35"/>
+      <c r="J14" s="42"/>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B15" s="44"/>
+      <c r="C15" s="49"/>
+      <c r="D15" s="46" t="s">
+        <v>177</v>
+      </c>
+      <c r="E15" s="30" t="s">
+        <v>174</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H15" s="3" t="str">
+        <f>VLOOKUP(G15,K$4:L$10,2,FALSE)</f>
+        <v>PHH</v>
+      </c>
+      <c r="I15" s="3">
+        <v>2</v>
+      </c>
+      <c r="J15" s="42"/>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B16" s="44"/>
+      <c r="C16" s="49"/>
+      <c r="D16" s="46"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="34"/>
+      <c r="G16" s="34"/>
+      <c r="H16" s="34"/>
+      <c r="I16" s="34"/>
+      <c r="J16" s="42"/>
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B17" s="44"/>
+      <c r="C17" s="49"/>
+      <c r="D17" s="46"/>
+      <c r="E17" s="30" t="s">
+        <v>175</v>
+      </c>
+      <c r="F17" s="46" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H17" s="3" t="str">
+        <f>VLOOKUP(G17,K$4:L$10,2,FALSE)</f>
+        <v>PHH</v>
+      </c>
+      <c r="I17" s="3">
+        <v>2</v>
+      </c>
+      <c r="J17" s="42"/>
+    </row>
+    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B18" s="44"/>
+      <c r="C18" s="49"/>
+      <c r="D18" s="46"/>
+      <c r="E18" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="F18" s="46"/>
+      <c r="G18" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H18" s="3" t="str">
+        <f>VLOOKUP(G18,K$4:L$10,2,FALSE)</f>
+        <v>PIW</v>
+      </c>
+      <c r="I18" s="3">
+        <v>1</v>
+      </c>
+      <c r="J18" s="42"/>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B19" s="44"/>
+      <c r="C19" s="49"/>
+      <c r="D19" s="46"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="34"/>
+      <c r="H19" s="34"/>
+      <c r="I19" s="34"/>
+      <c r="J19" s="42"/>
+    </row>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B20" s="44"/>
+      <c r="C20" s="49"/>
+      <c r="D20" s="46"/>
+      <c r="E20" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H20" s="3" t="str">
+        <f>VLOOKUP(G20,K$4:L$10,2,FALSE)</f>
+        <v>PIW</v>
+      </c>
+      <c r="I20" s="3">
+        <v>1</v>
+      </c>
+      <c r="J20" s="42"/>
+    </row>
+    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B21" s="44"/>
+      <c r="C21" s="49"/>
+      <c r="D21" s="35"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="35"/>
+      <c r="G21" s="35"/>
+      <c r="H21" s="35"/>
+      <c r="I21" s="35"/>
+      <c r="J21" s="42"/>
+    </row>
+    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B22" s="44"/>
+      <c r="C22" s="49"/>
+      <c r="D22" s="46" t="s">
+        <v>178</v>
+      </c>
+      <c r="E22" s="30" t="s">
+        <v>174</v>
+      </c>
+      <c r="F22" s="46" t="s">
+        <v>25</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H22" s="3" t="str">
+        <f>VLOOKUP(G22,K$4:L$10,2,FALSE)</f>
+        <v>PHH</v>
+      </c>
+      <c r="I22" s="3">
+        <v>2</v>
+      </c>
+      <c r="J22" s="42"/>
+    </row>
+    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B23" s="44"/>
+      <c r="C23" s="49"/>
+      <c r="D23" s="46"/>
+      <c r="E23" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="F23" s="46"/>
+      <c r="G23" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H23" s="3" t="str">
+        <f>VLOOKUP(G23,K$4:L$10,2,FALSE)</f>
+        <v>PBR</v>
+      </c>
+      <c r="I23" s="3">
+        <v>1</v>
+      </c>
+      <c r="J23" s="42"/>
+    </row>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B24" s="44"/>
+      <c r="C24" s="49"/>
+      <c r="D24" s="46"/>
+      <c r="E24" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F24" s="46"/>
+      <c r="G24" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H24" s="3" t="str">
+        <f>VLOOKUP(G24,K$4:L$10,2,FALSE)</f>
+        <v>PBR</v>
+      </c>
+      <c r="I24" s="3">
+        <v>1</v>
+      </c>
+      <c r="J24" s="42"/>
+    </row>
+    <row r="25" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B25" s="44"/>
+      <c r="C25" s="49"/>
+      <c r="D25" s="46"/>
+      <c r="E25" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="F25" s="46"/>
+      <c r="G25" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H25" s="3" t="str">
+        <f>VLOOKUP(G25,K$4:L$10,2,FALSE)</f>
+        <v>PBR</v>
+      </c>
+      <c r="I25" s="3">
+        <v>1</v>
+      </c>
+      <c r="J25" s="42"/>
+    </row>
+    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B26" s="44"/>
+      <c r="C26" s="49"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F26" s="46"/>
+      <c r="G26" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H26" s="3" t="str">
+        <f>VLOOKUP(G26,K$4:L$10,2,FALSE)</f>
+        <v>PBR</v>
+      </c>
+      <c r="I26" s="3">
+        <v>1</v>
+      </c>
+      <c r="J26" s="42"/>
+    </row>
+    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B27" s="44"/>
+      <c r="C27" s="49"/>
+      <c r="D27" s="46"/>
+      <c r="E27" s="34"/>
+      <c r="F27" s="34"/>
+      <c r="G27" s="34"/>
+      <c r="H27" s="34"/>
+      <c r="I27" s="34"/>
+      <c r="J27" s="42"/>
+    </row>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B28" s="44"/>
+      <c r="C28" s="49"/>
+      <c r="D28" s="46"/>
+      <c r="E28" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H28" s="3" t="str">
+        <f>VLOOKUP(G28,K$4:L$10,2,FALSE)</f>
+        <v>PBR</v>
+      </c>
+      <c r="I28" s="3">
+        <v>1</v>
+      </c>
+      <c r="J28" s="42"/>
+    </row>
+    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B29" s="44"/>
+      <c r="C29" s="49"/>
+      <c r="D29" s="46"/>
+      <c r="E29" s="34"/>
+      <c r="F29" s="34"/>
+      <c r="G29" s="34"/>
+      <c r="H29" s="34"/>
+      <c r="I29" s="34"/>
+      <c r="J29" s="42"/>
+    </row>
+    <row r="30" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B30" s="44"/>
+      <c r="C30" s="49"/>
+      <c r="D30" s="46"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G30" s="4"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
+      <c r="J30" s="42"/>
+      <c r="K30" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="L30" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="M30" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="N30" s="3" t="str">
+        <f>VLOOKUP(M30,K$4:N$10,2,FALSE)</f>
+        <v>PBR</v>
+      </c>
+      <c r="O30" s="32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B31" s="44"/>
+      <c r="C31" s="49"/>
+      <c r="D31" s="35"/>
+      <c r="E31" s="35"/>
+      <c r="F31" s="35"/>
+      <c r="G31" s="35"/>
+      <c r="H31" s="35"/>
+      <c r="I31" s="35"/>
+      <c r="J31" s="42"/>
+    </row>
+    <row r="32" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B32" s="44"/>
+      <c r="C32" s="49"/>
+      <c r="D32" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H32" s="3" t="str">
+        <f>VLOOKUP(G32,K$4:L$10,2,FALSE)</f>
+        <v>PDU</v>
+      </c>
+      <c r="I32" s="3">
+        <v>3</v>
+      </c>
+      <c r="J32" s="42"/>
+    </row>
+    <row r="33" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B33" s="44"/>
+      <c r="C33" s="51"/>
+      <c r="D33" s="51"/>
+      <c r="E33" s="51"/>
+      <c r="F33" s="51"/>
+      <c r="G33" s="51"/>
+      <c r="H33" s="51"/>
+      <c r="I33" s="51"/>
+      <c r="J33" s="42"/>
+    </row>
+    <row r="34" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B34" s="44"/>
+      <c r="C34" s="31" t="s">
+        <v>210</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="E34" s="3"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
+      <c r="J34" s="42"/>
+    </row>
+    <row r="35" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B35" s="45"/>
+      <c r="C35" s="50"/>
+      <c r="D35" s="50"/>
+      <c r="E35" s="50"/>
+      <c r="F35" s="50"/>
+      <c r="G35" s="50"/>
+      <c r="H35" s="50"/>
+      <c r="I35" s="50"/>
+      <c r="J35" s="43"/>
+    </row>
+  </sheetData>
+  <mergeCells count="24">
+    <mergeCell ref="K3:N3"/>
+    <mergeCell ref="B2:J2"/>
+    <mergeCell ref="B35:J35"/>
+    <mergeCell ref="B3:B34"/>
+    <mergeCell ref="J3:J34"/>
+    <mergeCell ref="C33:I33"/>
+    <mergeCell ref="D31:I31"/>
+    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="F22:F26"/>
+    <mergeCell ref="E19:I19"/>
+    <mergeCell ref="E16:I16"/>
+    <mergeCell ref="C5:I5"/>
+    <mergeCell ref="D14:I14"/>
+    <mergeCell ref="D21:I21"/>
+    <mergeCell ref="C6:C32"/>
+    <mergeCell ref="E27:I27"/>
+    <mergeCell ref="E29:I29"/>
+    <mergeCell ref="E9:I9"/>
+    <mergeCell ref="E12:I12"/>
+    <mergeCell ref="D6:D13"/>
+    <mergeCell ref="D15:D20"/>
+    <mergeCell ref="D22:D30"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Testes.xlsx
+++ b/Testes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\utilizador\Documents\CTESP\4semestre\LP2\ProjetoTesteLP2\TrabalhoTesteLP2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1449C5A4-D388-4B24-9534-489117247C7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7DC74CE1-F1E8-4357-A95F-DBD58EF78C1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38940" yWindow="-3750" windowWidth="10185" windowHeight="10905" activeTab="1" xr2:uid="{17050BBC-8C72-4C7C-BB9E-52ED50A4B6E1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{17050BBC-8C72-4C7C-BB9E-52ED50A4B6E1}"/>
   </bookViews>
   <sheets>
     <sheet name="Menus" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="Escola" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="181029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="241">
   <si>
     <t>1 - Adicionar Departamento</t>
   </si>
@@ -230,12 +231,6 @@
     <t>Coimbra</t>
   </si>
   <si>
-    <t>Cláudio Renato Silva</t>
-  </si>
-  <si>
-    <t>Aveiro</t>
-  </si>
-  <si>
     <t>Daniela Filipa Pires</t>
   </si>
   <si>
@@ -323,9 +318,6 @@
     <t>20260007@issmf.ipp.pt</t>
   </si>
   <si>
-    <t>20260008@issmf.ipp.pt</t>
-  </si>
-  <si>
     <t>[ATIVO] SIE : Sistemas de Energia</t>
   </si>
   <si>
@@ -396,9 +388,6 @@
   </si>
   <si>
     <t>14-06-2004</t>
-  </si>
-  <si>
-    <t>22-12-2003</t>
   </si>
   <si>
     <t>08-04-2002</t>
@@ -670,106 +659,106 @@
     <t>[INATIVO] REA1 : Reatores 1</t>
   </si>
   <si>
-    <t>PKF</t>
-  </si>
-  <si>
-    <t>pkf@issmf.ipp.pt</t>
-  </si>
-  <si>
-    <t>GzZvpVu3</t>
-  </si>
-  <si>
-    <t>PHH</t>
-  </si>
-  <si>
-    <t>phh@issmf.ipp.pt</t>
-  </si>
-  <si>
-    <t>PDU</t>
-  </si>
-  <si>
-    <t>pdu@issmf.ipp.pt</t>
-  </si>
-  <si>
-    <t>RgbjQBEq</t>
-  </si>
-  <si>
-    <t>PTW</t>
-  </si>
-  <si>
-    <t>ptw@issmf.ipp.pt</t>
-  </si>
-  <si>
-    <t>5kHRR2MS</t>
-  </si>
-  <si>
-    <t>PIW</t>
-  </si>
-  <si>
-    <t>piw@issmf.ipp.pt</t>
-  </si>
-  <si>
-    <t>nsNDz5jU</t>
-  </si>
-  <si>
-    <t>pbr@issmf.ipp.pt</t>
-  </si>
-  <si>
-    <t>rUU3Zypq</t>
-  </si>
-  <si>
-    <t>PBR</t>
-  </si>
-  <si>
-    <t>PAY</t>
-  </si>
-  <si>
-    <t>pay@issmf.ipp.pt</t>
-  </si>
-  <si>
-    <t>emvUipW5</t>
-  </si>
-  <si>
-    <t>uGGeeIQK</t>
-  </si>
-  <si>
-    <t>tUI7CGjC</t>
-  </si>
-  <si>
-    <t>DfgH3J7f</t>
-  </si>
-  <si>
-    <t>ZFymXJYt</t>
-  </si>
-  <si>
-    <t>5RE65Aos</t>
-  </si>
-  <si>
-    <t>Pffw8aDE</t>
-  </si>
-  <si>
-    <t>5EYoKChp</t>
-  </si>
-  <si>
-    <t>miBfIPQ8</t>
-  </si>
-  <si>
-    <t>J0NvIfDG</t>
-  </si>
-  <si>
-    <t>ZESsuAJn</t>
-  </si>
-  <si>
-    <t>D3EyYfxw</t>
+    <t>[INATIVO] DCS : Departamento de Ciencias Sociais</t>
+  </si>
+  <si>
+    <t>pbe@issmf.ipp.pt</t>
+  </si>
+  <si>
+    <t>PBE</t>
+  </si>
+  <si>
+    <t>22-02-2003</t>
+  </si>
+  <si>
+    <t>vC9Rv6K2</t>
+  </si>
+  <si>
+    <t>gYr6lZ0I</t>
+  </si>
+  <si>
+    <t>pnq@issmf.ipp.pt</t>
+  </si>
+  <si>
+    <t>OeBdaytL</t>
+  </si>
+  <si>
+    <t>PNQ</t>
+  </si>
+  <si>
+    <t>ZOvcpGJj</t>
+  </si>
+  <si>
+    <t>pgq@issmf.ipp.pt</t>
+  </si>
+  <si>
+    <t>PGQ</t>
+  </si>
+  <si>
+    <t>pxc@issmf.ipp.pt</t>
+  </si>
+  <si>
+    <t>ITt8HAcv</t>
+  </si>
+  <si>
+    <t>PXC</t>
+  </si>
+  <si>
+    <t>PWC</t>
+  </si>
+  <si>
+    <t>pwc@issmf.ipp.pt</t>
+  </si>
+  <si>
+    <t>c4Fa28Mq</t>
+  </si>
+  <si>
+    <t>PSG</t>
+  </si>
+  <si>
+    <t>kKee0ZHT</t>
+  </si>
+  <si>
+    <t>psg@issmf.ipp.pt</t>
+  </si>
+  <si>
+    <t>wbWQ7r1t</t>
+  </si>
+  <si>
+    <t>pfo@issmf.ipp.pt</t>
+  </si>
+  <si>
+    <t>Vvfr9h47</t>
+  </si>
+  <si>
+    <t>PFO</t>
+  </si>
+  <si>
+    <t>puoC4pv3</t>
+  </si>
+  <si>
+    <t>F18ZTLEK</t>
+  </si>
+  <si>
+    <t>gALRNpIz</t>
+  </si>
+  <si>
+    <t>denGlK7P</t>
+  </si>
+  <si>
+    <t>3yn006vk</t>
+  </si>
+  <si>
+    <t>KBgtFxD8</t>
+  </si>
+  <si>
+    <t>arzoI5uB</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0000"/>
-  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -851,7 +840,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -1004,12 +993,36 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1044,7 +1057,6 @@
     <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1066,6 +1078,53 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1073,6 +1132,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1081,98 +1149,67 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperligação" xfId="1" builtinId="8"/>
@@ -1497,1043 +1534,1047 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B2" s="39"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="41"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="49"/>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B3" s="44"/>
-      <c r="C3" s="36" t="s">
-        <v>201</v>
-      </c>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="42"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="59" t="s">
+        <v>197</v>
+      </c>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="50"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B4" s="44"/>
+      <c r="B4" s="52"/>
       <c r="C4" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="42"/>
+        <v>127</v>
+      </c>
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="50"/>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B5" s="44"/>
+      <c r="B5" s="52"/>
       <c r="C5" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="42"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="50"/>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B6" s="44"/>
+      <c r="B6" s="52"/>
       <c r="C6" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D6" s="34"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="42"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="50"/>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B7" s="44"/>
+      <c r="B7" s="52"/>
       <c r="C7" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="42"/>
+        <v>128</v>
+      </c>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54"/>
+      <c r="F7" s="50"/>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B8" s="44"/>
+      <c r="B8" s="52"/>
       <c r="C8" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="D8" s="34"/>
-      <c r="E8" s="34"/>
-      <c r="F8" s="42"/>
+        <v>129</v>
+      </c>
+      <c r="D8" s="54"/>
+      <c r="E8" s="54"/>
+      <c r="F8" s="50"/>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B9" s="44"/>
+      <c r="B9" s="52"/>
       <c r="C9" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="42"/>
+        <v>130</v>
+      </c>
+      <c r="D9" s="54"/>
+      <c r="E9" s="54"/>
+      <c r="F9" s="50"/>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B10" s="44"/>
+      <c r="B10" s="52"/>
       <c r="C10" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D10" s="34"/>
-      <c r="E10" s="34"/>
-      <c r="F10" s="42"/>
+      <c r="D10" s="54"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="50"/>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B11" s="44"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="35"/>
-      <c r="F11" s="42"/>
+      <c r="B11" s="52"/>
+      <c r="C11" s="55"/>
+      <c r="D11" s="55"/>
+      <c r="E11" s="55"/>
+      <c r="F11" s="50"/>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B12" s="44"/>
-      <c r="C12" s="47" t="s">
-        <v>200</v>
+      <c r="B12" s="52"/>
+      <c r="C12" s="57" t="s">
+        <v>196</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="E12" s="34"/>
-      <c r="F12" s="42"/>
+        <v>138</v>
+      </c>
+      <c r="E12" s="54"/>
+      <c r="F12" s="50"/>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B13" s="44"/>
-      <c r="C13" s="48"/>
+      <c r="B13" s="52"/>
+      <c r="C13" s="58"/>
       <c r="D13" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E13" s="54"/>
+      <c r="F13" s="50"/>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B14" s="52"/>
+      <c r="C14" s="58"/>
+      <c r="D14" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E14" s="54"/>
+      <c r="F14" s="50"/>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B15" s="52"/>
+      <c r="C15" s="58"/>
+      <c r="D15" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E15" s="54"/>
+      <c r="F15" s="50"/>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B16" s="52"/>
+      <c r="C16" s="58"/>
+      <c r="D16" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E16" s="54"/>
+      <c r="F16" s="50"/>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B17" s="52"/>
+      <c r="C17" s="58"/>
+      <c r="D17" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="E13" s="34"/>
-      <c r="F13" s="42"/>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B14" s="44"/>
-      <c r="C14" s="48"/>
-      <c r="D14" s="3" t="s">
+      <c r="E17" s="54"/>
+      <c r="F17" s="50"/>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B18" s="52"/>
+      <c r="C18" s="58"/>
+      <c r="D18" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="E14" s="34"/>
-      <c r="F14" s="42"/>
-    </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B15" s="44"/>
-      <c r="C15" s="48"/>
-      <c r="D15" s="3" t="s">
+      <c r="E18" s="54"/>
+      <c r="F18" s="50"/>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B19" s="52"/>
+      <c r="C19" s="58"/>
+      <c r="D19" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="E15" s="34"/>
-      <c r="F15" s="42"/>
-    </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B16" s="44"/>
-      <c r="C16" s="48"/>
-      <c r="D16" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="E16" s="34"/>
-      <c r="F16" s="42"/>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B17" s="44"/>
-      <c r="C17" s="48"/>
-      <c r="D17" s="3" t="s">
+      <c r="E19" s="54"/>
+      <c r="F19" s="50"/>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B20" s="52"/>
+      <c r="C20" s="58"/>
+      <c r="D20" s="60"/>
+      <c r="E20" s="61"/>
+      <c r="F20" s="50"/>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B21" s="52"/>
+      <c r="C21" s="58"/>
+      <c r="D21" s="54"/>
+      <c r="E21" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="E17" s="34"/>
-      <c r="F17" s="42"/>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B18" s="44"/>
-      <c r="C18" s="48"/>
-      <c r="D18" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="E18" s="34"/>
-      <c r="F18" s="42"/>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B19" s="44"/>
-      <c r="C19" s="48"/>
-      <c r="D19" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="E19" s="34"/>
-      <c r="F19" s="42"/>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B20" s="44"/>
-      <c r="C20" s="48"/>
-      <c r="D20" s="37"/>
-      <c r="E20" s="38"/>
-      <c r="F20" s="42"/>
-    </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B21" s="44"/>
-      <c r="C21" s="48"/>
-      <c r="D21" s="34"/>
-      <c r="E21" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="F21" s="42"/>
+      <c r="F21" s="50"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B22" s="44"/>
-      <c r="C22" s="48"/>
-      <c r="D22" s="34"/>
+      <c r="B22" s="52"/>
+      <c r="C22" s="58"/>
+      <c r="D22" s="54"/>
       <c r="E22" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="F22" s="42"/>
+      <c r="F22" s="50"/>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B23" s="44"/>
-      <c r="C23" s="48"/>
-      <c r="D23" s="34"/>
+      <c r="B23" s="52"/>
+      <c r="C23" s="58"/>
+      <c r="D23" s="54"/>
       <c r="E23" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="F23" s="42"/>
+      <c r="F23" s="50"/>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B24" s="44"/>
-      <c r="C24" s="48"/>
-      <c r="D24" s="34"/>
+      <c r="B24" s="52"/>
+      <c r="C24" s="58"/>
+      <c r="D24" s="54"/>
       <c r="E24" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="F24" s="42"/>
+      <c r="F24" s="50"/>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B25" s="44"/>
-      <c r="C25" s="48"/>
-      <c r="D25" s="34"/>
+      <c r="B25" s="52"/>
+      <c r="C25" s="58"/>
+      <c r="D25" s="54"/>
       <c r="E25" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F25" s="42"/>
+      <c r="F25" s="50"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B26" s="44"/>
-      <c r="C26" s="48"/>
-      <c r="D26" s="34"/>
+      <c r="B26" s="52"/>
+      <c r="C26" s="58"/>
+      <c r="D26" s="54"/>
       <c r="E26" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F26" s="42"/>
+      <c r="F26" s="50"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B27" s="44"/>
-      <c r="C27" s="48"/>
-      <c r="D27" s="34"/>
+      <c r="B27" s="52"/>
+      <c r="C27" s="58"/>
+      <c r="D27" s="54"/>
       <c r="E27" s="7"/>
-      <c r="F27" s="42"/>
+      <c r="F27" s="50"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B28" s="44"/>
-      <c r="C28" s="48"/>
-      <c r="D28" s="34"/>
+      <c r="B28" s="52"/>
+      <c r="C28" s="58"/>
+      <c r="D28" s="54"/>
       <c r="E28" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="F28" s="42"/>
+        <v>140</v>
+      </c>
+      <c r="F28" s="50"/>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B29" s="44"/>
-      <c r="C29" s="48"/>
-      <c r="D29" s="34"/>
+      <c r="B29" s="52"/>
+      <c r="C29" s="58"/>
+      <c r="D29" s="54"/>
       <c r="E29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F29" s="42"/>
+      <c r="F29" s="50"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B30" s="44"/>
-      <c r="C30" s="48"/>
-      <c r="D30" s="34"/>
+      <c r="B30" s="52"/>
+      <c r="C30" s="58"/>
+      <c r="D30" s="54"/>
       <c r="E30" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F30" s="42"/>
+      <c r="F30" s="50"/>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B31" s="44"/>
-      <c r="C31" s="48"/>
-      <c r="D31" s="34"/>
+      <c r="B31" s="52"/>
+      <c r="C31" s="58"/>
+      <c r="D31" s="54"/>
       <c r="E31" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="F31" s="42"/>
+        <v>141</v>
+      </c>
+      <c r="F31" s="50"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B32" s="44"/>
-      <c r="C32" s="48"/>
-      <c r="D32" s="34"/>
+      <c r="B32" s="52"/>
+      <c r="C32" s="58"/>
+      <c r="D32" s="54"/>
       <c r="E32" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="F32" s="42"/>
+        <v>142</v>
+      </c>
+      <c r="F32" s="50"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B33" s="44"/>
-      <c r="C33" s="48"/>
-      <c r="D33" s="34"/>
+      <c r="B33" s="52"/>
+      <c r="C33" s="58"/>
+      <c r="D33" s="54"/>
       <c r="E33" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="F33" s="42"/>
+        <v>143</v>
+      </c>
+      <c r="F33" s="50"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B34" s="44"/>
-      <c r="C34" s="48"/>
-      <c r="D34" s="34"/>
+      <c r="B34" s="52"/>
+      <c r="C34" s="58"/>
+      <c r="D34" s="54"/>
       <c r="E34" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="F34" s="42"/>
+        <v>144</v>
+      </c>
+      <c r="F34" s="50"/>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B35" s="44"/>
-      <c r="C35" s="48"/>
-      <c r="D35" s="34"/>
+      <c r="B35" s="52"/>
+      <c r="C35" s="58"/>
+      <c r="D35" s="54"/>
       <c r="E35" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="F35" s="42"/>
+        <v>204</v>
+      </c>
+      <c r="F35" s="50"/>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B36" s="44"/>
-      <c r="C36" s="48"/>
-      <c r="D36" s="34"/>
+      <c r="B36" s="52"/>
+      <c r="C36" s="58"/>
+      <c r="D36" s="54"/>
       <c r="E36" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="F36" s="42"/>
+        <v>207</v>
+      </c>
+      <c r="F36" s="50"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B37" s="44"/>
-      <c r="C37" s="48"/>
-      <c r="D37" s="34"/>
+      <c r="B37" s="52"/>
+      <c r="C37" s="58"/>
+      <c r="D37" s="54"/>
       <c r="E37" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F37" s="42"/>
+      <c r="F37" s="50"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B38" s="44"/>
-      <c r="C38" s="48"/>
-      <c r="D38" s="34"/>
+      <c r="B38" s="52"/>
+      <c r="C38" s="58"/>
+      <c r="D38" s="54"/>
       <c r="E38" s="7"/>
-      <c r="F38" s="42"/>
+      <c r="F38" s="50"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B39" s="44"/>
-      <c r="C39" s="48"/>
-      <c r="D39" s="34"/>
+      <c r="B39" s="52"/>
+      <c r="C39" s="58"/>
+      <c r="D39" s="54"/>
       <c r="E39" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="F39" s="42"/>
+        <v>145</v>
+      </c>
+      <c r="F39" s="50"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B40" s="44"/>
-      <c r="C40" s="48"/>
-      <c r="D40" s="34"/>
+      <c r="B40" s="52"/>
+      <c r="C40" s="58"/>
+      <c r="D40" s="54"/>
       <c r="E40" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="F40" s="42"/>
+      <c r="F40" s="50"/>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B41" s="44"/>
-      <c r="C41" s="48"/>
-      <c r="D41" s="34"/>
+      <c r="B41" s="52"/>
+      <c r="C41" s="58"/>
+      <c r="D41" s="54"/>
       <c r="E41" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F41" s="42"/>
+      <c r="F41" s="50"/>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B42" s="44"/>
-      <c r="C42" s="48"/>
-      <c r="D42" s="34"/>
+      <c r="B42" s="52"/>
+      <c r="C42" s="58"/>
+      <c r="D42" s="54"/>
       <c r="E42" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F42" s="42"/>
+      <c r="F42" s="50"/>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B43" s="44"/>
-      <c r="C43" s="48"/>
-      <c r="D43" s="34"/>
+      <c r="B43" s="52"/>
+      <c r="C43" s="58"/>
+      <c r="D43" s="54"/>
       <c r="E43" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="F43" s="42"/>
+      <c r="F43" s="50"/>
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B44" s="44"/>
-      <c r="C44" s="48"/>
-      <c r="D44" s="34"/>
+      <c r="B44" s="52"/>
+      <c r="C44" s="58"/>
+      <c r="D44" s="54"/>
       <c r="E44" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="F44" s="42"/>
+      <c r="F44" s="50"/>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B45" s="44"/>
-      <c r="C45" s="48"/>
-      <c r="D45" s="34"/>
+      <c r="B45" s="52"/>
+      <c r="C45" s="58"/>
+      <c r="D45" s="54"/>
       <c r="E45" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="F45" s="42"/>
+      <c r="F45" s="50"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B46" s="44"/>
-      <c r="C46" s="48"/>
-      <c r="D46" s="34"/>
+      <c r="B46" s="52"/>
+      <c r="C46" s="58"/>
+      <c r="D46" s="54"/>
       <c r="E46" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="F46" s="42"/>
+        <v>146</v>
+      </c>
+      <c r="F46" s="50"/>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B47" s="44"/>
-      <c r="C47" s="48"/>
-      <c r="D47" s="34"/>
+      <c r="B47" s="52"/>
+      <c r="C47" s="58"/>
+      <c r="D47" s="54"/>
       <c r="E47" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="F47" s="42"/>
+        <v>147</v>
+      </c>
+      <c r="F47" s="50"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B48" s="44"/>
-      <c r="C48" s="48"/>
-      <c r="D48" s="34"/>
+      <c r="B48" s="52"/>
+      <c r="C48" s="58"/>
+      <c r="D48" s="54"/>
       <c r="E48" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F48" s="42"/>
+      <c r="F48" s="50"/>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B49" s="44"/>
-      <c r="C49" s="48"/>
-      <c r="D49" s="34"/>
+      <c r="B49" s="52"/>
+      <c r="C49" s="58"/>
+      <c r="D49" s="54"/>
       <c r="E49" s="7"/>
-      <c r="F49" s="42"/>
+      <c r="F49" s="50"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B50" s="44"/>
-      <c r="C50" s="48"/>
-      <c r="D50" s="34"/>
+      <c r="B50" s="52"/>
+      <c r="C50" s="58"/>
+      <c r="D50" s="54"/>
       <c r="E50" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="F50" s="42"/>
+        <v>148</v>
+      </c>
+      <c r="F50" s="50"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B51" s="44"/>
-      <c r="C51" s="48"/>
-      <c r="D51" s="34"/>
+      <c r="B51" s="52"/>
+      <c r="C51" s="58"/>
+      <c r="D51" s="54"/>
       <c r="E51" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F51" s="42"/>
+      <c r="F51" s="50"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B52" s="44"/>
-      <c r="C52" s="48"/>
-      <c r="D52" s="34"/>
+      <c r="B52" s="52"/>
+      <c r="C52" s="58"/>
+      <c r="D52" s="54"/>
       <c r="E52" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F52" s="42"/>
+      <c r="F52" s="50"/>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B53" s="44"/>
-      <c r="C53" s="48"/>
-      <c r="D53" s="34"/>
+      <c r="B53" s="52"/>
+      <c r="C53" s="58"/>
+      <c r="D53" s="54"/>
       <c r="E53" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="F53" s="42"/>
+        <v>149</v>
+      </c>
+      <c r="F53" s="50"/>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B54" s="44"/>
-      <c r="C54" s="48"/>
-      <c r="D54" s="34"/>
+      <c r="B54" s="52"/>
+      <c r="C54" s="58"/>
+      <c r="D54" s="54"/>
       <c r="E54" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F54" s="42"/>
+      <c r="F54" s="50"/>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B55" s="44"/>
-      <c r="C55" s="48"/>
-      <c r="D55" s="34"/>
+      <c r="B55" s="52"/>
+      <c r="C55" s="58"/>
+      <c r="D55" s="54"/>
       <c r="E55" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="F55" s="42"/>
+        <v>150</v>
+      </c>
+      <c r="F55" s="50"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B56" s="44"/>
-      <c r="C56" s="48"/>
-      <c r="D56" s="34"/>
+      <c r="B56" s="52"/>
+      <c r="C56" s="58"/>
+      <c r="D56" s="54"/>
       <c r="E56" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F56" s="42"/>
+      <c r="F56" s="50"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B57" s="44"/>
-      <c r="C57" s="48"/>
-      <c r="D57" s="34"/>
+      <c r="B57" s="52"/>
+      <c r="C57" s="58"/>
+      <c r="D57" s="54"/>
       <c r="E57" s="7"/>
-      <c r="F57" s="42"/>
+      <c r="F57" s="50"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B58" s="44"/>
-      <c r="C58" s="48"/>
-      <c r="D58" s="34"/>
+      <c r="B58" s="52"/>
+      <c r="C58" s="58"/>
+      <c r="D58" s="54"/>
       <c r="E58" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="F58" s="42"/>
+        <v>151</v>
+      </c>
+      <c r="F58" s="50"/>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B59" s="44"/>
-      <c r="C59" s="48"/>
-      <c r="D59" s="34"/>
+      <c r="B59" s="52"/>
+      <c r="C59" s="58"/>
+      <c r="D59" s="54"/>
       <c r="E59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F59" s="42"/>
+      <c r="F59" s="50"/>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B60" s="44"/>
-      <c r="C60" s="48"/>
-      <c r="D60" s="34"/>
+      <c r="B60" s="52"/>
+      <c r="C60" s="58"/>
+      <c r="D60" s="54"/>
       <c r="E60" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F60" s="42"/>
+      <c r="F60" s="50"/>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B61" s="44"/>
-      <c r="C61" s="48"/>
-      <c r="D61" s="34"/>
+      <c r="B61" s="52"/>
+      <c r="C61" s="58"/>
+      <c r="D61" s="54"/>
       <c r="E61" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="F61" s="42"/>
+        <v>152</v>
+      </c>
+      <c r="F61" s="50"/>
     </row>
     <row r="62" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B62" s="44"/>
-      <c r="C62" s="48"/>
-      <c r="D62" s="34"/>
+      <c r="B62" s="52"/>
+      <c r="C62" s="58"/>
+      <c r="D62" s="54"/>
       <c r="E62" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F62" s="42"/>
+      <c r="F62" s="50"/>
     </row>
     <row r="63" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B63" s="44"/>
-      <c r="C63" s="48"/>
-      <c r="D63" s="34"/>
+      <c r="B63" s="52"/>
+      <c r="C63" s="58"/>
+      <c r="D63" s="54"/>
       <c r="E63" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="F63" s="42"/>
+        <v>153</v>
+      </c>
+      <c r="F63" s="50"/>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B64" s="44"/>
-      <c r="C64" s="48"/>
-      <c r="D64" s="34"/>
+      <c r="B64" s="52"/>
+      <c r="C64" s="58"/>
+      <c r="D64" s="54"/>
       <c r="E64" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F64" s="42"/>
+      <c r="F64" s="50"/>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B65" s="44"/>
-      <c r="C65" s="48"/>
-      <c r="D65" s="34"/>
+      <c r="B65" s="52"/>
+      <c r="C65" s="58"/>
+      <c r="D65" s="54"/>
       <c r="E65" s="7"/>
-      <c r="F65" s="42"/>
+      <c r="F65" s="50"/>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B66" s="44"/>
-      <c r="C66" s="48"/>
-      <c r="D66" s="34"/>
+      <c r="B66" s="52"/>
+      <c r="C66" s="58"/>
+      <c r="D66" s="54"/>
       <c r="E66" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="F66" s="42"/>
+        <v>154</v>
+      </c>
+      <c r="F66" s="50"/>
     </row>
     <row r="67" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B67" s="44"/>
-      <c r="C67" s="48"/>
-      <c r="D67" s="34"/>
+      <c r="B67" s="52"/>
+      <c r="C67" s="58"/>
+      <c r="D67" s="54"/>
       <c r="E67" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F67" s="42"/>
+      <c r="F67" s="50"/>
     </row>
     <row r="68" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B68" s="44"/>
-      <c r="C68" s="48"/>
-      <c r="D68" s="34"/>
+      <c r="B68" s="52"/>
+      <c r="C68" s="58"/>
+      <c r="D68" s="54"/>
       <c r="E68" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="F68" s="42"/>
+      <c r="F68" s="50"/>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B69" s="44"/>
-      <c r="C69" s="48"/>
-      <c r="D69" s="34"/>
+      <c r="B69" s="52"/>
+      <c r="C69" s="58"/>
+      <c r="D69" s="54"/>
       <c r="E69" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F69" s="42"/>
+      <c r="F69" s="50"/>
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B70" s="44"/>
-      <c r="C70" s="48"/>
-      <c r="D70" s="34"/>
+      <c r="B70" s="52"/>
+      <c r="C70" s="58"/>
+      <c r="D70" s="54"/>
       <c r="E70" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="F70" s="42"/>
+        <v>155</v>
+      </c>
+      <c r="F70" s="50"/>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B71" s="44"/>
-      <c r="C71" s="48"/>
-      <c r="D71" s="34"/>
+      <c r="B71" s="52"/>
+      <c r="C71" s="58"/>
+      <c r="D71" s="54"/>
       <c r="E71" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F71" s="42"/>
+      <c r="F71" s="50"/>
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B72" s="44"/>
-      <c r="C72" s="48"/>
-      <c r="D72" s="34"/>
+      <c r="B72" s="52"/>
+      <c r="C72" s="58"/>
+      <c r="D72" s="54"/>
       <c r="E72" s="7"/>
-      <c r="F72" s="42"/>
+      <c r="F72" s="50"/>
     </row>
     <row r="73" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B73" s="44"/>
-      <c r="C73" s="48"/>
-      <c r="D73" s="34"/>
+      <c r="B73" s="52"/>
+      <c r="C73" s="58"/>
+      <c r="D73" s="54"/>
       <c r="E73" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="F73" s="42"/>
+        <v>156</v>
+      </c>
+      <c r="F73" s="50"/>
     </row>
     <row r="74" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B74" s="44"/>
-      <c r="C74" s="48"/>
-      <c r="D74" s="34"/>
+      <c r="B74" s="52"/>
+      <c r="C74" s="58"/>
+      <c r="D74" s="54"/>
       <c r="E74" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="F74" s="42"/>
+        <v>157</v>
+      </c>
+      <c r="F74" s="50"/>
     </row>
     <row r="75" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B75" s="44"/>
-      <c r="C75" s="48"/>
-      <c r="D75" s="34"/>
+      <c r="B75" s="52"/>
+      <c r="C75" s="58"/>
+      <c r="D75" s="54"/>
       <c r="E75" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F75" s="42"/>
+      <c r="F75" s="50"/>
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B76" s="44"/>
-      <c r="C76" s="35"/>
-      <c r="D76" s="35"/>
-      <c r="E76" s="35"/>
-      <c r="F76" s="42"/>
+      <c r="B76" s="52"/>
+      <c r="C76" s="55"/>
+      <c r="D76" s="55"/>
+      <c r="E76" s="55"/>
+      <c r="F76" s="50"/>
     </row>
     <row r="77" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B77" s="44"/>
-      <c r="C77" s="46" t="s">
-        <v>172</v>
+      <c r="B77" s="52"/>
+      <c r="C77" s="56" t="s">
+        <v>168</v>
       </c>
       <c r="D77" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E77" s="54"/>
+      <c r="F77" s="50"/>
+    </row>
+    <row r="78" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B78" s="52"/>
+      <c r="C78" s="56"/>
+      <c r="D78" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="E78" s="54"/>
+      <c r="F78" s="50"/>
+    </row>
+    <row r="79" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B79" s="52"/>
+      <c r="C79" s="56"/>
+      <c r="D79" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="E79" s="54"/>
+      <c r="F79" s="50"/>
+    </row>
+    <row r="80" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B80" s="52"/>
+      <c r="C80" s="56"/>
+      <c r="D80" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="E80" s="54"/>
+      <c r="F80" s="50"/>
+    </row>
+    <row r="81" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B81" s="52"/>
+      <c r="C81" s="56"/>
+      <c r="D81" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="E77" s="34"/>
-      <c r="F77" s="42"/>
-    </row>
-    <row r="78" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B78" s="44"/>
-      <c r="C78" s="46"/>
-      <c r="D78" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="E78" s="34"/>
-      <c r="F78" s="42"/>
-    </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B79" s="44"/>
-      <c r="C79" s="46"/>
-      <c r="D79" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E79" s="34"/>
-      <c r="F79" s="42"/>
-    </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B80" s="44"/>
-      <c r="C80" s="46"/>
-      <c r="D80" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="E80" s="34"/>
-      <c r="F80" s="42"/>
-    </row>
-    <row r="81" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B81" s="44"/>
-      <c r="C81" s="46"/>
-      <c r="D81" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="E81" s="34"/>
-      <c r="F81" s="42"/>
+      <c r="E81" s="54"/>
+      <c r="F81" s="50"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B82" s="44"/>
-      <c r="C82" s="46"/>
+      <c r="B82" s="52"/>
+      <c r="C82" s="56"/>
       <c r="D82" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E82" s="34"/>
-      <c r="F82" s="42"/>
+      <c r="E82" s="54"/>
+      <c r="F82" s="50"/>
     </row>
     <row r="83" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B83" s="44"/>
-      <c r="C83" s="46"/>
-      <c r="D83" s="34"/>
-      <c r="E83" s="34"/>
-      <c r="F83" s="42"/>
+      <c r="B83" s="52"/>
+      <c r="C83" s="56"/>
+      <c r="D83" s="54"/>
+      <c r="E83" s="54"/>
+      <c r="F83" s="50"/>
     </row>
     <row r="84" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B84" s="44"/>
-      <c r="C84" s="46"/>
-      <c r="D84" s="34"/>
+      <c r="B84" s="52"/>
+      <c r="C84" s="56"/>
+      <c r="D84" s="54"/>
       <c r="E84" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="F84" s="42"/>
+        <v>193</v>
+      </c>
+      <c r="F84" s="50"/>
     </row>
     <row r="85" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B85" s="44"/>
-      <c r="C85" s="46"/>
-      <c r="D85" s="34"/>
+      <c r="B85" s="52"/>
+      <c r="C85" s="56"/>
+      <c r="D85" s="54"/>
       <c r="E85" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="F85" s="42"/>
+        <v>185</v>
+      </c>
+      <c r="F85" s="50"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B86" s="44"/>
-      <c r="C86" s="46"/>
-      <c r="D86" s="34"/>
+      <c r="B86" s="52"/>
+      <c r="C86" s="56"/>
+      <c r="D86" s="54"/>
       <c r="E86" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="F86" s="42"/>
+        <v>186</v>
+      </c>
+      <c r="F86" s="50"/>
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B87" s="44"/>
-      <c r="C87" s="46"/>
-      <c r="D87" s="34"/>
+      <c r="B87" s="52"/>
+      <c r="C87" s="56"/>
+      <c r="D87" s="54"/>
       <c r="E87" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="F87" s="42"/>
+        <v>187</v>
+      </c>
+      <c r="F87" s="50"/>
     </row>
     <row r="88" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B88" s="44"/>
-      <c r="C88" s="46"/>
-      <c r="D88" s="34"/>
+      <c r="B88" s="52"/>
+      <c r="C88" s="56"/>
+      <c r="D88" s="54"/>
       <c r="E88" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="F88" s="42"/>
+        <v>155</v>
+      </c>
+      <c r="F88" s="50"/>
     </row>
     <row r="89" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B89" s="44"/>
-      <c r="C89" s="46"/>
-      <c r="D89" s="34"/>
+      <c r="B89" s="52"/>
+      <c r="C89" s="56"/>
+      <c r="D89" s="54"/>
       <c r="E89" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F89" s="42"/>
+      <c r="F89" s="50"/>
     </row>
     <row r="90" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B90" s="44"/>
-      <c r="C90" s="46"/>
-      <c r="D90" s="34"/>
+      <c r="B90" s="52"/>
+      <c r="C90" s="56"/>
+      <c r="D90" s="54"/>
       <c r="E90" s="7"/>
-      <c r="F90" s="42"/>
+      <c r="F90" s="50"/>
     </row>
     <row r="91" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B91" s="44"/>
-      <c r="C91" s="46"/>
-      <c r="D91" s="34"/>
+      <c r="B91" s="52"/>
+      <c r="C91" s="56"/>
+      <c r="D91" s="54"/>
       <c r="E91" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="F91" s="50"/>
+    </row>
+    <row r="92" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B92" s="52"/>
+      <c r="C92" s="56"/>
+      <c r="D92" s="54"/>
+      <c r="E92" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="F92" s="50"/>
+    </row>
+    <row r="93" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B93" s="52"/>
+      <c r="C93" s="56"/>
+      <c r="D93" s="54"/>
+      <c r="E93" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="F93" s="50"/>
+    </row>
+    <row r="94" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B94" s="52"/>
+      <c r="C94" s="56"/>
+      <c r="D94" s="54"/>
+      <c r="E94" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="F94" s="50"/>
+    </row>
+    <row r="95" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B95" s="52"/>
+      <c r="C95" s="56"/>
+      <c r="D95" s="54"/>
+      <c r="E95" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="F91" s="42"/>
-    </row>
-    <row r="92" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B92" s="44"/>
-      <c r="C92" s="46"/>
-      <c r="D92" s="34"/>
-      <c r="E92" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="F92" s="42"/>
-    </row>
-    <row r="93" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B93" s="44"/>
-      <c r="C93" s="46"/>
-      <c r="D93" s="34"/>
-      <c r="E93" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="F93" s="42"/>
-    </row>
-    <row r="94" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B94" s="44"/>
-      <c r="C94" s="46"/>
-      <c r="D94" s="34"/>
-      <c r="E94" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="F94" s="42"/>
-    </row>
-    <row r="95" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B95" s="44"/>
-      <c r="C95" s="46"/>
-      <c r="D95" s="34"/>
-      <c r="E95" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="F95" s="42"/>
+      <c r="F95" s="50"/>
     </row>
     <row r="96" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B96" s="44"/>
-      <c r="C96" s="46"/>
-      <c r="D96" s="34"/>
+      <c r="B96" s="52"/>
+      <c r="C96" s="56"/>
+      <c r="D96" s="54"/>
       <c r="E96" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F96" s="42"/>
+      <c r="F96" s="50"/>
     </row>
     <row r="97" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B97" s="44"/>
-      <c r="C97" s="35"/>
-      <c r="D97" s="35"/>
-      <c r="E97" s="35"/>
-      <c r="F97" s="42"/>
+      <c r="B97" s="52"/>
+      <c r="C97" s="55"/>
+      <c r="D97" s="55"/>
+      <c r="E97" s="55"/>
+      <c r="F97" s="50"/>
     </row>
     <row r="98" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B98" s="44"/>
-      <c r="C98" s="46" t="s">
-        <v>196</v>
+      <c r="B98" s="52"/>
+      <c r="C98" s="56" t="s">
+        <v>192</v>
       </c>
       <c r="D98" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="E98" s="54"/>
+      <c r="F98" s="50"/>
+    </row>
+    <row r="99" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B99" s="52"/>
+      <c r="C99" s="56"/>
+      <c r="D99" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E99" s="54"/>
+      <c r="F99" s="50"/>
+    </row>
+    <row r="100" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B100" s="52"/>
+      <c r="C100" s="56"/>
+      <c r="D100" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="E100" s="54"/>
+      <c r="F100" s="50"/>
+    </row>
+    <row r="101" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B101" s="52"/>
+      <c r="C101" s="56"/>
+      <c r="D101" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E101" s="54"/>
+      <c r="F101" s="50"/>
+    </row>
+    <row r="102" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B102" s="52"/>
+      <c r="C102" s="56"/>
+      <c r="D102" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="E98" s="34"/>
-      <c r="F98" s="42"/>
-    </row>
-    <row r="99" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B99" s="44"/>
-      <c r="C99" s="46"/>
-      <c r="D99" s="3" t="s">
+      <c r="E102" s="54"/>
+      <c r="F102" s="50"/>
+    </row>
+    <row r="103" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B103" s="52"/>
+      <c r="C103" s="56"/>
+      <c r="D103" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="E99" s="34"/>
-      <c r="F99" s="42"/>
-    </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B100" s="44"/>
-      <c r="C100" s="46"/>
-      <c r="D100" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="E100" s="34"/>
-      <c r="F100" s="42"/>
-    </row>
-    <row r="101" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B101" s="44"/>
-      <c r="C101" s="46"/>
-      <c r="D101" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="E101" s="34"/>
-      <c r="F101" s="42"/>
-    </row>
-    <row r="102" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B102" s="44"/>
-      <c r="C102" s="46"/>
-      <c r="D102" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="E102" s="34"/>
-      <c r="F102" s="42"/>
-    </row>
-    <row r="103" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B103" s="44"/>
-      <c r="C103" s="46"/>
-      <c r="D103" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="E103" s="34"/>
-      <c r="F103" s="42"/>
+      <c r="E103" s="54"/>
+      <c r="F103" s="50"/>
     </row>
     <row r="104" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B104" s="44"/>
-      <c r="C104" s="46"/>
+      <c r="B104" s="52"/>
+      <c r="C104" s="56"/>
       <c r="D104" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E104" s="34"/>
-      <c r="F104" s="42"/>
+      <c r="E104" s="54"/>
+      <c r="F104" s="50"/>
     </row>
     <row r="105" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B105" s="44"/>
-      <c r="C105" s="46"/>
-      <c r="D105" s="34"/>
-      <c r="E105" s="34"/>
-      <c r="F105" s="42"/>
+      <c r="B105" s="52"/>
+      <c r="C105" s="56"/>
+      <c r="D105" s="54"/>
+      <c r="E105" s="54"/>
+      <c r="F105" s="50"/>
     </row>
     <row r="106" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B106" s="44"/>
-      <c r="C106" s="46"/>
-      <c r="D106" s="34"/>
+      <c r="B106" s="52"/>
+      <c r="C106" s="56"/>
+      <c r="D106" s="54"/>
       <c r="E106" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="F106" s="50"/>
+    </row>
+    <row r="107" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B107" s="52"/>
+      <c r="C107" s="56"/>
+      <c r="D107" s="54"/>
+      <c r="E107" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="F107" s="50"/>
+    </row>
+    <row r="108" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B108" s="52"/>
+      <c r="C108" s="56"/>
+      <c r="D108" s="54"/>
+      <c r="E108" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F108" s="50"/>
+    </row>
+    <row r="109" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B109" s="52"/>
+      <c r="C109" s="56"/>
+      <c r="D109" s="54"/>
+      <c r="E109" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F109" s="50"/>
+    </row>
+    <row r="110" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B110" s="52"/>
+      <c r="C110" s="56"/>
+      <c r="D110" s="54"/>
+      <c r="E110" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F110" s="50"/>
+    </row>
+    <row r="111" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B111" s="52"/>
+      <c r="C111" s="56"/>
+      <c r="D111" s="54"/>
+      <c r="E111" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="F106" s="42"/>
-    </row>
-    <row r="107" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B107" s="44"/>
-      <c r="C107" s="46"/>
-      <c r="D107" s="34"/>
-      <c r="E107" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="F107" s="42"/>
-    </row>
-    <row r="108" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B108" s="44"/>
-      <c r="C108" s="46"/>
-      <c r="D108" s="34"/>
-      <c r="E108" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="F108" s="42"/>
-    </row>
-    <row r="109" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B109" s="44"/>
-      <c r="C109" s="46"/>
-      <c r="D109" s="34"/>
-      <c r="E109" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="F109" s="42"/>
-    </row>
-    <row r="110" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B110" s="44"/>
-      <c r="C110" s="46"/>
-      <c r="D110" s="34"/>
-      <c r="E110" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="F110" s="42"/>
-    </row>
-    <row r="111" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B111" s="44"/>
-      <c r="C111" s="46"/>
-      <c r="D111" s="34"/>
-      <c r="E111" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="F111" s="42"/>
+      <c r="F111" s="50"/>
     </row>
     <row r="112" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B112" s="44"/>
-      <c r="C112" s="46"/>
-      <c r="D112" s="34"/>
+      <c r="B112" s="52"/>
+      <c r="C112" s="56"/>
+      <c r="D112" s="54"/>
       <c r="E112" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F112" s="42"/>
+      <c r="F112" s="50"/>
     </row>
     <row r="113" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B113" s="44"/>
-      <c r="C113" s="46"/>
-      <c r="D113" s="34"/>
+      <c r="B113" s="52"/>
+      <c r="C113" s="56"/>
+      <c r="D113" s="54"/>
       <c r="E113" s="7"/>
-      <c r="F113" s="42"/>
+      <c r="F113" s="50"/>
     </row>
     <row r="114" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B114" s="44"/>
-      <c r="C114" s="46"/>
-      <c r="D114" s="34"/>
+      <c r="B114" s="52"/>
+      <c r="C114" s="56"/>
+      <c r="D114" s="54"/>
       <c r="E114" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="F114" s="42"/>
+        <v>189</v>
+      </c>
+      <c r="F114" s="50"/>
     </row>
     <row r="115" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B115" s="44"/>
-      <c r="C115" s="46"/>
-      <c r="D115" s="34"/>
+      <c r="B115" s="52"/>
+      <c r="C115" s="56"/>
+      <c r="D115" s="54"/>
       <c r="E115" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="F115" s="42"/>
+        <v>194</v>
+      </c>
+      <c r="F115" s="50"/>
     </row>
     <row r="116" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B116" s="44"/>
-      <c r="C116" s="46"/>
-      <c r="D116" s="34"/>
+      <c r="B116" s="52"/>
+      <c r="C116" s="56"/>
+      <c r="D116" s="54"/>
       <c r="E116" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="F116" s="42"/>
+        <v>195</v>
+      </c>
+      <c r="F116" s="50"/>
     </row>
     <row r="117" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B117" s="44"/>
-      <c r="C117" s="46"/>
-      <c r="D117" s="34"/>
+      <c r="B117" s="52"/>
+      <c r="C117" s="56"/>
+      <c r="D117" s="54"/>
       <c r="E117" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="F117" s="42"/>
+        <v>190</v>
+      </c>
+      <c r="F117" s="50"/>
     </row>
     <row r="118" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B118" s="44"/>
-      <c r="C118" s="46"/>
-      <c r="D118" s="34"/>
+      <c r="B118" s="52"/>
+      <c r="C118" s="56"/>
+      <c r="D118" s="54"/>
       <c r="E118" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="F118" s="42"/>
+        <v>191</v>
+      </c>
+      <c r="F118" s="50"/>
     </row>
     <row r="119" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B119" s="45"/>
+      <c r="B119" s="53"/>
       <c r="C119" s="8"/>
       <c r="D119" s="8"/>
       <c r="E119" s="8"/>
-      <c r="F119" s="43"/>
+      <c r="F119" s="51"/>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="C76:E76"/>
+    <mergeCell ref="D105:E105"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="D20:E20"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="F3:F119"/>
     <mergeCell ref="B3:B119"/>
@@ -2550,10 +2591,6 @@
     <mergeCell ref="C77:C96"/>
     <mergeCell ref="E12:E19"/>
     <mergeCell ref="E77:E82"/>
-    <mergeCell ref="C76:E76"/>
-    <mergeCell ref="D105:E105"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="D20:E20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2562,55 +2599,57 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F6FFC68-BC6E-45A7-9925-0DFE4309B06B}">
-  <dimension ref="B2:O34"/>
+  <dimension ref="B2:O33"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="11.21875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="24" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.33203125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="30.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="34" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B2" s="39"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="40"/>
-      <c r="L2" s="40"/>
-      <c r="M2" s="40"/>
-      <c r="N2" s="40"/>
-      <c r="O2" s="41"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="48"/>
+      <c r="N2" s="48"/>
+      <c r="O2" s="49"/>
     </row>
     <row r="3" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B3" s="44"/>
-      <c r="C3" s="65" t="s">
-        <v>202</v>
-      </c>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="65"/>
-      <c r="K3" s="65"/>
-      <c r="L3" s="65"/>
-      <c r="M3" s="65"/>
-      <c r="N3" s="65"/>
-      <c r="O3" s="42"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="63" t="s">
+        <v>198</v>
+      </c>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="63"/>
+      <c r="K3" s="63"/>
+      <c r="L3" s="63"/>
+      <c r="M3" s="63"/>
+      <c r="N3" s="63"/>
+      <c r="O3" s="50"/>
     </row>
     <row r="4" spans="2:15" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="44"/>
+      <c r="B4" s="52"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -2627,130 +2666,130 @@
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
-      <c r="O4" s="42"/>
+      <c r="O4" s="50"/>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B5" s="44"/>
-      <c r="C5" s="34"/>
+      <c r="B5" s="52"/>
+      <c r="C5" s="54"/>
       <c r="D5" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="66"/>
+      <c r="F5" s="77"/>
       <c r="G5" s="10" t="s">
         <v>11</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="53" t="s">
-        <v>109</v>
-      </c>
-      <c r="J5" s="54"/>
+      <c r="I5" s="65" t="s">
+        <v>106</v>
+      </c>
+      <c r="J5" s="66"/>
       <c r="K5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="L5" s="56" t="s">
-        <v>104</v>
-      </c>
-      <c r="M5" s="57"/>
-      <c r="N5" s="58"/>
-      <c r="O5" s="42"/>
+      <c r="L5" s="68" t="s">
+        <v>101</v>
+      </c>
+      <c r="M5" s="69"/>
+      <c r="N5" s="70"/>
+      <c r="O5" s="50"/>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B6" s="44"/>
-      <c r="C6" s="34"/>
+      <c r="B6" s="52"/>
+      <c r="C6" s="54"/>
       <c r="D6" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="F6" s="66"/>
+      <c r="F6" s="77"/>
       <c r="G6" s="10" t="s">
         <v>62</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="I6" s="53" t="s">
-        <v>103</v>
-      </c>
-      <c r="J6" s="54"/>
+        <v>213</v>
+      </c>
+      <c r="I6" s="65" t="s">
+        <v>100</v>
+      </c>
+      <c r="J6" s="66"/>
       <c r="K6" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="L6" s="59"/>
-      <c r="M6" s="60"/>
-      <c r="N6" s="61"/>
-      <c r="O6" s="42"/>
+      <c r="L6" s="71"/>
+      <c r="M6" s="72"/>
+      <c r="N6" s="73"/>
+      <c r="O6" s="50"/>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B7" s="44"/>
-      <c r="C7" s="34"/>
+      <c r="B7" s="52"/>
+      <c r="C7" s="54"/>
       <c r="D7" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F7" s="66"/>
+      <c r="F7" s="77"/>
       <c r="G7" s="10" t="s">
         <v>45</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="I7" s="53" t="s">
+        <v>214</v>
+      </c>
+      <c r="I7" s="65" t="s">
         <v>60</v>
       </c>
-      <c r="J7" s="54"/>
+      <c r="J7" s="66"/>
       <c r="K7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="L7" s="62"/>
-      <c r="M7" s="63"/>
-      <c r="N7" s="64"/>
-      <c r="O7" s="42"/>
+      <c r="L7" s="74"/>
+      <c r="M7" s="75"/>
+      <c r="N7" s="76"/>
+      <c r="O7" s="50"/>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B8" s="44"/>
-      <c r="C8" s="67"/>
-      <c r="D8" s="67"/>
-      <c r="E8" s="67"/>
-      <c r="F8" s="67"/>
-      <c r="G8" s="67"/>
-      <c r="H8" s="67"/>
-      <c r="I8" s="67"/>
-      <c r="J8" s="67"/>
-      <c r="K8" s="67"/>
-      <c r="L8" s="67"/>
-      <c r="M8" s="67"/>
-      <c r="N8" s="67"/>
-      <c r="O8" s="42"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="62"/>
+      <c r="D8" s="62"/>
+      <c r="E8" s="62"/>
+      <c r="F8" s="62"/>
+      <c r="G8" s="62"/>
+      <c r="H8" s="62"/>
+      <c r="I8" s="62"/>
+      <c r="J8" s="62"/>
+      <c r="K8" s="62"/>
+      <c r="L8" s="62"/>
+      <c r="M8" s="62"/>
+      <c r="N8" s="62"/>
+      <c r="O8" s="50"/>
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B9" s="44"/>
-      <c r="C9" s="65" t="s">
-        <v>203</v>
-      </c>
-      <c r="D9" s="65"/>
-      <c r="E9" s="65"/>
-      <c r="F9" s="65"/>
-      <c r="G9" s="65"/>
-      <c r="H9" s="65"/>
-      <c r="I9" s="65"/>
-      <c r="J9" s="65"/>
-      <c r="K9" s="65"/>
-      <c r="L9" s="65"/>
-      <c r="M9" s="65"/>
-      <c r="N9" s="65"/>
-      <c r="O9" s="42"/>
+      <c r="B9" s="52"/>
+      <c r="C9" s="63" t="s">
+        <v>199</v>
+      </c>
+      <c r="D9" s="63"/>
+      <c r="E9" s="63"/>
+      <c r="F9" s="63"/>
+      <c r="G9" s="63"/>
+      <c r="H9" s="63"/>
+      <c r="I9" s="63"/>
+      <c r="J9" s="63"/>
+      <c r="K9" s="63"/>
+      <c r="L9" s="63"/>
+      <c r="M9" s="63"/>
+      <c r="N9" s="63"/>
+      <c r="O9" s="50"/>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B10" s="44"/>
+      <c r="B10" s="52"/>
       <c r="C10" s="3" t="s">
         <v>42</v>
       </c>
@@ -2761,13 +2800,13 @@
         <v>17</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I10" s="3">
         <v>142536748</v>
@@ -2779,16 +2818,16 @@
         <v>23</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="M10" s="55" t="s">
-        <v>104</v>
-      </c>
-      <c r="N10" s="55"/>
-      <c r="O10" s="42"/>
+        <v>107</v>
+      </c>
+      <c r="M10" s="67" t="s">
+        <v>101</v>
+      </c>
+      <c r="N10" s="67"/>
+      <c r="O10" s="50"/>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B11" s="44"/>
+      <c r="B11" s="52"/>
       <c r="C11" s="3" t="s">
         <v>42</v>
       </c>
@@ -2799,13 +2838,13 @@
         <v>19</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="I11" s="3">
         <v>142536747</v>
@@ -2817,14 +2856,14 @@
         <v>23</v>
       </c>
       <c r="L11" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="M11" s="55"/>
-      <c r="N11" s="55"/>
-      <c r="O11" s="42"/>
+        <v>108</v>
+      </c>
+      <c r="M11" s="67"/>
+      <c r="N11" s="67"/>
+      <c r="O11" s="50"/>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B12" s="44"/>
+      <c r="B12" s="52"/>
       <c r="C12" s="3" t="s">
         <v>42</v>
       </c>
@@ -2835,13 +2874,13 @@
         <v>20</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
+      </c>
+      <c r="H12" s="82" t="s">
+        <v>222</v>
       </c>
       <c r="I12" s="3">
         <v>142536746</v>
@@ -2853,14 +2892,14 @@
         <v>24</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="M12" s="55"/>
-      <c r="N12" s="55"/>
-      <c r="O12" s="42"/>
+        <v>109</v>
+      </c>
+      <c r="M12" s="67"/>
+      <c r="N12" s="67"/>
+      <c r="O12" s="50"/>
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B13" s="44"/>
+      <c r="B13" s="52"/>
       <c r="C13" s="3" t="s">
         <v>42</v>
       </c>
@@ -2871,13 +2910,13 @@
         <v>30</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="I13" s="3">
         <v>142536745</v>
@@ -2889,14 +2928,14 @@
         <v>23</v>
       </c>
       <c r="L13" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="M13" s="55"/>
-      <c r="N13" s="55"/>
-      <c r="O13" s="42"/>
+        <v>110</v>
+      </c>
+      <c r="M13" s="67"/>
+      <c r="N13" s="67"/>
+      <c r="O13" s="50"/>
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B14" s="44"/>
+      <c r="B14" s="52"/>
       <c r="C14" s="3" t="s">
         <v>40</v>
       </c>
@@ -2907,13 +2946,13 @@
         <v>36</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="I14" s="3">
         <v>142536744</v>
@@ -2925,14 +2964,14 @@
         <v>23</v>
       </c>
       <c r="L14" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="M14" s="55"/>
-      <c r="N14" s="55"/>
-      <c r="O14" s="42"/>
+        <v>111</v>
+      </c>
+      <c r="M14" s="67"/>
+      <c r="N14" s="67"/>
+      <c r="O14" s="50"/>
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B15" s="44"/>
+      <c r="B15" s="52"/>
       <c r="C15" s="3" t="s">
         <v>41</v>
       </c>
@@ -2943,13 +2982,13 @@
         <v>39</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>227</v>
+        <v>210</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I15" s="3">
         <v>142536743</v>
@@ -2961,25 +3000,25 @@
         <v>23</v>
       </c>
       <c r="L15" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="M15" s="55"/>
-      <c r="N15" s="55"/>
-      <c r="O15" s="42"/>
+        <v>112</v>
+      </c>
+      <c r="M15" s="67"/>
+      <c r="N15" s="67"/>
+      <c r="O15" s="50"/>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B16" s="44"/>
+      <c r="B16" s="52"/>
       <c r="C16" s="3"/>
       <c r="D16" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="G16" t="s">
+        <v>233</v>
+      </c>
+      <c r="G16" s="46" t="s">
         <v>231</v>
       </c>
       <c r="H16" s="3" t="s">
@@ -2989,59 +3028,59 @@
         <v>142536742</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="K16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="L16" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="M16" s="55"/>
-      <c r="N16" s="55"/>
-      <c r="O16" s="42"/>
+        <v>113</v>
+      </c>
+      <c r="M16" s="67"/>
+      <c r="N16" s="67"/>
+      <c r="O16" s="50"/>
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B17" s="44"/>
-      <c r="C17" s="67"/>
-      <c r="D17" s="67"/>
-      <c r="E17" s="67"/>
-      <c r="F17" s="67"/>
-      <c r="G17" s="67"/>
-      <c r="H17" s="67"/>
-      <c r="I17" s="67"/>
-      <c r="J17" s="67"/>
-      <c r="K17" s="67"/>
-      <c r="L17" s="67"/>
-      <c r="M17" s="67"/>
-      <c r="N17" s="67"/>
-      <c r="O17" s="42"/>
+      <c r="B17" s="52"/>
+      <c r="C17" s="62"/>
+      <c r="D17" s="62"/>
+      <c r="E17" s="62"/>
+      <c r="F17" s="62"/>
+      <c r="G17" s="62"/>
+      <c r="H17" s="62"/>
+      <c r="I17" s="62"/>
+      <c r="J17" s="62"/>
+      <c r="K17" s="62"/>
+      <c r="L17" s="62"/>
+      <c r="M17" s="62"/>
+      <c r="N17" s="62"/>
+      <c r="O17" s="50"/>
     </row>
     <row r="18" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B18" s="44"/>
-      <c r="C18" s="65" t="s">
-        <v>204</v>
-      </c>
-      <c r="D18" s="65"/>
-      <c r="E18" s="65"/>
-      <c r="F18" s="65"/>
-      <c r="G18" s="65"/>
-      <c r="H18" s="65"/>
-      <c r="I18" s="65"/>
-      <c r="J18" s="65"/>
-      <c r="K18" s="65"/>
-      <c r="L18" s="65"/>
-      <c r="M18" s="65"/>
-      <c r="N18" s="65"/>
-      <c r="O18" s="42"/>
+      <c r="B18" s="52"/>
+      <c r="C18" s="63" t="s">
+        <v>200</v>
+      </c>
+      <c r="D18" s="63"/>
+      <c r="E18" s="63"/>
+      <c r="F18" s="63"/>
+      <c r="G18" s="63"/>
+      <c r="H18" s="63"/>
+      <c r="I18" s="63"/>
+      <c r="J18" s="63"/>
+      <c r="K18" s="63"/>
+      <c r="L18" s="63"/>
+      <c r="M18" s="63"/>
+      <c r="N18" s="63"/>
+      <c r="O18" s="50"/>
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B19" s="44"/>
+      <c r="B19" s="52"/>
       <c r="C19" s="3" t="s">
         <v>42</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>63</v>
@@ -3050,7 +3089,7 @@
         <v>20260001</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>234</v>
@@ -3065,21 +3104,21 @@
         <v>23</v>
       </c>
       <c r="L19" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="M19" s="55" t="s">
-        <v>104</v>
-      </c>
-      <c r="N19" s="55"/>
-      <c r="O19" s="42"/>
+        <v>114</v>
+      </c>
+      <c r="M19" s="67" t="s">
+        <v>101</v>
+      </c>
+      <c r="N19" s="67"/>
+      <c r="O19" s="50"/>
     </row>
     <row r="20" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B20" s="44"/>
+      <c r="B20" s="52"/>
       <c r="C20" s="3" t="s">
         <v>42</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>65</v>
@@ -3088,13 +3127,13 @@
         <v>20260002</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>235</v>
       </c>
       <c r="I20" s="3">
-        <v>241536789</v>
+        <v>233654789</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>66</v>
@@ -3103,468 +3142,432 @@
         <v>23</v>
       </c>
       <c r="L20" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="M20" s="55"/>
-      <c r="N20" s="55"/>
-      <c r="O20" s="42"/>
+        <v>115</v>
+      </c>
+      <c r="M20" s="67"/>
+      <c r="N20" s="67"/>
+      <c r="O20" s="50"/>
     </row>
     <row r="21" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B21" s="44"/>
+      <c r="B21" s="52"/>
       <c r="C21" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="E21" s="3" t="s">
+      <c r="D21" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="E21" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="F21" s="6">
+      <c r="F21" s="25">
         <v>20260003</v>
       </c>
-      <c r="G21" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="H21" s="3" t="s">
+      <c r="G21" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="H21" s="12" t="s">
         <v>236</v>
       </c>
-      <c r="I21" s="3">
-        <v>267489123</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="K21" s="3" t="s">
+      <c r="I21" s="12">
+        <v>241536789</v>
+      </c>
+      <c r="J21" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K21" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="L21" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="M21" s="55"/>
-      <c r="N21" s="55"/>
-      <c r="O21" s="42"/>
+      <c r="L21" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="M21" s="67"/>
+      <c r="N21" s="67"/>
+      <c r="O21" s="50"/>
     </row>
     <row r="22" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B22" s="44"/>
+      <c r="B22" s="52"/>
       <c r="C22" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D22" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="E22" s="12" t="s">
-        <v>69</v>
+      <c r="D22" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="E22" s="15" t="s">
+        <v>68</v>
       </c>
       <c r="F22" s="26">
         <v>20260004</v>
       </c>
-      <c r="G22" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="H22" s="12" t="s">
+      <c r="G22" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="H22" s="15" t="s">
         <v>237</v>
       </c>
-      <c r="I22" s="12">
-        <v>233654789</v>
-      </c>
-      <c r="J22" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="K22" s="12" t="s">
+      <c r="I22" s="15">
+        <v>259874123</v>
+      </c>
+      <c r="J22" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="K22" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="L22" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="M22" s="55"/>
-      <c r="N22" s="55"/>
-      <c r="O22" s="42"/>
+      <c r="L22" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="M22" s="67"/>
+      <c r="N22" s="67"/>
+      <c r="O22" s="50"/>
     </row>
     <row r="23" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B23" s="44"/>
+      <c r="B23" s="52"/>
       <c r="C23" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D23" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="E23" s="15" t="s">
+      <c r="D23" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="E23" s="18" t="s">
         <v>70</v>
       </c>
       <c r="F23" s="27">
         <v>20260005</v>
       </c>
-      <c r="G23" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="H23" s="15" t="s">
-        <v>238</v>
-      </c>
-      <c r="I23" s="15">
-        <v>259874123</v>
-      </c>
-      <c r="J23" s="15" t="s">
+      <c r="G23" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="H23" s="20" t="s">
+        <v>240</v>
+      </c>
+      <c r="I23" s="18">
+        <v>210456789</v>
+      </c>
+      <c r="J23" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="K23" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="L23" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="M23" s="67"/>
+      <c r="N23" s="67"/>
+      <c r="O23" s="50"/>
+    </row>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B24" s="52"/>
+      <c r="C24" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="D24" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="E24" s="22" t="s">
         <v>71</v>
-      </c>
-      <c r="K23" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="L23" s="17" t="s">
-        <v>120</v>
-      </c>
-      <c r="M23" s="55"/>
-      <c r="N23" s="55"/>
-      <c r="O23" s="42"/>
-    </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B24" s="44"/>
-      <c r="C24" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D24" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="E24" s="18" t="s">
-        <v>72</v>
       </c>
       <c r="F24" s="28">
         <v>20260006</v>
       </c>
-      <c r="G24" s="19" t="s">
-        <v>96</v>
-      </c>
-      <c r="H24" s="20" t="s">
-        <v>239</v>
-      </c>
-      <c r="I24" s="18">
-        <v>210456789</v>
-      </c>
-      <c r="J24" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="K24" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="L24" s="21" t="s">
-        <v>121</v>
-      </c>
-      <c r="M24" s="55"/>
-      <c r="N24" s="55"/>
-      <c r="O24" s="42"/>
+      <c r="G24" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="H24" s="23" t="s">
+        <v>238</v>
+      </c>
+      <c r="I24" s="22">
+        <v>225147896</v>
+      </c>
+      <c r="J24" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="K24" s="22" t="s">
+        <v>203</v>
+      </c>
+      <c r="L24" s="36" t="s">
+        <v>119</v>
+      </c>
+      <c r="M24" s="67"/>
+      <c r="N24" s="67"/>
+      <c r="O24" s="50"/>
     </row>
     <row r="25" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B25" s="44"/>
+      <c r="B25" s="52"/>
       <c r="C25" s="22" t="s">
         <v>40</v>
       </c>
       <c r="D25" s="22" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E25" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="F25" s="29">
+      <c r="F25" s="28">
         <v>20260007</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H25" s="23" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="I25" s="22">
-        <v>225147896</v>
+        <v>278963254</v>
       </c>
       <c r="J25" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="K25" s="22" t="s">
+        <v>203</v>
+      </c>
+      <c r="L25" s="36" t="s">
+        <v>212</v>
+      </c>
+      <c r="M25" s="67"/>
+      <c r="N25" s="67"/>
+      <c r="O25" s="50"/>
+    </row>
+    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B26" s="52"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E26" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="K25" s="22" t="s">
-        <v>207</v>
-      </c>
-      <c r="L25" s="70" t="s">
-        <v>122</v>
-      </c>
-      <c r="M25" s="55"/>
-      <c r="N25" s="55"/>
-      <c r="O25" s="42"/>
-    </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B26" s="44"/>
-      <c r="C26" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="D26" s="22" t="s">
-        <v>90</v>
-      </c>
-      <c r="E26" s="22" t="s">
+      <c r="F26" s="6"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="24"/>
+      <c r="I26" s="3">
+        <v>244123654</v>
+      </c>
+      <c r="J26" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="F26" s="29">
-        <v>20260008</v>
-      </c>
-      <c r="G26" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="H26" s="23" t="s">
-        <v>241</v>
-      </c>
-      <c r="I26" s="22">
-        <v>278963254</v>
-      </c>
-      <c r="J26" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="K26" s="22" t="s">
-        <v>207</v>
-      </c>
-      <c r="L26" s="24" t="s">
-        <v>123</v>
-      </c>
-      <c r="M26" s="55"/>
-      <c r="N26" s="55"/>
-      <c r="O26" s="42"/>
+      <c r="K26" s="3"/>
+      <c r="L26" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="M26" s="67"/>
+      <c r="N26" s="67"/>
+      <c r="O26" s="50"/>
     </row>
     <row r="27" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B27" s="44"/>
+      <c r="B27" s="52"/>
       <c r="C27" s="3"/>
       <c r="D27" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>76</v>
       </c>
       <c r="F27" s="6"/>
       <c r="G27" s="10"/>
-      <c r="H27" s="25"/>
+      <c r="H27" s="24"/>
       <c r="I27" s="3">
-        <v>244123654</v>
+        <v>251478963</v>
       </c>
       <c r="J27" s="3" t="s">
         <v>77</v>
       </c>
       <c r="K27" s="3"/>
       <c r="L27" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="M27" s="55"/>
-      <c r="N27" s="55"/>
-      <c r="O27" s="42"/>
+        <v>121</v>
+      </c>
+      <c r="M27" s="67"/>
+      <c r="N27" s="67"/>
+      <c r="O27" s="50"/>
     </row>
     <row r="28" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B28" s="44"/>
+      <c r="B28" s="52"/>
       <c r="C28" s="3"/>
       <c r="D28" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>78</v>
       </c>
       <c r="F28" s="6"/>
       <c r="G28" s="10"/>
-      <c r="H28" s="25"/>
+      <c r="H28" s="24"/>
       <c r="I28" s="3">
-        <v>251478963</v>
+        <v>266321458</v>
       </c>
       <c r="J28" s="3" t="s">
         <v>79</v>
       </c>
       <c r="K28" s="3"/>
       <c r="L28" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="M28" s="55"/>
-      <c r="N28" s="55"/>
-      <c r="O28" s="42"/>
+        <v>122</v>
+      </c>
+      <c r="M28" s="67"/>
+      <c r="N28" s="67"/>
+      <c r="O28" s="50"/>
     </row>
     <row r="29" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B29" s="44"/>
+      <c r="B29" s="52"/>
       <c r="C29" s="3"/>
       <c r="D29" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>80</v>
       </c>
       <c r="F29" s="6"/>
-      <c r="G29" s="10"/>
-      <c r="H29" s="25"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="24"/>
       <c r="I29" s="3">
-        <v>266321458</v>
+        <v>239852147</v>
       </c>
       <c r="J29" s="3" t="s">
         <v>81</v>
       </c>
       <c r="K29" s="3"/>
       <c r="L29" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="M29" s="55"/>
-      <c r="N29" s="55"/>
-      <c r="O29" s="42"/>
+        <v>123</v>
+      </c>
+      <c r="M29" s="67"/>
+      <c r="N29" s="67"/>
+      <c r="O29" s="50"/>
     </row>
     <row r="30" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B30" s="44"/>
+      <c r="B30" s="52"/>
       <c r="C30" s="3"/>
       <c r="D30" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>82</v>
       </c>
       <c r="F30" s="6"/>
       <c r="G30" s="3"/>
-      <c r="H30" s="25"/>
+      <c r="H30" s="24"/>
       <c r="I30" s="3">
-        <v>239852147</v>
+        <v>288741256</v>
       </c>
       <c r="J30" s="3" t="s">
         <v>83</v>
       </c>
       <c r="K30" s="3"/>
       <c r="L30" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="M30" s="55"/>
-      <c r="N30" s="55"/>
-      <c r="O30" s="42"/>
+        <v>124</v>
+      </c>
+      <c r="M30" s="67"/>
+      <c r="N30" s="67"/>
+      <c r="O30" s="50"/>
     </row>
     <row r="31" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B31" s="44"/>
+      <c r="B31" s="52"/>
       <c r="C31" s="3"/>
       <c r="D31" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>84</v>
       </c>
       <c r="F31" s="6"/>
       <c r="G31" s="3"/>
-      <c r="H31" s="25"/>
+      <c r="H31" s="24"/>
       <c r="I31" s="3">
-        <v>288741256</v>
+        <v>255698147</v>
       </c>
       <c r="J31" s="3" t="s">
         <v>85</v>
       </c>
       <c r="K31" s="3"/>
       <c r="L31" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="M31" s="55"/>
-      <c r="N31" s="55"/>
-      <c r="O31" s="42"/>
+        <v>125</v>
+      </c>
+      <c r="M31" s="67"/>
+      <c r="N31" s="67"/>
+      <c r="O31" s="50"/>
     </row>
     <row r="32" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B32" s="44"/>
+      <c r="B32" s="52"/>
       <c r="C32" s="3"/>
       <c r="D32" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>86</v>
       </c>
       <c r="F32" s="6"/>
       <c r="G32" s="3"/>
-      <c r="H32" s="25"/>
+      <c r="H32" s="3"/>
       <c r="I32" s="3">
-        <v>255698147</v>
+        <v>242365147</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>87</v>
       </c>
       <c r="K32" s="3"/>
       <c r="L32" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="M32" s="55"/>
-      <c r="N32" s="55"/>
-      <c r="O32" s="42"/>
+        <v>126</v>
+      </c>
+      <c r="M32" s="67"/>
+      <c r="N32" s="67"/>
+      <c r="O32" s="50"/>
     </row>
     <row r="33" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B33" s="44"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="F33" s="6"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3">
-        <v>242365147</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="K33" s="3"/>
-      <c r="L33" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="M33" s="55"/>
-      <c r="N33" s="55"/>
-      <c r="O33" s="42"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B34" s="45"/>
-      <c r="C34" s="50"/>
-      <c r="D34" s="50"/>
-      <c r="E34" s="50"/>
-      <c r="F34" s="50"/>
-      <c r="G34" s="50"/>
-      <c r="H34" s="50"/>
-      <c r="I34" s="50"/>
-      <c r="J34" s="50"/>
-      <c r="K34" s="50"/>
-      <c r="L34" s="50"/>
-      <c r="M34" s="50"/>
-      <c r="N34" s="50"/>
-      <c r="O34" s="43"/>
+      <c r="B33" s="53"/>
+      <c r="C33" s="64"/>
+      <c r="D33" s="64"/>
+      <c r="E33" s="64"/>
+      <c r="F33" s="64"/>
+      <c r="G33" s="64"/>
+      <c r="H33" s="64"/>
+      <c r="I33" s="64"/>
+      <c r="J33" s="64"/>
+      <c r="K33" s="64"/>
+      <c r="L33" s="64"/>
+      <c r="M33" s="64"/>
+      <c r="N33" s="64"/>
+      <c r="O33" s="51"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B2:O2"/>
-    <mergeCell ref="O3:O33"/>
-    <mergeCell ref="B3:B33"/>
-    <mergeCell ref="C8:N8"/>
-    <mergeCell ref="C17:N17"/>
-    <mergeCell ref="C3:N3"/>
-    <mergeCell ref="B34:O34"/>
+    <mergeCell ref="B33:O33"/>
     <mergeCell ref="I7:J7"/>
     <mergeCell ref="I5:J5"/>
     <mergeCell ref="M10:N16"/>
-    <mergeCell ref="M19:N33"/>
+    <mergeCell ref="M19:N32"/>
     <mergeCell ref="L5:N7"/>
     <mergeCell ref="I6:J6"/>
     <mergeCell ref="C18:N18"/>
     <mergeCell ref="C9:N9"/>
     <mergeCell ref="C5:C7"/>
     <mergeCell ref="F5:F7"/>
+    <mergeCell ref="B2:O2"/>
+    <mergeCell ref="O3:O32"/>
+    <mergeCell ref="B3:B32"/>
+    <mergeCell ref="C8:N8"/>
+    <mergeCell ref="C17:N17"/>
+    <mergeCell ref="C3:N3"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="G4" r:id="rId1" xr:uid="{90136737-50D8-4624-BF9F-7BB076958402}"/>
     <hyperlink ref="G5" r:id="rId2" xr:uid="{9B3EB29C-D4D1-4DE8-950C-D636533C4ACC}"/>
     <hyperlink ref="L5" r:id="rId3" xr:uid="{4CEB1E42-A151-45A2-9B0C-B4A90B4D0D5F}"/>
-    <hyperlink ref="G19" r:id="rId4" xr:uid="{19ED9BF7-712A-4DC1-8755-8EF0FCFF0B53}"/>
-    <hyperlink ref="G20" r:id="rId5" xr:uid="{73FA2062-31DC-43F6-87BF-4CAD4118EDC0}"/>
-    <hyperlink ref="G21" r:id="rId6" xr:uid="{C9A706E5-980E-4F35-AC05-0CAA97DB6C86}"/>
-    <hyperlink ref="G22" r:id="rId7" xr:uid="{1638B543-22A0-4123-BFF1-150CE5050E28}"/>
-    <hyperlink ref="G23" r:id="rId8" xr:uid="{D691BEA8-794F-47A6-A4F5-E83DC2372430}"/>
-    <hyperlink ref="G24" r:id="rId9" xr:uid="{10013824-D875-4ED4-BB1D-3CB1D985BC39}"/>
-    <hyperlink ref="G25" r:id="rId10" xr:uid="{0ABFA8B0-714A-4556-B801-F31F8ACC5FCF}"/>
-    <hyperlink ref="G26" r:id="rId11" xr:uid="{B7F3917F-0DF5-41C1-AA91-81F7691BF7EE}"/>
-    <hyperlink ref="G6" r:id="rId12" xr:uid="{BCAA6600-DE24-422D-96D4-0791B494C9D2}"/>
-    <hyperlink ref="G7" r:id="rId13" xr:uid="{EAF8ADB9-58E9-4CBC-AAD5-DA37B223DFD2}"/>
-    <hyperlink ref="M10" r:id="rId14" xr:uid="{889087D1-E240-4465-90CC-97DF6ABEF439}"/>
-    <hyperlink ref="G10" r:id="rId15" xr:uid="{BF051BD1-75FB-4461-962C-7EF5E5C1AE60}"/>
-    <hyperlink ref="G11" r:id="rId16" xr:uid="{140DDC62-C64B-477C-A68A-862BD945F18D}"/>
-    <hyperlink ref="G12" r:id="rId17" xr:uid="{852FABFE-D926-4FF9-88CA-E3EE084E98A0}"/>
-    <hyperlink ref="G13" r:id="rId18" xr:uid="{93C9AE13-3AEE-4784-B47E-237396405ABB}"/>
-    <hyperlink ref="G14" r:id="rId19" xr:uid="{7BFFBDC4-2665-4081-9203-07EDBD46AD4A}"/>
-    <hyperlink ref="G15" r:id="rId20" xr:uid="{C36D3D31-89F6-4BF8-8D42-4F100C606AB9}"/>
-    <hyperlink ref="M19" r:id="rId21" xr:uid="{6FC1A60E-B0CE-457F-BEEE-3AC36283B66B}"/>
+    <hyperlink ref="G20" r:id="rId4" xr:uid="{73FA2062-31DC-43F6-87BF-4CAD4118EDC0}"/>
+    <hyperlink ref="G21" r:id="rId5" xr:uid="{1638B543-22A0-4123-BFF1-150CE5050E28}"/>
+    <hyperlink ref="G22" r:id="rId6" xr:uid="{D691BEA8-794F-47A6-A4F5-E83DC2372430}"/>
+    <hyperlink ref="G23" r:id="rId7" xr:uid="{10013824-D875-4ED4-BB1D-3CB1D985BC39}"/>
+    <hyperlink ref="G24" r:id="rId8" xr:uid="{0ABFA8B0-714A-4556-B801-F31F8ACC5FCF}"/>
+    <hyperlink ref="G25" r:id="rId9" xr:uid="{B7F3917F-0DF5-41C1-AA91-81F7691BF7EE}"/>
+    <hyperlink ref="G6" r:id="rId10" xr:uid="{BCAA6600-DE24-422D-96D4-0791B494C9D2}"/>
+    <hyperlink ref="G7" r:id="rId11" xr:uid="{EAF8ADB9-58E9-4CBC-AAD5-DA37B223DFD2}"/>
+    <hyperlink ref="M10" r:id="rId12" xr:uid="{889087D1-E240-4465-90CC-97DF6ABEF439}"/>
+    <hyperlink ref="M19" r:id="rId13" xr:uid="{6FC1A60E-B0CE-457F-BEEE-3AC36283B66B}"/>
+    <hyperlink ref="G19" r:id="rId14" xr:uid="{19ED9BF7-712A-4DC1-8755-8EF0FCFF0B53}"/>
+    <hyperlink ref="G10" r:id="rId15" xr:uid="{6A83FB18-5AFC-4808-9223-36DE7F856746}"/>
+    <hyperlink ref="G11" r:id="rId16" xr:uid="{F189FF88-B0C7-41DA-9069-997A29D81085}"/>
+    <hyperlink ref="G12" r:id="rId17" xr:uid="{A12A5870-CCA3-494F-B7E5-19C1B5759D91}"/>
+    <hyperlink ref="G13" r:id="rId18" xr:uid="{0873C2BC-57F8-4B2F-98B0-44819F7126D2}"/>
+    <hyperlink ref="G14" r:id="rId19" xr:uid="{1FE56E63-763E-4AB4-A0DE-6EE1C841581B}"/>
+    <hyperlink ref="G15" r:id="rId20" xr:uid="{2C87F2FE-31DC-43C7-890C-23A02A930C8F}"/>
+    <hyperlink ref="G16" r:id="rId21" xr:uid="{1666FE38-BBA2-4EA0-BFB9-23AD0FEC9DAB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId22"/>
@@ -3573,7 +3576,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F3342F1-B6E7-460B-9E26-5A8DC1C1AFB6}">
-  <dimension ref="B2:O35"/>
+  <dimension ref="B2:O37"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="4" width="49.5546875" bestFit="1" customWidth="1"/>
@@ -3589,25 +3592,25 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B2" s="39"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="41"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="49"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="44"/>
-      <c r="C3" s="31" t="s">
+      <c r="B3" s="52"/>
+      <c r="C3" s="30" t="s">
         <v>14</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="31" t="s">
+      <c r="E3" s="30" t="s">
         <v>28</v>
       </c>
       <c r="F3" s="4" t="s">
@@ -3620,24 +3623,24 @@
       <c r="I3" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="68"/>
-      <c r="K3" s="36" t="s">
-        <v>203</v>
-      </c>
-      <c r="L3" s="36"/>
-      <c r="M3" s="36"/>
-      <c r="N3" s="36"/>
+      <c r="J3" s="78"/>
+      <c r="K3" s="59" t="s">
+        <v>199</v>
+      </c>
+      <c r="L3" s="59"/>
+      <c r="M3" s="59"/>
+      <c r="N3" s="59"/>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B4" s="44"/>
-      <c r="C4" s="31" t="s">
-        <v>206</v>
+      <c r="B4" s="52"/>
+      <c r="C4" s="30" t="s">
+        <v>202</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>25</v>
@@ -3647,38 +3650,38 @@
       </c>
       <c r="H4" s="3" t="str">
         <f>VLOOKUP(G4,K$4:L$10,2,FALSE)</f>
-        <v>PHH</v>
+        <v>PGQ</v>
       </c>
       <c r="I4" s="3">
         <v>2</v>
       </c>
-      <c r="J4" s="42"/>
-      <c r="K4" s="69" t="s">
+      <c r="J4" s="50"/>
+      <c r="K4" s="3" t="s">
         <v>17</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="M4" s="3"/>
-      <c r="N4" s="69" t="s">
+      <c r="N4" s="35" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B5" s="44"/>
-      <c r="C5" s="52"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="52"/>
-      <c r="H5" s="52"/>
-      <c r="I5" s="52"/>
-      <c r="J5" s="42"/>
+      <c r="B5" s="52"/>
+      <c r="C5" s="80"/>
+      <c r="D5" s="80"/>
+      <c r="E5" s="80"/>
+      <c r="F5" s="80"/>
+      <c r="G5" s="80"/>
+      <c r="H5" s="80"/>
+      <c r="I5" s="80"/>
+      <c r="J5" s="50"/>
       <c r="K5" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="M5" s="3"/>
       <c r="N5" s="3" t="s">
@@ -3686,17 +3689,17 @@
       </c>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B6" s="44"/>
-      <c r="C6" s="49" t="s">
-        <v>209</v>
-      </c>
-      <c r="D6" s="46" t="s">
-        <v>100</v>
+      <c r="B6" s="52"/>
+      <c r="C6" s="81" t="s">
+        <v>205</v>
+      </c>
+      <c r="D6" s="56" t="s">
+        <v>97</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="F6" s="46" t="s">
+        <v>170</v>
+      </c>
+      <c r="F6" s="56" t="s">
         <v>25</v>
       </c>
       <c r="G6" s="3" t="s">
@@ -3704,17 +3707,17 @@
       </c>
       <c r="H6" s="3" t="str">
         <f>VLOOKUP(G6,K$4:L$10,2,FALSE)</f>
-        <v>PHH</v>
+        <v>PGQ</v>
       </c>
       <c r="I6" s="3">
         <v>2</v>
       </c>
-      <c r="J6" s="42"/>
+      <c r="J6" s="50"/>
       <c r="K6" s="3" t="s">
         <v>20</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="M6" s="3"/>
       <c r="N6" s="3" t="s">
@@ -3722,29 +3725,29 @@
       </c>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B7" s="44"/>
-      <c r="C7" s="49"/>
-      <c r="D7" s="46"/>
+      <c r="B7" s="52"/>
+      <c r="C7" s="81"/>
+      <c r="D7" s="56"/>
       <c r="E7" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="46"/>
+      <c r="F7" s="56"/>
       <c r="G7" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H7" s="3" t="str">
         <f>VLOOKUP(G7,K$4:L$10,2,FALSE)</f>
-        <v>PKF</v>
+        <v>PNQ</v>
       </c>
       <c r="I7" s="3">
         <v>1</v>
       </c>
-      <c r="J7" s="42"/>
+      <c r="J7" s="50"/>
       <c r="K7" s="3" t="s">
         <v>30</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="M7" s="3"/>
       <c r="N7" s="3" t="s">
@@ -3752,29 +3755,29 @@
       </c>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B8" s="44"/>
-      <c r="C8" s="49"/>
-      <c r="D8" s="46"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="81"/>
+      <c r="D8" s="56"/>
       <c r="E8" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="F8" s="46"/>
+        <v>99</v>
+      </c>
+      <c r="F8" s="56"/>
       <c r="G8" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H8" s="3" t="str">
         <f>VLOOKUP(G8,K$4:L$10,2,FALSE)</f>
-        <v>PKF</v>
+        <v>PNQ</v>
       </c>
       <c r="I8" s="3">
         <v>1</v>
       </c>
-      <c r="J8" s="42"/>
+      <c r="J8" s="50"/>
       <c r="K8" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="M8" s="3"/>
       <c r="N8" s="3" t="s">
@@ -3782,20 +3785,20 @@
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B9" s="44"/>
-      <c r="C9" s="49"/>
-      <c r="D9" s="46"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="34"/>
-      <c r="G9" s="34"/>
-      <c r="H9" s="34"/>
-      <c r="I9" s="34"/>
-      <c r="J9" s="42"/>
+      <c r="B9" s="52"/>
+      <c r="C9" s="81"/>
+      <c r="D9" s="56"/>
+      <c r="E9" s="54"/>
+      <c r="F9" s="54"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="54"/>
+      <c r="I9" s="54"/>
+      <c r="J9" s="50"/>
       <c r="K9" s="3" t="s">
         <v>39</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="M9" s="3"/>
       <c r="N9" s="3" t="s">
@@ -3803,13 +3806,13 @@
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B10" s="44"/>
-      <c r="C10" s="49"/>
-      <c r="D10" s="46"/>
+      <c r="B10" s="52"/>
+      <c r="C10" s="81"/>
+      <c r="D10" s="56"/>
       <c r="E10" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="F10" s="46" t="s">
+        <v>171</v>
+      </c>
+      <c r="F10" s="56" t="s">
         <v>26</v>
       </c>
       <c r="G10" s="3" t="s">
@@ -3817,17 +3820,17 @@
       </c>
       <c r="H10" s="3" t="str">
         <f>VLOOKUP(G10,K$4:L$10,2,FALSE)</f>
-        <v>PHH</v>
+        <v>PGQ</v>
       </c>
       <c r="I10" s="3">
         <v>2</v>
       </c>
-      <c r="J10" s="42"/>
+      <c r="J10" s="50"/>
       <c r="K10" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="M10" s="3"/>
       <c r="N10" s="3" t="s">
@@ -3835,40 +3838,40 @@
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B11" s="44"/>
-      <c r="C11" s="49"/>
-      <c r="D11" s="46"/>
+      <c r="B11" s="52"/>
+      <c r="C11" s="81"/>
+      <c r="D11" s="56"/>
       <c r="E11" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F11" s="46"/>
+      <c r="F11" s="56"/>
       <c r="G11" s="3" t="s">
         <v>30</v>
       </c>
       <c r="H11" s="3" t="str">
         <f>VLOOKUP(G11,K$4:L$10,2,FALSE)</f>
-        <v>PTW</v>
+        <v>PWC</v>
       </c>
       <c r="I11" s="3">
         <v>1</v>
       </c>
-      <c r="J11" s="42"/>
+      <c r="J11" s="50"/>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B12" s="44"/>
-      <c r="C12" s="49"/>
-      <c r="D12" s="46"/>
-      <c r="E12" s="34"/>
-      <c r="F12" s="34"/>
-      <c r="G12" s="34"/>
-      <c r="H12" s="34"/>
-      <c r="I12" s="34"/>
-      <c r="J12" s="42"/>
+      <c r="B12" s="52"/>
+      <c r="C12" s="81"/>
+      <c r="D12" s="56"/>
+      <c r="E12" s="54"/>
+      <c r="F12" s="54"/>
+      <c r="G12" s="54"/>
+      <c r="H12" s="54"/>
+      <c r="I12" s="54"/>
+      <c r="J12" s="50"/>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B13" s="44"/>
-      <c r="C13" s="49"/>
-      <c r="D13" s="46"/>
+      <c r="B13" s="52"/>
+      <c r="C13" s="81"/>
+      <c r="D13" s="56"/>
       <c r="E13" s="3" t="s">
         <v>34</v>
       </c>
@@ -3880,32 +3883,32 @@
       </c>
       <c r="H13" s="3" t="str">
         <f>VLOOKUP(G13,K$4:L$10,2,FALSE)</f>
-        <v>PTW</v>
+        <v>PWC</v>
       </c>
       <c r="I13" s="3">
         <v>1</v>
       </c>
-      <c r="J13" s="42"/>
+      <c r="J13" s="50"/>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B14" s="44"/>
-      <c r="C14" s="49"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="35"/>
-      <c r="J14" s="42"/>
+      <c r="B14" s="52"/>
+      <c r="C14" s="81"/>
+      <c r="D14" s="55"/>
+      <c r="E14" s="55"/>
+      <c r="F14" s="55"/>
+      <c r="G14" s="55"/>
+      <c r="H14" s="55"/>
+      <c r="I14" s="55"/>
+      <c r="J14" s="50"/>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B15" s="44"/>
-      <c r="C15" s="49"/>
-      <c r="D15" s="46" t="s">
-        <v>177</v>
-      </c>
-      <c r="E15" s="30" t="s">
-        <v>174</v>
+      <c r="B15" s="52"/>
+      <c r="C15" s="81"/>
+      <c r="D15" s="56" t="s">
+        <v>173</v>
+      </c>
+      <c r="E15" s="29" t="s">
+        <v>170</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>25</v>
@@ -3915,32 +3918,32 @@
       </c>
       <c r="H15" s="3" t="str">
         <f>VLOOKUP(G15,K$4:L$10,2,FALSE)</f>
-        <v>PHH</v>
+        <v>PGQ</v>
       </c>
       <c r="I15" s="3">
         <v>2</v>
       </c>
-      <c r="J15" s="42"/>
+      <c r="J15" s="50"/>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B16" s="44"/>
-      <c r="C16" s="49"/>
-      <c r="D16" s="46"/>
-      <c r="E16" s="34"/>
-      <c r="F16" s="34"/>
-      <c r="G16" s="34"/>
-      <c r="H16" s="34"/>
-      <c r="I16" s="34"/>
-      <c r="J16" s="42"/>
+      <c r="B16" s="52"/>
+      <c r="C16" s="81"/>
+      <c r="D16" s="56"/>
+      <c r="E16" s="54"/>
+      <c r="F16" s="54"/>
+      <c r="G16" s="54"/>
+      <c r="H16" s="54"/>
+      <c r="I16" s="54"/>
+      <c r="J16" s="50"/>
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B17" s="44"/>
-      <c r="C17" s="49"/>
-      <c r="D17" s="46"/>
-      <c r="E17" s="30" t="s">
-        <v>175</v>
-      </c>
-      <c r="F17" s="46" t="s">
+      <c r="B17" s="52"/>
+      <c r="C17" s="81"/>
+      <c r="D17" s="56"/>
+      <c r="E17" s="29" t="s">
+        <v>171</v>
+      </c>
+      <c r="F17" s="56" t="s">
         <v>26</v>
       </c>
       <c r="G17" s="3" t="s">
@@ -3948,50 +3951,50 @@
       </c>
       <c r="H17" s="3" t="str">
         <f>VLOOKUP(G17,K$4:L$10,2,FALSE)</f>
-        <v>PHH</v>
+        <v>PGQ</v>
       </c>
       <c r="I17" s="3">
         <v>2</v>
       </c>
-      <c r="J17" s="42"/>
+      <c r="J17" s="50"/>
     </row>
     <row r="18" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B18" s="44"/>
-      <c r="C18" s="49"/>
-      <c r="D18" s="46"/>
+      <c r="B18" s="52"/>
+      <c r="C18" s="81"/>
+      <c r="D18" s="56"/>
       <c r="E18" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="F18" s="46"/>
+        <v>172</v>
+      </c>
+      <c r="F18" s="56"/>
       <c r="G18" s="3" t="s">
         <v>36</v>
       </c>
       <c r="H18" s="3" t="str">
         <f>VLOOKUP(G18,K$4:L$10,2,FALSE)</f>
-        <v>PIW</v>
+        <v>PSG</v>
       </c>
       <c r="I18" s="3">
         <v>1</v>
       </c>
-      <c r="J18" s="42"/>
+      <c r="J18" s="50"/>
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B19" s="44"/>
-      <c r="C19" s="49"/>
-      <c r="D19" s="46"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="34"/>
-      <c r="H19" s="34"/>
-      <c r="I19" s="34"/>
-      <c r="J19" s="42"/>
+      <c r="B19" s="52"/>
+      <c r="C19" s="81"/>
+      <c r="D19" s="56"/>
+      <c r="E19" s="54"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="54"/>
+      <c r="H19" s="54"/>
+      <c r="I19" s="54"/>
+      <c r="J19" s="50"/>
     </row>
     <row r="20" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B20" s="44"/>
-      <c r="C20" s="49"/>
-      <c r="D20" s="46"/>
+      <c r="B20" s="52"/>
+      <c r="C20" s="81"/>
+      <c r="D20" s="56"/>
       <c r="E20" s="3" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>35</v>
@@ -4001,34 +4004,34 @@
       </c>
       <c r="H20" s="3" t="str">
         <f>VLOOKUP(G20,K$4:L$10,2,FALSE)</f>
-        <v>PIW</v>
+        <v>PSG</v>
       </c>
       <c r="I20" s="3">
         <v>1</v>
       </c>
-      <c r="J20" s="42"/>
+      <c r="J20" s="50"/>
     </row>
     <row r="21" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B21" s="44"/>
-      <c r="C21" s="49"/>
-      <c r="D21" s="35"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="35"/>
-      <c r="H21" s="35"/>
-      <c r="I21" s="35"/>
-      <c r="J21" s="42"/>
+      <c r="B21" s="52"/>
+      <c r="C21" s="81"/>
+      <c r="D21" s="55"/>
+      <c r="E21" s="55"/>
+      <c r="F21" s="55"/>
+      <c r="G21" s="55"/>
+      <c r="H21" s="55"/>
+      <c r="I21" s="55"/>
+      <c r="J21" s="50"/>
     </row>
     <row r="22" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B22" s="44"/>
-      <c r="C22" s="49"/>
-      <c r="D22" s="46" t="s">
-        <v>178</v>
-      </c>
-      <c r="E22" s="30" t="s">
+      <c r="B22" s="52"/>
+      <c r="C22" s="81"/>
+      <c r="D22" s="56" t="s">
         <v>174</v>
       </c>
-      <c r="F22" s="46" t="s">
+      <c r="E22" s="29" t="s">
+        <v>170</v>
+      </c>
+      <c r="F22" s="56" t="s">
         <v>25</v>
       </c>
       <c r="G22" s="3" t="s">
@@ -4036,110 +4039,110 @@
       </c>
       <c r="H22" s="3" t="str">
         <f>VLOOKUP(G22,K$4:L$10,2,FALSE)</f>
-        <v>PHH</v>
+        <v>PGQ</v>
       </c>
       <c r="I22" s="3">
         <v>2</v>
       </c>
-      <c r="J22" s="42"/>
+      <c r="J22" s="50"/>
     </row>
     <row r="23" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B23" s="44"/>
-      <c r="C23" s="49"/>
-      <c r="D23" s="46"/>
+      <c r="B23" s="52"/>
+      <c r="C23" s="81"/>
+      <c r="D23" s="56"/>
       <c r="E23" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="F23" s="46"/>
+        <v>104</v>
+      </c>
+      <c r="F23" s="56"/>
       <c r="G23" s="3" t="s">
         <v>39</v>
       </c>
       <c r="H23" s="3" t="str">
         <f>VLOOKUP(G23,K$4:L$10,2,FALSE)</f>
-        <v>PBR</v>
+        <v>PBE</v>
       </c>
       <c r="I23" s="3">
         <v>1</v>
       </c>
-      <c r="J23" s="42"/>
+      <c r="J23" s="50"/>
     </row>
     <row r="24" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B24" s="44"/>
-      <c r="C24" s="49"/>
-      <c r="D24" s="46"/>
+      <c r="B24" s="52"/>
+      <c r="C24" s="81"/>
+      <c r="D24" s="56"/>
       <c r="E24" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F24" s="46"/>
+      <c r="F24" s="56"/>
       <c r="G24" s="3" t="s">
         <v>39</v>
       </c>
       <c r="H24" s="3" t="str">
         <f>VLOOKUP(G24,K$4:L$10,2,FALSE)</f>
-        <v>PBR</v>
+        <v>PBE</v>
       </c>
       <c r="I24" s="3">
         <v>1</v>
       </c>
-      <c r="J24" s="42"/>
+      <c r="J24" s="50"/>
     </row>
     <row r="25" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B25" s="44"/>
-      <c r="C25" s="49"/>
-      <c r="D25" s="46"/>
+      <c r="B25" s="52"/>
+      <c r="C25" s="81"/>
+      <c r="D25" s="56"/>
       <c r="E25" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="F25" s="46"/>
+        <v>177</v>
+      </c>
+      <c r="F25" s="56"/>
       <c r="G25" s="3" t="s">
         <v>39</v>
       </c>
       <c r="H25" s="3" t="str">
         <f>VLOOKUP(G25,K$4:L$10,2,FALSE)</f>
-        <v>PBR</v>
+        <v>PBE</v>
       </c>
       <c r="I25" s="3">
         <v>1</v>
       </c>
-      <c r="J25" s="42"/>
+      <c r="J25" s="50"/>
     </row>
     <row r="26" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B26" s="44"/>
-      <c r="C26" s="49"/>
-      <c r="D26" s="46"/>
+      <c r="B26" s="52"/>
+      <c r="C26" s="81"/>
+      <c r="D26" s="56"/>
       <c r="E26" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="F26" s="46"/>
+      <c r="F26" s="56"/>
       <c r="G26" s="3" t="s">
         <v>39</v>
       </c>
       <c r="H26" s="3" t="str">
         <f>VLOOKUP(G26,K$4:L$10,2,FALSE)</f>
-        <v>PBR</v>
+        <v>PBE</v>
       </c>
       <c r="I26" s="3">
         <v>1</v>
       </c>
-      <c r="J26" s="42"/>
+      <c r="J26" s="50"/>
     </row>
     <row r="27" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B27" s="44"/>
-      <c r="C27" s="49"/>
-      <c r="D27" s="46"/>
-      <c r="E27" s="34"/>
-      <c r="F27" s="34"/>
-      <c r="G27" s="34"/>
-      <c r="H27" s="34"/>
-      <c r="I27" s="34"/>
-      <c r="J27" s="42"/>
+      <c r="B27" s="52"/>
+      <c r="C27" s="81"/>
+      <c r="D27" s="56"/>
+      <c r="E27" s="54"/>
+      <c r="F27" s="54"/>
+      <c r="G27" s="54"/>
+      <c r="H27" s="54"/>
+      <c r="I27" s="54"/>
+      <c r="J27" s="50"/>
     </row>
     <row r="28" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B28" s="44"/>
-      <c r="C28" s="49"/>
-      <c r="D28" s="46"/>
+      <c r="B28" s="52"/>
+      <c r="C28" s="81"/>
+      <c r="D28" s="56"/>
       <c r="E28" s="3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>26</v>
@@ -4149,28 +4152,28 @@
       </c>
       <c r="H28" s="3" t="str">
         <f>VLOOKUP(G28,K$4:L$10,2,FALSE)</f>
-        <v>PBR</v>
+        <v>PBE</v>
       </c>
       <c r="I28" s="3">
         <v>1</v>
       </c>
-      <c r="J28" s="42"/>
+      <c r="J28" s="50"/>
     </row>
     <row r="29" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B29" s="44"/>
-      <c r="C29" s="49"/>
-      <c r="D29" s="46"/>
-      <c r="E29" s="34"/>
-      <c r="F29" s="34"/>
-      <c r="G29" s="34"/>
-      <c r="H29" s="34"/>
-      <c r="I29" s="34"/>
-      <c r="J29" s="42"/>
+      <c r="B29" s="52"/>
+      <c r="C29" s="81"/>
+      <c r="D29" s="56"/>
+      <c r="E29" s="54"/>
+      <c r="F29" s="54"/>
+      <c r="G29" s="54"/>
+      <c r="H29" s="54"/>
+      <c r="I29" s="54"/>
+      <c r="J29" s="50"/>
     </row>
     <row r="30" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B30" s="44"/>
-      <c r="C30" s="49"/>
-      <c r="D30" s="46"/>
+      <c r="B30" s="52"/>
+      <c r="C30" s="81"/>
+      <c r="D30" s="56"/>
       <c r="E30" s="3"/>
       <c r="F30" s="4" t="s">
         <v>35</v>
@@ -4178,43 +4181,43 @@
       <c r="G30" s="4"/>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
-      <c r="J30" s="42"/>
-      <c r="K30" s="32" t="s">
-        <v>99</v>
-      </c>
-      <c r="L30" s="33" t="s">
+      <c r="J30" s="50"/>
+      <c r="K30" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="L30" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="M30" s="33" t="s">
+      <c r="M30" s="32" t="s">
         <v>39</v>
       </c>
       <c r="N30" s="3" t="str">
         <f>VLOOKUP(M30,K$4:N$10,2,FALSE)</f>
-        <v>PBR</v>
-      </c>
-      <c r="O30" s="32">
+        <v>PBE</v>
+      </c>
+      <c r="O30" s="31">
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B31" s="44"/>
-      <c r="C31" s="49"/>
-      <c r="D31" s="35"/>
-      <c r="E31" s="35"/>
-      <c r="F31" s="35"/>
-      <c r="G31" s="35"/>
-      <c r="H31" s="35"/>
-      <c r="I31" s="35"/>
-      <c r="J31" s="42"/>
+      <c r="B31" s="52"/>
+      <c r="C31" s="81"/>
+      <c r="D31" s="55"/>
+      <c r="E31" s="55"/>
+      <c r="F31" s="55"/>
+      <c r="G31" s="55"/>
+      <c r="H31" s="55"/>
+      <c r="I31" s="55"/>
+      <c r="J31" s="50"/>
     </row>
     <row r="32" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B32" s="44"/>
-      <c r="C32" s="49"/>
+      <c r="B32" s="52"/>
+      <c r="C32" s="81"/>
       <c r="D32" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>25</v>
@@ -4224,55 +4227,87 @@
       </c>
       <c r="H32" s="3" t="str">
         <f>VLOOKUP(G32,K$4:L$10,2,FALSE)</f>
-        <v>PDU</v>
+        <v>PXC</v>
       </c>
       <c r="I32" s="3">
         <v>3</v>
       </c>
-      <c r="J32" s="42"/>
+      <c r="J32" s="50"/>
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B33" s="44"/>
-      <c r="C33" s="51"/>
-      <c r="D33" s="51"/>
-      <c r="E33" s="51"/>
-      <c r="F33" s="51"/>
-      <c r="G33" s="51"/>
-      <c r="H33" s="51"/>
-      <c r="I33" s="51"/>
-      <c r="J33" s="42"/>
+      <c r="B33" s="52"/>
+      <c r="C33" s="79"/>
+      <c r="D33" s="79"/>
+      <c r="E33" s="79"/>
+      <c r="F33" s="79"/>
+      <c r="G33" s="79"/>
+      <c r="H33" s="79"/>
+      <c r="I33" s="79"/>
+      <c r="J33" s="50"/>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B34" s="44"/>
-      <c r="C34" s="31" t="s">
-        <v>210</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="E34" s="3"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="3"/>
-      <c r="I34" s="3"/>
-      <c r="J34" s="42"/>
+      <c r="B34" s="52"/>
+      <c r="C34" s="37" t="s">
+        <v>206</v>
+      </c>
+      <c r="D34" s="38" t="s">
+        <v>175</v>
+      </c>
+      <c r="E34" s="39"/>
+      <c r="F34" s="38"/>
+      <c r="G34" s="38"/>
+      <c r="H34" s="39"/>
+      <c r="I34" s="39"/>
+      <c r="J34" s="50"/>
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B35" s="45"/>
-      <c r="C35" s="50"/>
-      <c r="D35" s="50"/>
-      <c r="E35" s="50"/>
-      <c r="F35" s="50"/>
-      <c r="G35" s="50"/>
-      <c r="H35" s="50"/>
-      <c r="I35" s="50"/>
-      <c r="J35" s="43"/>
+      <c r="B35" s="42"/>
+      <c r="C35" s="43"/>
+      <c r="D35" s="44"/>
+      <c r="E35" s="44"/>
+      <c r="F35" s="44"/>
+      <c r="G35" s="44"/>
+      <c r="H35" s="44"/>
+      <c r="I35" s="45"/>
+      <c r="J35" s="42"/>
+    </row>
+    <row r="36" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B36" s="34"/>
+      <c r="C36" s="40" t="s">
+        <v>209</v>
+      </c>
+      <c r="D36" s="41"/>
+      <c r="E36" s="35"/>
+      <c r="F36" s="41"/>
+      <c r="G36" s="41"/>
+      <c r="H36" s="35"/>
+      <c r="I36" s="35"/>
+      <c r="J36" s="33"/>
+    </row>
+    <row r="37" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B37" s="53"/>
+      <c r="C37" s="64"/>
+      <c r="D37" s="64"/>
+      <c r="E37" s="64"/>
+      <c r="F37" s="64"/>
+      <c r="G37" s="64"/>
+      <c r="H37" s="64"/>
+      <c r="I37" s="64"/>
+      <c r="J37" s="51"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="C6:C32"/>
+    <mergeCell ref="E27:I27"/>
+    <mergeCell ref="E29:I29"/>
+    <mergeCell ref="E9:I9"/>
+    <mergeCell ref="E12:I12"/>
+    <mergeCell ref="D6:D13"/>
+    <mergeCell ref="D15:D20"/>
+    <mergeCell ref="D22:D30"/>
     <mergeCell ref="K3:N3"/>
     <mergeCell ref="B2:J2"/>
-    <mergeCell ref="B35:J35"/>
+    <mergeCell ref="B37:J37"/>
     <mergeCell ref="B3:B34"/>
     <mergeCell ref="J3:J34"/>
     <mergeCell ref="C33:I33"/>
@@ -4286,14 +4321,6 @@
     <mergeCell ref="C5:I5"/>
     <mergeCell ref="D14:I14"/>
     <mergeCell ref="D21:I21"/>
-    <mergeCell ref="C6:C32"/>
-    <mergeCell ref="E27:I27"/>
-    <mergeCell ref="E29:I29"/>
-    <mergeCell ref="E9:I9"/>
-    <mergeCell ref="E12:I12"/>
-    <mergeCell ref="D6:D13"/>
-    <mergeCell ref="D15:D20"/>
-    <mergeCell ref="D22:D30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Testes.xlsx
+++ b/Testes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\utilizador\Documents\CTESP\4semestre\LP2\ProjetoTesteLP2\TrabalhoTesteLP2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7DC74CE1-F1E8-4357-A95F-DBD58EF78C1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF5B3076-E676-4F07-8DDB-666FEA0CC14C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{17050BBC-8C72-4C7C-BB9E-52ED50A4B6E1}"/>
+    <workbookView xWindow="28695" yWindow="-12330" windowWidth="19410" windowHeight="20985" xr2:uid="{17050BBC-8C72-4C7C-BB9E-52ED50A4B6E1}"/>
   </bookViews>
   <sheets>
     <sheet name="Menus" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,6 @@
     <sheet name="Escola" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="181029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="243">
   <si>
     <t>1 - Adicionar Departamento</t>
   </si>
@@ -662,97 +661,103 @@
     <t>[INATIVO] DCS : Departamento de Ciencias Sociais</t>
   </si>
   <si>
-    <t>pbe@issmf.ipp.pt</t>
-  </si>
-  <si>
-    <t>PBE</t>
-  </si>
-  <si>
     <t>22-02-2003</t>
   </si>
   <si>
-    <t>vC9Rv6K2</t>
-  </si>
-  <si>
-    <t>gYr6lZ0I</t>
-  </si>
-  <si>
-    <t>pnq@issmf.ipp.pt</t>
-  </si>
-  <si>
-    <t>OeBdaytL</t>
-  </si>
-  <si>
-    <t>PNQ</t>
-  </si>
-  <si>
-    <t>ZOvcpGJj</t>
-  </si>
-  <si>
-    <t>pgq@issmf.ipp.pt</t>
-  </si>
-  <si>
-    <t>PGQ</t>
-  </si>
-  <si>
-    <t>pxc@issmf.ipp.pt</t>
-  </si>
-  <si>
-    <t>ITt8HAcv</t>
-  </si>
-  <si>
-    <t>PXC</t>
-  </si>
-  <si>
-    <t>PWC</t>
-  </si>
-  <si>
-    <t>pwc@issmf.ipp.pt</t>
-  </si>
-  <si>
-    <t>c4Fa28Mq</t>
-  </si>
-  <si>
-    <t>PSG</t>
-  </si>
-  <si>
-    <t>kKee0ZHT</t>
-  </si>
-  <si>
-    <t>psg@issmf.ipp.pt</t>
-  </si>
-  <si>
-    <t>wbWQ7r1t</t>
-  </si>
-  <si>
-    <t>pfo@issmf.ipp.pt</t>
-  </si>
-  <si>
-    <t>Vvfr9h47</t>
-  </si>
-  <si>
-    <t>PFO</t>
-  </si>
-  <si>
-    <t>puoC4pv3</t>
-  </si>
-  <si>
-    <t>F18ZTLEK</t>
-  </si>
-  <si>
-    <t>gALRNpIz</t>
-  </si>
-  <si>
-    <t>denGlK7P</t>
-  </si>
-  <si>
-    <t>3yn006vk</t>
-  </si>
-  <si>
-    <t>KBgtFxD8</t>
-  </si>
-  <si>
-    <t>arzoI5uB</t>
+    <t>0P8h49rr</t>
+  </si>
+  <si>
+    <t>slhwDYvR</t>
+  </si>
+  <si>
+    <t>PLE</t>
+  </si>
+  <si>
+    <t>R3bxjdIj</t>
+  </si>
+  <si>
+    <t>ple@issmf.ipp.pt</t>
+  </si>
+  <si>
+    <t>prf@issmf.ipp.pt</t>
+  </si>
+  <si>
+    <t>cRca8nOz</t>
+  </si>
+  <si>
+    <t>PRF</t>
+  </si>
+  <si>
+    <t>pel@issmf.ipp.pt</t>
+  </si>
+  <si>
+    <t>Z7aaO6ou</t>
+  </si>
+  <si>
+    <t>PEL</t>
+  </si>
+  <si>
+    <t>PEG</t>
+  </si>
+  <si>
+    <t>yextGVo5</t>
+  </si>
+  <si>
+    <t>peg@issmf.ipp.pt</t>
+  </si>
+  <si>
+    <t>XaMVJuaR</t>
+  </si>
+  <si>
+    <t>ppi@issmf.ipp.pt</t>
+  </si>
+  <si>
+    <t>PPI</t>
+  </si>
+  <si>
+    <t>PCL</t>
+  </si>
+  <si>
+    <t>pcl@issmf.ipp.pt</t>
+  </si>
+  <si>
+    <t>4S0SvOt6</t>
+  </si>
+  <si>
+    <t>PIA</t>
+  </si>
+  <si>
+    <t>pia@issmf.ipp.pt</t>
+  </si>
+  <si>
+    <t>dQE2KwUU</t>
+  </si>
+  <si>
+    <t>scwR0qPn</t>
+  </si>
+  <si>
+    <t>kfhgmL8t</t>
+  </si>
+  <si>
+    <t>RNqLTmaI</t>
+  </si>
+  <si>
+    <t>JJrJzl6V</t>
+  </si>
+  <si>
+    <t>bony4SSI</t>
+  </si>
+  <si>
+    <t>sZQ4GwbM</t>
+  </si>
+  <si>
+    <t>BwgUfyzT</t>
+  </si>
+  <si>
+    <t>LEN</t>
+  </si>
+  <si>
+    <t>6 - Pedir Certificado de Conclusão de Curso</t>
   </si>
 </sst>
 </file>
@@ -1104,6 +1109,22 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1125,12 +1146,6 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1140,62 +1155,56 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1206,10 +1215,6 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperligação" xfId="1" builtinId="8"/>
@@ -1525,7 +1530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{781029DD-AB0E-45D2-BEA2-289639D498A2}">
-  <dimension ref="B2:F119"/>
+  <dimension ref="B2:F120"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="35" bestFit="1" customWidth="1"/>
@@ -1534,1063 +1539,1072 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B2" s="47"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="49"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="55"/>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B3" s="52"/>
-      <c r="C3" s="59" t="s">
+      <c r="B3" s="58"/>
+      <c r="C3" s="50" t="s">
         <v>197</v>
       </c>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="50"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="56"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B4" s="52"/>
+      <c r="B4" s="58"/>
       <c r="C4" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="D4" s="54"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="50"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="56"/>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B5" s="52"/>
+      <c r="B5" s="58"/>
       <c r="C5" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="50"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="56"/>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B6" s="52"/>
+      <c r="B6" s="58"/>
       <c r="C6" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D6" s="54"/>
-      <c r="E6" s="54"/>
-      <c r="F6" s="50"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="49"/>
+      <c r="F6" s="56"/>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B7" s="52"/>
+      <c r="B7" s="58"/>
       <c r="C7" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="D7" s="54"/>
-      <c r="E7" s="54"/>
-      <c r="F7" s="50"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="56"/>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B8" s="52"/>
+      <c r="B8" s="58"/>
       <c r="C8" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="D8" s="54"/>
-      <c r="E8" s="54"/>
-      <c r="F8" s="50"/>
+      <c r="D8" s="49"/>
+      <c r="E8" s="49"/>
+      <c r="F8" s="56"/>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B9" s="52"/>
+      <c r="B9" s="58"/>
       <c r="C9" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="D9" s="54"/>
-      <c r="E9" s="54"/>
-      <c r="F9" s="50"/>
+      <c r="D9" s="49"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="56"/>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B10" s="52"/>
+      <c r="B10" s="58"/>
       <c r="C10" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D10" s="54"/>
-      <c r="E10" s="54"/>
-      <c r="F10" s="50"/>
+      <c r="D10" s="49"/>
+      <c r="E10" s="49"/>
+      <c r="F10" s="56"/>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B11" s="52"/>
-      <c r="C11" s="55"/>
-      <c r="D11" s="55"/>
-      <c r="E11" s="55"/>
-      <c r="F11" s="50"/>
+      <c r="B11" s="58"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="48"/>
+      <c r="E11" s="48"/>
+      <c r="F11" s="56"/>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B12" s="52"/>
-      <c r="C12" s="57" t="s">
+      <c r="B12" s="58"/>
+      <c r="C12" s="61" t="s">
         <v>196</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="E12" s="54"/>
-      <c r="F12" s="50"/>
+      <c r="E12" s="49"/>
+      <c r="F12" s="56"/>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B13" s="52"/>
-      <c r="C13" s="58"/>
+      <c r="B13" s="58"/>
+      <c r="C13" s="62"/>
       <c r="D13" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="E13" s="54"/>
-      <c r="F13" s="50"/>
+      <c r="E13" s="49"/>
+      <c r="F13" s="56"/>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B14" s="52"/>
-      <c r="C14" s="58"/>
+      <c r="B14" s="58"/>
+      <c r="C14" s="62"/>
       <c r="D14" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="E14" s="54"/>
-      <c r="F14" s="50"/>
+      <c r="E14" s="49"/>
+      <c r="F14" s="56"/>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B15" s="52"/>
-      <c r="C15" s="58"/>
+      <c r="B15" s="58"/>
+      <c r="C15" s="62"/>
       <c r="D15" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="E15" s="54"/>
-      <c r="F15" s="50"/>
+      <c r="E15" s="49"/>
+      <c r="F15" s="56"/>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B16" s="52"/>
-      <c r="C16" s="58"/>
+      <c r="B16" s="58"/>
+      <c r="C16" s="62"/>
       <c r="D16" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="E16" s="54"/>
-      <c r="F16" s="50"/>
+      <c r="E16" s="49"/>
+      <c r="F16" s="56"/>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B17" s="52"/>
-      <c r="C17" s="58"/>
+      <c r="B17" s="58"/>
+      <c r="C17" s="62"/>
       <c r="D17" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="E17" s="54"/>
-      <c r="F17" s="50"/>
+      <c r="E17" s="49"/>
+      <c r="F17" s="56"/>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B18" s="52"/>
-      <c r="C18" s="58"/>
+      <c r="B18" s="58"/>
+      <c r="C18" s="62"/>
       <c r="D18" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="E18" s="54"/>
-      <c r="F18" s="50"/>
+      <c r="E18" s="49"/>
+      <c r="F18" s="56"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B19" s="52"/>
-      <c r="C19" s="58"/>
+      <c r="B19" s="58"/>
+      <c r="C19" s="62"/>
       <c r="D19" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="E19" s="54"/>
-      <c r="F19" s="50"/>
+      <c r="E19" s="49"/>
+      <c r="F19" s="56"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B20" s="52"/>
-      <c r="C20" s="58"/>
-      <c r="D20" s="60"/>
-      <c r="E20" s="61"/>
-      <c r="F20" s="50"/>
+      <c r="B20" s="58"/>
+      <c r="C20" s="62"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="52"/>
+      <c r="F20" s="56"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B21" s="52"/>
-      <c r="C21" s="58"/>
-      <c r="D21" s="54"/>
+      <c r="B21" s="58"/>
+      <c r="C21" s="62"/>
+      <c r="D21" s="49"/>
       <c r="E21" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="F21" s="50"/>
+      <c r="F21" s="56"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B22" s="52"/>
-      <c r="C22" s="58"/>
-      <c r="D22" s="54"/>
+      <c r="B22" s="58"/>
+      <c r="C22" s="62"/>
+      <c r="D22" s="49"/>
       <c r="E22" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="F22" s="50"/>
+      <c r="F22" s="56"/>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B23" s="52"/>
-      <c r="C23" s="58"/>
-      <c r="D23" s="54"/>
+      <c r="B23" s="58"/>
+      <c r="C23" s="62"/>
+      <c r="D23" s="49"/>
       <c r="E23" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="F23" s="50"/>
+      <c r="F23" s="56"/>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B24" s="52"/>
-      <c r="C24" s="58"/>
-      <c r="D24" s="54"/>
+      <c r="B24" s="58"/>
+      <c r="C24" s="62"/>
+      <c r="D24" s="49"/>
       <c r="E24" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="F24" s="50"/>
+      <c r="F24" s="56"/>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B25" s="52"/>
-      <c r="C25" s="58"/>
-      <c r="D25" s="54"/>
+      <c r="B25" s="58"/>
+      <c r="C25" s="62"/>
+      <c r="D25" s="49"/>
       <c r="E25" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F25" s="50"/>
+      <c r="F25" s="56"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B26" s="52"/>
-      <c r="C26" s="58"/>
-      <c r="D26" s="54"/>
+      <c r="B26" s="58"/>
+      <c r="C26" s="62"/>
+      <c r="D26" s="49"/>
       <c r="E26" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F26" s="50"/>
+      <c r="F26" s="56"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B27" s="52"/>
-      <c r="C27" s="58"/>
-      <c r="D27" s="54"/>
+      <c r="B27" s="58"/>
+      <c r="C27" s="62"/>
+      <c r="D27" s="49"/>
       <c r="E27" s="7"/>
-      <c r="F27" s="50"/>
+      <c r="F27" s="56"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B28" s="52"/>
-      <c r="C28" s="58"/>
-      <c r="D28" s="54"/>
+      <c r="B28" s="58"/>
+      <c r="C28" s="62"/>
+      <c r="D28" s="49"/>
       <c r="E28" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="F28" s="50"/>
+      <c r="F28" s="56"/>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B29" s="52"/>
-      <c r="C29" s="58"/>
-      <c r="D29" s="54"/>
+      <c r="B29" s="58"/>
+      <c r="C29" s="62"/>
+      <c r="D29" s="49"/>
       <c r="E29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F29" s="50"/>
+      <c r="F29" s="56"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B30" s="52"/>
-      <c r="C30" s="58"/>
-      <c r="D30" s="54"/>
+      <c r="B30" s="58"/>
+      <c r="C30" s="62"/>
+      <c r="D30" s="49"/>
       <c r="E30" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F30" s="50"/>
+      <c r="F30" s="56"/>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B31" s="52"/>
-      <c r="C31" s="58"/>
-      <c r="D31" s="54"/>
+      <c r="B31" s="58"/>
+      <c r="C31" s="62"/>
+      <c r="D31" s="49"/>
       <c r="E31" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="F31" s="50"/>
+      <c r="F31" s="56"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B32" s="52"/>
-      <c r="C32" s="58"/>
-      <c r="D32" s="54"/>
+      <c r="B32" s="58"/>
+      <c r="C32" s="62"/>
+      <c r="D32" s="49"/>
       <c r="E32" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="F32" s="50"/>
+      <c r="F32" s="56"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B33" s="52"/>
-      <c r="C33" s="58"/>
-      <c r="D33" s="54"/>
+      <c r="B33" s="58"/>
+      <c r="C33" s="62"/>
+      <c r="D33" s="49"/>
       <c r="E33" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="F33" s="50"/>
+      <c r="F33" s="56"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B34" s="52"/>
-      <c r="C34" s="58"/>
-      <c r="D34" s="54"/>
+      <c r="B34" s="58"/>
+      <c r="C34" s="62"/>
+      <c r="D34" s="49"/>
       <c r="E34" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="F34" s="50"/>
+      <c r="F34" s="56"/>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B35" s="52"/>
-      <c r="C35" s="58"/>
-      <c r="D35" s="54"/>
+      <c r="B35" s="58"/>
+      <c r="C35" s="62"/>
+      <c r="D35" s="49"/>
       <c r="E35" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="F35" s="50"/>
+      <c r="F35" s="56"/>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B36" s="52"/>
-      <c r="C36" s="58"/>
-      <c r="D36" s="54"/>
+      <c r="B36" s="58"/>
+      <c r="C36" s="62"/>
+      <c r="D36" s="49"/>
       <c r="E36" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="F36" s="50"/>
+      <c r="F36" s="56"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B37" s="52"/>
-      <c r="C37" s="58"/>
-      <c r="D37" s="54"/>
+      <c r="B37" s="58"/>
+      <c r="C37" s="62"/>
+      <c r="D37" s="49"/>
       <c r="E37" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F37" s="50"/>
+      <c r="F37" s="56"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B38" s="52"/>
-      <c r="C38" s="58"/>
-      <c r="D38" s="54"/>
+      <c r="B38" s="58"/>
+      <c r="C38" s="62"/>
+      <c r="D38" s="49"/>
       <c r="E38" s="7"/>
-      <c r="F38" s="50"/>
+      <c r="F38" s="56"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B39" s="52"/>
-      <c r="C39" s="58"/>
-      <c r="D39" s="54"/>
+      <c r="B39" s="58"/>
+      <c r="C39" s="62"/>
+      <c r="D39" s="49"/>
       <c r="E39" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="F39" s="50"/>
+      <c r="F39" s="56"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B40" s="52"/>
-      <c r="C40" s="58"/>
-      <c r="D40" s="54"/>
+      <c r="B40" s="58"/>
+      <c r="C40" s="62"/>
+      <c r="D40" s="49"/>
       <c r="E40" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="F40" s="50"/>
+      <c r="F40" s="56"/>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B41" s="52"/>
-      <c r="C41" s="58"/>
-      <c r="D41" s="54"/>
+      <c r="B41" s="58"/>
+      <c r="C41" s="62"/>
+      <c r="D41" s="49"/>
       <c r="E41" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F41" s="50"/>
+      <c r="F41" s="56"/>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B42" s="52"/>
-      <c r="C42" s="58"/>
-      <c r="D42" s="54"/>
+      <c r="B42" s="58"/>
+      <c r="C42" s="62"/>
+      <c r="D42" s="49"/>
       <c r="E42" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F42" s="50"/>
+      <c r="F42" s="56"/>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B43" s="52"/>
-      <c r="C43" s="58"/>
-      <c r="D43" s="54"/>
+      <c r="B43" s="58"/>
+      <c r="C43" s="62"/>
+      <c r="D43" s="49"/>
       <c r="E43" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="F43" s="50"/>
+      <c r="F43" s="56"/>
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B44" s="52"/>
-      <c r="C44" s="58"/>
-      <c r="D44" s="54"/>
+      <c r="B44" s="58"/>
+      <c r="C44" s="62"/>
+      <c r="D44" s="49"/>
       <c r="E44" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="F44" s="50"/>
+      <c r="F44" s="56"/>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B45" s="52"/>
-      <c r="C45" s="58"/>
-      <c r="D45" s="54"/>
+      <c r="B45" s="58"/>
+      <c r="C45" s="62"/>
+      <c r="D45" s="49"/>
       <c r="E45" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="F45" s="50"/>
+      <c r="F45" s="56"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B46" s="52"/>
-      <c r="C46" s="58"/>
-      <c r="D46" s="54"/>
+      <c r="B46" s="58"/>
+      <c r="C46" s="62"/>
+      <c r="D46" s="49"/>
       <c r="E46" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="F46" s="50"/>
+      <c r="F46" s="56"/>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B47" s="52"/>
-      <c r="C47" s="58"/>
-      <c r="D47" s="54"/>
+      <c r="B47" s="58"/>
+      <c r="C47" s="62"/>
+      <c r="D47" s="49"/>
       <c r="E47" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="F47" s="50"/>
+      <c r="F47" s="56"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B48" s="52"/>
-      <c r="C48" s="58"/>
-      <c r="D48" s="54"/>
+      <c r="B48" s="58"/>
+      <c r="C48" s="62"/>
+      <c r="D48" s="49"/>
       <c r="E48" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F48" s="50"/>
+      <c r="F48" s="56"/>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B49" s="52"/>
-      <c r="C49" s="58"/>
-      <c r="D49" s="54"/>
+      <c r="B49" s="58"/>
+      <c r="C49" s="62"/>
+      <c r="D49" s="49"/>
       <c r="E49" s="7"/>
-      <c r="F49" s="50"/>
+      <c r="F49" s="56"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B50" s="52"/>
-      <c r="C50" s="58"/>
-      <c r="D50" s="54"/>
+      <c r="B50" s="58"/>
+      <c r="C50" s="62"/>
+      <c r="D50" s="49"/>
       <c r="E50" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="F50" s="50"/>
+      <c r="F50" s="56"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B51" s="52"/>
-      <c r="C51" s="58"/>
-      <c r="D51" s="54"/>
+      <c r="B51" s="58"/>
+      <c r="C51" s="62"/>
+      <c r="D51" s="49"/>
       <c r="E51" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F51" s="50"/>
+      <c r="F51" s="56"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B52" s="52"/>
-      <c r="C52" s="58"/>
-      <c r="D52" s="54"/>
+      <c r="B52" s="58"/>
+      <c r="C52" s="62"/>
+      <c r="D52" s="49"/>
       <c r="E52" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F52" s="50"/>
+      <c r="F52" s="56"/>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B53" s="52"/>
-      <c r="C53" s="58"/>
-      <c r="D53" s="54"/>
+      <c r="B53" s="58"/>
+      <c r="C53" s="62"/>
+      <c r="D53" s="49"/>
       <c r="E53" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="F53" s="50"/>
+      <c r="F53" s="56"/>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B54" s="52"/>
-      <c r="C54" s="58"/>
-      <c r="D54" s="54"/>
+      <c r="B54" s="58"/>
+      <c r="C54" s="62"/>
+      <c r="D54" s="49"/>
       <c r="E54" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F54" s="50"/>
+      <c r="F54" s="56"/>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B55" s="52"/>
-      <c r="C55" s="58"/>
-      <c r="D55" s="54"/>
+      <c r="B55" s="58"/>
+      <c r="C55" s="62"/>
+      <c r="D55" s="49"/>
       <c r="E55" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="F55" s="50"/>
+      <c r="F55" s="56"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B56" s="52"/>
-      <c r="C56" s="58"/>
-      <c r="D56" s="54"/>
+      <c r="B56" s="58"/>
+      <c r="C56" s="62"/>
+      <c r="D56" s="49"/>
       <c r="E56" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F56" s="50"/>
+      <c r="F56" s="56"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B57" s="52"/>
-      <c r="C57" s="58"/>
-      <c r="D57" s="54"/>
+      <c r="B57" s="58"/>
+      <c r="C57" s="62"/>
+      <c r="D57" s="49"/>
       <c r="E57" s="7"/>
-      <c r="F57" s="50"/>
+      <c r="F57" s="56"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B58" s="52"/>
-      <c r="C58" s="58"/>
-      <c r="D58" s="54"/>
+      <c r="B58" s="58"/>
+      <c r="C58" s="62"/>
+      <c r="D58" s="49"/>
       <c r="E58" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="F58" s="50"/>
+      <c r="F58" s="56"/>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B59" s="52"/>
-      <c r="C59" s="58"/>
-      <c r="D59" s="54"/>
+      <c r="B59" s="58"/>
+      <c r="C59" s="62"/>
+      <c r="D59" s="49"/>
       <c r="E59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F59" s="50"/>
+      <c r="F59" s="56"/>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B60" s="52"/>
-      <c r="C60" s="58"/>
-      <c r="D60" s="54"/>
+      <c r="B60" s="58"/>
+      <c r="C60" s="62"/>
+      <c r="D60" s="49"/>
       <c r="E60" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F60" s="50"/>
+      <c r="F60" s="56"/>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B61" s="52"/>
-      <c r="C61" s="58"/>
-      <c r="D61" s="54"/>
+      <c r="B61" s="58"/>
+      <c r="C61" s="62"/>
+      <c r="D61" s="49"/>
       <c r="E61" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="F61" s="50"/>
+      <c r="F61" s="56"/>
     </row>
     <row r="62" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B62" s="52"/>
-      <c r="C62" s="58"/>
-      <c r="D62" s="54"/>
+      <c r="B62" s="58"/>
+      <c r="C62" s="62"/>
+      <c r="D62" s="49"/>
       <c r="E62" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F62" s="50"/>
+      <c r="F62" s="56"/>
     </row>
     <row r="63" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B63" s="52"/>
-      <c r="C63" s="58"/>
-      <c r="D63" s="54"/>
+      <c r="B63" s="58"/>
+      <c r="C63" s="62"/>
+      <c r="D63" s="49"/>
       <c r="E63" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="F63" s="50"/>
+      <c r="F63" s="56"/>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B64" s="52"/>
-      <c r="C64" s="58"/>
-      <c r="D64" s="54"/>
+      <c r="B64" s="58"/>
+      <c r="C64" s="62"/>
+      <c r="D64" s="49"/>
       <c r="E64" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F64" s="50"/>
+      <c r="F64" s="56"/>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B65" s="52"/>
-      <c r="C65" s="58"/>
-      <c r="D65" s="54"/>
+      <c r="B65" s="58"/>
+      <c r="C65" s="62"/>
+      <c r="D65" s="49"/>
       <c r="E65" s="7"/>
-      <c r="F65" s="50"/>
+      <c r="F65" s="56"/>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B66" s="52"/>
-      <c r="C66" s="58"/>
-      <c r="D66" s="54"/>
+      <c r="B66" s="58"/>
+      <c r="C66" s="62"/>
+      <c r="D66" s="49"/>
       <c r="E66" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="F66" s="50"/>
+      <c r="F66" s="56"/>
     </row>
     <row r="67" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B67" s="52"/>
-      <c r="C67" s="58"/>
-      <c r="D67" s="54"/>
+      <c r="B67" s="58"/>
+      <c r="C67" s="62"/>
+      <c r="D67" s="49"/>
       <c r="E67" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F67" s="50"/>
+      <c r="F67" s="56"/>
     </row>
     <row r="68" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B68" s="52"/>
-      <c r="C68" s="58"/>
-      <c r="D68" s="54"/>
+      <c r="B68" s="58"/>
+      <c r="C68" s="62"/>
+      <c r="D68" s="49"/>
       <c r="E68" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="F68" s="50"/>
+      <c r="F68" s="56"/>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B69" s="52"/>
-      <c r="C69" s="58"/>
-      <c r="D69" s="54"/>
+      <c r="B69" s="58"/>
+      <c r="C69" s="62"/>
+      <c r="D69" s="49"/>
       <c r="E69" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F69" s="50"/>
+      <c r="F69" s="56"/>
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B70" s="52"/>
-      <c r="C70" s="58"/>
-      <c r="D70" s="54"/>
+      <c r="B70" s="58"/>
+      <c r="C70" s="62"/>
+      <c r="D70" s="49"/>
       <c r="E70" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="F70" s="50"/>
+      <c r="F70" s="56"/>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B71" s="52"/>
-      <c r="C71" s="58"/>
-      <c r="D71" s="54"/>
+      <c r="B71" s="58"/>
+      <c r="C71" s="62"/>
+      <c r="D71" s="49"/>
       <c r="E71" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F71" s="50"/>
+      <c r="F71" s="56"/>
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B72" s="52"/>
-      <c r="C72" s="58"/>
-      <c r="D72" s="54"/>
+      <c r="B72" s="58"/>
+      <c r="C72" s="62"/>
+      <c r="D72" s="49"/>
       <c r="E72" s="7"/>
-      <c r="F72" s="50"/>
+      <c r="F72" s="56"/>
     </row>
     <row r="73" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B73" s="52"/>
-      <c r="C73" s="58"/>
-      <c r="D73" s="54"/>
+      <c r="B73" s="58"/>
+      <c r="C73" s="62"/>
+      <c r="D73" s="49"/>
       <c r="E73" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="F73" s="50"/>
+      <c r="F73" s="56"/>
     </row>
     <row r="74" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B74" s="52"/>
-      <c r="C74" s="58"/>
-      <c r="D74" s="54"/>
+      <c r="B74" s="58"/>
+      <c r="C74" s="62"/>
+      <c r="D74" s="49"/>
       <c r="E74" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="F74" s="50"/>
+      <c r="F74" s="56"/>
     </row>
     <row r="75" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B75" s="52"/>
-      <c r="C75" s="58"/>
-      <c r="D75" s="54"/>
+      <c r="B75" s="58"/>
+      <c r="C75" s="62"/>
+      <c r="D75" s="49"/>
       <c r="E75" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F75" s="50"/>
+      <c r="F75" s="56"/>
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B76" s="52"/>
-      <c r="C76" s="55"/>
-      <c r="D76" s="55"/>
-      <c r="E76" s="55"/>
-      <c r="F76" s="50"/>
+      <c r="B76" s="58"/>
+      <c r="C76" s="48"/>
+      <c r="D76" s="48"/>
+      <c r="E76" s="48"/>
+      <c r="F76" s="56"/>
     </row>
     <row r="77" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B77" s="52"/>
-      <c r="C77" s="56" t="s">
+      <c r="B77" s="58"/>
+      <c r="C77" s="60" t="s">
         <v>168</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="E77" s="54"/>
-      <c r="F77" s="50"/>
+      <c r="E77" s="49"/>
+      <c r="F77" s="56"/>
     </row>
     <row r="78" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B78" s="52"/>
-      <c r="C78" s="56"/>
+      <c r="B78" s="58"/>
+      <c r="C78" s="60"/>
       <c r="D78" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E78" s="54"/>
-      <c r="F78" s="50"/>
+      <c r="E78" s="49"/>
+      <c r="F78" s="56"/>
     </row>
     <row r="79" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B79" s="52"/>
-      <c r="C79" s="56"/>
+      <c r="B79" s="58"/>
+      <c r="C79" s="60"/>
       <c r="D79" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="E79" s="54"/>
-      <c r="F79" s="50"/>
+      <c r="E79" s="49"/>
+      <c r="F79" s="56"/>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B80" s="52"/>
-      <c r="C80" s="56"/>
+      <c r="B80" s="58"/>
+      <c r="C80" s="60"/>
       <c r="D80" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="E80" s="54"/>
-      <c r="F80" s="50"/>
+      <c r="E80" s="49"/>
+      <c r="F80" s="56"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B81" s="52"/>
-      <c r="C81" s="56"/>
+      <c r="B81" s="58"/>
+      <c r="C81" s="60"/>
       <c r="D81" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="E81" s="54"/>
-      <c r="F81" s="50"/>
+      <c r="E81" s="49"/>
+      <c r="F81" s="56"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B82" s="52"/>
-      <c r="C82" s="56"/>
+      <c r="B82" s="58"/>
+      <c r="C82" s="60"/>
       <c r="D82" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E82" s="54"/>
-      <c r="F82" s="50"/>
+      <c r="E82" s="49"/>
+      <c r="F82" s="56"/>
     </row>
     <row r="83" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B83" s="52"/>
-      <c r="C83" s="56"/>
-      <c r="D83" s="54"/>
-      <c r="E83" s="54"/>
-      <c r="F83" s="50"/>
+      <c r="B83" s="58"/>
+      <c r="C83" s="60"/>
+      <c r="D83" s="49"/>
+      <c r="E83" s="49"/>
+      <c r="F83" s="56"/>
     </row>
     <row r="84" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B84" s="52"/>
-      <c r="C84" s="56"/>
-      <c r="D84" s="54"/>
+      <c r="B84" s="58"/>
+      <c r="C84" s="60"/>
+      <c r="D84" s="49"/>
       <c r="E84" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="F84" s="50"/>
+      <c r="F84" s="56"/>
     </row>
     <row r="85" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B85" s="52"/>
-      <c r="C85" s="56"/>
-      <c r="D85" s="54"/>
+      <c r="B85" s="58"/>
+      <c r="C85" s="60"/>
+      <c r="D85" s="49"/>
       <c r="E85" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="F85" s="50"/>
+      <c r="F85" s="56"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B86" s="52"/>
-      <c r="C86" s="56"/>
-      <c r="D86" s="54"/>
+      <c r="B86" s="58"/>
+      <c r="C86" s="60"/>
+      <c r="D86" s="49"/>
       <c r="E86" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="F86" s="50"/>
+      <c r="F86" s="56"/>
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B87" s="52"/>
-      <c r="C87" s="56"/>
-      <c r="D87" s="54"/>
+      <c r="B87" s="58"/>
+      <c r="C87" s="60"/>
+      <c r="D87" s="49"/>
       <c r="E87" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="F87" s="50"/>
+      <c r="F87" s="56"/>
     </row>
     <row r="88" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B88" s="52"/>
-      <c r="C88" s="56"/>
-      <c r="D88" s="54"/>
+      <c r="B88" s="58"/>
+      <c r="C88" s="60"/>
+      <c r="D88" s="49"/>
       <c r="E88" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="F88" s="50"/>
+      <c r="F88" s="56"/>
     </row>
     <row r="89" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B89" s="52"/>
-      <c r="C89" s="56"/>
-      <c r="D89" s="54"/>
+      <c r="B89" s="58"/>
+      <c r="C89" s="60"/>
+      <c r="D89" s="49"/>
       <c r="E89" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F89" s="50"/>
+      <c r="F89" s="56"/>
     </row>
     <row r="90" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B90" s="52"/>
-      <c r="C90" s="56"/>
-      <c r="D90" s="54"/>
+      <c r="B90" s="58"/>
+      <c r="C90" s="60"/>
+      <c r="D90" s="49"/>
       <c r="E90" s="7"/>
-      <c r="F90" s="50"/>
+      <c r="F90" s="56"/>
     </row>
     <row r="91" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B91" s="52"/>
-      <c r="C91" s="56"/>
-      <c r="D91" s="54"/>
+      <c r="B91" s="58"/>
+      <c r="C91" s="60"/>
+      <c r="D91" s="49"/>
       <c r="E91" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="F91" s="50"/>
+      <c r="F91" s="56"/>
     </row>
     <row r="92" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B92" s="52"/>
-      <c r="C92" s="56"/>
-      <c r="D92" s="54"/>
+      <c r="B92" s="58"/>
+      <c r="C92" s="60"/>
+      <c r="D92" s="49"/>
       <c r="E92" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="F92" s="50"/>
+      <c r="F92" s="56"/>
     </row>
     <row r="93" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B93" s="52"/>
-      <c r="C93" s="56"/>
-      <c r="D93" s="54"/>
+      <c r="B93" s="58"/>
+      <c r="C93" s="60"/>
+      <c r="D93" s="49"/>
       <c r="E93" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="F93" s="50"/>
+      <c r="F93" s="56"/>
     </row>
     <row r="94" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B94" s="52"/>
-      <c r="C94" s="56"/>
-      <c r="D94" s="54"/>
+      <c r="B94" s="58"/>
+      <c r="C94" s="60"/>
+      <c r="D94" s="49"/>
       <c r="E94" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="F94" s="50"/>
+      <c r="F94" s="56"/>
     </row>
     <row r="95" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B95" s="52"/>
-      <c r="C95" s="56"/>
-      <c r="D95" s="54"/>
+      <c r="B95" s="58"/>
+      <c r="C95" s="60"/>
+      <c r="D95" s="49"/>
       <c r="E95" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="F95" s="50"/>
+      <c r="F95" s="56"/>
     </row>
     <row r="96" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B96" s="52"/>
-      <c r="C96" s="56"/>
-      <c r="D96" s="54"/>
+      <c r="B96" s="58"/>
+      <c r="C96" s="60"/>
+      <c r="D96" s="49"/>
       <c r="E96" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F96" s="50"/>
+      <c r="F96" s="56"/>
     </row>
     <row r="97" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B97" s="52"/>
-      <c r="C97" s="55"/>
-      <c r="D97" s="55"/>
-      <c r="E97" s="55"/>
-      <c r="F97" s="50"/>
+      <c r="B97" s="58"/>
+      <c r="C97" s="48"/>
+      <c r="D97" s="48"/>
+      <c r="E97" s="48"/>
+      <c r="F97" s="56"/>
     </row>
     <row r="98" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B98" s="52"/>
-      <c r="C98" s="56" t="s">
+      <c r="B98" s="58"/>
+      <c r="C98" s="60" t="s">
         <v>192</v>
       </c>
       <c r="D98" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="E98" s="54"/>
-      <c r="F98" s="50"/>
+      <c r="E98" s="49"/>
+      <c r="F98" s="56"/>
     </row>
     <row r="99" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B99" s="52"/>
-      <c r="C99" s="56"/>
+      <c r="B99" s="58"/>
+      <c r="C99" s="60"/>
       <c r="D99" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="E99" s="54"/>
-      <c r="F99" s="50"/>
+      <c r="E99" s="49"/>
+      <c r="F99" s="56"/>
     </row>
     <row r="100" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B100" s="52"/>
-      <c r="C100" s="56"/>
+      <c r="B100" s="58"/>
+      <c r="C100" s="60"/>
       <c r="D100" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="E100" s="54"/>
-      <c r="F100" s="50"/>
+      <c r="E100" s="49"/>
+      <c r="F100" s="56"/>
     </row>
     <row r="101" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B101" s="52"/>
-      <c r="C101" s="56"/>
+      <c r="B101" s="58"/>
+      <c r="C101" s="60"/>
       <c r="D101" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="E101" s="54"/>
-      <c r="F101" s="50"/>
+      <c r="E101" s="49"/>
+      <c r="F101" s="56"/>
     </row>
     <row r="102" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B102" s="52"/>
-      <c r="C102" s="56"/>
+      <c r="B102" s="58"/>
+      <c r="C102" s="60"/>
       <c r="D102" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="E102" s="54"/>
-      <c r="F102" s="50"/>
+      <c r="E102" s="49"/>
+      <c r="F102" s="56"/>
     </row>
     <row r="103" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B103" s="52"/>
-      <c r="C103" s="56"/>
+      <c r="B103" s="58"/>
+      <c r="C103" s="60"/>
       <c r="D103" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="E103" s="54"/>
-      <c r="F103" s="50"/>
+      <c r="E103" s="49"/>
+      <c r="F103" s="56"/>
     </row>
     <row r="104" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B104" s="52"/>
-      <c r="C104" s="56"/>
+      <c r="B104" s="58"/>
+      <c r="C104" s="60"/>
       <c r="D104" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="E104" s="49"/>
+      <c r="F104" s="56"/>
+    </row>
+    <row r="105" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B105" s="58"/>
+      <c r="C105" s="60"/>
+      <c r="D105" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E104" s="54"/>
-      <c r="F104" s="50"/>
-    </row>
-    <row r="105" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B105" s="52"/>
-      <c r="C105" s="56"/>
-      <c r="D105" s="54"/>
-      <c r="E105" s="54"/>
-      <c r="F105" s="50"/>
+      <c r="E105" s="49"/>
+      <c r="F105" s="56"/>
     </row>
     <row r="106" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B106" s="52"/>
-      <c r="C106" s="56"/>
-      <c r="D106" s="54"/>
-      <c r="E106" s="3" t="s">
+      <c r="B106" s="58"/>
+      <c r="C106" s="60"/>
+      <c r="D106" s="49"/>
+      <c r="E106" s="49"/>
+      <c r="F106" s="56"/>
+    </row>
+    <row r="107" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B107" s="58"/>
+      <c r="C107" s="60"/>
+      <c r="D107" s="49"/>
+      <c r="E107" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="F106" s="50"/>
-    </row>
-    <row r="107" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B107" s="52"/>
-      <c r="C107" s="56"/>
-      <c r="D107" s="54"/>
-      <c r="E107" s="3" t="s">
+      <c r="F107" s="56"/>
+    </row>
+    <row r="108" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B108" s="58"/>
+      <c r="C108" s="60"/>
+      <c r="D108" s="49"/>
+      <c r="E108" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="F107" s="50"/>
-    </row>
-    <row r="108" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B108" s="52"/>
-      <c r="C108" s="56"/>
-      <c r="D108" s="54"/>
-      <c r="E108" s="3" t="s">
+      <c r="F108" s="56"/>
+    </row>
+    <row r="109" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B109" s="58"/>
+      <c r="C109" s="60"/>
+      <c r="D109" s="49"/>
+      <c r="E109" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="F108" s="50"/>
-    </row>
-    <row r="109" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B109" s="52"/>
-      <c r="C109" s="56"/>
-      <c r="D109" s="54"/>
-      <c r="E109" s="3" t="s">
+      <c r="F109" s="56"/>
+    </row>
+    <row r="110" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B110" s="58"/>
+      <c r="C110" s="60"/>
+      <c r="D110" s="49"/>
+      <c r="E110" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="F109" s="50"/>
-    </row>
-    <row r="110" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B110" s="52"/>
-      <c r="C110" s="56"/>
-      <c r="D110" s="54"/>
-      <c r="E110" s="3" t="s">
+      <c r="F110" s="56"/>
+    </row>
+    <row r="111" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B111" s="58"/>
+      <c r="C111" s="60"/>
+      <c r="D111" s="49"/>
+      <c r="E111" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="F110" s="50"/>
-    </row>
-    <row r="111" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B111" s="52"/>
-      <c r="C111" s="56"/>
-      <c r="D111" s="54"/>
-      <c r="E111" s="3" t="s">
+      <c r="F111" s="56"/>
+    </row>
+    <row r="112" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B112" s="58"/>
+      <c r="C112" s="60"/>
+      <c r="D112" s="49"/>
+      <c r="E112" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="F111" s="50"/>
-    </row>
-    <row r="112" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B112" s="52"/>
-      <c r="C112" s="56"/>
-      <c r="D112" s="54"/>
-      <c r="E112" s="3" t="s">
+      <c r="F112" s="56"/>
+    </row>
+    <row r="113" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B113" s="58"/>
+      <c r="C113" s="60"/>
+      <c r="D113" s="49"/>
+      <c r="E113" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F112" s="50"/>
-    </row>
-    <row r="113" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B113" s="52"/>
-      <c r="C113" s="56"/>
-      <c r="D113" s="54"/>
-      <c r="E113" s="7"/>
-      <c r="F113" s="50"/>
+      <c r="F113" s="56"/>
     </row>
     <row r="114" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B114" s="52"/>
-      <c r="C114" s="56"/>
-      <c r="D114" s="54"/>
-      <c r="E114" s="3" t="s">
+      <c r="B114" s="58"/>
+      <c r="C114" s="60"/>
+      <c r="D114" s="49"/>
+      <c r="E114" s="7"/>
+      <c r="F114" s="56"/>
+    </row>
+    <row r="115" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B115" s="58"/>
+      <c r="C115" s="60"/>
+      <c r="D115" s="49"/>
+      <c r="E115" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="F114" s="50"/>
-    </row>
-    <row r="115" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B115" s="52"/>
-      <c r="C115" s="56"/>
-      <c r="D115" s="54"/>
-      <c r="E115" s="3" t="s">
+      <c r="F115" s="56"/>
+    </row>
+    <row r="116" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B116" s="58"/>
+      <c r="C116" s="60"/>
+      <c r="D116" s="49"/>
+      <c r="E116" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F115" s="50"/>
-    </row>
-    <row r="116" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B116" s="52"/>
-      <c r="C116" s="56"/>
-      <c r="D116" s="54"/>
-      <c r="E116" s="3" t="s">
+      <c r="F116" s="56"/>
+    </row>
+    <row r="117" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B117" s="58"/>
+      <c r="C117" s="60"/>
+      <c r="D117" s="49"/>
+      <c r="E117" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="F116" s="50"/>
-    </row>
-    <row r="117" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B117" s="52"/>
-      <c r="C117" s="56"/>
-      <c r="D117" s="54"/>
-      <c r="E117" s="3" t="s">
+      <c r="F117" s="56"/>
+    </row>
+    <row r="118" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B118" s="58"/>
+      <c r="C118" s="60"/>
+      <c r="D118" s="49"/>
+      <c r="E118" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="F117" s="50"/>
-    </row>
-    <row r="118" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B118" s="52"/>
-      <c r="C118" s="56"/>
-      <c r="D118" s="54"/>
-      <c r="E118" s="3" t="s">
+      <c r="F118" s="56"/>
+    </row>
+    <row r="119" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B119" s="58"/>
+      <c r="C119" s="60"/>
+      <c r="D119" s="49"/>
+      <c r="E119" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="F118" s="50"/>
-    </row>
-    <row r="119" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B119" s="53"/>
-      <c r="C119" s="8"/>
-      <c r="D119" s="8"/>
-      <c r="E119" s="8"/>
-      <c r="F119" s="51"/>
+      <c r="F119" s="56"/>
+    </row>
+    <row r="120" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B120" s="59"/>
+      <c r="C120" s="8"/>
+      <c r="D120" s="8"/>
+      <c r="E120" s="8"/>
+      <c r="F120" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="D21:D75"/>
+    <mergeCell ref="C77:C96"/>
+    <mergeCell ref="E12:E19"/>
+    <mergeCell ref="E77:E82"/>
     <mergeCell ref="C76:E76"/>
-    <mergeCell ref="D105:E105"/>
+    <mergeCell ref="D106:E106"/>
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="D20:E20"/>
     <mergeCell ref="B2:F2"/>
-    <mergeCell ref="F3:F119"/>
-    <mergeCell ref="B3:B119"/>
-    <mergeCell ref="D106:D118"/>
+    <mergeCell ref="F3:F120"/>
+    <mergeCell ref="B3:B120"/>
+    <mergeCell ref="D107:D119"/>
     <mergeCell ref="C97:E97"/>
-    <mergeCell ref="C98:C118"/>
+    <mergeCell ref="C98:C119"/>
     <mergeCell ref="D4:E10"/>
     <mergeCell ref="C11:E11"/>
     <mergeCell ref="D83:E83"/>
     <mergeCell ref="D84:D96"/>
-    <mergeCell ref="E98:E104"/>
+    <mergeCell ref="E98:E105"/>
     <mergeCell ref="C12:C75"/>
-    <mergeCell ref="D21:D75"/>
-    <mergeCell ref="C77:C96"/>
-    <mergeCell ref="E12:E19"/>
-    <mergeCell ref="E77:E82"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2615,41 +2629,41 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B2" s="47"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="48"/>
-      <c r="L2" s="48"/>
-      <c r="M2" s="48"/>
-      <c r="N2" s="48"/>
-      <c r="O2" s="49"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="54"/>
+      <c r="L2" s="54"/>
+      <c r="M2" s="54"/>
+      <c r="N2" s="54"/>
+      <c r="O2" s="55"/>
     </row>
     <row r="3" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B3" s="52"/>
-      <c r="C3" s="63" t="s">
+      <c r="B3" s="58"/>
+      <c r="C3" s="76" t="s">
         <v>198</v>
       </c>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="63"/>
-      <c r="K3" s="63"/>
-      <c r="L3" s="63"/>
-      <c r="M3" s="63"/>
-      <c r="N3" s="63"/>
-      <c r="O3" s="50"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="76"/>
+      <c r="K3" s="76"/>
+      <c r="L3" s="76"/>
+      <c r="M3" s="76"/>
+      <c r="N3" s="76"/>
+      <c r="O3" s="56"/>
     </row>
     <row r="4" spans="2:15" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="52"/>
+      <c r="B4" s="58"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -2666,11 +2680,11 @@
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
-      <c r="O4" s="50"/>
+      <c r="O4" s="56"/>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B5" s="52"/>
-      <c r="C5" s="54"/>
+      <c r="B5" s="58"/>
+      <c r="C5" s="49"/>
       <c r="D5" s="3" t="s">
         <v>10</v>
       </c>
@@ -2684,23 +2698,23 @@
       <c r="H5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="65" t="s">
+      <c r="I5" s="64" t="s">
         <v>106</v>
       </c>
-      <c r="J5" s="66"/>
+      <c r="J5" s="65"/>
       <c r="K5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="L5" s="68" t="s">
+      <c r="L5" s="67" t="s">
         <v>101</v>
       </c>
-      <c r="M5" s="69"/>
-      <c r="N5" s="70"/>
-      <c r="O5" s="50"/>
+      <c r="M5" s="68"/>
+      <c r="N5" s="69"/>
+      <c r="O5" s="56"/>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B6" s="52"/>
-      <c r="C6" s="54"/>
+      <c r="B6" s="58"/>
+      <c r="C6" s="49"/>
       <c r="D6" s="3" t="s">
         <v>10</v>
       </c>
@@ -2712,23 +2726,23 @@
         <v>62</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="I6" s="65" t="s">
+        <v>211</v>
+      </c>
+      <c r="I6" s="64" t="s">
         <v>100</v>
       </c>
-      <c r="J6" s="66"/>
+      <c r="J6" s="65"/>
       <c r="K6" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="L6" s="71"/>
-      <c r="M6" s="72"/>
-      <c r="N6" s="73"/>
-      <c r="O6" s="50"/>
+      <c r="L6" s="70"/>
+      <c r="M6" s="71"/>
+      <c r="N6" s="72"/>
+      <c r="O6" s="56"/>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B7" s="52"/>
-      <c r="C7" s="54"/>
+      <c r="B7" s="58"/>
+      <c r="C7" s="49"/>
       <c r="D7" s="3" t="s">
         <v>10</v>
       </c>
@@ -2740,56 +2754,56 @@
         <v>45</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="I7" s="65" t="s">
+        <v>212</v>
+      </c>
+      <c r="I7" s="64" t="s">
         <v>60</v>
       </c>
-      <c r="J7" s="66"/>
+      <c r="J7" s="65"/>
       <c r="K7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="L7" s="74"/>
-      <c r="M7" s="75"/>
-      <c r="N7" s="76"/>
-      <c r="O7" s="50"/>
+      <c r="L7" s="73"/>
+      <c r="M7" s="74"/>
+      <c r="N7" s="75"/>
+      <c r="O7" s="56"/>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B8" s="52"/>
-      <c r="C8" s="62"/>
-      <c r="D8" s="62"/>
-      <c r="E8" s="62"/>
-      <c r="F8" s="62"/>
-      <c r="G8" s="62"/>
-      <c r="H8" s="62"/>
-      <c r="I8" s="62"/>
-      <c r="J8" s="62"/>
-      <c r="K8" s="62"/>
-      <c r="L8" s="62"/>
-      <c r="M8" s="62"/>
-      <c r="N8" s="62"/>
-      <c r="O8" s="50"/>
+      <c r="B8" s="58"/>
+      <c r="C8" s="78"/>
+      <c r="D8" s="78"/>
+      <c r="E8" s="78"/>
+      <c r="F8" s="78"/>
+      <c r="G8" s="78"/>
+      <c r="H8" s="78"/>
+      <c r="I8" s="78"/>
+      <c r="J8" s="78"/>
+      <c r="K8" s="78"/>
+      <c r="L8" s="78"/>
+      <c r="M8" s="78"/>
+      <c r="N8" s="78"/>
+      <c r="O8" s="56"/>
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B9" s="52"/>
-      <c r="C9" s="63" t="s">
+      <c r="B9" s="58"/>
+      <c r="C9" s="76" t="s">
         <v>199</v>
       </c>
-      <c r="D9" s="63"/>
-      <c r="E9" s="63"/>
-      <c r="F9" s="63"/>
-      <c r="G9" s="63"/>
-      <c r="H9" s="63"/>
-      <c r="I9" s="63"/>
-      <c r="J9" s="63"/>
-      <c r="K9" s="63"/>
-      <c r="L9" s="63"/>
-      <c r="M9" s="63"/>
-      <c r="N9" s="63"/>
-      <c r="O9" s="50"/>
+      <c r="D9" s="76"/>
+      <c r="E9" s="76"/>
+      <c r="F9" s="76"/>
+      <c r="G9" s="76"/>
+      <c r="H9" s="76"/>
+      <c r="I9" s="76"/>
+      <c r="J9" s="76"/>
+      <c r="K9" s="76"/>
+      <c r="L9" s="76"/>
+      <c r="M9" s="76"/>
+      <c r="N9" s="76"/>
+      <c r="O9" s="56"/>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B10" s="52"/>
+      <c r="B10" s="58"/>
       <c r="C10" s="3" t="s">
         <v>42</v>
       </c>
@@ -2800,13 +2814,13 @@
         <v>17</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="G10" s="10" t="s">
         <v>215</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="I10" s="3">
         <v>142536748</v>
@@ -2820,14 +2834,14 @@
       <c r="L10" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="M10" s="67" t="s">
+      <c r="M10" s="66" t="s">
         <v>101</v>
       </c>
-      <c r="N10" s="67"/>
-      <c r="O10" s="50"/>
+      <c r="N10" s="66"/>
+      <c r="O10" s="56"/>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B11" s="52"/>
+      <c r="B11" s="58"/>
       <c r="C11" s="3" t="s">
         <v>42</v>
       </c>
@@ -2838,13 +2852,13 @@
         <v>19</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I11" s="3">
         <v>142536747</v>
@@ -2858,14 +2872,14 @@
       <c r="L11" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="M11" s="67"/>
-      <c r="N11" s="67"/>
-      <c r="O11" s="50"/>
+      <c r="M11" s="66"/>
+      <c r="N11" s="66"/>
+      <c r="O11" s="56"/>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B12" s="52"/>
+      <c r="B12" s="58"/>
       <c r="C12" s="3" t="s">
-        <v>42</v>
+        <v>241</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>16</v>
@@ -2874,13 +2888,13 @@
         <v>20</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>221</v>
-      </c>
-      <c r="H12" s="82" t="s">
-        <v>222</v>
+        <v>219</v>
+      </c>
+      <c r="H12" s="47" t="s">
+        <v>220</v>
       </c>
       <c r="I12" s="3">
         <v>142536746</v>
@@ -2894,12 +2908,12 @@
       <c r="L12" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="M12" s="67"/>
-      <c r="N12" s="67"/>
-      <c r="O12" s="50"/>
+      <c r="M12" s="66"/>
+      <c r="N12" s="66"/>
+      <c r="O12" s="56"/>
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B13" s="52"/>
+      <c r="B13" s="58"/>
       <c r="C13" s="3" t="s">
         <v>42</v>
       </c>
@@ -2910,13 +2924,13 @@
         <v>30</v>
       </c>
       <c r="F13" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="G13" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="G13" s="10" t="s">
-        <v>225</v>
-      </c>
       <c r="H13" s="3" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I13" s="3">
         <v>142536745</v>
@@ -2930,12 +2944,12 @@
       <c r="L13" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="M13" s="67"/>
-      <c r="N13" s="67"/>
-      <c r="O13" s="50"/>
+      <c r="M13" s="66"/>
+      <c r="N13" s="66"/>
+      <c r="O13" s="56"/>
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B14" s="52"/>
+      <c r="B14" s="58"/>
       <c r="C14" s="3" t="s">
         <v>40</v>
       </c>
@@ -2949,10 +2963,10 @@
         <v>227</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="I14" s="3">
         <v>142536744</v>
@@ -2966,12 +2980,12 @@
       <c r="L14" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="M14" s="67"/>
-      <c r="N14" s="67"/>
-      <c r="O14" s="50"/>
+      <c r="M14" s="66"/>
+      <c r="N14" s="66"/>
+      <c r="O14" s="56"/>
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B15" s="52"/>
+      <c r="B15" s="58"/>
       <c r="C15" s="3" t="s">
         <v>41</v>
       </c>
@@ -2982,10 +2996,10 @@
         <v>39</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>210</v>
+        <v>229</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>230</v>
@@ -3002,12 +3016,12 @@
       <c r="L15" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="M15" s="67"/>
-      <c r="N15" s="67"/>
-      <c r="O15" s="50"/>
+      <c r="M15" s="66"/>
+      <c r="N15" s="66"/>
+      <c r="O15" s="56"/>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B16" s="52"/>
+      <c r="B16" s="58"/>
       <c r="C16" s="3"/>
       <c r="D16" s="3" t="s">
         <v>16</v>
@@ -3016,13 +3030,13 @@
         <v>102</v>
       </c>
       <c r="F16" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="G16" s="46" t="s">
+        <v>232</v>
+      </c>
+      <c r="H16" s="3" t="s">
         <v>233</v>
-      </c>
-      <c r="G16" s="46" t="s">
-        <v>231</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>232</v>
       </c>
       <c r="I16" s="3">
         <v>142536742</v>
@@ -3036,46 +3050,46 @@
       <c r="L16" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="M16" s="67"/>
-      <c r="N16" s="67"/>
-      <c r="O16" s="50"/>
+      <c r="M16" s="66"/>
+      <c r="N16" s="66"/>
+      <c r="O16" s="56"/>
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B17" s="52"/>
-      <c r="C17" s="62"/>
-      <c r="D17" s="62"/>
-      <c r="E17" s="62"/>
-      <c r="F17" s="62"/>
-      <c r="G17" s="62"/>
-      <c r="H17" s="62"/>
-      <c r="I17" s="62"/>
-      <c r="J17" s="62"/>
-      <c r="K17" s="62"/>
-      <c r="L17" s="62"/>
-      <c r="M17" s="62"/>
-      <c r="N17" s="62"/>
-      <c r="O17" s="50"/>
+      <c r="B17" s="58"/>
+      <c r="C17" s="78"/>
+      <c r="D17" s="78"/>
+      <c r="E17" s="78"/>
+      <c r="F17" s="78"/>
+      <c r="G17" s="78"/>
+      <c r="H17" s="78"/>
+      <c r="I17" s="78"/>
+      <c r="J17" s="78"/>
+      <c r="K17" s="78"/>
+      <c r="L17" s="78"/>
+      <c r="M17" s="78"/>
+      <c r="N17" s="78"/>
+      <c r="O17" s="56"/>
     </row>
     <row r="18" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B18" s="52"/>
-      <c r="C18" s="63" t="s">
+      <c r="B18" s="58"/>
+      <c r="C18" s="76" t="s">
         <v>200</v>
       </c>
-      <c r="D18" s="63"/>
-      <c r="E18" s="63"/>
-      <c r="F18" s="63"/>
-      <c r="G18" s="63"/>
-      <c r="H18" s="63"/>
-      <c r="I18" s="63"/>
-      <c r="J18" s="63"/>
-      <c r="K18" s="63"/>
-      <c r="L18" s="63"/>
-      <c r="M18" s="63"/>
-      <c r="N18" s="63"/>
-      <c r="O18" s="50"/>
+      <c r="D18" s="76"/>
+      <c r="E18" s="76"/>
+      <c r="F18" s="76"/>
+      <c r="G18" s="76"/>
+      <c r="H18" s="76"/>
+      <c r="I18" s="76"/>
+      <c r="J18" s="76"/>
+      <c r="K18" s="76"/>
+      <c r="L18" s="76"/>
+      <c r="M18" s="76"/>
+      <c r="N18" s="76"/>
+      <c r="O18" s="56"/>
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B19" s="52"/>
+      <c r="B19" s="58"/>
       <c r="C19" s="3" t="s">
         <v>42</v>
       </c>
@@ -3106,14 +3120,14 @@
       <c r="L19" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="M19" s="67" t="s">
+      <c r="M19" s="66" t="s">
         <v>101</v>
       </c>
-      <c r="N19" s="67"/>
-      <c r="O19" s="50"/>
+      <c r="N19" s="66"/>
+      <c r="O19" s="56"/>
     </row>
     <row r="20" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B20" s="52"/>
+      <c r="B20" s="58"/>
       <c r="C20" s="3" t="s">
         <v>42</v>
       </c>
@@ -3144,12 +3158,12 @@
       <c r="L20" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="M20" s="67"/>
-      <c r="N20" s="67"/>
-      <c r="O20" s="50"/>
+      <c r="M20" s="66"/>
+      <c r="N20" s="66"/>
+      <c r="O20" s="56"/>
     </row>
     <row r="21" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B21" s="52"/>
+      <c r="B21" s="58"/>
       <c r="C21" s="3" t="s">
         <v>42</v>
       </c>
@@ -3180,12 +3194,12 @@
       <c r="L21" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="M21" s="67"/>
-      <c r="N21" s="67"/>
-      <c r="O21" s="50"/>
+      <c r="M21" s="66"/>
+      <c r="N21" s="66"/>
+      <c r="O21" s="56"/>
     </row>
     <row r="22" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B22" s="52"/>
+      <c r="B22" s="58"/>
       <c r="C22" s="3" t="s">
         <v>42</v>
       </c>
@@ -3216,12 +3230,12 @@
       <c r="L22" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="M22" s="67"/>
-      <c r="N22" s="67"/>
-      <c r="O22" s="50"/>
+      <c r="M22" s="66"/>
+      <c r="N22" s="66"/>
+      <c r="O22" s="56"/>
     </row>
     <row r="23" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B23" s="52"/>
+      <c r="B23" s="58"/>
       <c r="C23" s="3" t="s">
         <v>42</v>
       </c>
@@ -3238,7 +3252,7 @@
         <v>93</v>
       </c>
       <c r="H23" s="20" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="I23" s="18">
         <v>210456789</v>
@@ -3252,12 +3266,12 @@
       <c r="L23" s="21" t="s">
         <v>118</v>
       </c>
-      <c r="M23" s="67"/>
-      <c r="N23" s="67"/>
-      <c r="O23" s="50"/>
+      <c r="M23" s="66"/>
+      <c r="N23" s="66"/>
+      <c r="O23" s="56"/>
     </row>
     <row r="24" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B24" s="52"/>
+      <c r="B24" s="58"/>
       <c r="C24" s="22" t="s">
         <v>40</v>
       </c>
@@ -3274,7 +3288,7 @@
         <v>94</v>
       </c>
       <c r="H24" s="23" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I24" s="22">
         <v>225147896</v>
@@ -3288,12 +3302,12 @@
       <c r="L24" s="36" t="s">
         <v>119</v>
       </c>
-      <c r="M24" s="67"/>
-      <c r="N24" s="67"/>
-      <c r="O24" s="50"/>
+      <c r="M24" s="66"/>
+      <c r="N24" s="66"/>
+      <c r="O24" s="56"/>
     </row>
     <row r="25" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B25" s="52"/>
+      <c r="B25" s="58"/>
       <c r="C25" s="22" t="s">
         <v>40</v>
       </c>
@@ -3310,7 +3324,7 @@
         <v>95</v>
       </c>
       <c r="H25" s="23" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I25" s="22">
         <v>278963254</v>
@@ -3322,14 +3336,14 @@
         <v>203</v>
       </c>
       <c r="L25" s="36" t="s">
-        <v>212</v>
-      </c>
-      <c r="M25" s="67"/>
-      <c r="N25" s="67"/>
-      <c r="O25" s="50"/>
+        <v>210</v>
+      </c>
+      <c r="M25" s="66"/>
+      <c r="N25" s="66"/>
+      <c r="O25" s="56"/>
     </row>
     <row r="26" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B26" s="52"/>
+      <c r="B26" s="58"/>
       <c r="C26" s="3"/>
       <c r="D26" s="3" t="s">
         <v>88</v>
@@ -3350,12 +3364,12 @@
       <c r="L26" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="M26" s="67"/>
-      <c r="N26" s="67"/>
-      <c r="O26" s="50"/>
+      <c r="M26" s="66"/>
+      <c r="N26" s="66"/>
+      <c r="O26" s="56"/>
     </row>
     <row r="27" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B27" s="52"/>
+      <c r="B27" s="58"/>
       <c r="C27" s="3"/>
       <c r="D27" s="3" t="s">
         <v>88</v>
@@ -3376,12 +3390,12 @@
       <c r="L27" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="M27" s="67"/>
-      <c r="N27" s="67"/>
-      <c r="O27" s="50"/>
+      <c r="M27" s="66"/>
+      <c r="N27" s="66"/>
+      <c r="O27" s="56"/>
     </row>
     <row r="28" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B28" s="52"/>
+      <c r="B28" s="58"/>
       <c r="C28" s="3"/>
       <c r="D28" s="3" t="s">
         <v>88</v>
@@ -3402,12 +3416,12 @@
       <c r="L28" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="M28" s="67"/>
-      <c r="N28" s="67"/>
-      <c r="O28" s="50"/>
+      <c r="M28" s="66"/>
+      <c r="N28" s="66"/>
+      <c r="O28" s="56"/>
     </row>
     <row r="29" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B29" s="52"/>
+      <c r="B29" s="58"/>
       <c r="C29" s="3"/>
       <c r="D29" s="3" t="s">
         <v>88</v>
@@ -3428,12 +3442,12 @@
       <c r="L29" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="M29" s="67"/>
-      <c r="N29" s="67"/>
-      <c r="O29" s="50"/>
+      <c r="M29" s="66"/>
+      <c r="N29" s="66"/>
+      <c r="O29" s="56"/>
     </row>
     <row r="30" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B30" s="52"/>
+      <c r="B30" s="58"/>
       <c r="C30" s="3"/>
       <c r="D30" s="3" t="s">
         <v>88</v>
@@ -3454,12 +3468,12 @@
       <c r="L30" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="M30" s="67"/>
-      <c r="N30" s="67"/>
-      <c r="O30" s="50"/>
+      <c r="M30" s="66"/>
+      <c r="N30" s="66"/>
+      <c r="O30" s="56"/>
     </row>
     <row r="31" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B31" s="52"/>
+      <c r="B31" s="58"/>
       <c r="C31" s="3"/>
       <c r="D31" s="3" t="s">
         <v>88</v>
@@ -3480,12 +3494,12 @@
       <c r="L31" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="M31" s="67"/>
-      <c r="N31" s="67"/>
-      <c r="O31" s="50"/>
+      <c r="M31" s="66"/>
+      <c r="N31" s="66"/>
+      <c r="O31" s="56"/>
     </row>
     <row r="32" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B32" s="52"/>
+      <c r="B32" s="58"/>
       <c r="C32" s="3"/>
       <c r="D32" s="3" t="s">
         <v>88</v>
@@ -3506,28 +3520,34 @@
       <c r="L32" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="M32" s="67"/>
-      <c r="N32" s="67"/>
-      <c r="O32" s="50"/>
+      <c r="M32" s="66"/>
+      <c r="N32" s="66"/>
+      <c r="O32" s="56"/>
     </row>
     <row r="33" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B33" s="53"/>
-      <c r="C33" s="64"/>
-      <c r="D33" s="64"/>
-      <c r="E33" s="64"/>
-      <c r="F33" s="64"/>
-      <c r="G33" s="64"/>
-      <c r="H33" s="64"/>
-      <c r="I33" s="64"/>
-      <c r="J33" s="64"/>
-      <c r="K33" s="64"/>
-      <c r="L33" s="64"/>
-      <c r="M33" s="64"/>
-      <c r="N33" s="64"/>
-      <c r="O33" s="51"/>
+      <c r="B33" s="59"/>
+      <c r="C33" s="63"/>
+      <c r="D33" s="63"/>
+      <c r="E33" s="63"/>
+      <c r="F33" s="63"/>
+      <c r="G33" s="63"/>
+      <c r="H33" s="63"/>
+      <c r="I33" s="63"/>
+      <c r="J33" s="63"/>
+      <c r="K33" s="63"/>
+      <c r="L33" s="63"/>
+      <c r="M33" s="63"/>
+      <c r="N33" s="63"/>
+      <c r="O33" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B2:O2"/>
+    <mergeCell ref="O3:O32"/>
+    <mergeCell ref="B3:B32"/>
+    <mergeCell ref="C8:N8"/>
+    <mergeCell ref="C17:N17"/>
+    <mergeCell ref="C3:N3"/>
     <mergeCell ref="B33:O33"/>
     <mergeCell ref="I7:J7"/>
     <mergeCell ref="I5:J5"/>
@@ -3539,12 +3559,6 @@
     <mergeCell ref="C9:N9"/>
     <mergeCell ref="C5:C7"/>
     <mergeCell ref="F5:F7"/>
-    <mergeCell ref="B2:O2"/>
-    <mergeCell ref="O3:O32"/>
-    <mergeCell ref="B3:B32"/>
-    <mergeCell ref="C8:N8"/>
-    <mergeCell ref="C17:N17"/>
-    <mergeCell ref="C3:N3"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="G4" r:id="rId1" xr:uid="{90136737-50D8-4624-BF9F-7BB076958402}"/>
@@ -3561,13 +3575,13 @@
     <hyperlink ref="M10" r:id="rId12" xr:uid="{889087D1-E240-4465-90CC-97DF6ABEF439}"/>
     <hyperlink ref="M19" r:id="rId13" xr:uid="{6FC1A60E-B0CE-457F-BEEE-3AC36283B66B}"/>
     <hyperlink ref="G19" r:id="rId14" xr:uid="{19ED9BF7-712A-4DC1-8755-8EF0FCFF0B53}"/>
-    <hyperlink ref="G10" r:id="rId15" xr:uid="{6A83FB18-5AFC-4808-9223-36DE7F856746}"/>
-    <hyperlink ref="G11" r:id="rId16" xr:uid="{F189FF88-B0C7-41DA-9069-997A29D81085}"/>
-    <hyperlink ref="G12" r:id="rId17" xr:uid="{A12A5870-CCA3-494F-B7E5-19C1B5759D91}"/>
-    <hyperlink ref="G13" r:id="rId18" xr:uid="{0873C2BC-57F8-4B2F-98B0-44819F7126D2}"/>
-    <hyperlink ref="G14" r:id="rId19" xr:uid="{1FE56E63-763E-4AB4-A0DE-6EE1C841581B}"/>
-    <hyperlink ref="G15" r:id="rId20" xr:uid="{2C87F2FE-31DC-43C7-890C-23A02A930C8F}"/>
-    <hyperlink ref="G16" r:id="rId21" xr:uid="{1666FE38-BBA2-4EA0-BFB9-23AD0FEC9DAB}"/>
+    <hyperlink ref="G10" r:id="rId15" xr:uid="{5BC82569-082E-4B06-9F60-F2F776251C3F}"/>
+    <hyperlink ref="G11" r:id="rId16" xr:uid="{5F4C98E1-EC04-4A40-A37D-BF2340C074C1}"/>
+    <hyperlink ref="G12" r:id="rId17" xr:uid="{463289AA-CFB3-45FF-8E6A-823B51177A5F}"/>
+    <hyperlink ref="G14" r:id="rId18" xr:uid="{6E194B47-C47F-4A3F-A696-524297FF0681}"/>
+    <hyperlink ref="G13" r:id="rId19" xr:uid="{77BE6733-6657-4053-ABA1-9AD21A969252}"/>
+    <hyperlink ref="G15" r:id="rId20" xr:uid="{1EE423C9-680C-4C89-94AB-DCD13351D8A5}"/>
+    <hyperlink ref="G16" r:id="rId21" xr:uid="{960498F5-B778-4517-B133-C2A43D62055C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId22"/>
@@ -3592,18 +3606,18 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B2" s="47"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="49"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="55"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="52"/>
+      <c r="B3" s="58"/>
       <c r="C3" s="30" t="s">
         <v>14</v>
       </c>
@@ -3623,16 +3637,16 @@
       <c r="I3" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="78"/>
-      <c r="K3" s="59" t="s">
+      <c r="J3" s="80"/>
+      <c r="K3" s="50" t="s">
         <v>199</v>
       </c>
-      <c r="L3" s="59"/>
-      <c r="M3" s="59"/>
-      <c r="N3" s="59"/>
+      <c r="L3" s="50"/>
+      <c r="M3" s="50"/>
+      <c r="N3" s="50"/>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B4" s="52"/>
+      <c r="B4" s="58"/>
       <c r="C4" s="30" t="s">
         <v>202</v>
       </c>
@@ -3650,17 +3664,17 @@
       </c>
       <c r="H4" s="3" t="str">
         <f>VLOOKUP(G4,K$4:L$10,2,FALSE)</f>
-        <v>PGQ</v>
+        <v>PRF</v>
       </c>
       <c r="I4" s="3">
         <v>2</v>
       </c>
-      <c r="J4" s="50"/>
+      <c r="J4" s="56"/>
       <c r="K4" s="3" t="s">
         <v>17</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="M4" s="3"/>
       <c r="N4" s="35" t="s">
@@ -3668,20 +3682,20 @@
       </c>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B5" s="52"/>
-      <c r="C5" s="80"/>
-      <c r="D5" s="80"/>
-      <c r="E5" s="80"/>
-      <c r="F5" s="80"/>
-      <c r="G5" s="80"/>
-      <c r="H5" s="80"/>
-      <c r="I5" s="80"/>
-      <c r="J5" s="50"/>
+      <c r="B5" s="58"/>
+      <c r="C5" s="82"/>
+      <c r="D5" s="82"/>
+      <c r="E5" s="82"/>
+      <c r="F5" s="82"/>
+      <c r="G5" s="82"/>
+      <c r="H5" s="82"/>
+      <c r="I5" s="82"/>
+      <c r="J5" s="56"/>
       <c r="K5" s="3" t="s">
         <v>19</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="M5" s="3"/>
       <c r="N5" s="3" t="s">
@@ -3689,17 +3703,17 @@
       </c>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B6" s="52"/>
-      <c r="C6" s="81" t="s">
+      <c r="B6" s="58"/>
+      <c r="C6" s="79" t="s">
         <v>205</v>
       </c>
-      <c r="D6" s="56" t="s">
+      <c r="D6" s="60" t="s">
         <v>97</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="F6" s="56" t="s">
+      <c r="F6" s="60" t="s">
         <v>25</v>
       </c>
       <c r="G6" s="3" t="s">
@@ -3707,17 +3721,17 @@
       </c>
       <c r="H6" s="3" t="str">
         <f>VLOOKUP(G6,K$4:L$10,2,FALSE)</f>
-        <v>PGQ</v>
+        <v>PRF</v>
       </c>
       <c r="I6" s="3">
         <v>2</v>
       </c>
-      <c r="J6" s="50"/>
+      <c r="J6" s="56"/>
       <c r="K6" s="3" t="s">
         <v>20</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="M6" s="3"/>
       <c r="N6" s="3" t="s">
@@ -3725,29 +3739,29 @@
       </c>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B7" s="52"/>
-      <c r="C7" s="81"/>
-      <c r="D7" s="56"/>
+      <c r="B7" s="58"/>
+      <c r="C7" s="79"/>
+      <c r="D7" s="60"/>
       <c r="E7" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="56"/>
+      <c r="F7" s="60"/>
       <c r="G7" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H7" s="3" t="str">
         <f>VLOOKUP(G7,K$4:L$10,2,FALSE)</f>
-        <v>PNQ</v>
+        <v>PLE</v>
       </c>
       <c r="I7" s="3">
         <v>1</v>
       </c>
-      <c r="J7" s="50"/>
+      <c r="J7" s="56"/>
       <c r="K7" s="3" t="s">
         <v>30</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="M7" s="3"/>
       <c r="N7" s="3" t="s">
@@ -3755,24 +3769,24 @@
       </c>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B8" s="52"/>
-      <c r="C8" s="81"/>
-      <c r="D8" s="56"/>
+      <c r="B8" s="58"/>
+      <c r="C8" s="79"/>
+      <c r="D8" s="60"/>
       <c r="E8" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="F8" s="56"/>
+      <c r="F8" s="60"/>
       <c r="G8" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H8" s="3" t="str">
         <f>VLOOKUP(G8,K$4:L$10,2,FALSE)</f>
-        <v>PNQ</v>
+        <v>PLE</v>
       </c>
       <c r="I8" s="3">
         <v>1</v>
       </c>
-      <c r="J8" s="50"/>
+      <c r="J8" s="56"/>
       <c r="K8" s="3" t="s">
         <v>36</v>
       </c>
@@ -3785,20 +3799,20 @@
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B9" s="52"/>
-      <c r="C9" s="81"/>
-      <c r="D9" s="56"/>
-      <c r="E9" s="54"/>
-      <c r="F9" s="54"/>
-      <c r="G9" s="54"/>
-      <c r="H9" s="54"/>
-      <c r="I9" s="54"/>
-      <c r="J9" s="50"/>
+      <c r="B9" s="58"/>
+      <c r="C9" s="79"/>
+      <c r="D9" s="60"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="49"/>
+      <c r="H9" s="49"/>
+      <c r="I9" s="49"/>
+      <c r="J9" s="56"/>
       <c r="K9" s="3" t="s">
         <v>39</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="M9" s="3"/>
       <c r="N9" s="3" t="s">
@@ -3806,13 +3820,13 @@
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B10" s="52"/>
-      <c r="C10" s="81"/>
-      <c r="D10" s="56"/>
+      <c r="B10" s="58"/>
+      <c r="C10" s="79"/>
+      <c r="D10" s="60"/>
       <c r="E10" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="F10" s="56" t="s">
+      <c r="F10" s="60" t="s">
         <v>26</v>
       </c>
       <c r="G10" s="3" t="s">
@@ -3820,17 +3834,17 @@
       </c>
       <c r="H10" s="3" t="str">
         <f>VLOOKUP(G10,K$4:L$10,2,FALSE)</f>
-        <v>PGQ</v>
+        <v>PRF</v>
       </c>
       <c r="I10" s="3">
         <v>2</v>
       </c>
-      <c r="J10" s="50"/>
+      <c r="J10" s="56"/>
       <c r="K10" s="3" t="s">
         <v>102</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="M10" s="3"/>
       <c r="N10" s="3" t="s">
@@ -3838,40 +3852,40 @@
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B11" s="52"/>
-      <c r="C11" s="81"/>
-      <c r="D11" s="56"/>
+      <c r="B11" s="58"/>
+      <c r="C11" s="79"/>
+      <c r="D11" s="60"/>
       <c r="E11" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F11" s="56"/>
+      <c r="F11" s="60"/>
       <c r="G11" s="3" t="s">
         <v>30</v>
       </c>
       <c r="H11" s="3" t="str">
         <f>VLOOKUP(G11,K$4:L$10,2,FALSE)</f>
-        <v>PWC</v>
+        <v>PEG</v>
       </c>
       <c r="I11" s="3">
         <v>1</v>
       </c>
-      <c r="J11" s="50"/>
+      <c r="J11" s="56"/>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B12" s="52"/>
-      <c r="C12" s="81"/>
-      <c r="D12" s="56"/>
-      <c r="E12" s="54"/>
-      <c r="F12" s="54"/>
-      <c r="G12" s="54"/>
-      <c r="H12" s="54"/>
-      <c r="I12" s="54"/>
-      <c r="J12" s="50"/>
+      <c r="B12" s="58"/>
+      <c r="C12" s="79"/>
+      <c r="D12" s="60"/>
+      <c r="E12" s="49"/>
+      <c r="F12" s="49"/>
+      <c r="G12" s="49"/>
+      <c r="H12" s="49"/>
+      <c r="I12" s="49"/>
+      <c r="J12" s="56"/>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B13" s="52"/>
-      <c r="C13" s="81"/>
-      <c r="D13" s="56"/>
+      <c r="B13" s="58"/>
+      <c r="C13" s="79"/>
+      <c r="D13" s="60"/>
       <c r="E13" s="3" t="s">
         <v>34</v>
       </c>
@@ -3883,28 +3897,28 @@
       </c>
       <c r="H13" s="3" t="str">
         <f>VLOOKUP(G13,K$4:L$10,2,FALSE)</f>
-        <v>PWC</v>
+        <v>PEG</v>
       </c>
       <c r="I13" s="3">
         <v>1</v>
       </c>
-      <c r="J13" s="50"/>
+      <c r="J13" s="56"/>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B14" s="52"/>
-      <c r="C14" s="81"/>
-      <c r="D14" s="55"/>
-      <c r="E14" s="55"/>
-      <c r="F14" s="55"/>
-      <c r="G14" s="55"/>
-      <c r="H14" s="55"/>
-      <c r="I14" s="55"/>
-      <c r="J14" s="50"/>
+      <c r="B14" s="58"/>
+      <c r="C14" s="79"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="48"/>
+      <c r="H14" s="48"/>
+      <c r="I14" s="48"/>
+      <c r="J14" s="56"/>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B15" s="52"/>
-      <c r="C15" s="81"/>
-      <c r="D15" s="56" t="s">
+      <c r="B15" s="58"/>
+      <c r="C15" s="79"/>
+      <c r="D15" s="60" t="s">
         <v>173</v>
       </c>
       <c r="E15" s="29" t="s">
@@ -3918,32 +3932,32 @@
       </c>
       <c r="H15" s="3" t="str">
         <f>VLOOKUP(G15,K$4:L$10,2,FALSE)</f>
-        <v>PGQ</v>
+        <v>PRF</v>
       </c>
       <c r="I15" s="3">
         <v>2</v>
       </c>
-      <c r="J15" s="50"/>
+      <c r="J15" s="56"/>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B16" s="52"/>
-      <c r="C16" s="81"/>
-      <c r="D16" s="56"/>
-      <c r="E16" s="54"/>
-      <c r="F16" s="54"/>
-      <c r="G16" s="54"/>
-      <c r="H16" s="54"/>
-      <c r="I16" s="54"/>
-      <c r="J16" s="50"/>
+      <c r="B16" s="58"/>
+      <c r="C16" s="79"/>
+      <c r="D16" s="60"/>
+      <c r="E16" s="49"/>
+      <c r="F16" s="49"/>
+      <c r="G16" s="49"/>
+      <c r="H16" s="49"/>
+      <c r="I16" s="49"/>
+      <c r="J16" s="56"/>
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B17" s="52"/>
-      <c r="C17" s="81"/>
-      <c r="D17" s="56"/>
+      <c r="B17" s="58"/>
+      <c r="C17" s="79"/>
+      <c r="D17" s="60"/>
       <c r="E17" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="F17" s="56" t="s">
+      <c r="F17" s="60" t="s">
         <v>26</v>
       </c>
       <c r="G17" s="3" t="s">
@@ -3951,48 +3965,48 @@
       </c>
       <c r="H17" s="3" t="str">
         <f>VLOOKUP(G17,K$4:L$10,2,FALSE)</f>
-        <v>PGQ</v>
+        <v>PRF</v>
       </c>
       <c r="I17" s="3">
         <v>2</v>
       </c>
-      <c r="J17" s="50"/>
+      <c r="J17" s="56"/>
     </row>
     <row r="18" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B18" s="52"/>
-      <c r="C18" s="81"/>
-      <c r="D18" s="56"/>
+      <c r="B18" s="58"/>
+      <c r="C18" s="79"/>
+      <c r="D18" s="60"/>
       <c r="E18" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="F18" s="56"/>
+      <c r="F18" s="60"/>
       <c r="G18" s="3" t="s">
         <v>36</v>
       </c>
       <c r="H18" s="3" t="str">
         <f>VLOOKUP(G18,K$4:L$10,2,FALSE)</f>
-        <v>PSG</v>
+        <v>PPI</v>
       </c>
       <c r="I18" s="3">
         <v>1</v>
       </c>
-      <c r="J18" s="50"/>
+      <c r="J18" s="56"/>
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B19" s="52"/>
-      <c r="C19" s="81"/>
-      <c r="D19" s="56"/>
-      <c r="E19" s="54"/>
-      <c r="F19" s="54"/>
-      <c r="G19" s="54"/>
-      <c r="H19" s="54"/>
-      <c r="I19" s="54"/>
-      <c r="J19" s="50"/>
+      <c r="B19" s="58"/>
+      <c r="C19" s="79"/>
+      <c r="D19" s="60"/>
+      <c r="E19" s="49"/>
+      <c r="F19" s="49"/>
+      <c r="G19" s="49"/>
+      <c r="H19" s="49"/>
+      <c r="I19" s="49"/>
+      <c r="J19" s="56"/>
     </row>
     <row r="20" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B20" s="52"/>
-      <c r="C20" s="81"/>
-      <c r="D20" s="56"/>
+      <c r="B20" s="58"/>
+      <c r="C20" s="79"/>
+      <c r="D20" s="60"/>
       <c r="E20" s="3" t="s">
         <v>176</v>
       </c>
@@ -4004,34 +4018,34 @@
       </c>
       <c r="H20" s="3" t="str">
         <f>VLOOKUP(G20,K$4:L$10,2,FALSE)</f>
-        <v>PSG</v>
+        <v>PPI</v>
       </c>
       <c r="I20" s="3">
         <v>1</v>
       </c>
-      <c r="J20" s="50"/>
+      <c r="J20" s="56"/>
     </row>
     <row r="21" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B21" s="52"/>
-      <c r="C21" s="81"/>
-      <c r="D21" s="55"/>
-      <c r="E21" s="55"/>
-      <c r="F21" s="55"/>
-      <c r="G21" s="55"/>
-      <c r="H21" s="55"/>
-      <c r="I21" s="55"/>
-      <c r="J21" s="50"/>
+      <c r="B21" s="58"/>
+      <c r="C21" s="79"/>
+      <c r="D21" s="48"/>
+      <c r="E21" s="48"/>
+      <c r="F21" s="48"/>
+      <c r="G21" s="48"/>
+      <c r="H21" s="48"/>
+      <c r="I21" s="48"/>
+      <c r="J21" s="56"/>
     </row>
     <row r="22" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B22" s="52"/>
-      <c r="C22" s="81"/>
-      <c r="D22" s="56" t="s">
+      <c r="B22" s="58"/>
+      <c r="C22" s="79"/>
+      <c r="D22" s="60" t="s">
         <v>174</v>
       </c>
       <c r="E22" s="29" t="s">
         <v>170</v>
       </c>
-      <c r="F22" s="56" t="s">
+      <c r="F22" s="60" t="s">
         <v>25</v>
       </c>
       <c r="G22" s="3" t="s">
@@ -4039,108 +4053,108 @@
       </c>
       <c r="H22" s="3" t="str">
         <f>VLOOKUP(G22,K$4:L$10,2,FALSE)</f>
-        <v>PGQ</v>
+        <v>PRF</v>
       </c>
       <c r="I22" s="3">
         <v>2</v>
       </c>
-      <c r="J22" s="50"/>
+      <c r="J22" s="56"/>
     </row>
     <row r="23" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B23" s="52"/>
-      <c r="C23" s="81"/>
-      <c r="D23" s="56"/>
+      <c r="B23" s="58"/>
+      <c r="C23" s="79"/>
+      <c r="D23" s="60"/>
       <c r="E23" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="F23" s="56"/>
+      <c r="F23" s="60"/>
       <c r="G23" s="3" t="s">
         <v>39</v>
       </c>
       <c r="H23" s="3" t="str">
         <f>VLOOKUP(G23,K$4:L$10,2,FALSE)</f>
-        <v>PBE</v>
+        <v>PCL</v>
       </c>
       <c r="I23" s="3">
         <v>1</v>
       </c>
-      <c r="J23" s="50"/>
+      <c r="J23" s="56"/>
     </row>
     <row r="24" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B24" s="52"/>
-      <c r="C24" s="81"/>
-      <c r="D24" s="56"/>
+      <c r="B24" s="58"/>
+      <c r="C24" s="79"/>
+      <c r="D24" s="60"/>
       <c r="E24" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F24" s="56"/>
+      <c r="F24" s="60"/>
       <c r="G24" s="3" t="s">
         <v>39</v>
       </c>
       <c r="H24" s="3" t="str">
         <f>VLOOKUP(G24,K$4:L$10,2,FALSE)</f>
-        <v>PBE</v>
+        <v>PCL</v>
       </c>
       <c r="I24" s="3">
         <v>1</v>
       </c>
-      <c r="J24" s="50"/>
+      <c r="J24" s="56"/>
     </row>
     <row r="25" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B25" s="52"/>
-      <c r="C25" s="81"/>
-      <c r="D25" s="56"/>
+      <c r="B25" s="58"/>
+      <c r="C25" s="79"/>
+      <c r="D25" s="60"/>
       <c r="E25" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="F25" s="56"/>
+      <c r="F25" s="60"/>
       <c r="G25" s="3" t="s">
         <v>39</v>
       </c>
       <c r="H25" s="3" t="str">
         <f>VLOOKUP(G25,K$4:L$10,2,FALSE)</f>
-        <v>PBE</v>
+        <v>PCL</v>
       </c>
       <c r="I25" s="3">
         <v>1</v>
       </c>
-      <c r="J25" s="50"/>
+      <c r="J25" s="56"/>
     </row>
     <row r="26" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B26" s="52"/>
-      <c r="C26" s="81"/>
-      <c r="D26" s="56"/>
+      <c r="B26" s="58"/>
+      <c r="C26" s="79"/>
+      <c r="D26" s="60"/>
       <c r="E26" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="F26" s="56"/>
+      <c r="F26" s="60"/>
       <c r="G26" s="3" t="s">
         <v>39</v>
       </c>
       <c r="H26" s="3" t="str">
         <f>VLOOKUP(G26,K$4:L$10,2,FALSE)</f>
-        <v>PBE</v>
+        <v>PCL</v>
       </c>
       <c r="I26" s="3">
         <v>1</v>
       </c>
-      <c r="J26" s="50"/>
+      <c r="J26" s="56"/>
     </row>
     <row r="27" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B27" s="52"/>
-      <c r="C27" s="81"/>
-      <c r="D27" s="56"/>
-      <c r="E27" s="54"/>
-      <c r="F27" s="54"/>
-      <c r="G27" s="54"/>
-      <c r="H27" s="54"/>
-      <c r="I27" s="54"/>
-      <c r="J27" s="50"/>
+      <c r="B27" s="58"/>
+      <c r="C27" s="79"/>
+      <c r="D27" s="60"/>
+      <c r="E27" s="49"/>
+      <c r="F27" s="49"/>
+      <c r="G27" s="49"/>
+      <c r="H27" s="49"/>
+      <c r="I27" s="49"/>
+      <c r="J27" s="56"/>
     </row>
     <row r="28" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B28" s="52"/>
-      <c r="C28" s="81"/>
-      <c r="D28" s="56"/>
+      <c r="B28" s="58"/>
+      <c r="C28" s="79"/>
+      <c r="D28" s="60"/>
       <c r="E28" s="3" t="s">
         <v>105</v>
       </c>
@@ -4152,28 +4166,28 @@
       </c>
       <c r="H28" s="3" t="str">
         <f>VLOOKUP(G28,K$4:L$10,2,FALSE)</f>
-        <v>PBE</v>
+        <v>PCL</v>
       </c>
       <c r="I28" s="3">
         <v>1</v>
       </c>
-      <c r="J28" s="50"/>
+      <c r="J28" s="56"/>
     </row>
     <row r="29" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B29" s="52"/>
-      <c r="C29" s="81"/>
-      <c r="D29" s="56"/>
-      <c r="E29" s="54"/>
-      <c r="F29" s="54"/>
-      <c r="G29" s="54"/>
-      <c r="H29" s="54"/>
-      <c r="I29" s="54"/>
-      <c r="J29" s="50"/>
+      <c r="B29" s="58"/>
+      <c r="C29" s="79"/>
+      <c r="D29" s="60"/>
+      <c r="E29" s="49"/>
+      <c r="F29" s="49"/>
+      <c r="G29" s="49"/>
+      <c r="H29" s="49"/>
+      <c r="I29" s="49"/>
+      <c r="J29" s="56"/>
     </row>
     <row r="30" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B30" s="52"/>
-      <c r="C30" s="81"/>
-      <c r="D30" s="56"/>
+      <c r="B30" s="58"/>
+      <c r="C30" s="79"/>
+      <c r="D30" s="60"/>
       <c r="E30" s="3"/>
       <c r="F30" s="4" t="s">
         <v>35</v>
@@ -4181,7 +4195,7 @@
       <c r="G30" s="4"/>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
-      <c r="J30" s="50"/>
+      <c r="J30" s="56"/>
       <c r="K30" s="31" t="s">
         <v>96</v>
       </c>
@@ -4193,26 +4207,26 @@
       </c>
       <c r="N30" s="3" t="str">
         <f>VLOOKUP(M30,K$4:N$10,2,FALSE)</f>
-        <v>PBE</v>
+        <v>PCL</v>
       </c>
       <c r="O30" s="31">
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B31" s="52"/>
-      <c r="C31" s="81"/>
-      <c r="D31" s="55"/>
-      <c r="E31" s="55"/>
-      <c r="F31" s="55"/>
-      <c r="G31" s="55"/>
-      <c r="H31" s="55"/>
-      <c r="I31" s="55"/>
-      <c r="J31" s="50"/>
+      <c r="B31" s="58"/>
+      <c r="C31" s="79"/>
+      <c r="D31" s="48"/>
+      <c r="E31" s="48"/>
+      <c r="F31" s="48"/>
+      <c r="G31" s="48"/>
+      <c r="H31" s="48"/>
+      <c r="I31" s="48"/>
+      <c r="J31" s="56"/>
     </row>
     <row r="32" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B32" s="52"/>
-      <c r="C32" s="81"/>
+      <c r="B32" s="58"/>
+      <c r="C32" s="79"/>
       <c r="D32" s="4" t="s">
         <v>98</v>
       </c>
@@ -4227,26 +4241,26 @@
       </c>
       <c r="H32" s="3" t="str">
         <f>VLOOKUP(G32,K$4:L$10,2,FALSE)</f>
-        <v>PXC</v>
+        <v>PEL</v>
       </c>
       <c r="I32" s="3">
         <v>3</v>
       </c>
-      <c r="J32" s="50"/>
+      <c r="J32" s="56"/>
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B33" s="52"/>
-      <c r="C33" s="79"/>
-      <c r="D33" s="79"/>
-      <c r="E33" s="79"/>
-      <c r="F33" s="79"/>
-      <c r="G33" s="79"/>
-      <c r="H33" s="79"/>
-      <c r="I33" s="79"/>
-      <c r="J33" s="50"/>
+      <c r="B33" s="58"/>
+      <c r="C33" s="81"/>
+      <c r="D33" s="81"/>
+      <c r="E33" s="81"/>
+      <c r="F33" s="81"/>
+      <c r="G33" s="81"/>
+      <c r="H33" s="81"/>
+      <c r="I33" s="81"/>
+      <c r="J33" s="56"/>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B34" s="52"/>
+      <c r="B34" s="58"/>
       <c r="C34" s="37" t="s">
         <v>206</v>
       </c>
@@ -4258,7 +4272,7 @@
       <c r="G34" s="38"/>
       <c r="H34" s="39"/>
       <c r="I34" s="39"/>
-      <c r="J34" s="50"/>
+      <c r="J34" s="56"/>
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B35" s="42"/>
@@ -4285,26 +4299,18 @@
       <c r="J36" s="33"/>
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B37" s="53"/>
-      <c r="C37" s="64"/>
-      <c r="D37" s="64"/>
-      <c r="E37" s="64"/>
-      <c r="F37" s="64"/>
-      <c r="G37" s="64"/>
-      <c r="H37" s="64"/>
-      <c r="I37" s="64"/>
-      <c r="J37" s="51"/>
+      <c r="B37" s="59"/>
+      <c r="C37" s="63"/>
+      <c r="D37" s="63"/>
+      <c r="E37" s="63"/>
+      <c r="F37" s="63"/>
+      <c r="G37" s="63"/>
+      <c r="H37" s="63"/>
+      <c r="I37" s="63"/>
+      <c r="J37" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="C6:C32"/>
-    <mergeCell ref="E27:I27"/>
-    <mergeCell ref="E29:I29"/>
-    <mergeCell ref="E9:I9"/>
-    <mergeCell ref="E12:I12"/>
-    <mergeCell ref="D6:D13"/>
-    <mergeCell ref="D15:D20"/>
-    <mergeCell ref="D22:D30"/>
     <mergeCell ref="K3:N3"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B37:J37"/>
@@ -4321,6 +4327,14 @@
     <mergeCell ref="C5:I5"/>
     <mergeCell ref="D14:I14"/>
     <mergeCell ref="D21:I21"/>
+    <mergeCell ref="C6:C32"/>
+    <mergeCell ref="E27:I27"/>
+    <mergeCell ref="E29:I29"/>
+    <mergeCell ref="E9:I9"/>
+    <mergeCell ref="E12:I12"/>
+    <mergeCell ref="D6:D13"/>
+    <mergeCell ref="D15:D20"/>
+    <mergeCell ref="D22:D30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
